--- a/images/events/cf25dat.xlsx
+++ b/images/events/cf25dat.xlsx
@@ -897,7 +897,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>PROMPTING ARCHITECTURE</t>
+          <t>S-S5</t>
         </is>
       </c>
       <c r="AR2" t="n">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>ARCHITECTURAL COMPUTING &amp; REASONING</t>
+          <t>S-S5</t>
         </is>
       </c>
       <c r="AR3" t="n">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>INTELLIGENT ROBOTIC ASSEMBLY</t>
+          <t>S-S1</t>
         </is>
       </c>
       <c r="AR4" t="n">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>ARCHITECTURAL COMPUTING &amp; REASONING</t>
+          <t>S-S5</t>
         </is>
       </c>
       <c r="AR5" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>PROMPTING ARCHITECTURE</t>
+          <t>S-S5</t>
         </is>
       </c>
       <c r="AR6" t="n">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>INTELLIGENT ROBOTIC ASSEMBLY</t>
+          <t>S-S1</t>
         </is>
       </c>
       <c r="AR7" t="n">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>URBAN PERCEPTIONS &amp; PATTERNS I</t>
+          <t>S-S2</t>
         </is>
       </c>
       <c r="AR8" t="n">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>URBAN PERCEPTIONS &amp; PATTERNS I</t>
+          <t>S-S2</t>
         </is>
       </c>
       <c r="AR9" t="n">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>ARCHITECTURAL COMPUTING &amp; REASONING</t>
+          <t>S-S5</t>
         </is>
       </c>
       <c r="AR10" t="n">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>PROMPTING ARCHITECTURE</t>
+          <t>S-S5</t>
         </is>
       </c>
       <c r="AR11" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>URBAN PERCEPTIONS &amp; PATTERNS I</t>
+          <t>S-S2</t>
         </is>
       </c>
       <c r="AR12" t="n">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>URBAN PERCEPTIONS &amp; PATTERNS I</t>
+          <t>S-S2</t>
         </is>
       </c>
       <c r="AR13" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>URBAN PERCEPTIONS &amp; PATTERNS II</t>
+          <t>S-3</t>
         </is>
       </c>
       <c r="AR14" t="n">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>INTELLIGENT ROBOTIC ASSEMBLY</t>
+          <t>S-S1</t>
         </is>
       </c>
       <c r="AR15" t="n">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>MORPHOLOGY ACROSS SCALES</t>
+          <t>S-S2</t>
         </is>
       </c>
       <c r="AR16" t="n">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>STRUCTURAL, FABRICATION &amp; MATERIAL LOGIC</t>
+          <t>S-2</t>
         </is>
       </c>
       <c r="AR17" t="n">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>STRUCTURAL, FABRICATION &amp; MATERIAL LOGIC</t>
+          <t>S-2</t>
         </is>
       </c>
       <c r="AR18" t="n">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>GENERATING BUILDING LAYOUT</t>
+          <t>S-1</t>
         </is>
       </c>
       <c r="AR19" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>MORPHOLOGY ACROSS SCALES</t>
+          <t>S-S2</t>
         </is>
       </c>
       <c r="AR20" t="n">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>URBAN PERCEPTIONS &amp; PATTERNS II</t>
+          <t>S-3</t>
         </is>
       </c>
       <c r="AR21" t="n">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>AUGMENTING &amp; ADVANCING DESIGN</t>
+          <t>S-2</t>
         </is>
       </c>
       <c r="AR22" t="n">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>GENERATING BUILDING LAYOUT</t>
+          <t>S-1</t>
         </is>
       </c>
       <c r="AR23" t="n">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>STRUCTURAL, FABRICATION &amp; MATERIAL LOGIC</t>
+          <t>S-2</t>
         </is>
       </c>
       <c r="AR24" t="n">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>GENERATING BUILDING LAYOUT</t>
+          <t>S-1</t>
         </is>
       </c>
       <c r="AR25" t="n">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>URBAN PERCEPTIONS &amp; PATTERNS II</t>
+          <t>S-3</t>
         </is>
       </c>
       <c r="AR26" t="n">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>MORPHOLOGY ACROSS SCALES</t>
+          <t>S-S2</t>
         </is>
       </c>
       <c r="AR27" t="n">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>STRUCTURAL, FABRICATION &amp; MATERIAL LOGIC</t>
+          <t>S-2</t>
         </is>
       </c>
       <c r="AR28" t="n">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>AUGMENTING &amp; ADVANCING DESIGN</t>
+          <t>S-2</t>
         </is>
       </c>
       <c r="AR29" t="n">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>EVALUATING &amp; EXPANDING AI</t>
+          <t>P-A3</t>
         </is>
       </c>
       <c r="AR30" t="n">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>MORPHOLOGY ACROSS SCALES</t>
+          <t>S-S2</t>
         </is>
       </c>
       <c r="AR31" t="n">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>SUSTAINABLE BUILDING DESIGN PROCESSES</t>
+          <t>P-D1</t>
         </is>
       </c>
       <c r="AR32" t="n">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>AUGMENTING DESIGN GENERATION</t>
+          <t>P-B1</t>
         </is>
       </c>
       <c r="AR33" t="n">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>EVALUATING &amp; EXPANDING AI</t>
+          <t>P-A3</t>
         </is>
       </c>
       <c r="AR34" t="n">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>URBAN PERCEPTIONS &amp; PATTERNS</t>
+          <t>P-A1</t>
         </is>
       </c>
       <c r="AR35" t="n">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>IMMERSIVE LEARNING &amp; DESIGN</t>
+          <t>P-B3</t>
         </is>
       </c>
       <c r="AR36" t="n">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>INTELLIGENT ROBOTICS &amp; LAYOUT PLANNING</t>
+          <t>P-C1</t>
         </is>
       </c>
       <c r="AR37" t="n">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>INTELLIGENT ROBOTICS &amp; LAYOUT PLANNING</t>
+          <t>P-C1</t>
         </is>
       </c>
       <c r="AR38" t="n">
@@ -10219,7 +10219,7 @@
       </c>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>STRUCTURAL, FABRICATION &amp; MATERIAL LOGIC</t>
+          <t>P-C2</t>
         </is>
       </c>
       <c r="AR39" t="n">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="AQ40" t="inlineStr">
         <is>
-          <t>AI FOR DESIGN EVALUATION</t>
+          <t>P-B2</t>
         </is>
       </c>
       <c r="AR40" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>AUGMENTING DESIGN GENERATION</t>
+          <t>P-B1</t>
         </is>
       </c>
       <c r="AR41" t="n">
@@ -10939,7 +10939,7 @@
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>AUGMENTING DESIGN GENERATION</t>
+          <t>P-B1</t>
         </is>
       </c>
       <c r="AR42" t="n">
@@ -11182,7 +11182,7 @@
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>IMMERSIVE LEARNING &amp; DESIGN</t>
+          <t>P-B3</t>
         </is>
       </c>
       <c r="AR43" t="n">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>AI FOR DESIGN EVALUATION</t>
+          <t>P-B2</t>
         </is>
       </c>
       <c r="AR45" t="n">
@@ -11970,7 +11970,7 @@
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>AUGMENTING &amp; ADVANCING DESIGN</t>
+          <t>S-2</t>
         </is>
       </c>
       <c r="AR46" t="n">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="AQ47" t="inlineStr">
         <is>
-          <t>SUSTAINABLE BUILDING DESIGN PROCESSES</t>
+          <t>P-D1</t>
         </is>
       </c>
       <c r="AR47" t="n">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>INTELLIGENT ROBOTICS &amp; LAYOUT PLANNING</t>
+          <t>P-C1</t>
         </is>
       </c>
       <c r="AR48" t="n">
@@ -12693,7 +12693,7 @@
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>INTELLIGENT ROBOTICS &amp; LAYOUT PLANNING</t>
+          <t>P-C1</t>
         </is>
       </c>
       <c r="AR49" t="n">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>STRUCTURAL, FABRICATION &amp; MATERIAL LOGIC</t>
+          <t>P-C2</t>
         </is>
       </c>
       <c r="AR50" t="n">
@@ -13172,7 +13172,7 @@
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>BUILDING ARCHITECTURAL INSIGHTS</t>
+          <t>P-C3</t>
         </is>
       </c>
       <c r="AR51" t="n">
@@ -13411,7 +13411,7 @@
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>SUSTAINABLE BUILDING DESIGN PROCESSES</t>
+          <t>P-D1</t>
         </is>
       </c>
       <c r="AR52" t="n">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>AI FOR DESIGN EVALUATION</t>
+          <t>P-B2</t>
         </is>
       </c>
       <c r="AR54" t="n">
@@ -14108,7 +14108,7 @@
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>URBAN INFRASTRUCTURE &amp; ENVIRONMENTAL SYSTEMS</t>
+          <t>P-A2</t>
         </is>
       </c>
       <c r="AR55" t="n">
@@ -14349,7 +14349,7 @@
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>URBAN INFRASTRUCTURE &amp; ENVIRONMENTAL SYSTEMS</t>
+          <t>P-A2</t>
         </is>
       </c>
       <c r="AR56" t="n">
@@ -14589,7 +14589,7 @@
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>IMMERSIVE LEARNING &amp; DESIGN</t>
+          <t>P-B3</t>
         </is>
       </c>
       <c r="AR57" t="n">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>AI FOR DESIGN EVALUATION</t>
+          <t>P-B2</t>
         </is>
       </c>
       <c r="AR58" t="n">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>STRUCTURAL, FABRICATION &amp; MATERIAL LOGIC</t>
+          <t>P-C2</t>
         </is>
       </c>
       <c r="AR59" t="n">
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>INTELLIGENT ROBOTICS &amp; LAYOUT PLANNING</t>
+          <t>P-C1</t>
         </is>
       </c>
       <c r="AR60" t="n">
@@ -15537,7 +15537,7 @@
       </c>
       <c r="AQ61" t="inlineStr">
         <is>
-          <t>AUGMENTING DESIGN GENERATION</t>
+          <t>P-B1</t>
         </is>
       </c>
       <c r="AR61" t="n">
@@ -15773,7 +15773,7 @@
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>URBAN PERCEPTIONS &amp; PATTERNS</t>
+          <t>P-A1</t>
         </is>
       </c>
       <c r="AR62" t="n">
@@ -16014,7 +16014,7 @@
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>COMMUNITY &amp; COLLECTIVE INTELLIGENCE</t>
+          <t>P-D2</t>
         </is>
       </c>
       <c r="AR63" t="n">
@@ -16243,7 +16243,7 @@
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>IMMERSIVE LEARNING &amp; DESIGN</t>
+          <t>P-B3</t>
         </is>
       </c>
       <c r="AR64" t="n">
@@ -16482,7 +16482,7 @@
       </c>
       <c r="AQ65" t="inlineStr">
         <is>
-          <t>AUGMENTING DESIGN GENERATION</t>
+          <t>P-B1</t>
         </is>
       </c>
       <c r="AR65" t="n">
@@ -16951,7 +16951,7 @@
       </c>
       <c r="AQ67" t="inlineStr">
         <is>
-          <t>URBAN INFRASTRUCTURE &amp; ENVIRONMENTAL SYSTEMS</t>
+          <t>P-A2</t>
         </is>
       </c>
       <c r="AR67" t="n">
@@ -17217,7 +17217,7 @@
       </c>
       <c r="AQ68" t="inlineStr">
         <is>
-          <t>BUILDING ARCHITECTURAL INSIGHTS</t>
+          <t>P-C3</t>
         </is>
       </c>
       <c r="AR68" t="n">
@@ -17450,7 +17450,7 @@
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
-          <t>IMMERSIVE LEARNING &amp; DESIGN</t>
+          <t>P-B3</t>
         </is>
       </c>
       <c r="AR69" t="n">
@@ -17697,7 +17697,7 @@
       </c>
       <c r="AQ70" t="inlineStr">
         <is>
-          <t>COMMUNITY &amp; COLLECTIVE INTELLIGENCE</t>
+          <t>P-D2</t>
         </is>
       </c>
       <c r="AR70" t="n">
@@ -18154,7 +18154,7 @@
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>COMMUNITY &amp; COLLECTIVE INTELLIGENCE</t>
+          <t>P-D2</t>
         </is>
       </c>
       <c r="AR72" t="n">
@@ -18396,7 +18396,7 @@
       </c>
       <c r="AQ73" t="inlineStr">
         <is>
-          <t>URBAN INFRASTRUCTURE &amp; ENVIRONMENTAL SYSTEMS</t>
+          <t>P-A2</t>
         </is>
       </c>
       <c r="AR73" t="n">
@@ -18644,7 +18644,7 @@
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>URBAN INFRASTRUCTURE &amp; ENVIRONMENTAL SYSTEMS</t>
+          <t>P-A2</t>
         </is>
       </c>
       <c r="AR74" t="n">
@@ -18878,7 +18878,7 @@
       </c>
       <c r="AQ75" t="inlineStr">
         <is>
-          <t>BUILDING ARCHITECTURAL INSIGHTS</t>
+          <t>P-C3</t>
         </is>
       </c>
       <c r="AR75" t="n">
@@ -19120,7 +19120,7 @@
       </c>
       <c r="AQ76" t="inlineStr">
         <is>
-          <t>EVALUATING &amp; EXPANDING AI</t>
+          <t>P-A3</t>
         </is>
       </c>
       <c r="AR76" t="n">
@@ -19355,7 +19355,7 @@
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>URBAN PERCEPTIONS &amp; PATTERNS</t>
+          <t>P-A1</t>
         </is>
       </c>
       <c r="AR77" t="n">
@@ -19593,7 +19593,7 @@
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>STRUCTURAL, FABRICATION &amp; MATERIAL LOGIC</t>
+          <t>P-C2</t>
         </is>
       </c>
       <c r="AR78" t="n">
@@ -19828,7 +19828,7 @@
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>BUILDING ARCHITECTURAL INSIGHTS</t>
+          <t>P-C3</t>
         </is>
       </c>
       <c r="AR79" t="n">
@@ -20068,7 +20068,7 @@
       </c>
       <c r="AQ80" t="inlineStr">
         <is>
-          <t>AI FOR DESIGN EVALUATION</t>
+          <t>P-B2</t>
         </is>
       </c>
       <c r="AR80" t="n">
@@ -20298,7 +20298,7 @@
       </c>
       <c r="AQ81" t="inlineStr">
         <is>
-          <t>URBAN PERCEPTIONS &amp; PATTERNS</t>
+          <t>P-A1</t>
         </is>
       </c>
       <c r="AR81" t="n">
@@ -20536,7 +20536,7 @@
       </c>
       <c r="AQ82" t="inlineStr">
         <is>
-          <t>EVALUATING &amp; EXPANDING AI</t>
+          <t>P-A3</t>
         </is>
       </c>
       <c r="AR82" t="n">
@@ -20800,7 +20800,7 @@
       </c>
       <c r="AQ83" t="inlineStr">
         <is>
-          <t>COMMUNITY &amp; COLLECTIVE INTELLIGENCE</t>
+          <t>P-D2</t>
         </is>
       </c>
       <c r="AR83" t="n">
@@ -21028,7 +21028,7 @@
       </c>
       <c r="AQ84" t="inlineStr">
         <is>
-          <t>SUSTAINABLE BUILDING DESIGN PROCESSES</t>
+          <t>P-D1</t>
         </is>
       </c>
       <c r="AR84" t="n">
@@ -21260,7 +21260,7 @@
       </c>
       <c r="AQ85" t="inlineStr">
         <is>
-          <t>STRUCTURAL, FABRICATION &amp; MATERIAL LOGIC</t>
+          <t>P-C2</t>
         </is>
       </c>
       <c r="AR85" t="n">
@@ -21487,7 +21487,7 @@
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>SUSTAINABLE BUILDING DESIGN PROCESSES</t>
+          <t>P-D1</t>
         </is>
       </c>
       <c r="AR86" t="n">

--- a/images/events/cf25dat.xlsx
+++ b/images/events/cf25dat.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>S-S5</t>
+          <t>S-S4</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>S-S5</t>
+          <t>S-S4</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>S-S5</t>
+          <t>S-S4</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>S-2</t>
+          <t>S-4</t>
         </is>
       </c>
     </row>
@@ -5113,7 +5113,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>S-2</t>
+          <t>S-4</t>
         </is>
       </c>
     </row>
@@ -5315,7 +5315,7 @@
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>GENERATING BUILDING LAYOUT</t>
+          <t xml:space="preserve">GENERATING BUILDING LAYOUT </t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>GENERATING BUILDING LAYOUT</t>
+          <t xml:space="preserve">GENERATING BUILDING LAYOUT </t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>S-2</t>
+          <t>S-4</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>GENERATING BUILDING LAYOUT</t>
+          <t xml:space="preserve">GENERATING BUILDING LAYOUT </t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>S-2</t>
+          <t>S-4</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>P-C1</t>
+          <t xml:space="preserve">P-C1 </t>
         </is>
       </c>
     </row>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>P-C1</t>
+          <t xml:space="preserve">P-C1 </t>
         </is>
       </c>
     </row>
@@ -12543,7 +12543,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>P-C1</t>
+          <t xml:space="preserve">P-C1 </t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>P-C1</t>
+          <t xml:space="preserve">P-C1 </t>
         </is>
       </c>
     </row>
@@ -15382,7 +15382,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>P-C1</t>
+          <t xml:space="preserve">P-C1 </t>
         </is>
       </c>
     </row>

--- a/images/events/cf25dat.xlsx
+++ b/images/events/cf25dat.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10714"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hsg/tprojs/clementinec.github.io/images/events/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4850558F-5658-6B4A-81D7-3360F3FFF344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="660" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -3804,9 +3810,6 @@
 human, ecological, and environmental health.</t>
   </si>
   <si>
-    <t>TBU</t>
-  </si>
-  <si>
     <t>7/4/2025</t>
   </si>
   <si>
@@ -3946,13 +3949,17 @@
   </si>
   <si>
     <t>16:50 - 17:10</t>
+  </si>
+  <si>
+    <t>This paper presents HIKARI, a working prototype and design methodology for integrating generative AI into architectural design, focusing on automated compliance and building massing generation. Unlike purely speculative studies, HIKARI was developed in collaboration with a leading design firm to navigate complex building codes, offering concrete lessons on embedding AI within professional practice. The platform functions as a catalytic interface, combining generative algorithms for massing exploration, a regulatory engine for automated compliance checking against Japanese building codes, and a Retrieval-Augmented Generation (RAG) pipeline for explainable, natural-language queries. We discuss the co-creation methodology, system architecture, and key lessons on operationalizing trust and harmonizing data. Furthermore, we propose a workshop framework to empirically evaluate the platform's efficacy not only as a design tool but also as a pedagogical instrument for teaching complex regulations. This is measured by assessing knowledge acquisition through a pre- and post-test methodology, demonstrating how AI can serve as an interactive guide
+in architectural education and practice.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4004,10 +4011,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4015,13 +4025,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4059,7 +4077,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4093,6 +4111,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4127,9 +4146,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4302,11 +4322,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K89"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4338,7 +4358,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -4367,13 +4387,13 @@
         <v>224</v>
       </c>
       <c r="J2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K2" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -4402,13 +4422,13 @@
         <v>225</v>
       </c>
       <c r="J3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K3" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -4437,13 +4457,13 @@
         <v>226</v>
       </c>
       <c r="J4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K4" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -4472,13 +4492,13 @@
         <v>227</v>
       </c>
       <c r="J5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K5" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -4507,13 +4527,13 @@
         <v>228</v>
       </c>
       <c r="J6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K6" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -4542,13 +4562,13 @@
         <v>229</v>
       </c>
       <c r="J7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K7" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -4577,13 +4597,13 @@
         <v>230</v>
       </c>
       <c r="J8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K8" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -4612,13 +4632,13 @@
         <v>231</v>
       </c>
       <c r="J9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K9" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -4647,13 +4667,13 @@
         <v>232</v>
       </c>
       <c r="J10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K10" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -4682,13 +4702,13 @@
         <v>233</v>
       </c>
       <c r="J11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K11" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -4717,13 +4737,13 @@
         <v>234</v>
       </c>
       <c r="J12" t="s">
+        <v>313</v>
+      </c>
+      <c r="K12" t="s">
         <v>314</v>
       </c>
-      <c r="K12" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -4752,13 +4772,13 @@
         <v>235</v>
       </c>
       <c r="J13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K13" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -4787,13 +4807,13 @@
         <v>236</v>
       </c>
       <c r="J14" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -4822,13 +4842,13 @@
         <v>237</v>
       </c>
       <c r="J15" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K15" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -4857,13 +4877,13 @@
         <v>238</v>
       </c>
       <c r="J16" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K16" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -4892,13 +4912,13 @@
         <v>239</v>
       </c>
       <c r="J17" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K17" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -4927,13 +4947,13 @@
         <v>240</v>
       </c>
       <c r="J18" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K18" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -4962,13 +4982,13 @@
         <v>241</v>
       </c>
       <c r="J19" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K19" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -4997,13 +5017,13 @@
         <v>242</v>
       </c>
       <c r="J20" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K20" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -5032,13 +5052,13 @@
         <v>243</v>
       </c>
       <c r="J21" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K21" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -5067,13 +5087,13 @@
         <v>244</v>
       </c>
       <c r="J22" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K22" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -5102,13 +5122,13 @@
         <v>245</v>
       </c>
       <c r="J23" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K23" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -5137,13 +5157,13 @@
         <v>246</v>
       </c>
       <c r="J24" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K24" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -5172,13 +5192,13 @@
         <v>247</v>
       </c>
       <c r="J25" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K25" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -5207,13 +5227,13 @@
         <v>248</v>
       </c>
       <c r="J26" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K26" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -5242,13 +5262,13 @@
         <v>249</v>
       </c>
       <c r="J27" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K27" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -5277,13 +5297,13 @@
         <v>250</v>
       </c>
       <c r="J28" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K28" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -5312,13 +5332,13 @@
         <v>251</v>
       </c>
       <c r="J29" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K29" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -5347,13 +5367,13 @@
         <v>252</v>
       </c>
       <c r="J30" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K30" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -5382,13 +5402,13 @@
         <v>253</v>
       </c>
       <c r="J31" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K31" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -5417,13 +5437,13 @@
         <v>254</v>
       </c>
       <c r="J32" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K32" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -5452,13 +5472,13 @@
         <v>255</v>
       </c>
       <c r="J33" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K33" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -5487,13 +5507,13 @@
         <v>256</v>
       </c>
       <c r="J34" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K34" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -5522,13 +5542,13 @@
         <v>257</v>
       </c>
       <c r="J35" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K35" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -5557,13 +5577,13 @@
         <v>258</v>
       </c>
       <c r="J36" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K36" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -5592,13 +5612,13 @@
         <v>259</v>
       </c>
       <c r="J37" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K37" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -5627,13 +5647,13 @@
         <v>260</v>
       </c>
       <c r="J38" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K38" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -5662,13 +5682,13 @@
         <v>261</v>
       </c>
       <c r="J39" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K39" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -5697,13 +5717,13 @@
         <v>262</v>
       </c>
       <c r="J40" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K40" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -5732,13 +5752,13 @@
         <v>263</v>
       </c>
       <c r="J41" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K41" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -5767,13 +5787,13 @@
         <v>264</v>
       </c>
       <c r="J42" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K42" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -5802,13 +5822,13 @@
         <v>265</v>
       </c>
       <c r="J43" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K43" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -5837,13 +5857,13 @@
         <v>266</v>
       </c>
       <c r="J44" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K44" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -5872,13 +5892,13 @@
         <v>267</v>
       </c>
       <c r="J45" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K45" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -5907,13 +5927,13 @@
         <v>268</v>
       </c>
       <c r="J46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K46" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -5942,13 +5962,13 @@
         <v>269</v>
       </c>
       <c r="J47" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K47" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -5977,13 +5997,13 @@
         <v>270</v>
       </c>
       <c r="J48" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K48" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -6012,13 +6032,13 @@
         <v>271</v>
       </c>
       <c r="J49" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K49" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -6047,13 +6067,13 @@
         <v>272</v>
       </c>
       <c r="J50" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K50" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -6082,13 +6102,13 @@
         <v>273</v>
       </c>
       <c r="J51" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K51" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -6117,13 +6137,13 @@
         <v>274</v>
       </c>
       <c r="J52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K52" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -6152,13 +6172,13 @@
         <v>275</v>
       </c>
       <c r="J53" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K53" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -6187,13 +6207,13 @@
         <v>276</v>
       </c>
       <c r="J54" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K54" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -6222,13 +6242,13 @@
         <v>277</v>
       </c>
       <c r="J55" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K55" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -6257,13 +6277,13 @@
         <v>278</v>
       </c>
       <c r="J56" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K56" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -6292,13 +6312,13 @@
         <v>279</v>
       </c>
       <c r="J57" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K57" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -6327,13 +6347,13 @@
         <v>280</v>
       </c>
       <c r="J58" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K58" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -6362,13 +6382,13 @@
         <v>281</v>
       </c>
       <c r="J59" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K59" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -6397,13 +6417,13 @@
         <v>282</v>
       </c>
       <c r="J60" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K60" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -6432,13 +6452,13 @@
         <v>283</v>
       </c>
       <c r="J61" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K61" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -6467,13 +6487,13 @@
         <v>284</v>
       </c>
       <c r="J62" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K62" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -6502,13 +6522,13 @@
         <v>285</v>
       </c>
       <c r="J63" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K63" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -6537,13 +6557,13 @@
         <v>286</v>
       </c>
       <c r="J64" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K64" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -6572,13 +6592,13 @@
         <v>287</v>
       </c>
       <c r="J65" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K65" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -6607,13 +6627,13 @@
         <v>288</v>
       </c>
       <c r="J66" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K66" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -6642,13 +6662,13 @@
         <v>289</v>
       </c>
       <c r="J67" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K67" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -6677,13 +6697,13 @@
         <v>290</v>
       </c>
       <c r="J68" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K68" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -6712,13 +6732,13 @@
         <v>291</v>
       </c>
       <c r="J69" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K69" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -6747,13 +6767,13 @@
         <v>292</v>
       </c>
       <c r="J70" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K70" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -6782,13 +6802,13 @@
         <v>293</v>
       </c>
       <c r="J71" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K71" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -6817,13 +6837,13 @@
         <v>294</v>
       </c>
       <c r="J72" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K72" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -6852,13 +6872,13 @@
         <v>295</v>
       </c>
       <c r="J73" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K73" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -6887,13 +6907,13 @@
         <v>296</v>
       </c>
       <c r="J74" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K74" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -6922,13 +6942,13 @@
         <v>297</v>
       </c>
       <c r="J75" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K75" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -6957,13 +6977,13 @@
         <v>298</v>
       </c>
       <c r="J76" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K76" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -6992,13 +7012,13 @@
         <v>299</v>
       </c>
       <c r="J77" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K77" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -7027,13 +7047,13 @@
         <v>300</v>
       </c>
       <c r="J78" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K78" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -7062,13 +7082,13 @@
         <v>301</v>
       </c>
       <c r="J79" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K79" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -7097,13 +7117,13 @@
         <v>302</v>
       </c>
       <c r="J80" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K80" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -7132,13 +7152,13 @@
         <v>303</v>
       </c>
       <c r="J81" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K81" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -7167,13 +7187,13 @@
         <v>304</v>
       </c>
       <c r="J82" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K82" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -7202,10 +7222,10 @@
         <v>305</v>
       </c>
       <c r="K83" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -7234,13 +7254,13 @@
         <v>306</v>
       </c>
       <c r="J84" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K84" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -7269,13 +7289,13 @@
         <v>307</v>
       </c>
       <c r="J85" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K85" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -7304,13 +7324,13 @@
         <v>308</v>
       </c>
       <c r="J86" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K86" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -7339,13 +7359,13 @@
         <v>309</v>
       </c>
       <c r="J87" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K87" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -7374,13 +7394,13 @@
         <v>310</v>
       </c>
       <c r="J88" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K88" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -7405,14 +7425,14 @@
       <c r="H89" t="s">
         <v>223</v>
       </c>
-      <c r="I89" t="s">
+      <c r="I89" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J89" t="s">
         <v>311</v>
       </c>
-      <c r="J89" t="s">
-        <v>312</v>
-      </c>
       <c r="K89" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>

--- a/images/events/cf25dat.xlsx
+++ b/images/events/cf25dat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hsg/tprojs/clementinec.github.io/images/events/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4850558F-5658-6B4A-81D7-3360F3FFF344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB33B27A-F4EE-D34F-9101-F20CEC4DA458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="660" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="360">
+  <si>
+    <t>Unnamed: 0.1</t>
+  </si>
   <si>
     <t>Unnamed: 0</t>
   </si>
@@ -657,6 +660,9 @@
     <t>Catalytic Interface</t>
   </si>
   <si>
+    <t>S-S4</t>
+  </si>
+  <si>
     <t>S-S5</t>
   </si>
   <si>
@@ -669,12 +675,18 @@
     <t>S-3</t>
   </si>
   <si>
+    <t>S-S3</t>
+  </si>
+  <si>
+    <t>S-4</t>
+  </si>
+  <si>
+    <t>S-1</t>
+  </si>
+  <si>
     <t>S-2</t>
   </si>
   <si>
-    <t>S-1</t>
-  </si>
-  <si>
     <t>P-A3</t>
   </si>
   <si>
@@ -690,7 +702,7 @@
     <t>P-B3</t>
   </si>
   <si>
-    <t>P-C1</t>
+    <t xml:space="preserve">P-C1 </t>
   </si>
   <si>
     <t>P-C2</t>
@@ -3810,155 +3822,149 @@
 human, ecological, and environmental health.</t>
   </si>
   <si>
-    <t>7/4/2025</t>
-  </si>
-  <si>
-    <t>7/2/2025</t>
-  </si>
-  <si>
-    <t>7/3/2025</t>
-  </si>
-  <si>
-    <t>10:50 - 11:05</t>
-  </si>
-  <si>
-    <t>13:45 - 14:00</t>
-  </si>
-  <si>
-    <t>11:25 - 11:40</t>
-  </si>
-  <si>
-    <t>14:00 - 14:15</t>
-  </si>
-  <si>
-    <t>10:35 - 10:50</t>
-  </si>
-  <si>
-    <t>11:40 - 11:55</t>
-  </si>
-  <si>
-    <t>11:05 - 11:20</t>
-  </si>
-  <si>
-    <t>14:15 - 14:30</t>
-  </si>
-  <si>
-    <t>11:20 - 11:35</t>
-  </si>
-  <si>
-    <t>16:10 - 16:25</t>
-  </si>
-  <si>
-    <t>11:55 - 12:10</t>
-  </si>
-  <si>
-    <t>14:30 - 14:45</t>
-  </si>
-  <si>
-    <t>1/0/1900</t>
-  </si>
-  <si>
-    <t>17:30 - 17:45</t>
-  </si>
-  <si>
-    <t>15:05 - 15:20</t>
-  </si>
-  <si>
-    <t>15:55 - 16:10</t>
-  </si>
-  <si>
-    <t>14:20 - 14:35</t>
-  </si>
-  <si>
-    <t>17:00 - 17:15</t>
-  </si>
-  <si>
-    <t>14:35 - 14:50</t>
-  </si>
-  <si>
-    <t>15:40 - 16:25</t>
-  </si>
-  <si>
-    <t>14:45 - 15:00</t>
-  </si>
-  <si>
-    <t>17:15 - 17:30</t>
-  </si>
-  <si>
-    <t>12:00 - 12:10</t>
-  </si>
-  <si>
-    <t>13:30 - 13:40</t>
-  </si>
-  <si>
-    <t>13:10 - 13:20</t>
-  </si>
-  <si>
-    <t>12:30 - 12:40</t>
-  </si>
-  <si>
-    <t>12:20 - 12:30</t>
-  </si>
-  <si>
-    <t>13:20 - 13:30</t>
-  </si>
-  <si>
-    <t>13:05 - 13:15</t>
-  </si>
-  <si>
-    <t>12:45 - 12:55</t>
-  </si>
-  <si>
-    <t>13:50 - 14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:10 - 12:20 </t>
-  </si>
-  <si>
-    <t>15:40 - 15:55</t>
-  </si>
-  <si>
-    <t>12:55 - 13:05</t>
-  </si>
-  <si>
-    <t>13:15 - 13:25</t>
-  </si>
-  <si>
-    <t>12:40 - 12:50</t>
-  </si>
-  <si>
-    <t>13:25 - 13:35</t>
-  </si>
-  <si>
-    <t>13:40 - 13:50</t>
-  </si>
-  <si>
-    <t>15:10 - 15:30</t>
-  </si>
-  <si>
-    <t>15:30 - 15:50</t>
-  </si>
-  <si>
-    <t>15:50 - 16:10</t>
-  </si>
-  <si>
-    <t>16:10 - 16:30</t>
-  </si>
-  <si>
-    <t>16:30 - 16:50</t>
-  </si>
-  <si>
-    <t>16:50 - 17:10</t>
-  </si>
-  <si>
     <t>This paper presents HIKARI, a working prototype and design methodology for integrating generative AI into architectural design, focusing on automated compliance and building massing generation. Unlike purely speculative studies, HIKARI was developed in collaboration with a leading design firm to navigate complex building codes, offering concrete lessons on embedding AI within professional practice. The platform functions as a catalytic interface, combining generative algorithms for massing exploration, a regulatory engine for automated compliance checking against Japanese building codes, and a Retrieval-Augmented Generation (RAG) pipeline for explainable, natural-language queries. We discuss the co-creation methodology, system architecture, and key lessons on operationalizing trust and harmonizing data. Furthermore, we propose a workshop framework to empirically evaluate the platform's efficacy not only as a design tool but also as a pedagogical instrument for teaching complex regulations. This is measured by assessing knowledge acquisition through a pre- and post-test methodology, demonstrating how AI can serve as an interactive guide
 in architectural education and practice.</t>
+  </si>
+  <si>
+    <t>10:50 - 11:05</t>
+  </si>
+  <si>
+    <t>13:45 - 14:00</t>
+  </si>
+  <si>
+    <t>11:25 - 11:40</t>
+  </si>
+  <si>
+    <t>14:00 - 14:15</t>
+  </si>
+  <si>
+    <t>10:35 - 10:50</t>
+  </si>
+  <si>
+    <t>11:40 - 11:55</t>
+  </si>
+  <si>
+    <t>11:05 - 11:20</t>
+  </si>
+  <si>
+    <t>14:15 - 14:30</t>
+  </si>
+  <si>
+    <t>11:20 - 11:35</t>
+  </si>
+  <si>
+    <t>16:10 - 16:25</t>
+  </si>
+  <si>
+    <t>11:55 - 12:10</t>
+  </si>
+  <si>
+    <t>14:30 - 14:45</t>
+  </si>
+  <si>
+    <t>17:30 - 17:45</t>
+  </si>
+  <si>
+    <t>15:05 - 15:20</t>
+  </si>
+  <si>
+    <t>15:55 - 16:10</t>
+  </si>
+  <si>
+    <t>14:20 - 14:35</t>
+  </si>
+  <si>
+    <t>17:00 - 17:15</t>
+  </si>
+  <si>
+    <t>14:35 - 14:50</t>
+  </si>
+  <si>
+    <t>15:40 - 16:25</t>
+  </si>
+  <si>
+    <t>14:45 - 15:00</t>
+  </si>
+  <si>
+    <t>17:15 - 17:30</t>
+  </si>
+  <si>
+    <t>12:00 - 12:10</t>
+  </si>
+  <si>
+    <t>13:30 - 13:40</t>
+  </si>
+  <si>
+    <t>13:10 - 13:20</t>
+  </si>
+  <si>
+    <t>12:30 - 12:40</t>
+  </si>
+  <si>
+    <t>12:20 - 12:30</t>
+  </si>
+  <si>
+    <t>13:20 - 13:30</t>
+  </si>
+  <si>
+    <t>13:05 - 13:15</t>
+  </si>
+  <si>
+    <t>12:45 - 12:55</t>
+  </si>
+  <si>
+    <t>13:50 - 14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:10 - 12:20 </t>
+  </si>
+  <si>
+    <t>15:40 - 15:55</t>
+  </si>
+  <si>
+    <t>12:55 - 13:05</t>
+  </si>
+  <si>
+    <t>13:15 - 13:25</t>
+  </si>
+  <si>
+    <t>12:40 - 12:50</t>
+  </si>
+  <si>
+    <t>13:25 - 13:35</t>
+  </si>
+  <si>
+    <t>13:40 - 13:50</t>
+  </si>
+  <si>
+    <t>15:10 - 15:30</t>
+  </si>
+  <si>
+    <t>15:30 - 15:50</t>
+  </si>
+  <si>
+    <t>15:50 - 16:10</t>
+  </si>
+  <si>
+    <t>16:10 - 16:30</t>
+  </si>
+  <si>
+    <t>16:30 - 16:50</t>
+  </si>
+  <si>
+    <t>16:50 - 17:10</t>
+  </si>
+  <si>
+    <t>16:45 - 17:45</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -4016,9 +4022,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4323,10 +4327,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K89"/>
+  <dimension ref="A1:L89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4357,8 +4361,11 @@
       <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -4369,31 +4376,34 @@
         <v>0</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>403</v>
       </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
       <c r="F2" t="s">
-        <v>98</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>186</v>
+        <v>99</v>
       </c>
       <c r="H2" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="I2" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="J2" t="s">
-        <v>311</v>
-      </c>
-      <c r="K2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+      <c r="K2" s="2">
+        <v>45842</v>
+      </c>
+      <c r="L2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -4404,31 +4414,34 @@
         <v>1</v>
       </c>
       <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>114</v>
       </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
       <c r="F3" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>187</v>
+        <v>100</v>
       </c>
       <c r="H3" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="I3" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="J3" t="s">
-        <v>311</v>
-      </c>
-      <c r="K3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+        <v>229</v>
+      </c>
+      <c r="K3" s="2">
+        <v>45842</v>
+      </c>
+      <c r="L3" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -4439,31 +4452,34 @@
         <v>2</v>
       </c>
       <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
         <v>238</v>
       </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
       <c r="F4" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>188</v>
+        <v>101</v>
       </c>
       <c r="H4" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I4" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="J4" t="s">
-        <v>312</v>
-      </c>
-      <c r="K4" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+        <v>230</v>
+      </c>
+      <c r="K4" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -4474,31 +4490,34 @@
         <v>3</v>
       </c>
       <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
         <v>231</v>
       </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
       <c r="F5" t="s">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>187</v>
+        <v>102</v>
       </c>
       <c r="H5" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="I5" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="J5" t="s">
-        <v>311</v>
-      </c>
-      <c r="K5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+        <v>231</v>
+      </c>
+      <c r="K5" s="2">
+        <v>45842</v>
+      </c>
+      <c r="L5" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -4509,31 +4528,34 @@
         <v>4</v>
       </c>
       <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
         <v>444</v>
       </c>
-      <c r="E6" t="s">
-        <v>14</v>
-      </c>
       <c r="F6" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>186</v>
+        <v>103</v>
       </c>
       <c r="H6" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="I6" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="J6" t="s">
-        <v>311</v>
-      </c>
-      <c r="K6" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+        <v>232</v>
+      </c>
+      <c r="K6" s="2">
+        <v>45842</v>
+      </c>
+      <c r="L6" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -4544,31 +4566,34 @@
         <v>5</v>
       </c>
       <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
         <v>349</v>
       </c>
-      <c r="E7" t="s">
-        <v>15</v>
-      </c>
       <c r="F7" t="s">
-        <v>103</v>
+        <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>188</v>
+        <v>104</v>
       </c>
       <c r="H7" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I7" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="J7" t="s">
-        <v>312</v>
-      </c>
-      <c r="K7" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+        <v>233</v>
+      </c>
+      <c r="K7" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L7" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -4579,31 +4604,34 @@
         <v>6</v>
       </c>
       <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="E8">
         <v>329</v>
       </c>
-      <c r="E8" t="s">
-        <v>16</v>
-      </c>
       <c r="F8" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>189</v>
+        <v>105</v>
       </c>
       <c r="H8" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="I8" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="J8" t="s">
-        <v>313</v>
-      </c>
-      <c r="K8" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+        <v>234</v>
+      </c>
+      <c r="K8" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L8" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -4614,31 +4642,34 @@
         <v>7</v>
       </c>
       <c r="D9">
+        <v>7</v>
+      </c>
+      <c r="E9">
         <v>148</v>
       </c>
-      <c r="E9" t="s">
-        <v>17</v>
-      </c>
       <c r="F9" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="H9" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="I9" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="J9" t="s">
-        <v>313</v>
-      </c>
-      <c r="K9" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+        <v>235</v>
+      </c>
+      <c r="K9" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L9" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -4649,31 +4680,34 @@
         <v>8</v>
       </c>
       <c r="D10">
+        <v>8</v>
+      </c>
+      <c r="E10">
         <v>230</v>
       </c>
-      <c r="E10" t="s">
-        <v>18</v>
-      </c>
       <c r="F10" t="s">
-        <v>106</v>
+        <v>19</v>
       </c>
       <c r="G10" t="s">
-        <v>187</v>
+        <v>107</v>
       </c>
       <c r="H10" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="I10" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="J10" t="s">
-        <v>311</v>
-      </c>
-      <c r="K10" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+        <v>236</v>
+      </c>
+      <c r="K10" s="2">
+        <v>45842</v>
+      </c>
+      <c r="L10" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -4684,31 +4718,34 @@
         <v>9</v>
       </c>
       <c r="D11">
+        <v>9</v>
+      </c>
+      <c r="E11">
         <v>253</v>
       </c>
-      <c r="E11" t="s">
-        <v>19</v>
-      </c>
       <c r="F11" t="s">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="G11" t="s">
-        <v>186</v>
+        <v>108</v>
       </c>
       <c r="H11" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="I11" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="J11" t="s">
-        <v>311</v>
-      </c>
-      <c r="K11" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+        <v>237</v>
+      </c>
+      <c r="K11" s="2">
+        <v>45842</v>
+      </c>
+      <c r="L11" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -4719,31 +4756,34 @@
         <v>10</v>
       </c>
       <c r="D12">
+        <v>10</v>
+      </c>
+      <c r="E12">
         <v>55</v>
       </c>
-      <c r="E12" t="s">
-        <v>20</v>
-      </c>
       <c r="F12" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="G12" t="s">
-        <v>189</v>
+        <v>109</v>
       </c>
       <c r="H12" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="I12" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="J12" t="s">
-        <v>313</v>
-      </c>
-      <c r="K12" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+        <v>238</v>
+      </c>
+      <c r="K12" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L12" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -4754,31 +4794,34 @@
         <v>11</v>
       </c>
       <c r="D13">
+        <v>11</v>
+      </c>
+      <c r="E13">
         <v>262</v>
       </c>
-      <c r="E13" t="s">
-        <v>21</v>
-      </c>
       <c r="F13" t="s">
-        <v>109</v>
+        <v>22</v>
       </c>
       <c r="G13" t="s">
-        <v>189</v>
+        <v>110</v>
       </c>
       <c r="H13" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="I13" t="s">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="J13" t="s">
-        <v>313</v>
-      </c>
-      <c r="K13" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+        <v>239</v>
+      </c>
+      <c r="K13" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L13" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -4789,31 +4832,34 @@
         <v>12</v>
       </c>
       <c r="D14">
+        <v>12</v>
+      </c>
+      <c r="E14">
         <v>250</v>
       </c>
-      <c r="E14" t="s">
-        <v>22</v>
-      </c>
       <c r="F14" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
-        <v>190</v>
+        <v>111</v>
       </c>
       <c r="H14" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="I14" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="J14" t="s">
-        <v>313</v>
-      </c>
-      <c r="K14" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+        <v>240</v>
+      </c>
+      <c r="K14" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L14" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -4824,31 +4870,34 @@
         <v>13</v>
       </c>
       <c r="D15">
+        <v>13</v>
+      </c>
+      <c r="E15">
         <v>36</v>
       </c>
-      <c r="E15" t="s">
-        <v>23</v>
-      </c>
       <c r="F15" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="G15" t="s">
-        <v>188</v>
+        <v>112</v>
       </c>
       <c r="H15" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I15" t="s">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="J15" t="s">
-        <v>312</v>
-      </c>
-      <c r="K15" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+        <v>241</v>
+      </c>
+      <c r="K15" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L15" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -4859,31 +4908,34 @@
         <v>14</v>
       </c>
       <c r="D16">
+        <v>14</v>
+      </c>
+      <c r="E16">
         <v>431</v>
       </c>
-      <c r="E16" t="s">
-        <v>24</v>
-      </c>
       <c r="F16" t="s">
-        <v>112</v>
+        <v>25</v>
       </c>
       <c r="G16" t="s">
-        <v>191</v>
+        <v>113</v>
       </c>
       <c r="H16" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="I16" t="s">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="J16" t="s">
-        <v>313</v>
-      </c>
-      <c r="K16" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+        <v>242</v>
+      </c>
+      <c r="K16" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L16" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -4894,31 +4946,34 @@
         <v>15</v>
       </c>
       <c r="D17">
+        <v>15</v>
+      </c>
+      <c r="E17">
         <v>132</v>
       </c>
-      <c r="E17" t="s">
-        <v>25</v>
-      </c>
       <c r="F17" t="s">
-        <v>113</v>
+        <v>26</v>
       </c>
       <c r="G17" t="s">
-        <v>192</v>
+        <v>114</v>
       </c>
       <c r="H17" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="I17" t="s">
-        <v>239</v>
+        <v>213</v>
       </c>
       <c r="J17" t="s">
-        <v>313</v>
-      </c>
-      <c r="K17" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+        <v>243</v>
+      </c>
+      <c r="K17" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L17" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -4929,31 +4984,34 @@
         <v>16</v>
       </c>
       <c r="D18">
+        <v>16</v>
+      </c>
+      <c r="E18">
         <v>178</v>
       </c>
-      <c r="E18" t="s">
-        <v>26</v>
-      </c>
       <c r="F18" t="s">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c r="G18" t="s">
-        <v>192</v>
+        <v>115</v>
       </c>
       <c r="H18" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="I18" t="s">
-        <v>240</v>
+        <v>213</v>
       </c>
       <c r="J18" t="s">
-        <v>313</v>
-      </c>
-      <c r="K18" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+        <v>244</v>
+      </c>
+      <c r="K18" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L18" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -4964,31 +5022,34 @@
         <v>17</v>
       </c>
       <c r="D19">
+        <v>17</v>
+      </c>
+      <c r="E19">
         <v>151</v>
       </c>
-      <c r="E19" t="s">
-        <v>27</v>
-      </c>
       <c r="F19" t="s">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="G19" t="s">
-        <v>193</v>
+        <v>116</v>
       </c>
       <c r="H19" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="I19" t="s">
-        <v>241</v>
+        <v>214</v>
       </c>
       <c r="J19" t="s">
-        <v>312</v>
-      </c>
-      <c r="K19" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+        <v>245</v>
+      </c>
+      <c r="K19" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L19" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -4999,31 +5060,34 @@
         <v>18</v>
       </c>
       <c r="D20">
+        <v>18</v>
+      </c>
+      <c r="E20">
         <v>440</v>
       </c>
-      <c r="E20" t="s">
-        <v>28</v>
-      </c>
       <c r="F20" t="s">
-        <v>116</v>
+        <v>29</v>
       </c>
       <c r="G20" t="s">
-        <v>191</v>
+        <v>117</v>
       </c>
       <c r="H20" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="I20" t="s">
-        <v>242</v>
+        <v>212</v>
       </c>
       <c r="J20" t="s">
-        <v>313</v>
-      </c>
-      <c r="K20" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+        <v>246</v>
+      </c>
+      <c r="K20" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L20" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -5034,31 +5098,34 @@
         <v>19</v>
       </c>
       <c r="D21">
+        <v>19</v>
+      </c>
+      <c r="E21">
         <v>198</v>
       </c>
-      <c r="E21" t="s">
-        <v>29</v>
-      </c>
       <c r="F21" t="s">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="G21" t="s">
-        <v>190</v>
+        <v>118</v>
       </c>
       <c r="H21" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="I21" t="s">
-        <v>243</v>
+        <v>211</v>
       </c>
       <c r="J21" t="s">
-        <v>313</v>
-      </c>
-      <c r="K21" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+        <v>247</v>
+      </c>
+      <c r="K21" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L21" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -5069,31 +5136,34 @@
         <v>20</v>
       </c>
       <c r="D22">
+        <v>20</v>
+      </c>
+      <c r="E22">
         <v>426</v>
       </c>
-      <c r="E22" t="s">
-        <v>30</v>
-      </c>
       <c r="F22" t="s">
-        <v>118</v>
+        <v>31</v>
       </c>
       <c r="G22" t="s">
-        <v>194</v>
+        <v>119</v>
       </c>
       <c r="H22" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="I22" t="s">
-        <v>244</v>
+        <v>215</v>
       </c>
       <c r="J22" t="s">
-        <v>312</v>
-      </c>
-      <c r="K22" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+        <v>248</v>
+      </c>
+      <c r="K22" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L22" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -5104,31 +5174,34 @@
         <v>21</v>
       </c>
       <c r="D23">
+        <v>21</v>
+      </c>
+      <c r="E23">
         <v>126</v>
       </c>
-      <c r="E23" t="s">
-        <v>31</v>
-      </c>
       <c r="F23" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="G23" t="s">
-        <v>193</v>
+        <v>120</v>
       </c>
       <c r="H23" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="I23" t="s">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="J23" t="s">
-        <v>312</v>
-      </c>
-      <c r="K23" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+        <v>249</v>
+      </c>
+      <c r="K23" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L23" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -5139,31 +5212,34 @@
         <v>22</v>
       </c>
       <c r="D24">
+        <v>22</v>
+      </c>
+      <c r="E24">
         <v>193</v>
       </c>
-      <c r="E24" t="s">
-        <v>32</v>
-      </c>
       <c r="F24" t="s">
-        <v>120</v>
+        <v>33</v>
       </c>
       <c r="G24" t="s">
-        <v>192</v>
+        <v>121</v>
       </c>
       <c r="H24" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="I24" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="J24" t="s">
-        <v>313</v>
-      </c>
-      <c r="K24" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+        <v>250</v>
+      </c>
+      <c r="K24" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L24" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -5174,31 +5250,34 @@
         <v>23</v>
       </c>
       <c r="D25">
+        <v>23</v>
+      </c>
+      <c r="E25">
         <v>134</v>
       </c>
-      <c r="E25" t="s">
-        <v>33</v>
-      </c>
       <c r="F25" t="s">
-        <v>121</v>
+        <v>34</v>
       </c>
       <c r="G25" t="s">
-        <v>193</v>
+        <v>122</v>
       </c>
       <c r="H25" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="I25" t="s">
-        <v>247</v>
+        <v>214</v>
       </c>
       <c r="J25" t="s">
-        <v>312</v>
-      </c>
-      <c r="K25" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+        <v>251</v>
+      </c>
+      <c r="K25" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L25" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -5209,31 +5288,34 @@
         <v>24</v>
       </c>
       <c r="D26">
+        <v>24</v>
+      </c>
+      <c r="E26">
         <v>50</v>
       </c>
-      <c r="E26" t="s">
-        <v>34</v>
-      </c>
       <c r="F26" t="s">
-        <v>122</v>
+        <v>35</v>
       </c>
       <c r="G26" t="s">
-        <v>190</v>
+        <v>123</v>
       </c>
       <c r="H26" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="I26" t="s">
-        <v>248</v>
+        <v>211</v>
       </c>
       <c r="J26" t="s">
-        <v>313</v>
-      </c>
-      <c r="K26" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+        <v>252</v>
+      </c>
+      <c r="K26" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L26" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -5244,31 +5326,34 @@
         <v>25</v>
       </c>
       <c r="D27">
+        <v>25</v>
+      </c>
+      <c r="E27">
         <v>314</v>
       </c>
-      <c r="E27" t="s">
-        <v>35</v>
-      </c>
       <c r="F27" t="s">
-        <v>123</v>
+        <v>36</v>
       </c>
       <c r="G27" t="s">
-        <v>191</v>
+        <v>124</v>
       </c>
       <c r="H27" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="I27" t="s">
-        <v>249</v>
+        <v>212</v>
       </c>
       <c r="J27" t="s">
-        <v>313</v>
-      </c>
-      <c r="K27" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+        <v>253</v>
+      </c>
+      <c r="K27" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L27" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -5279,31 +5364,34 @@
         <v>26</v>
       </c>
       <c r="D28">
+        <v>26</v>
+      </c>
+      <c r="E28">
         <v>386</v>
       </c>
-      <c r="E28" t="s">
-        <v>36</v>
-      </c>
       <c r="F28" t="s">
-        <v>124</v>
+        <v>37</v>
       </c>
       <c r="G28" t="s">
-        <v>192</v>
+        <v>125</v>
       </c>
       <c r="H28" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="I28" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="J28" t="s">
-        <v>313</v>
-      </c>
-      <c r="K28" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+        <v>254</v>
+      </c>
+      <c r="K28" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L28" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -5314,31 +5402,34 @@
         <v>27</v>
       </c>
       <c r="D29">
+        <v>27</v>
+      </c>
+      <c r="E29">
         <v>196</v>
       </c>
-      <c r="E29" t="s">
-        <v>37</v>
-      </c>
       <c r="F29" t="s">
-        <v>125</v>
+        <v>38</v>
       </c>
       <c r="G29" t="s">
-        <v>194</v>
+        <v>126</v>
       </c>
       <c r="H29" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="I29" t="s">
-        <v>251</v>
+        <v>215</v>
       </c>
       <c r="J29" t="s">
-        <v>312</v>
-      </c>
-      <c r="K29" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+        <v>255</v>
+      </c>
+      <c r="K29" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L29" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -5349,31 +5440,34 @@
         <v>28</v>
       </c>
       <c r="D30">
+        <v>28</v>
+      </c>
+      <c r="E30">
         <v>135</v>
       </c>
-      <c r="E30" t="s">
-        <v>38</v>
-      </c>
       <c r="F30" t="s">
-        <v>126</v>
+        <v>39</v>
       </c>
       <c r="G30" t="s">
-        <v>195</v>
+        <v>127</v>
       </c>
       <c r="H30" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="I30" t="s">
-        <v>252</v>
+        <v>216</v>
       </c>
       <c r="J30" t="s">
-        <v>311</v>
-      </c>
-      <c r="K30" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+        <v>256</v>
+      </c>
+      <c r="K30" s="2">
+        <v>45842</v>
+      </c>
+      <c r="L30" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -5384,31 +5478,34 @@
         <v>29</v>
       </c>
       <c r="D31">
+        <v>29</v>
+      </c>
+      <c r="E31">
         <v>210</v>
       </c>
-      <c r="E31" t="s">
-        <v>39</v>
-      </c>
       <c r="F31" t="s">
-        <v>127</v>
+        <v>40</v>
       </c>
       <c r="G31" t="s">
-        <v>191</v>
+        <v>128</v>
       </c>
       <c r="H31" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="I31" t="s">
-        <v>253</v>
+        <v>212</v>
       </c>
       <c r="J31" t="s">
-        <v>313</v>
-      </c>
-      <c r="K31" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+        <v>257</v>
+      </c>
+      <c r="K31" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L31" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -5419,31 +5516,34 @@
         <v>30</v>
       </c>
       <c r="D32">
+        <v>30</v>
+      </c>
+      <c r="E32">
         <v>162</v>
       </c>
-      <c r="E32" t="s">
-        <v>40</v>
-      </c>
       <c r="F32" t="s">
-        <v>128</v>
+        <v>41</v>
       </c>
       <c r="G32" t="s">
-        <v>196</v>
+        <v>129</v>
       </c>
       <c r="H32" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="I32" t="s">
-        <v>254</v>
+        <v>217</v>
       </c>
       <c r="J32" t="s">
-        <v>312</v>
-      </c>
-      <c r="K32" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+        <v>258</v>
+      </c>
+      <c r="K32" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L32" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -5454,31 +5554,34 @@
         <v>31</v>
       </c>
       <c r="D33">
+        <v>31</v>
+      </c>
+      <c r="E33">
         <v>169</v>
       </c>
-      <c r="E33" t="s">
-        <v>41</v>
-      </c>
       <c r="F33" t="s">
-        <v>129</v>
+        <v>42</v>
       </c>
       <c r="G33" t="s">
-        <v>197</v>
+        <v>130</v>
       </c>
       <c r="H33" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="I33" t="s">
-        <v>255</v>
+        <v>218</v>
       </c>
       <c r="J33" t="s">
-        <v>312</v>
-      </c>
-      <c r="K33" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+        <v>259</v>
+      </c>
+      <c r="K33" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L33" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -5489,31 +5592,34 @@
         <v>32</v>
       </c>
       <c r="D34">
+        <v>32</v>
+      </c>
+      <c r="E34">
         <v>19</v>
       </c>
-      <c r="E34" t="s">
-        <v>42</v>
-      </c>
       <c r="F34" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="G34" t="s">
-        <v>195</v>
+        <v>131</v>
       </c>
       <c r="H34" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="I34" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="J34" t="s">
-        <v>311</v>
-      </c>
-      <c r="K34" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+        <v>260</v>
+      </c>
+      <c r="K34" s="2">
+        <v>45842</v>
+      </c>
+      <c r="L34" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -5524,31 +5630,34 @@
         <v>33</v>
       </c>
       <c r="D35">
+        <v>33</v>
+      </c>
+      <c r="E35">
         <v>240</v>
       </c>
-      <c r="E35" t="s">
-        <v>43</v>
-      </c>
       <c r="F35" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="G35" t="s">
-        <v>198</v>
+        <v>132</v>
       </c>
       <c r="H35" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="I35" t="s">
-        <v>257</v>
+        <v>219</v>
       </c>
       <c r="J35" t="s">
-        <v>312</v>
-      </c>
-      <c r="K35" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+        <v>261</v>
+      </c>
+      <c r="K35" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L35" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -5559,31 +5668,34 @@
         <v>34</v>
       </c>
       <c r="D36">
+        <v>34</v>
+      </c>
+      <c r="E36">
         <v>379</v>
       </c>
-      <c r="E36" t="s">
-        <v>44</v>
-      </c>
       <c r="F36" t="s">
-        <v>132</v>
+        <v>45</v>
       </c>
       <c r="G36" t="s">
-        <v>199</v>
+        <v>133</v>
       </c>
       <c r="H36" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="I36" t="s">
-        <v>258</v>
+        <v>220</v>
       </c>
       <c r="J36" t="s">
-        <v>311</v>
-      </c>
-      <c r="K36" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+        <v>262</v>
+      </c>
+      <c r="K36" s="2">
+        <v>45842</v>
+      </c>
+      <c r="L36" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -5594,31 +5706,34 @@
         <v>35</v>
       </c>
       <c r="D37">
+        <v>35</v>
+      </c>
+      <c r="E37">
         <v>149</v>
       </c>
-      <c r="E37" t="s">
-        <v>45</v>
-      </c>
       <c r="F37" t="s">
-        <v>133</v>
+        <v>46</v>
       </c>
       <c r="G37" t="s">
-        <v>200</v>
+        <v>134</v>
       </c>
       <c r="H37" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="I37" t="s">
-        <v>259</v>
+        <v>221</v>
       </c>
       <c r="J37" t="s">
-        <v>312</v>
-      </c>
-      <c r="K37" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+        <v>263</v>
+      </c>
+      <c r="K37" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L37" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -5629,31 +5744,34 @@
         <v>36</v>
       </c>
       <c r="D38">
+        <v>36</v>
+      </c>
+      <c r="E38">
         <v>87</v>
       </c>
-      <c r="E38" t="s">
-        <v>46</v>
-      </c>
       <c r="F38" t="s">
-        <v>134</v>
+        <v>47</v>
       </c>
       <c r="G38" t="s">
-        <v>200</v>
+        <v>135</v>
       </c>
       <c r="H38" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="I38" t="s">
-        <v>260</v>
+        <v>221</v>
       </c>
       <c r="J38" t="s">
-        <v>312</v>
-      </c>
-      <c r="K38" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+        <v>264</v>
+      </c>
+      <c r="K38" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L38" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -5664,31 +5782,34 @@
         <v>37</v>
       </c>
       <c r="D39">
+        <v>37</v>
+      </c>
+      <c r="E39">
         <v>221</v>
       </c>
-      <c r="E39" t="s">
-        <v>47</v>
-      </c>
       <c r="F39" t="s">
-        <v>135</v>
+        <v>48</v>
       </c>
       <c r="G39" t="s">
-        <v>192</v>
+        <v>136</v>
       </c>
       <c r="H39" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="I39" t="s">
-        <v>261</v>
+        <v>222</v>
       </c>
       <c r="J39" t="s">
-        <v>313</v>
-      </c>
-      <c r="K39" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+        <v>265</v>
+      </c>
+      <c r="K39" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L39" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -5699,31 +5820,34 @@
         <v>38</v>
       </c>
       <c r="D40">
+        <v>38</v>
+      </c>
+      <c r="E40">
         <v>45</v>
       </c>
-      <c r="E40" t="s">
-        <v>48</v>
-      </c>
       <c r="F40" t="s">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="G40" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="H40" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="I40" t="s">
-        <v>262</v>
+        <v>223</v>
       </c>
       <c r="J40" t="s">
-        <v>313</v>
-      </c>
-      <c r="K40" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+        <v>266</v>
+      </c>
+      <c r="K40" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L40" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -5734,31 +5858,34 @@
         <v>39</v>
       </c>
       <c r="D41">
+        <v>39</v>
+      </c>
+      <c r="E41">
         <v>141</v>
       </c>
-      <c r="E41" t="s">
-        <v>49</v>
-      </c>
       <c r="F41" t="s">
-        <v>137</v>
+        <v>50</v>
       </c>
       <c r="G41" t="s">
-        <v>197</v>
+        <v>138</v>
       </c>
       <c r="H41" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="I41" t="s">
-        <v>263</v>
+        <v>218</v>
       </c>
       <c r="J41" t="s">
-        <v>312</v>
-      </c>
-      <c r="K41" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+        <v>267</v>
+      </c>
+      <c r="K41" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L41" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -5769,31 +5896,34 @@
         <v>40</v>
       </c>
       <c r="D42">
+        <v>40</v>
+      </c>
+      <c r="E42">
         <v>255</v>
       </c>
-      <c r="E42" t="s">
-        <v>50</v>
-      </c>
       <c r="F42" t="s">
-        <v>138</v>
+        <v>51</v>
       </c>
       <c r="G42" t="s">
-        <v>197</v>
+        <v>139</v>
       </c>
       <c r="H42" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="I42" t="s">
-        <v>264</v>
+        <v>218</v>
       </c>
       <c r="J42" t="s">
-        <v>312</v>
-      </c>
-      <c r="K42" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+        <v>268</v>
+      </c>
+      <c r="K42" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L42" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -5804,31 +5934,34 @@
         <v>41</v>
       </c>
       <c r="D43">
+        <v>41</v>
+      </c>
+      <c r="E43">
         <v>276</v>
       </c>
-      <c r="E43" t="s">
-        <v>51</v>
-      </c>
       <c r="F43" t="s">
-        <v>139</v>
+        <v>52</v>
       </c>
       <c r="G43" t="s">
-        <v>199</v>
+        <v>140</v>
       </c>
       <c r="H43" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="I43" t="s">
-        <v>265</v>
+        <v>220</v>
       </c>
       <c r="J43" t="s">
-        <v>311</v>
-      </c>
-      <c r="K43" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+        <v>269</v>
+      </c>
+      <c r="K43" s="2">
+        <v>45842</v>
+      </c>
+      <c r="L43" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -5836,34 +5969,37 @@
         <v>42</v>
       </c>
       <c r="C44">
+        <v>42</v>
+      </c>
+      <c r="D44">
         <v>43</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>304</v>
       </c>
-      <c r="E44" t="s">
-        <v>52</v>
-      </c>
       <c r="F44" t="s">
-        <v>140</v>
+        <v>53</v>
       </c>
       <c r="G44" t="s">
-        <v>201</v>
+        <v>141</v>
       </c>
       <c r="H44" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="I44" t="s">
-        <v>266</v>
+        <v>223</v>
       </c>
       <c r="J44" t="s">
-        <v>313</v>
-      </c>
-      <c r="K44" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+        <v>270</v>
+      </c>
+      <c r="K44" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L44" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -5871,34 +6007,37 @@
         <v>43</v>
       </c>
       <c r="C45">
+        <v>43</v>
+      </c>
+      <c r="D45">
         <v>44</v>
       </c>
-      <c r="D45">
+      <c r="E45">
         <v>33</v>
       </c>
-      <c r="E45" t="s">
-        <v>53</v>
-      </c>
       <c r="F45" t="s">
-        <v>141</v>
+        <v>54</v>
       </c>
       <c r="G45" t="s">
-        <v>194</v>
+        <v>142</v>
       </c>
       <c r="H45" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="I45" t="s">
-        <v>267</v>
+        <v>215</v>
       </c>
       <c r="J45" t="s">
-        <v>312</v>
-      </c>
-      <c r="K45" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="K45" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L45" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -5906,34 +6045,37 @@
         <v>44</v>
       </c>
       <c r="C46">
+        <v>44</v>
+      </c>
+      <c r="D46">
         <v>45</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>127</v>
       </c>
-      <c r="E46" t="s">
-        <v>54</v>
-      </c>
       <c r="F46" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="G46" t="s">
-        <v>196</v>
+        <v>143</v>
       </c>
       <c r="H46" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="I46" t="s">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="J46" t="s">
-        <v>312</v>
-      </c>
-      <c r="K46" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+        <v>272</v>
+      </c>
+      <c r="K46" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L46" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -5941,34 +6083,37 @@
         <v>45</v>
       </c>
       <c r="C47">
+        <v>45</v>
+      </c>
+      <c r="D47">
         <v>46</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>222</v>
       </c>
-      <c r="E47" t="s">
-        <v>55</v>
-      </c>
       <c r="F47" t="s">
-        <v>143</v>
+        <v>56</v>
       </c>
       <c r="G47" t="s">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="H47" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="I47" t="s">
-        <v>269</v>
+        <v>221</v>
       </c>
       <c r="J47" t="s">
-        <v>312</v>
-      </c>
-      <c r="K47" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+        <v>273</v>
+      </c>
+      <c r="K47" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L47" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -5976,34 +6121,37 @@
         <v>46</v>
       </c>
       <c r="C48">
+        <v>46</v>
+      </c>
+      <c r="D48">
         <v>47</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>252</v>
       </c>
-      <c r="E48" t="s">
-        <v>56</v>
-      </c>
       <c r="F48" t="s">
-        <v>144</v>
+        <v>57</v>
       </c>
       <c r="G48" t="s">
-        <v>200</v>
+        <v>145</v>
       </c>
       <c r="H48" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="I48" t="s">
-        <v>270</v>
+        <v>221</v>
       </c>
       <c r="J48" t="s">
-        <v>312</v>
-      </c>
-      <c r="K48" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+      <c r="K48" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L48" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -6011,34 +6159,37 @@
         <v>47</v>
       </c>
       <c r="C49">
+        <v>47</v>
+      </c>
+      <c r="D49">
         <v>48</v>
       </c>
-      <c r="D49">
+      <c r="E49">
         <v>155</v>
       </c>
-      <c r="E49" t="s">
-        <v>57</v>
-      </c>
       <c r="F49" t="s">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="G49" t="s">
-        <v>192</v>
+        <v>146</v>
       </c>
       <c r="H49" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="I49" t="s">
-        <v>271</v>
+        <v>222</v>
       </c>
       <c r="J49" t="s">
-        <v>313</v>
-      </c>
-      <c r="K49" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+        <v>275</v>
+      </c>
+      <c r="K49" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L49" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -6046,34 +6197,37 @@
         <v>48</v>
       </c>
       <c r="C50">
+        <v>48</v>
+      </c>
+      <c r="D50">
         <v>49</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>133</v>
       </c>
-      <c r="E50" t="s">
-        <v>58</v>
-      </c>
       <c r="F50" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="G50" t="s">
-        <v>202</v>
+        <v>147</v>
       </c>
       <c r="H50" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="I50" t="s">
-        <v>272</v>
+        <v>224</v>
       </c>
       <c r="J50" t="s">
-        <v>311</v>
-      </c>
-      <c r="K50" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+        <v>276</v>
+      </c>
+      <c r="K50" s="2">
+        <v>45842</v>
+      </c>
+      <c r="L50" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -6081,34 +6235,37 @@
         <v>49</v>
       </c>
       <c r="C51">
+        <v>49</v>
+      </c>
+      <c r="D51">
         <v>50</v>
       </c>
-      <c r="D51">
+      <c r="E51">
         <v>447</v>
       </c>
-      <c r="E51" t="s">
-        <v>59</v>
-      </c>
       <c r="F51" t="s">
-        <v>147</v>
+        <v>60</v>
       </c>
       <c r="G51" t="s">
-        <v>196</v>
+        <v>148</v>
       </c>
       <c r="H51" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="I51" t="s">
-        <v>273</v>
+        <v>217</v>
       </c>
       <c r="J51" t="s">
-        <v>312</v>
-      </c>
-      <c r="K51" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+        <v>277</v>
+      </c>
+      <c r="K51" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L51" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -6116,34 +6273,37 @@
         <v>50</v>
       </c>
       <c r="C52">
+        <v>50</v>
+      </c>
+      <c r="D52">
         <v>52</v>
       </c>
-      <c r="D52">
+      <c r="E52">
         <v>150</v>
       </c>
-      <c r="E52" t="s">
-        <v>60</v>
-      </c>
       <c r="F52" t="s">
-        <v>148</v>
+        <v>61</v>
       </c>
       <c r="G52" t="s">
-        <v>201</v>
+        <v>149</v>
       </c>
       <c r="H52" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="I52" t="s">
-        <v>274</v>
+        <v>223</v>
       </c>
       <c r="J52" t="s">
-        <v>313</v>
-      </c>
-      <c r="K52" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+        <v>278</v>
+      </c>
+      <c r="K52" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L52" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -6151,34 +6311,37 @@
         <v>51</v>
       </c>
       <c r="C53">
+        <v>51</v>
+      </c>
+      <c r="D53">
         <v>53</v>
       </c>
-      <c r="D53">
+      <c r="E53">
         <v>29</v>
       </c>
-      <c r="E53" t="s">
-        <v>61</v>
-      </c>
       <c r="F53" t="s">
-        <v>149</v>
+        <v>62</v>
       </c>
       <c r="G53" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="H53" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="I53" t="s">
-        <v>275</v>
+        <v>225</v>
       </c>
       <c r="J53" t="s">
-        <v>313</v>
-      </c>
-      <c r="K53" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+        <v>279</v>
+      </c>
+      <c r="K53" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L53" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -6186,34 +6349,37 @@
         <v>52</v>
       </c>
       <c r="C54">
+        <v>52</v>
+      </c>
+      <c r="D54">
         <v>54</v>
       </c>
-      <c r="D54">
+      <c r="E54">
         <v>121</v>
       </c>
-      <c r="E54" t="s">
-        <v>62</v>
-      </c>
       <c r="F54" t="s">
-        <v>150</v>
+        <v>63</v>
       </c>
       <c r="G54" t="s">
-        <v>203</v>
+        <v>151</v>
       </c>
       <c r="H54" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="I54" t="s">
-        <v>276</v>
+        <v>225</v>
       </c>
       <c r="J54" t="s">
-        <v>313</v>
-      </c>
-      <c r="K54" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+        <v>280</v>
+      </c>
+      <c r="K54" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L54" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -6221,34 +6387,37 @@
         <v>53</v>
       </c>
       <c r="C55">
+        <v>53</v>
+      </c>
+      <c r="D55">
         <v>55</v>
       </c>
-      <c r="D55">
+      <c r="E55">
         <v>111</v>
       </c>
-      <c r="E55" t="s">
-        <v>63</v>
-      </c>
       <c r="F55" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="G55" t="s">
-        <v>199</v>
+        <v>152</v>
       </c>
       <c r="H55" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="I55" t="s">
-        <v>277</v>
+        <v>220</v>
       </c>
       <c r="J55" t="s">
-        <v>311</v>
-      </c>
-      <c r="K55" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+        <v>281</v>
+      </c>
+      <c r="K55" s="2">
+        <v>45842</v>
+      </c>
+      <c r="L55" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -6256,34 +6425,37 @@
         <v>54</v>
       </c>
       <c r="C56">
+        <v>54</v>
+      </c>
+      <c r="D56">
         <v>56</v>
       </c>
-      <c r="D56">
+      <c r="E56">
         <v>59</v>
       </c>
-      <c r="E56" t="s">
-        <v>64</v>
-      </c>
       <c r="F56" t="s">
-        <v>152</v>
+        <v>65</v>
       </c>
       <c r="G56" t="s">
-        <v>201</v>
+        <v>153</v>
       </c>
       <c r="H56" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="I56" t="s">
-        <v>278</v>
+        <v>223</v>
       </c>
       <c r="J56" t="s">
-        <v>313</v>
-      </c>
-      <c r="K56" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+        <v>282</v>
+      </c>
+      <c r="K56" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L56" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -6291,34 +6463,37 @@
         <v>55</v>
       </c>
       <c r="C57">
+        <v>55</v>
+      </c>
+      <c r="D57">
         <v>57</v>
       </c>
-      <c r="D57">
+      <c r="E57">
         <v>34</v>
       </c>
-      <c r="E57" t="s">
-        <v>65</v>
-      </c>
       <c r="F57" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
       <c r="G57" t="s">
-        <v>192</v>
+        <v>154</v>
       </c>
       <c r="H57" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="I57" t="s">
-        <v>279</v>
+        <v>222</v>
       </c>
       <c r="J57" t="s">
-        <v>313</v>
-      </c>
-      <c r="K57" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+        <v>283</v>
+      </c>
+      <c r="K57" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L57" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -6326,34 +6501,37 @@
         <v>56</v>
       </c>
       <c r="C58">
+        <v>56</v>
+      </c>
+      <c r="D58">
         <v>58</v>
       </c>
-      <c r="D58">
+      <c r="E58">
         <v>357</v>
       </c>
-      <c r="E58" t="s">
-        <v>66</v>
-      </c>
       <c r="F58" t="s">
-        <v>154</v>
+        <v>67</v>
       </c>
       <c r="G58" t="s">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="H58" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="I58" t="s">
-        <v>280</v>
+        <v>221</v>
       </c>
       <c r="J58" t="s">
-        <v>312</v>
-      </c>
-      <c r="K58" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+        <v>284</v>
+      </c>
+      <c r="K58" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L58" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -6361,34 +6539,37 @@
         <v>57</v>
       </c>
       <c r="C59">
+        <v>57</v>
+      </c>
+      <c r="D59">
         <v>59</v>
       </c>
-      <c r="D59">
+      <c r="E59">
         <v>41</v>
       </c>
-      <c r="E59" t="s">
-        <v>67</v>
-      </c>
       <c r="F59" t="s">
-        <v>155</v>
+        <v>68</v>
       </c>
       <c r="G59" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="H59" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="I59" t="s">
-        <v>281</v>
+        <v>218</v>
       </c>
       <c r="J59" t="s">
-        <v>312</v>
-      </c>
-      <c r="K59" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+        <v>285</v>
+      </c>
+      <c r="K59" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L59" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -6396,34 +6577,37 @@
         <v>58</v>
       </c>
       <c r="C60">
+        <v>58</v>
+      </c>
+      <c r="D60">
         <v>60</v>
       </c>
-      <c r="D60">
+      <c r="E60">
         <v>46</v>
       </c>
-      <c r="E60" t="s">
-        <v>68</v>
-      </c>
       <c r="F60" t="s">
-        <v>156</v>
+        <v>69</v>
       </c>
       <c r="G60" t="s">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="H60" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="I60" t="s">
-        <v>282</v>
+        <v>219</v>
       </c>
       <c r="J60" t="s">
-        <v>312</v>
-      </c>
-      <c r="K60" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+        <v>286</v>
+      </c>
+      <c r="K60" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L60" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -6431,34 +6615,37 @@
         <v>59</v>
       </c>
       <c r="C61">
+        <v>59</v>
+      </c>
+      <c r="D61">
         <v>61</v>
       </c>
-      <c r="D61">
+      <c r="E61">
         <v>206</v>
       </c>
-      <c r="E61" t="s">
-        <v>69</v>
-      </c>
       <c r="F61" t="s">
-        <v>157</v>
+        <v>70</v>
       </c>
       <c r="G61" t="s">
-        <v>204</v>
+        <v>158</v>
       </c>
       <c r="H61" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="I61" t="s">
-        <v>283</v>
+        <v>226</v>
       </c>
       <c r="J61" t="s">
-        <v>313</v>
-      </c>
-      <c r="K61" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+        <v>287</v>
+      </c>
+      <c r="K61" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L61" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -6466,34 +6653,37 @@
         <v>60</v>
       </c>
       <c r="C62">
+        <v>60</v>
+      </c>
+      <c r="D62">
         <v>62</v>
       </c>
-      <c r="D62">
+      <c r="E62">
         <v>428</v>
       </c>
-      <c r="E62" t="s">
-        <v>70</v>
-      </c>
       <c r="F62" t="s">
-        <v>158</v>
+        <v>71</v>
       </c>
       <c r="G62" t="s">
-        <v>199</v>
+        <v>159</v>
       </c>
       <c r="H62" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="I62" t="s">
-        <v>284</v>
+        <v>220</v>
       </c>
       <c r="J62" t="s">
-        <v>311</v>
-      </c>
-      <c r="K62" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+        <v>288</v>
+      </c>
+      <c r="K62" s="2">
+        <v>45842</v>
+      </c>
+      <c r="L62" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -6501,34 +6691,37 @@
         <v>61</v>
       </c>
       <c r="C63">
+        <v>61</v>
+      </c>
+      <c r="D63">
         <v>63</v>
       </c>
-      <c r="D63">
+      <c r="E63">
         <v>217</v>
       </c>
-      <c r="E63" t="s">
-        <v>71</v>
-      </c>
       <c r="F63" t="s">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="G63" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="H63" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="I63" t="s">
-        <v>285</v>
+        <v>218</v>
       </c>
       <c r="J63" t="s">
-        <v>312</v>
-      </c>
-      <c r="K63" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+        <v>289</v>
+      </c>
+      <c r="K63" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L63" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -6536,34 +6729,37 @@
         <v>62</v>
       </c>
       <c r="C64">
+        <v>62</v>
+      </c>
+      <c r="D64">
         <v>65</v>
       </c>
-      <c r="D64">
+      <c r="E64">
         <v>71</v>
       </c>
-      <c r="E64" t="s">
-        <v>72</v>
-      </c>
       <c r="F64" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="G64" t="s">
-        <v>203</v>
+        <v>161</v>
       </c>
       <c r="H64" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="I64" t="s">
-        <v>286</v>
+        <v>225</v>
       </c>
       <c r="J64" t="s">
-        <v>313</v>
-      </c>
-      <c r="K64" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+        <v>290</v>
+      </c>
+      <c r="K64" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L64" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -6571,34 +6767,37 @@
         <v>63</v>
       </c>
       <c r="C65">
+        <v>63</v>
+      </c>
+      <c r="D65">
         <v>66</v>
       </c>
-      <c r="D65">
+      <c r="E65">
         <v>395</v>
       </c>
-      <c r="E65" t="s">
-        <v>73</v>
-      </c>
       <c r="F65" t="s">
-        <v>161</v>
+        <v>74</v>
       </c>
       <c r="G65" t="s">
-        <v>202</v>
+        <v>162</v>
       </c>
       <c r="H65" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="I65" t="s">
-        <v>287</v>
+        <v>224</v>
       </c>
       <c r="J65" t="s">
-        <v>311</v>
-      </c>
-      <c r="K65" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+        <v>291</v>
+      </c>
+      <c r="K65" s="2">
+        <v>45842</v>
+      </c>
+      <c r="L65" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -6606,34 +6805,37 @@
         <v>64</v>
       </c>
       <c r="C66">
+        <v>64</v>
+      </c>
+      <c r="D66">
         <v>67</v>
       </c>
-      <c r="D66">
+      <c r="E66">
         <v>68</v>
       </c>
-      <c r="E66" t="s">
-        <v>74</v>
-      </c>
       <c r="F66" t="s">
-        <v>162</v>
+        <v>75</v>
       </c>
       <c r="G66" t="s">
-        <v>199</v>
+        <v>163</v>
       </c>
       <c r="H66" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="I66" t="s">
-        <v>288</v>
+        <v>220</v>
       </c>
       <c r="J66" t="s">
-        <v>311</v>
-      </c>
-      <c r="K66" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="K66" s="2">
+        <v>45842</v>
+      </c>
+      <c r="L66" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -6641,34 +6843,37 @@
         <v>65</v>
       </c>
       <c r="C67">
+        <v>65</v>
+      </c>
+      <c r="D67">
         <v>68</v>
       </c>
-      <c r="D67">
+      <c r="E67">
         <v>137</v>
       </c>
-      <c r="E67" t="s">
-        <v>75</v>
-      </c>
       <c r="F67" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="G67" t="s">
-        <v>204</v>
+        <v>164</v>
       </c>
       <c r="H67" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="I67" t="s">
-        <v>289</v>
+        <v>226</v>
       </c>
       <c r="J67" t="s">
-        <v>313</v>
-      </c>
-      <c r="K67" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+        <v>293</v>
+      </c>
+      <c r="K67" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L67" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -6676,34 +6881,37 @@
         <v>66</v>
       </c>
       <c r="C68">
+        <v>66</v>
+      </c>
+      <c r="D68">
         <v>70</v>
       </c>
-      <c r="D68">
+      <c r="E68">
         <v>74</v>
       </c>
-      <c r="E68" t="s">
-        <v>76</v>
-      </c>
       <c r="F68" t="s">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="G68" t="s">
-        <v>204</v>
+        <v>165</v>
       </c>
       <c r="H68" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="I68" t="s">
-        <v>290</v>
+        <v>226</v>
       </c>
       <c r="J68" t="s">
-        <v>313</v>
-      </c>
-      <c r="K68" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+        <v>294</v>
+      </c>
+      <c r="K68" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L68" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -6711,34 +6919,37 @@
         <v>67</v>
       </c>
       <c r="C69">
+        <v>67</v>
+      </c>
+      <c r="D69">
         <v>71</v>
       </c>
-      <c r="D69">
+      <c r="E69">
         <v>278</v>
       </c>
-      <c r="E69" t="s">
-        <v>77</v>
-      </c>
       <c r="F69" t="s">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="G69" t="s">
-        <v>203</v>
+        <v>166</v>
       </c>
       <c r="H69" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="I69" t="s">
-        <v>291</v>
+        <v>225</v>
       </c>
       <c r="J69" t="s">
-        <v>313</v>
-      </c>
-      <c r="K69" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+        <v>295</v>
+      </c>
+      <c r="K69" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L69" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -6746,34 +6957,37 @@
         <v>68</v>
       </c>
       <c r="C70">
+        <v>68</v>
+      </c>
+      <c r="D70">
         <v>72</v>
       </c>
-      <c r="D70">
+      <c r="E70">
         <v>299</v>
       </c>
-      <c r="E70" t="s">
-        <v>78</v>
-      </c>
       <c r="F70" t="s">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="G70" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="H70" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="I70" t="s">
-        <v>292</v>
+        <v>225</v>
       </c>
       <c r="J70" t="s">
-        <v>313</v>
-      </c>
-      <c r="K70" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+        <v>296</v>
+      </c>
+      <c r="K70" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L70" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -6781,34 +6995,37 @@
         <v>69</v>
       </c>
       <c r="C71">
+        <v>69</v>
+      </c>
+      <c r="D71">
         <v>73</v>
       </c>
-      <c r="D71">
+      <c r="E71">
         <v>313</v>
       </c>
-      <c r="E71" t="s">
-        <v>79</v>
-      </c>
       <c r="F71" t="s">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="G71" t="s">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="H71" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="I71" t="s">
-        <v>293</v>
+        <v>224</v>
       </c>
       <c r="J71" t="s">
-        <v>311</v>
-      </c>
-      <c r="K71" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+        <v>297</v>
+      </c>
+      <c r="K71" s="2">
+        <v>45842</v>
+      </c>
+      <c r="L71" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -6816,34 +7033,37 @@
         <v>70</v>
       </c>
       <c r="C72">
+        <v>70</v>
+      </c>
+      <c r="D72">
         <v>74</v>
       </c>
-      <c r="D72">
+      <c r="E72">
         <v>145</v>
       </c>
-      <c r="E72" t="s">
-        <v>80</v>
-      </c>
       <c r="F72" t="s">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="G72" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="H72" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="I72" t="s">
-        <v>294</v>
+        <v>216</v>
       </c>
       <c r="J72" t="s">
-        <v>311</v>
-      </c>
-      <c r="K72" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+        <v>298</v>
+      </c>
+      <c r="K72" s="2">
+        <v>45842</v>
+      </c>
+      <c r="L72" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -6851,34 +7071,37 @@
         <v>71</v>
       </c>
       <c r="C73">
+        <v>71</v>
+      </c>
+      <c r="D73">
         <v>75</v>
       </c>
-      <c r="D73">
+      <c r="E73">
         <v>453</v>
       </c>
-      <c r="E73" t="s">
-        <v>81</v>
-      </c>
       <c r="F73" t="s">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="G73" t="s">
-        <v>198</v>
+        <v>170</v>
       </c>
       <c r="H73" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="I73" t="s">
-        <v>295</v>
+        <v>219</v>
       </c>
       <c r="J73" t="s">
-        <v>312</v>
-      </c>
-      <c r="K73" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+        <v>299</v>
+      </c>
+      <c r="K73" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L73" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -6886,34 +7109,37 @@
         <v>72</v>
       </c>
       <c r="C74">
+        <v>72</v>
+      </c>
+      <c r="D74">
         <v>76</v>
       </c>
-      <c r="D74">
+      <c r="E74">
         <v>408</v>
       </c>
-      <c r="E74" t="s">
-        <v>82</v>
-      </c>
       <c r="F74" t="s">
-        <v>170</v>
+        <v>83</v>
       </c>
       <c r="G74" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="H74" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="I74" t="s">
-        <v>296</v>
+        <v>222</v>
       </c>
       <c r="J74" t="s">
-        <v>313</v>
-      </c>
-      <c r="K74" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+      <c r="K74" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L74" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -6921,34 +7147,37 @@
         <v>73</v>
       </c>
       <c r="C75">
+        <v>73</v>
+      </c>
+      <c r="D75">
         <v>77</v>
       </c>
-      <c r="D75">
+      <c r="E75">
         <v>79</v>
       </c>
-      <c r="E75" t="s">
-        <v>83</v>
-      </c>
       <c r="F75" t="s">
-        <v>171</v>
+        <v>84</v>
       </c>
       <c r="G75" t="s">
-        <v>202</v>
+        <v>172</v>
       </c>
       <c r="H75" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="I75" t="s">
-        <v>297</v>
+        <v>224</v>
       </c>
       <c r="J75" t="s">
-        <v>311</v>
-      </c>
-      <c r="K75" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+        <v>301</v>
+      </c>
+      <c r="K75" s="2">
+        <v>45842</v>
+      </c>
+      <c r="L75" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -6956,34 +7185,37 @@
         <v>74</v>
       </c>
       <c r="C76">
+        <v>74</v>
+      </c>
+      <c r="D76">
         <v>78</v>
       </c>
-      <c r="D76">
+      <c r="E76">
         <v>456</v>
       </c>
-      <c r="E76" t="s">
-        <v>84</v>
-      </c>
       <c r="F76" t="s">
-        <v>172</v>
+        <v>85</v>
       </c>
       <c r="G76" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="H76" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="I76" t="s">
-        <v>298</v>
+        <v>223</v>
       </c>
       <c r="J76" t="s">
-        <v>313</v>
-      </c>
-      <c r="K76" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+        <v>302</v>
+      </c>
+      <c r="K76" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L76" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -6991,34 +7223,37 @@
         <v>75</v>
       </c>
       <c r="C77">
+        <v>75</v>
+      </c>
+      <c r="D77">
         <v>79</v>
       </c>
-      <c r="D77">
+      <c r="E77">
         <v>5</v>
       </c>
-      <c r="E77" t="s">
-        <v>85</v>
-      </c>
       <c r="F77" t="s">
-        <v>173</v>
+        <v>86</v>
       </c>
       <c r="G77" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="H77" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="I77" t="s">
-        <v>299</v>
+        <v>219</v>
       </c>
       <c r="J77" t="s">
-        <v>312</v>
-      </c>
-      <c r="K77" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+        <v>303</v>
+      </c>
+      <c r="K77" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L77" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -7026,34 +7261,37 @@
         <v>76</v>
       </c>
       <c r="C78">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D78">
         <v>80</v>
       </c>
-      <c r="E78" t="s">
-        <v>86</v>
+      <c r="E78">
+        <v>80</v>
       </c>
       <c r="F78" t="s">
-        <v>174</v>
+        <v>87</v>
       </c>
       <c r="G78" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="H78" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="I78" t="s">
-        <v>300</v>
+        <v>216</v>
       </c>
       <c r="J78" t="s">
-        <v>311</v>
-      </c>
-      <c r="K78" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+        <v>304</v>
+      </c>
+      <c r="K78" s="2">
+        <v>45842</v>
+      </c>
+      <c r="L78" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -7061,34 +7299,37 @@
         <v>77</v>
       </c>
       <c r="C79">
+        <v>77</v>
+      </c>
+      <c r="D79">
         <v>81</v>
       </c>
-      <c r="D79">
+      <c r="E79">
         <v>180</v>
       </c>
-      <c r="E79" t="s">
-        <v>87</v>
-      </c>
       <c r="F79" t="s">
-        <v>175</v>
+        <v>88</v>
       </c>
       <c r="G79" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="H79" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="I79" t="s">
-        <v>301</v>
+        <v>226</v>
       </c>
       <c r="J79" t="s">
-        <v>313</v>
-      </c>
-      <c r="K79" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+        <v>305</v>
+      </c>
+      <c r="K79" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L79" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -7096,34 +7337,37 @@
         <v>78</v>
       </c>
       <c r="C80">
+        <v>78</v>
+      </c>
+      <c r="D80">
         <v>82</v>
       </c>
-      <c r="D80">
+      <c r="E80">
         <v>48</v>
       </c>
-      <c r="E80" t="s">
-        <v>88</v>
-      </c>
       <c r="F80" t="s">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="G80" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="H80" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="I80" t="s">
-        <v>302</v>
+        <v>217</v>
       </c>
       <c r="J80" t="s">
-        <v>312</v>
-      </c>
-      <c r="K80" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+        <v>306</v>
+      </c>
+      <c r="K80" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L80" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -7131,34 +7375,37 @@
         <v>79</v>
       </c>
       <c r="C81">
+        <v>79</v>
+      </c>
+      <c r="D81">
         <v>83</v>
       </c>
-      <c r="D81">
+      <c r="E81">
         <v>339</v>
       </c>
-      <c r="E81" t="s">
-        <v>89</v>
-      </c>
       <c r="F81" t="s">
-        <v>177</v>
+        <v>90</v>
       </c>
       <c r="G81" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="H81" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="I81" t="s">
-        <v>303</v>
+        <v>222</v>
       </c>
       <c r="J81" t="s">
-        <v>313</v>
-      </c>
-      <c r="K81" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+        <v>307</v>
+      </c>
+      <c r="K81" s="2">
+        <v>45841</v>
+      </c>
+      <c r="L81" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -7166,34 +7413,37 @@
         <v>80</v>
       </c>
       <c r="C82">
+        <v>80</v>
+      </c>
+      <c r="D82">
         <v>84</v>
       </c>
-      <c r="D82">
+      <c r="E82">
         <v>187</v>
       </c>
-      <c r="E82" t="s">
-        <v>90</v>
-      </c>
       <c r="F82" t="s">
-        <v>178</v>
+        <v>91</v>
       </c>
       <c r="G82" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="H82" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="I82" t="s">
-        <v>304</v>
+        <v>217</v>
       </c>
       <c r="J82" t="s">
-        <v>312</v>
-      </c>
-      <c r="K82" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+        <v>308</v>
+      </c>
+      <c r="K82" s="2">
+        <v>45840</v>
+      </c>
+      <c r="L82" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -7201,31 +7451,31 @@
         <v>81</v>
       </c>
       <c r="C83">
+        <v>81</v>
+      </c>
+      <c r="D83">
         <v>85</v>
       </c>
-      <c r="D83">
+      <c r="E83">
         <v>457</v>
       </c>
-      <c r="E83" t="s">
-        <v>91</v>
-      </c>
       <c r="F83" t="s">
-        <v>179</v>
+        <v>92</v>
       </c>
       <c r="G83" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="H83" t="s">
-        <v>212</v>
-      </c>
-      <c r="I83" t="s">
-        <v>305</v>
-      </c>
-      <c r="K83" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+        <v>196</v>
+      </c>
+      <c r="J83" t="s">
+        <v>309</v>
+      </c>
+      <c r="L83" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -7233,34 +7483,37 @@
         <v>82</v>
       </c>
       <c r="C84">
+        <v>82</v>
+      </c>
+      <c r="D84">
         <v>86</v>
       </c>
-      <c r="D84">
+      <c r="E84">
         <v>82</v>
       </c>
-      <c r="E84" t="s">
-        <v>92</v>
-      </c>
       <c r="F84" t="s">
-        <v>180</v>
+        <v>93</v>
       </c>
       <c r="G84" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="H84" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="I84" t="s">
-        <v>306</v>
+        <v>227</v>
       </c>
       <c r="J84" t="s">
-        <v>311</v>
-      </c>
-      <c r="K84" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+        <v>310</v>
+      </c>
+      <c r="K84" s="2">
+        <v>45842</v>
+      </c>
+      <c r="L84" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -7268,34 +7521,37 @@
         <v>83</v>
       </c>
       <c r="C85">
+        <v>83</v>
+      </c>
+      <c r="D85">
         <v>87</v>
       </c>
-      <c r="D85">
+      <c r="E85">
         <v>330</v>
       </c>
-      <c r="E85" t="s">
-        <v>93</v>
-      </c>
       <c r="F85" t="s">
-        <v>181</v>
+        <v>94</v>
       </c>
       <c r="G85" t="s">
-        <v>205</v>
+        <v>182</v>
       </c>
       <c r="H85" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="I85" t="s">
-        <v>307</v>
+        <v>227</v>
       </c>
       <c r="J85" t="s">
         <v>311</v>
       </c>
-      <c r="K85" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="2">
+        <v>45842</v>
+      </c>
+      <c r="L85" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -7303,34 +7559,37 @@
         <v>84</v>
       </c>
       <c r="C86">
+        <v>84</v>
+      </c>
+      <c r="D86">
         <v>88</v>
       </c>
-      <c r="D86">
+      <c r="E86">
         <v>389</v>
       </c>
-      <c r="E86" t="s">
-        <v>94</v>
-      </c>
       <c r="F86" t="s">
-        <v>182</v>
+        <v>95</v>
       </c>
       <c r="G86" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="H86" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="I86" t="s">
-        <v>308</v>
+        <v>227</v>
       </c>
       <c r="J86" t="s">
-        <v>311</v>
-      </c>
-      <c r="K86" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+        <v>312</v>
+      </c>
+      <c r="K86" s="2">
+        <v>45842</v>
+      </c>
+      <c r="L86" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -7338,34 +7597,37 @@
         <v>85</v>
       </c>
       <c r="C87">
+        <v>85</v>
+      </c>
+      <c r="D87">
         <v>89</v>
       </c>
-      <c r="D87">
+      <c r="E87">
         <v>427</v>
       </c>
-      <c r="E87" t="s">
-        <v>95</v>
-      </c>
       <c r="F87" t="s">
-        <v>183</v>
+        <v>96</v>
       </c>
       <c r="G87" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="H87" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="I87" t="s">
-        <v>309</v>
+        <v>227</v>
       </c>
       <c r="J87" t="s">
-        <v>311</v>
-      </c>
-      <c r="K87" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+        <v>313</v>
+      </c>
+      <c r="K87" s="2">
+        <v>45842</v>
+      </c>
+      <c r="L87" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -7373,34 +7635,37 @@
         <v>86</v>
       </c>
       <c r="C88">
+        <v>86</v>
+      </c>
+      <c r="D88">
         <v>90</v>
       </c>
-      <c r="D88">
+      <c r="E88">
         <v>445</v>
       </c>
-      <c r="E88" t="s">
-        <v>96</v>
-      </c>
       <c r="F88" t="s">
-        <v>184</v>
+        <v>97</v>
       </c>
       <c r="G88" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="H88" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="I88" t="s">
-        <v>310</v>
+        <v>227</v>
       </c>
       <c r="J88" t="s">
-        <v>311</v>
-      </c>
-      <c r="K88" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+        <v>314</v>
+      </c>
+      <c r="K88" s="2">
+        <v>45842</v>
+      </c>
+      <c r="L88" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -7408,31 +7673,34 @@
         <v>87</v>
       </c>
       <c r="C89">
+        <v>87</v>
+      </c>
+      <c r="D89">
         <v>91</v>
       </c>
-      <c r="D89">
+      <c r="E89">
         <v>458</v>
       </c>
-      <c r="E89" t="s">
-        <v>97</v>
-      </c>
       <c r="F89" t="s">
-        <v>185</v>
+        <v>98</v>
       </c>
       <c r="G89" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="H89" t="s">
-        <v>223</v>
-      </c>
-      <c r="I89" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="I89" t="s">
+        <v>227</v>
+      </c>
+      <c r="J89" t="s">
+        <v>315</v>
+      </c>
+      <c r="K89" s="2">
+        <v>45842</v>
+      </c>
+      <c r="L89" t="s">
         <v>358</v>
-      </c>
-      <c r="J89" t="s">
-        <v>311</v>
-      </c>
-      <c r="K89" t="s">
-        <v>357</v>
       </c>
     </row>
   </sheetData>

--- a/images/events/cf25dat.xlsx
+++ b/images/events/cf25dat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hsg/tprojs/clementinec.github.io/images/events/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB33B27A-F4EE-D34F-9101-F20CEC4DA458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9852BD90-4313-B847-94B4-BEA48E0E8744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -655,9 +655,6 @@
   </si>
   <si>
     <t>COMMUNITY &amp; COLLECTIVE INTELLIGENCE</t>
-  </si>
-  <si>
-    <t>Catalytic Interface</t>
   </si>
   <si>
     <t>S-S4</t>
@@ -3956,6 +3953,9 @@
   </si>
   <si>
     <t>16:45 - 17:45</t>
+  </si>
+  <si>
+    <t>CATALYTIC INTERFACE</t>
   </si>
 </sst>
 </file>
@@ -4329,6 +4329,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="11" max="11" width="9.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="s">
@@ -4391,16 +4394,16 @@
         <v>187</v>
       </c>
       <c r="I2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K2" s="2">
         <v>45842</v>
       </c>
       <c r="L2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -4429,16 +4432,16 @@
         <v>188</v>
       </c>
       <c r="I3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K3" s="2">
         <v>45842</v>
       </c>
       <c r="L3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -4467,16 +4470,16 @@
         <v>189</v>
       </c>
       <c r="I4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K4" s="2">
         <v>45840</v>
       </c>
       <c r="L4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -4505,16 +4508,16 @@
         <v>188</v>
       </c>
       <c r="I5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K5" s="2">
         <v>45842</v>
       </c>
       <c r="L5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -4543,16 +4546,16 @@
         <v>187</v>
       </c>
       <c r="I6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K6" s="2">
         <v>45842</v>
       </c>
       <c r="L6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -4581,16 +4584,16 @@
         <v>189</v>
       </c>
       <c r="I7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K7" s="2">
         <v>45840</v>
       </c>
       <c r="L7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -4619,16 +4622,16 @@
         <v>190</v>
       </c>
       <c r="I8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K8" s="2">
         <v>45841</v>
       </c>
       <c r="L8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -4657,16 +4660,16 @@
         <v>190</v>
       </c>
       <c r="I9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K9" s="2">
         <v>45841</v>
       </c>
       <c r="L9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
@@ -4695,16 +4698,16 @@
         <v>188</v>
       </c>
       <c r="I10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K10" s="2">
         <v>45842</v>
       </c>
       <c r="L10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -4733,16 +4736,16 @@
         <v>187</v>
       </c>
       <c r="I11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K11" s="2">
         <v>45842</v>
       </c>
       <c r="L11" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
@@ -4771,16 +4774,16 @@
         <v>190</v>
       </c>
       <c r="I12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J12" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K12" s="2">
         <v>45841</v>
       </c>
       <c r="L12" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
@@ -4809,16 +4812,16 @@
         <v>190</v>
       </c>
       <c r="I13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K13" s="2">
         <v>45841</v>
       </c>
       <c r="L13" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
@@ -4847,16 +4850,16 @@
         <v>191</v>
       </c>
       <c r="I14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J14" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K14" s="2">
         <v>45841</v>
       </c>
       <c r="L14" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
@@ -4885,16 +4888,16 @@
         <v>189</v>
       </c>
       <c r="I15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J15" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K15" s="2">
         <v>45840</v>
       </c>
       <c r="L15" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
@@ -4923,16 +4926,16 @@
         <v>192</v>
       </c>
       <c r="I16" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K16" s="2">
         <v>45841</v>
       </c>
       <c r="L16" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
@@ -4961,16 +4964,16 @@
         <v>193</v>
       </c>
       <c r="I17" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K17" s="2">
         <v>45841</v>
       </c>
       <c r="L17" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
@@ -4999,16 +5002,16 @@
         <v>193</v>
       </c>
       <c r="I18" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J18" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K18" s="2">
         <v>45841</v>
       </c>
       <c r="L18" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
@@ -5037,16 +5040,16 @@
         <v>194</v>
       </c>
       <c r="I19" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J19" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K19" s="2">
         <v>45840</v>
       </c>
       <c r="L19" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
@@ -5075,16 +5078,16 @@
         <v>192</v>
       </c>
       <c r="I20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J20" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K20" s="2">
         <v>45841</v>
       </c>
       <c r="L20" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
@@ -5113,16 +5116,16 @@
         <v>191</v>
       </c>
       <c r="I21" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J21" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K21" s="2">
         <v>45841</v>
       </c>
       <c r="L21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
@@ -5151,16 +5154,16 @@
         <v>195</v>
       </c>
       <c r="I22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J22" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K22" s="2">
         <v>45840</v>
       </c>
       <c r="L22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
@@ -5189,16 +5192,16 @@
         <v>194</v>
       </c>
       <c r="I23" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J23" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K23" s="2">
         <v>45840</v>
       </c>
       <c r="L23" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
@@ -5227,16 +5230,16 @@
         <v>193</v>
       </c>
       <c r="I24" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K24" s="2">
         <v>45841</v>
       </c>
       <c r="L24" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
@@ -5265,16 +5268,16 @@
         <v>194</v>
       </c>
       <c r="I25" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J25" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K25" s="2">
         <v>45840</v>
       </c>
       <c r="L25" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
@@ -5303,16 +5306,16 @@
         <v>191</v>
       </c>
       <c r="I26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J26" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K26" s="2">
         <v>45841</v>
       </c>
       <c r="L26" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
@@ -5341,16 +5344,16 @@
         <v>192</v>
       </c>
       <c r="I27" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J27" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K27" s="2">
         <v>45841</v>
       </c>
       <c r="L27" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
@@ -5379,16 +5382,16 @@
         <v>193</v>
       </c>
       <c r="I28" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J28" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K28" s="2">
         <v>45841</v>
       </c>
       <c r="L28" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
@@ -5417,16 +5420,16 @@
         <v>195</v>
       </c>
       <c r="I29" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J29" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K29" s="2">
         <v>45840</v>
       </c>
       <c r="L29" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
@@ -5455,16 +5458,16 @@
         <v>196</v>
       </c>
       <c r="I30" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J30" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K30" s="2">
         <v>45842</v>
       </c>
       <c r="L30" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
@@ -5493,16 +5496,16 @@
         <v>192</v>
       </c>
       <c r="I31" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J31" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K31" s="2">
         <v>45841</v>
       </c>
       <c r="L31" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
@@ -5531,16 +5534,16 @@
         <v>197</v>
       </c>
       <c r="I32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J32" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K32" s="2">
         <v>45840</v>
       </c>
       <c r="L32" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
@@ -5569,16 +5572,16 @@
         <v>198</v>
       </c>
       <c r="I33" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J33" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K33" s="2">
         <v>45840</v>
       </c>
       <c r="L33" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
@@ -5607,16 +5610,16 @@
         <v>196</v>
       </c>
       <c r="I34" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J34" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="K34" s="2">
         <v>45842</v>
       </c>
       <c r="L34" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
@@ -5645,16 +5648,16 @@
         <v>199</v>
       </c>
       <c r="I35" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J35" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K35" s="2">
         <v>45840</v>
       </c>
       <c r="L35" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
@@ -5683,16 +5686,16 @@
         <v>200</v>
       </c>
       <c r="I36" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J36" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K36" s="2">
         <v>45842</v>
       </c>
       <c r="L36" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
@@ -5721,16 +5724,16 @@
         <v>201</v>
       </c>
       <c r="I37" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J37" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K37" s="2">
         <v>45840</v>
       </c>
       <c r="L37" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
@@ -5759,16 +5762,16 @@
         <v>201</v>
       </c>
       <c r="I38" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J38" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K38" s="2">
         <v>45840</v>
       </c>
       <c r="L38" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
@@ -5797,16 +5800,16 @@
         <v>193</v>
       </c>
       <c r="I39" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J39" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K39" s="2">
         <v>45841</v>
       </c>
       <c r="L39" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
@@ -5835,16 +5838,16 @@
         <v>202</v>
       </c>
       <c r="I40" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J40" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K40" s="2">
         <v>45841</v>
       </c>
       <c r="L40" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
@@ -5873,16 +5876,16 @@
         <v>198</v>
       </c>
       <c r="I41" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J41" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K41" s="2">
         <v>45840</v>
       </c>
       <c r="L41" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
@@ -5911,16 +5914,16 @@
         <v>198</v>
       </c>
       <c r="I42" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J42" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K42" s="2">
         <v>45840</v>
       </c>
       <c r="L42" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
@@ -5949,16 +5952,16 @@
         <v>200</v>
       </c>
       <c r="I43" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J43" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K43" s="2">
         <v>45842</v>
       </c>
       <c r="L43" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
@@ -5987,16 +5990,16 @@
         <v>202</v>
       </c>
       <c r="I44" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J44" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K44" s="2">
         <v>45841</v>
       </c>
       <c r="L44" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
@@ -6025,16 +6028,16 @@
         <v>195</v>
       </c>
       <c r="I45" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J45" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K45" s="2">
         <v>45840</v>
       </c>
       <c r="L45" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
@@ -6063,16 +6066,16 @@
         <v>197</v>
       </c>
       <c r="I46" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J46" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K46" s="2">
         <v>45840</v>
       </c>
       <c r="L46" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
@@ -6101,16 +6104,16 @@
         <v>201</v>
       </c>
       <c r="I47" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J47" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K47" s="2">
         <v>45840</v>
       </c>
       <c r="L47" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
@@ -6139,16 +6142,16 @@
         <v>201</v>
       </c>
       <c r="I48" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J48" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K48" s="2">
         <v>45840</v>
       </c>
       <c r="L48" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
@@ -6177,16 +6180,16 @@
         <v>193</v>
       </c>
       <c r="I49" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J49" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K49" s="2">
         <v>45841</v>
       </c>
       <c r="L49" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
@@ -6215,16 +6218,16 @@
         <v>203</v>
       </c>
       <c r="I50" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J50" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K50" s="2">
         <v>45842</v>
       </c>
       <c r="L50" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
@@ -6253,16 +6256,16 @@
         <v>197</v>
       </c>
       <c r="I51" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J51" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K51" s="2">
         <v>45840</v>
       </c>
       <c r="L51" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
@@ -6291,16 +6294,16 @@
         <v>202</v>
       </c>
       <c r="I52" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J52" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K52" s="2">
         <v>45841</v>
       </c>
       <c r="L52" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
@@ -6329,16 +6332,16 @@
         <v>204</v>
       </c>
       <c r="I53" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J53" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K53" s="2">
         <v>45841</v>
       </c>
       <c r="L53" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
@@ -6367,16 +6370,16 @@
         <v>204</v>
       </c>
       <c r="I54" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J54" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K54" s="2">
         <v>45841</v>
       </c>
       <c r="L54" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
@@ -6405,16 +6408,16 @@
         <v>200</v>
       </c>
       <c r="I55" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J55" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K55" s="2">
         <v>45842</v>
       </c>
       <c r="L55" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
@@ -6443,16 +6446,16 @@
         <v>202</v>
       </c>
       <c r="I56" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J56" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K56" s="2">
         <v>45841</v>
       </c>
       <c r="L56" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
@@ -6481,16 +6484,16 @@
         <v>193</v>
       </c>
       <c r="I57" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J57" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K57" s="2">
         <v>45841</v>
       </c>
       <c r="L57" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
@@ -6519,16 +6522,16 @@
         <v>201</v>
       </c>
       <c r="I58" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J58" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K58" s="2">
         <v>45840</v>
       </c>
       <c r="L58" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
@@ -6557,16 +6560,16 @@
         <v>198</v>
       </c>
       <c r="I59" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J59" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K59" s="2">
         <v>45840</v>
       </c>
       <c r="L59" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
@@ -6595,16 +6598,16 @@
         <v>199</v>
       </c>
       <c r="I60" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J60" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K60" s="2">
         <v>45840</v>
       </c>
       <c r="L60" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
@@ -6633,16 +6636,16 @@
         <v>205</v>
       </c>
       <c r="I61" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J61" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="K61" s="2">
         <v>45841</v>
       </c>
       <c r="L61" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
@@ -6671,16 +6674,16 @@
         <v>200</v>
       </c>
       <c r="I62" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J62" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K62" s="2">
         <v>45842</v>
       </c>
       <c r="L62" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
@@ -6709,16 +6712,16 @@
         <v>198</v>
       </c>
       <c r="I63" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J63" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K63" s="2">
         <v>45840</v>
       </c>
       <c r="L63" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
@@ -6747,16 +6750,16 @@
         <v>204</v>
       </c>
       <c r="I64" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J64" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K64" s="2">
         <v>45841</v>
       </c>
       <c r="L64" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
@@ -6785,16 +6788,16 @@
         <v>203</v>
       </c>
       <c r="I65" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J65" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K65" s="2">
         <v>45842</v>
       </c>
       <c r="L65" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
@@ -6823,16 +6826,16 @@
         <v>200</v>
       </c>
       <c r="I66" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J66" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K66" s="2">
         <v>45842</v>
       </c>
       <c r="L66" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
@@ -6861,16 +6864,16 @@
         <v>205</v>
       </c>
       <c r="I67" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J67" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="K67" s="2">
         <v>45841</v>
       </c>
       <c r="L67" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
@@ -6899,16 +6902,16 @@
         <v>205</v>
       </c>
       <c r="I68" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J68" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K68" s="2">
         <v>45841</v>
       </c>
       <c r="L68" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
@@ -6937,16 +6940,16 @@
         <v>204</v>
       </c>
       <c r="I69" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J69" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K69" s="2">
         <v>45841</v>
       </c>
       <c r="L69" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
@@ -6975,16 +6978,16 @@
         <v>204</v>
       </c>
       <c r="I70" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J70" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="K70" s="2">
         <v>45841</v>
       </c>
       <c r="L70" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
@@ -7013,16 +7016,16 @@
         <v>203</v>
       </c>
       <c r="I71" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J71" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="K71" s="2">
         <v>45842</v>
       </c>
       <c r="L71" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
@@ -7051,16 +7054,16 @@
         <v>196</v>
       </c>
       <c r="I72" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J72" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K72" s="2">
         <v>45842</v>
       </c>
       <c r="L72" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
@@ -7089,16 +7092,16 @@
         <v>199</v>
       </c>
       <c r="I73" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J73" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K73" s="2">
         <v>45840</v>
       </c>
       <c r="L73" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
@@ -7127,16 +7130,16 @@
         <v>193</v>
       </c>
       <c r="I74" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J74" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="K74" s="2">
         <v>45841</v>
       </c>
       <c r="L74" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
@@ -7165,16 +7168,16 @@
         <v>203</v>
       </c>
       <c r="I75" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J75" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K75" s="2">
         <v>45842</v>
       </c>
       <c r="L75" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
@@ -7203,16 +7206,16 @@
         <v>202</v>
       </c>
       <c r="I76" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J76" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K76" s="2">
         <v>45841</v>
       </c>
       <c r="L76" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
@@ -7241,16 +7244,16 @@
         <v>199</v>
       </c>
       <c r="I77" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J77" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K77" s="2">
         <v>45840</v>
       </c>
       <c r="L77" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
@@ -7279,16 +7282,16 @@
         <v>196</v>
       </c>
       <c r="I78" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J78" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K78" s="2">
         <v>45842</v>
       </c>
       <c r="L78" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
@@ -7317,16 +7320,16 @@
         <v>205</v>
       </c>
       <c r="I79" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J79" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="K79" s="2">
         <v>45841</v>
       </c>
       <c r="L79" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
@@ -7355,16 +7358,16 @@
         <v>197</v>
       </c>
       <c r="I80" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J80" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K80" s="2">
         <v>45840</v>
       </c>
       <c r="L80" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
@@ -7393,16 +7396,16 @@
         <v>193</v>
       </c>
       <c r="I81" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J81" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K81" s="2">
         <v>45841</v>
       </c>
       <c r="L81" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.2">
@@ -7431,16 +7434,16 @@
         <v>197</v>
       </c>
       <c r="I82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J82" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="K82" s="2">
         <v>45840</v>
       </c>
       <c r="L82" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
@@ -7469,10 +7472,10 @@
         <v>196</v>
       </c>
       <c r="J83" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L83" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
@@ -7498,19 +7501,19 @@
         <v>181</v>
       </c>
       <c r="H84" t="s">
-        <v>206</v>
+        <v>359</v>
       </c>
       <c r="I84" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J84" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="K84" s="2">
         <v>45842</v>
       </c>
       <c r="L84" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
@@ -7536,19 +7539,19 @@
         <v>182</v>
       </c>
       <c r="H85" t="s">
-        <v>206</v>
+        <v>359</v>
       </c>
       <c r="I85" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J85" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K85" s="2">
         <v>45842</v>
       </c>
       <c r="L85" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
@@ -7574,19 +7577,19 @@
         <v>183</v>
       </c>
       <c r="H86" t="s">
-        <v>206</v>
+        <v>359</v>
       </c>
       <c r="I86" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J86" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K86" s="2">
         <v>45842</v>
       </c>
       <c r="L86" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
@@ -7612,19 +7615,19 @@
         <v>184</v>
       </c>
       <c r="H87" t="s">
-        <v>206</v>
+        <v>359</v>
       </c>
       <c r="I87" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J87" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K87" s="2">
         <v>45842</v>
       </c>
       <c r="L87" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
@@ -7650,19 +7653,19 @@
         <v>185</v>
       </c>
       <c r="H88" t="s">
-        <v>206</v>
+        <v>359</v>
       </c>
       <c r="I88" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J88" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K88" s="2">
         <v>45842</v>
       </c>
       <c r="L88" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
@@ -7688,19 +7691,19 @@
         <v>186</v>
       </c>
       <c r="H89" t="s">
-        <v>206</v>
+        <v>359</v>
       </c>
       <c r="I89" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J89" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K89" s="2">
         <v>45842</v>
       </c>
       <c r="L89" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>

--- a/images/events/cf25dat.xlsx
+++ b/images/events/cf25dat.xlsx
@@ -1,26 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10714"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hsg/tprojs/clementinec.github.io/images/events/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9852BD90-4313-B847-94B4-BEA48E0E8744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="361">
+  <si>
+    <t>Unnamed: 0.2</t>
+  </si>
   <si>
     <t>Unnamed: 0.1</t>
   </si>
@@ -55,274 +52,274 @@
     <t>Time</t>
   </si>
   <si>
-    <t>Text-to-Siheyuan: LLM-based Multi-Agent Procedural Generation System of Vernacular Architecture in Beijing</t>
-  </si>
-  <si>
-    <t>ConStructGNN: A Graph Neural Network Framework for Adaptive 3D Architectural Layout</t>
-  </si>
-  <si>
-    <t>Design Validation for Robotic Fabrication: A Multi-Stage Framework for Complex and Non-Repetitive Processes (edited)</t>
-  </si>
-  <si>
-    <t>Reading Between the Lines: Bridging AI and Architectural Knowledge in Floorplan Understanding</t>
-  </si>
-  <si>
-    <t>Interactive BIM Modelling Assistant with Multi-Agent LLM</t>
-  </si>
-  <si>
-    <t>tPACS: Phygital-Aided Construction System based on Modular Customizable Timber Fabrication</t>
-  </si>
-  <si>
-    <t>A Graph-Based Prediction Model for Sustainable Urban Renewal: Integrating Graph Convolutional Networks for Concrete Recycling Potential Evaluation</t>
-  </si>
-  <si>
-    <t>An Urban Morphology Analysis Framework for Synergistic Improvement of Multiple Performance Objectives: Exemplified by Outdoor Thermal Comfort and Building Energy Efficiency</t>
-  </si>
-  <si>
-    <t>Computing Beyond the Vitruvian Canon: Ambiguity as a Catalyst in Computational Design Theory</t>
-  </si>
-  <si>
-    <t>Prompt-to-Production: AI-Driven Design and Robotic Fabrication for Rapidly Reconfigurable Circular Timber Assemblies</t>
-  </si>
-  <si>
-    <t>Shadow-Based Path Detection in Rapidly Expanding Urban Areas: Utilizing shadow detection and graph-based vectorization to uncover informal road networks in high-density slum areas</t>
-  </si>
-  <si>
-    <t>Digital Design Support for UAV Delivery Noise Reduction Strategies in High Density Urban Environments</t>
-  </si>
-  <si>
-    <t>How Chinese is Chinatown: Measuring the Relationship between Geographic Authenticity Perception and Streetscape Features through Machine Learning</t>
-  </si>
-  <si>
-    <t>Parametric Biomimicry: Translating Spiral Seashell Formation into Robotic 3D Printing</t>
-  </si>
-  <si>
-    <t>Improving Architectural Form Classification through Salingaros’ Metrics and Topological Data Analysis</t>
-  </si>
-  <si>
-    <t>Robotic fabrication and in-situ 3D printing for a natural timber-bamboo structure</t>
-  </si>
-  <si>
-    <t>CNT Fiber-woven prototypes: Zero weight, infinite span</t>
-  </si>
-  <si>
-    <t>Generating Open Office Layouts using Flexible Architectural Components</t>
-  </si>
-  <si>
-    <t>Encoding Performance in Digital Weave Design Using AI and Optimisation</t>
-  </si>
-  <si>
-    <t>Revealing the Relationship Between Site Planning Strategies and Sentiment Through Deep Learning: Enhancing Data-Driven Architectural Design Strategies</t>
-  </si>
-  <si>
-    <t>Evaluating Augmented Reality as a Tool for Democratizing Built Environment Design</t>
-  </si>
-  <si>
-    <t>Stepwise Generation Method for Competition-Level Floor Plans of Medium and Large-Scale Gymnasiums Based on Rule Constraints and Diffusion Models</t>
-  </si>
-  <si>
-    <t>Investigating self-shaping fibre composites: tunning curing parameters to optimise resulting curvature</t>
-  </si>
-  <si>
-    <t>Floor Plan Affordance Prediction:  Is the floor plan layout determined by its outline or the architect?</t>
-  </si>
-  <si>
-    <t>Urban Visual Heterogeneity: An Intelligent Approach to Examining Travel Preferences in Nanjing</t>
-  </si>
-  <si>
-    <t>Generative Design for Coastal Resilience: A Computational Approach to Living Shorelines</t>
-  </si>
-  <si>
-    <t>Predicting Stress-Strain Characteristics of 3D Printed BCC Lattice Structures with Variable Grid Gradation Using Neural Networks</t>
-  </si>
-  <si>
-    <t>Open-Source Approaches to Integrating Advanced Robotic Systems in Sustainable Design</t>
-  </si>
-  <si>
-    <t>Bridging the Gap: Enhancing AI-Generated Floor Plans with Multi-Modal Data Integration</t>
-  </si>
-  <si>
-    <t>Discovering Pareto-Efficient Urban Networks Through Shape Grammar, Multi-Objective Optimisation and Machine Learning</t>
+    <t>TEXT-TO-SIHEYUAN: LLM-BASED MULTI-AGENT PROCEDURAL GENERATION SYSTEM OF VERNACULAR ARCHITECTURE IN BEIJING</t>
+  </si>
+  <si>
+    <t>CONSTRUCTGNN: A GRAPH NEURAL NETWORK FRAMEWORK FOR ADAPTIVE 3D ARCHITECTURAL LAYOUT</t>
+  </si>
+  <si>
+    <t>DESIGN VALIDATION FOR ROBOTIC FABRICATION: A MULTI-STAGE FRAMEWORK FOR COMPLEX AND NON-REPETITIVE PROCESSES (EDITED)</t>
+  </si>
+  <si>
+    <t>READING BETWEEN THE LINES: BRIDGING AI AND ARCHITECTURAL KNOWLEDGE IN FLOORPLAN UNDERSTANDING</t>
+  </si>
+  <si>
+    <t>INTERACTIVE BIM MODELLING ASSISTANT WITH MULTI-AGENT LLM</t>
+  </si>
+  <si>
+    <t>TPACS: PHYGITAL-AIDED CONSTRUCTION SYSTEM BASED ON MODULAR CUSTOMIZABLE TIMBER FABRICATION</t>
+  </si>
+  <si>
+    <t>A GRAPH-BASED PREDICTION MODEL FOR SUSTAINABLE URBAN RENEWAL: INTEGRATING GRAPH CONVOLUTIONAL NETWORKS FOR CONCRETE RECYCLING POTENTIAL EVALUATION</t>
+  </si>
+  <si>
+    <t>AN URBAN MORPHOLOGY ANALYSIS FRAMEWORK FOR SYNERGISTIC IMPROVEMENT OF MULTIPLE PERFORMANCE OBJECTIVES: EXEMPLIFIED BY OUTDOOR THERMAL COMFORT AND BUILDING ENERGY EFFICIENCY</t>
+  </si>
+  <si>
+    <t>COMPUTING BEYOND THE VITRUVIAN CANON: AMBIGUITY AS A CATALYST IN COMPUTATIONAL DESIGN THEORY</t>
+  </si>
+  <si>
+    <t>PROMPT-TO-PRODUCTION: AI-DRIVEN DESIGN AND ROBOTIC FABRICATION FOR RAPIDLY RECONFIGURABLE CIRCULAR TIMBER ASSEMBLIES</t>
+  </si>
+  <si>
+    <t>SHADOW-BASED PATH DETECTION IN RAPIDLY EXPANDING URBAN AREAS: UTILIZING SHADOW DETECTION AND GRAPH-BASED VECTORIZATION TO UNCOVER INFORMAL ROAD NETWORKS IN HIGH-DENSITY SLUM AREAS</t>
+  </si>
+  <si>
+    <t>DIGITAL DESIGN SUPPORT FOR UAV DELIVERY NOISE REDUCTION STRATEGIES IN HIGH DENSITY URBAN ENVIRONMENTS</t>
+  </si>
+  <si>
+    <t>HOW CHINESE IS CHINATOWN: MEASURING THE RELATIONSHIP BETWEEN GEOGRAPHIC AUTHENTICITY PERCEPTION AND STREETSCAPE FEATURES THROUGH MACHINE LEARNING</t>
+  </si>
+  <si>
+    <t>PARAMETRIC BIOMIMICRY: TRANSLATING SPIRAL SEASHELL FORMATION INTO ROBOTIC 3D PRINTING</t>
+  </si>
+  <si>
+    <t>IMPROVING ARCHITECTURAL FORM CLASSIFICATION THROUGH SALINGAROS’ METRICS AND TOPOLOGICAL DATA ANALYSIS</t>
+  </si>
+  <si>
+    <t>ROBOTIC FABRICATION AND IN-SITU 3D PRINTING FOR A NATURAL TIMBER-BAMBOO STRUCTURE</t>
+  </si>
+  <si>
+    <t>CNT FIBER-WOVEN PROTOTYPES: ZERO WEIGHT, INFINITE SPAN</t>
+  </si>
+  <si>
+    <t>GENERATING OPEN OFFICE LAYOUTS USING FLEXIBLE ARCHITECTURAL COMPONENTS</t>
+  </si>
+  <si>
+    <t>ENCODING PERFORMANCE IN DIGITAL WEAVE DESIGN USING AI AND OPTIMISATION</t>
+  </si>
+  <si>
+    <t>REVEALING THE RELATIONSHIP BETWEEN SITE PLANNING STRATEGIES AND SENTIMENT THROUGH DEEP LEARNING: ENHANCING DATA-DRIVEN ARCHITECTURAL DESIGN STRATEGIES</t>
+  </si>
+  <si>
+    <t>EVALUATING AUGMENTED REALITY AS A TOOL FOR DEMOCRATIZING BUILT ENVIRONMENT DESIGN</t>
+  </si>
+  <si>
+    <t>STEPWISE GENERATION METHOD FOR COMPETITION-LEVEL FLOOR PLANS OF MEDIUM AND LARGE-SCALE GYMNASIUMS BASED ON RULE CONSTRAINTS AND DIFFUSION MODELS</t>
+  </si>
+  <si>
+    <t>INVESTIGATING SELF-SHAPING FIBRE COMPOSITES: TUNNING CURING PARAMETERS TO OPTIMISE RESULTING CURVATURE</t>
+  </si>
+  <si>
+    <t>FLOOR PLAN AFFORDANCE PREDICTION:  IS THE FLOOR PLAN LAYOUT DETERMINED BY ITS OUTLINE OR THE ARCHITECT?</t>
+  </si>
+  <si>
+    <t>URBAN VISUAL HETEROGENEITY: AN INTELLIGENT APPROACH TO EXAMINING TRAVEL PREFERENCES IN NANJING</t>
+  </si>
+  <si>
+    <t>GENERATIVE DESIGN FOR COASTAL RESILIENCE: A COMPUTATIONAL APPROACH TO LIVING SHORELINES</t>
+  </si>
+  <si>
+    <t>PREDICTING STRESS-STRAIN CHARACTERISTICS OF 3D PRINTED BCC LATTICE STRUCTURES WITH VARIABLE GRID GRADATION USING NEURAL NETWORKS</t>
+  </si>
+  <si>
+    <t>OPEN-SOURCE APPROACHES TO INTEGRATING ADVANCED ROBOTIC SYSTEMS IN SUSTAINABLE DESIGN</t>
+  </si>
+  <si>
+    <t>BRIDGING THE GAP: ENHANCING AI-GENERATED FLOOR PLANS WITH MULTI-MODAL DATA INTEGRATION</t>
+  </si>
+  <si>
+    <t>DISCOVERING PARETO-EFFICIENT URBAN NETWORKS THROUGH SHAPE GRAMMAR, MULTI-OBJECTIVE OPTIMISATION AND MACHINE LEARNING</t>
   </si>
   <si>
     <t>MATERIAL REUSE IN HERITAGE CONSERVATION:  DEVELOPING A DIGITAL DESIGN-TO-PRODUCTION CIRCULAR WORKFLOW</t>
   </si>
   <si>
-    <t>Rec-Arch: A Case Study Recommender System for Architects using Vision and Language Models</t>
-  </si>
-  <si>
-    <t>Integrating Regulatory Compliance In AI-Assisted Architectural Design</t>
-  </si>
-  <si>
-    <t>Enhancing End-to-End Processing, Analysis, and Visualization of Citizen Participation Data in Urban Design and Planning</t>
-  </si>
-  <si>
-    <t>Virtual Space Design Through Physical Object Recognition, HoloLens-Based Furniture Tracking and AI-Driven Real-Time Layout Generation</t>
-  </si>
-  <si>
-    <t>Enhancing Robotic Embodiment in Architecture: An Intelligent Approach Combining Vision Systems and Generative Neural Networks for Autonomous Design-to-Production</t>
-  </si>
-  <si>
-    <t>Machine Learning and Mixed Reality-Controlled Cable Robots for Real-Time Construction Automation</t>
-  </si>
-  <si>
-    <t>Developing Stress-Line ribbed Timber Slabs: Laminating Timber Ribs with Stay-in-Place Formwork</t>
-  </si>
-  <si>
-    <t>Quantifable and unquantifable machine learning model or architectural preference prediction based on MBTI</t>
-  </si>
-  <si>
-    <t>Integrating AI Tools and Methods in the Design Process</t>
-  </si>
-  <si>
-    <t>Two-Way Interventive Design and Manufacturing: Real-time design and materiality visualization through mixed reality systems based on hand tracking</t>
-  </si>
-  <si>
-    <t>Augmented Scale Perception: Exploring a Full-Scale Architectural Education Approach Based on MAR</t>
-  </si>
-  <si>
-    <t>Zero-Shot Architectural Style Classification with Large Language Models</t>
-  </si>
-  <si>
-    <t>Transforming Architectural Education: The Impact of VR and AR on Understanding Building Energy Efficiency</t>
-  </si>
-  <si>
-    <t>BPMN-based building project lifecycle analysis with a core of BIM: Taking a campus project as an example</t>
-  </si>
-  <si>
-    <t>Stock-Constrained Design of Irregular Material Based on Graph Neural Networks</t>
-  </si>
-  <si>
-    <t>Grasp-to-Mill (GtM) Integrated Workflow for Natural Log Joint Fabrication Based on Multi-Objective Optimization Algorithm</t>
-  </si>
-  <si>
-    <t>Adaptive Origami: Fabrication of Pneumatic-actuated Adaptive Folding System</t>
-  </si>
-  <si>
-    <t>Environmental-driven digital fabrication: controlling 3D-Printing parameters with data from CFD simulation</t>
-  </si>
-  <si>
-    <t>Design and manufacture of waste timber composite panels: sustainable and innovative use of recycled timber</t>
-  </si>
-  <si>
-    <t>Quantifying Architectural Experience using VLMs: Does AI Dream of Rendered Spaces?</t>
-  </si>
-  <si>
-    <t>Understand Urban Building Energy Consumption with Explainable Machine Learning Approaches</t>
-  </si>
-  <si>
-    <t>Enhancing Urban Vitality through Interactive XR Installations: Fostering Engagement and Environmental Awareness</t>
-  </si>
-  <si>
-    <t>Resonant Blech: Emergent Soundscapes Through Human-AI Interaction</t>
-  </si>
-  <si>
-    <t>Intelligent Spatial Planning:  A Multidimensional Study on Swiss Residential Design Using Large Language model (GPT-4)</t>
-  </si>
-  <si>
-    <t>Adaptive Design and Fabrication of Modular Topological Interlocking Assemblies</t>
-  </si>
-  <si>
-    <t>Augmented Assembly: an Exploration of Modular Design to Fabrication based on Extended Reality</t>
-  </si>
-  <si>
-    <t>Collaborative, conversational architectural design process between human designers and multimodal AI agents for early-stage design exploration</t>
-  </si>
-  <si>
-    <t>Boundary Vitality: Analyzing Urban Public Perception of Spatial and Visual Elements in Manhattan</t>
-  </si>
-  <si>
-    <t>Gamification as a Tool for Enhancing Public Engagement in Built-Environment Design.</t>
-  </si>
-  <si>
-    <t>A Framework for Virtual Windows to Enhance Indoor Spatial Experience in Extended Reality</t>
+    <t>REC-ARCH: A CASE STUDY RECOMMENDER SYSTEM FOR ARCHITECTS USING VISION AND LANGUAGE MODELS</t>
+  </si>
+  <si>
+    <t>INTEGRATING REGULATORY COMPLIANCE IN AI-ASSISTED ARCHITECTURAL DESIGN</t>
+  </si>
+  <si>
+    <t>ENHANCING END-TO-END PROCESSING, ANALYSIS, AND VISUALIZATION OF CITIZEN PARTICIPATION DATA IN URBAN DESIGN AND PLANNING</t>
+  </si>
+  <si>
+    <t>VIRTUAL SPACE DESIGN THROUGH PHYSICAL OBJECT RECOGNITION, HOLOLENS-BASED FURNITURE TRACKING AND AI-DRIVEN REAL-TIME LAYOUT GENERATION</t>
+  </si>
+  <si>
+    <t>ENHANCING ROBOTIC EMBODIMENT IN ARCHITECTURE: AN INTELLIGENT APPROACH COMBINING VISION SYSTEMS AND GENERATIVE NEURAL NETWORKS FOR AUTONOMOUS DESIGN-TO-PRODUCTION</t>
+  </si>
+  <si>
+    <t>MACHINE LEARNING AND MIXED REALITY-CONTROLLED CABLE ROBOTS FOR REAL-TIME CONSTRUCTION AUTOMATION</t>
+  </si>
+  <si>
+    <t>DEVELOPING STRESS-LINE RIBBED TIMBER SLABS: LAMINATING TIMBER RIBS WITH STAY-IN-PLACE FORMWORK</t>
+  </si>
+  <si>
+    <t>QUANTIFABLE AND UNQUANTIFABLE MACHINE LEARNING MODEL OR ARCHITECTURAL PREFERENCE PREDICTION BASED ON MBTI</t>
+  </si>
+  <si>
+    <t>INTEGRATING AI TOOLS AND METHODS IN THE DESIGN PROCESS</t>
+  </si>
+  <si>
+    <t>TWO-WAY INTERVENTIVE DESIGN AND MANUFACTURING: REAL-TIME DESIGN AND MATERIALITY VISUALIZATION THROUGH MIXED REALITY SYSTEMS BASED ON HAND TRACKING</t>
+  </si>
+  <si>
+    <t>AUGMENTED SCALE PERCEPTION: EXPLORING A FULL-SCALE ARCHITECTURAL EDUCATION APPROACH BASED ON MAR</t>
+  </si>
+  <si>
+    <t>ZERO-SHOT ARCHITECTURAL STYLE CLASSIFICATION WITH LARGE LANGUAGE MODELS</t>
+  </si>
+  <si>
+    <t>TRANSFORMING ARCHITECTURAL EDUCATION: THE IMPACT OF VR AND AR ON UNDERSTANDING BUILDING ENERGY EFFICIENCY</t>
+  </si>
+  <si>
+    <t>BPMN-BASED BUILDING PROJECT LIFECYCLE ANALYSIS WITH A CORE OF BIM: TAKING A CAMPUS PROJECT AS AN EXAMPLE</t>
+  </si>
+  <si>
+    <t>STOCK-CONSTRAINED DESIGN OF IRREGULAR MATERIAL BASED ON GRAPH NEURAL NETWORKS</t>
+  </si>
+  <si>
+    <t>GRASP-TO-MILL (GTM) INTEGRATED WORKFLOW FOR NATURAL LOG JOINT FABRICATION BASED ON MULTI-OBJECTIVE OPTIMIZATION ALGORITHM</t>
+  </si>
+  <si>
+    <t>ADAPTIVE ORIGAMI: FABRICATION OF PNEUMATIC-ACTUATED ADAPTIVE FOLDING SYSTEM</t>
+  </si>
+  <si>
+    <t>ENVIRONMENTAL-DRIVEN DIGITAL FABRICATION: CONTROLLING 3D-PRINTING PARAMETERS WITH DATA FROM CFD SIMULATION</t>
+  </si>
+  <si>
+    <t>DESIGN AND MANUFACTURE OF WASTE TIMBER COMPOSITE PANELS: SUSTAINABLE AND INNOVATIVE USE OF RECYCLED TIMBER</t>
+  </si>
+  <si>
+    <t>QUANTIFYING ARCHITECTURAL EXPERIENCE USING VLMS: DOES AI DREAM OF RENDERED SPACES?</t>
+  </si>
+  <si>
+    <t>UNDERSTAND URBAN BUILDING ENERGY CONSUMPTION WITH EXPLAINABLE MACHINE LEARNING APPROACHES</t>
+  </si>
+  <si>
+    <t>ENHANCING URBAN VITALITY THROUGH INTERACTIVE XR INSTALLATIONS: FOSTERING ENGAGEMENT AND ENVIRONMENTAL AWARENESS</t>
+  </si>
+  <si>
+    <t>RESONANT BLECH: EMERGENT SOUNDSCAPES THROUGH HUMAN-AI INTERACTION</t>
+  </si>
+  <si>
+    <t>INTELLIGENT SPATIAL PLANNING:  A MULTIDIMENSIONAL STUDY ON SWISS RESIDENTIAL DESIGN USING LARGE LANGUAGE MODEL (GPT-4)</t>
+  </si>
+  <si>
+    <t>ADAPTIVE DESIGN AND FABRICATION OF MODULAR TOPOLOGICAL INTERLOCKING ASSEMBLIES</t>
+  </si>
+  <si>
+    <t>AUGMENTED ASSEMBLY: AN EXPLORATION OF MODULAR DESIGN TO FABRICATION BASED ON EXTENDED REALITY</t>
+  </si>
+  <si>
+    <t>COLLABORATIVE, CONVERSATIONAL ARCHITECTURAL DESIGN PROCESS BETWEEN HUMAN DESIGNERS AND MULTIMODAL AI AGENTS FOR EARLY-STAGE DESIGN EXPLORATION</t>
+  </si>
+  <si>
+    <t>BOUNDARY VITALITY: ANALYZING URBAN PUBLIC PERCEPTION OF SPATIAL AND VISUAL ELEMENTS IN MANHATTAN</t>
+  </si>
+  <si>
+    <t>GAMIFICATION AS A TOOL FOR ENHANCING PUBLIC ENGAGEMENT IN BUILT-ENVIRONMENT DESIGN.</t>
+  </si>
+  <si>
+    <t>A FRAMEWORK FOR VIRTUAL WINDOWS TO ENHANCE INDOOR SPATIAL EXPERIENCE IN EXTENDED REALITY</t>
   </si>
   <si>
     <t>MORPHOLOGICAL SECTIONS THROUGH LATENT SPACE</t>
   </si>
   <si>
-    <t>Performance-based Urban Environmental Restoration: A Multi-Layer Cellular Automata Model for Ecological Design Simulation in High-Density Cities</t>
-  </si>
-  <si>
-    <t>Optimized Acoustics for Meeting Pods</t>
-  </si>
-  <si>
-    <t>Can AI-based Suggestions Support Designing in Immersive Environments? Observing the Use of Generated Images as Visual References for Architectural Design in Mixed Reality</t>
-  </si>
-  <si>
-    <t>Crafting a Participatory Approach towards Traditional Vietnamese Weaving and Digital Computation</t>
-  </si>
-  <si>
-    <t>Architectural Interfaces for Shared Spaces – A Multi-User Perspective on Intelligent Environment Interactions</t>
-  </si>
-  <si>
-    <t>Sustainable Sustainable Social Building Assistant (SSoBA): Transforming Energy Use via Digital Twins, Environmental Sensing and Occupant Behaviour Change</t>
-  </si>
-  <si>
-    <t>Computing Urban Tissue: Landslide Mitigation Strategy of Urban Infrastructure Design</t>
-  </si>
-  <si>
-    <t>Generative Design Intelligence: Extracting Design Specific Sustainability Insights and Material Metrics from Generative Artificial Intelligence output</t>
-  </si>
-  <si>
-    <t>Comparing different Building representations for readability by Large Language Models</t>
-  </si>
-  <si>
-    <t>Deep Perceptual Urban Form</t>
-  </si>
-  <si>
-    <t>From Tradition to Computation: Adaptive Ceramic ‎Façades Inspired by Persian Ice Caves (Yakhchals) for ‎Passive Cooling</t>
-  </si>
-  <si>
-    <t>Consolidated Empirical Bio-material Repository</t>
-  </si>
-  <si>
-    <t>Evaluation Method of AI-Generated Architectural Facade Images Based on DCNN</t>
-  </si>
-  <si>
-    <t>Superiority of High-Dimensional Latent Variable Representation in Urban Spatial Structure: Evidence from an Urban Climate Study</t>
-  </si>
-  <si>
-    <t>AI2D-Architecture: a Benchmark for Evaluating Multimodal Large Language Models in Architecture</t>
-  </si>
-  <si>
-    <t>Design Quality Housing Assessment Methodology: Supporting Heuristics with Evidence-Based Decision-Making</t>
-  </si>
-  <si>
-    <t>From Craft to Community: Participatory Upcycling in Public Housing via Digital Fabrication</t>
-  </si>
-  <si>
-    <t>A Fabrication Grammar for Robotic Sand Packing:  From Precise Actions to Emergent Shapes and Patterns</t>
-  </si>
-  <si>
-    <t>Collaborative Development of Earthquake-Resistant and Variable 3D Printed Housing</t>
-  </si>
-  <si>
-    <t>Augmenting IFC-Based BIM Models for Graph Neural Network
-Training of Non-Orthogonal Spatial Typologies: A
-Context-Informed Design Methodology</t>
-  </si>
-  <si>
-    <t>(CI) Collaborative Pathways to Sustainable Digital
-Innovation in AEC</t>
-  </si>
-  <si>
-    <t>Rethinking Participatory Architectural Design: Harnessing
-Immersive Environments &amp; AI for Facilitating
-Designer-Stakeholder Collaboration</t>
-  </si>
-  <si>
-    <t>(CI) Augmentation in Design and Fabrication: Expanding the
-Role of AR and Human-Machine Collaboration</t>
-  </si>
-  <si>
-    <t>Toward AIXR: Designing a Framework for AI-Informed
-Human-Robot Collaborative Assembly of Nonuniform Material
-in Extended Reality</t>
-  </si>
-  <si>
-    <t>Buildings as Symbiotic Systems: Cybernetic Adaptation
-between Technical and Biological Systems in Architecture</t>
+    <t>PERFORMANCE-BASED URBAN ENVIRONMENTAL RESTORATION: A MULTI-LAYER CELLULAR AUTOMATA MODEL FOR ECOLOGICAL DESIGN SIMULATION IN HIGH-DENSITY CITIES</t>
+  </si>
+  <si>
+    <t>OPTIMIZED ACOUSTICS FOR MEETING PODS</t>
+  </si>
+  <si>
+    <t>CAN AI-BASED SUGGESTIONS SUPPORT DESIGNING IN IMMERSIVE ENVIRONMENTS? OBSERVING THE USE OF GENERATED IMAGES AS VISUAL REFERENCES FOR ARCHITECTURAL DESIGN IN MIXED REALITY</t>
+  </si>
+  <si>
+    <t>CRAFTING A PARTICIPATORY APPROACH TOWARDS TRADITIONAL VIETNAMESE WEAVING AND DIGITAL COMPUTATION</t>
+  </si>
+  <si>
+    <t>ARCHITECTURAL INTERFACES FOR SHARED SPACES – A MULTI-USER PERSPECTIVE ON INTELLIGENT ENVIRONMENT INTERACTIONS</t>
+  </si>
+  <si>
+    <t>SUSTAINABLE SUSTAINABLE SOCIAL BUILDING ASSISTANT (SSOBA): TRANSFORMING ENERGY USE VIA DIGITAL TWINS, ENVIRONMENTAL SENSING AND OCCUPANT BEHAVIOUR CHANGE</t>
+  </si>
+  <si>
+    <t>COMPUTING URBAN TISSUE: LANDSLIDE MITIGATION STRATEGY OF URBAN INFRASTRUCTURE DESIGN</t>
+  </si>
+  <si>
+    <t>GENERATIVE DESIGN INTELLIGENCE: EXTRACTING DESIGN SPECIFIC SUSTAINABILITY INSIGHTS AND MATERIAL METRICS FROM GENERATIVE ARTIFICIAL INTELLIGENCE OUTPUT</t>
+  </si>
+  <si>
+    <t>COMPARING DIFFERENT BUILDING REPRESENTATIONS FOR READABILITY BY LARGE LANGUAGE MODELS</t>
+  </si>
+  <si>
+    <t>DEEP PERCEPTUAL URBAN FORM</t>
+  </si>
+  <si>
+    <t>FROM TRADITION TO COMPUTATION: ADAPTIVE CERAMIC ‎FAÇADES INSPIRED BY PERSIAN ICE CAVES (YAKHCHALS) FOR ‎PASSIVE COOLING</t>
+  </si>
+  <si>
+    <t>CONSOLIDATED EMPIRICAL BIO-MATERIAL REPOSITORY</t>
+  </si>
+  <si>
+    <t>EVALUATION METHOD OF AI-GENERATED ARCHITECTURAL FACADE IMAGES BASED ON DCNN</t>
+  </si>
+  <si>
+    <t>SUPERIORITY OF HIGH-DIMENSIONAL LATENT VARIABLE REPRESENTATION IN URBAN SPATIAL STRUCTURE: EVIDENCE FROM AN URBAN CLIMATE STUDY</t>
+  </si>
+  <si>
+    <t>AI2D-ARCHITECTURE: A BENCHMARK FOR EVALUATING MULTIMODAL LARGE LANGUAGE MODELS IN ARCHITECTURE</t>
+  </si>
+  <si>
+    <t>DESIGN QUALITY HOUSING ASSESSMENT METHODOLOGY: SUPPORTING HEURISTICS WITH EVIDENCE-BASED DECISION-MAKING</t>
+  </si>
+  <si>
+    <t>FROM CRAFT TO COMMUNITY: PARTICIPATORY UPCYCLING IN PUBLIC HOUSING VIA DIGITAL FABRICATION</t>
+  </si>
+  <si>
+    <t>A FABRICATION GRAMMAR FOR ROBOTIC SAND PACKING:  FROM PRECISE ACTIONS TO EMERGENT SHAPES AND PATTERNS</t>
+  </si>
+  <si>
+    <t>COLLABORATIVE DEVELOPMENT OF EARTHQUAKE-RESISTANT AND VARIABLE 3D PRINTED HOUSING</t>
+  </si>
+  <si>
+    <t>AUGMENTING IFC-BASED BIM MODELS FOR GRAPH NEURAL NETWORK
+TRAINING OF NON-ORTHOGONAL SPATIAL TYPOLOGIES: A
+CONTEXT-INFORMED DESIGN METHODOLOGY</t>
+  </si>
+  <si>
+    <t>(CI) COLLABORATIVE PATHWAYS TO SUSTAINABLE DIGITAL
+INNOVATION IN AEC</t>
+  </si>
+  <si>
+    <t>RETHINKING PARTICIPATORY ARCHITECTURAL DESIGN: HARNESSING
+IMMERSIVE ENVIRONMENTS &amp; AI FOR FACILITATING
+DESIGNER-STAKEHOLDER COLLABORATION</t>
+  </si>
+  <si>
+    <t>(CI) AUGMENTATION IN DESIGN AND FABRICATION: EXPANDING THE
+ROLE OF AR AND HUMAN-MACHINE COLLABORATION</t>
+  </si>
+  <si>
+    <t>TOWARD AIXR: DESIGNING A FRAMEWORK FOR AI-INFORMED
+HUMAN-ROBOT COLLABORATIVE ASSEMBLY OF NONUNIFORM MATERIAL
+IN EXTENDED REALITY</t>
+  </si>
+  <si>
+    <t>BUILDINGS AS SYMBIOTIC SYSTEMS: CYBERNETIC ADAPTATION
+BETWEEN TECHNICAL AND BIOLOGICAL SYSTEMS IN ARCHITECTURE</t>
   </si>
   <si>
     <t xml:space="preserve">CATALYTIC DESIGN INTERFACES: AI-GUIDED BUILDING MASSING AND AUTOMATED COMPLIANCE
@@ -655,6 +652,9 @@
   </si>
   <si>
     <t>COMMUNITY &amp; COLLECTIVE INTELLIGENCE</t>
+  </si>
+  <si>
+    <t>CATALYTIC INTERFACE</t>
   </si>
   <si>
     <t>S-S4</t>
@@ -3859,6 +3859,9 @@
     <t>14:30 - 14:45</t>
   </si>
   <si>
+    <t>16:45 - 17:45</t>
+  </si>
+  <si>
     <t>17:30 - 17:45</t>
   </si>
   <si>
@@ -3950,22 +3953,16 @@
   </si>
   <si>
     <t>16:50 - 17:10</t>
-  </si>
-  <si>
-    <t>16:45 - 17:45</t>
-  </si>
-  <si>
-    <t>CATALYTIC INTERFACE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4029,21 +4026,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4081,7 +4070,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4115,7 +4104,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4150,10 +4138,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4326,14 +4313,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="11" max="11" width="9.6640625" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M89"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4367,8 +4351,11 @@
       <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -4382,31 +4369,34 @@
         <v>0</v>
       </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>403</v>
       </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
       <c r="G2" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>187</v>
+        <v>100</v>
       </c>
       <c r="I2" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="J2" t="s">
-        <v>227</v>
-      </c>
-      <c r="K2" s="2">
+        <v>208</v>
+      </c>
+      <c r="K2" t="s">
+        <v>229</v>
+      </c>
+      <c r="L2" s="2">
         <v>45842</v>
       </c>
-      <c r="L2" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -4420,31 +4410,34 @@
         <v>1</v>
       </c>
       <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
         <v>114</v>
       </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
       <c r="G3" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>188</v>
+        <v>101</v>
       </c>
       <c r="I3" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="J3" t="s">
-        <v>228</v>
-      </c>
-      <c r="K3" s="2">
+        <v>209</v>
+      </c>
+      <c r="K3" t="s">
+        <v>230</v>
+      </c>
+      <c r="L3" s="2">
         <v>45842</v>
       </c>
-      <c r="L3" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -4458,31 +4451,34 @@
         <v>2</v>
       </c>
       <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
         <v>238</v>
       </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
       <c r="G4" t="s">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>189</v>
+        <v>102</v>
       </c>
       <c r="I4" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="J4" t="s">
-        <v>229</v>
-      </c>
-      <c r="K4" s="2">
+        <v>210</v>
+      </c>
+      <c r="K4" t="s">
+        <v>231</v>
+      </c>
+      <c r="L4" s="2">
         <v>45840</v>
       </c>
-      <c r="L4" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M4" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -4496,31 +4492,34 @@
         <v>3</v>
       </c>
       <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
         <v>231</v>
       </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
       <c r="G5" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="I5" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="J5" t="s">
-        <v>230</v>
-      </c>
-      <c r="K5" s="2">
+        <v>209</v>
+      </c>
+      <c r="K5" t="s">
+        <v>232</v>
+      </c>
+      <c r="L5" s="2">
         <v>45842</v>
       </c>
-      <c r="L5" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M5" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -4534,31 +4533,34 @@
         <v>4</v>
       </c>
       <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
         <v>444</v>
       </c>
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
       <c r="G6" t="s">
-        <v>103</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
-        <v>187</v>
+        <v>104</v>
       </c>
       <c r="I6" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="J6" t="s">
-        <v>231</v>
-      </c>
-      <c r="K6" s="2">
+        <v>208</v>
+      </c>
+      <c r="K6" t="s">
+        <v>233</v>
+      </c>
+      <c r="L6" s="2">
         <v>45842</v>
       </c>
-      <c r="L6" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -4572,31 +4574,34 @@
         <v>5</v>
       </c>
       <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
         <v>349</v>
       </c>
-      <c r="F7" t="s">
-        <v>16</v>
-      </c>
       <c r="G7" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>189</v>
+        <v>105</v>
       </c>
       <c r="I7" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="J7" t="s">
-        <v>232</v>
-      </c>
-      <c r="K7" s="2">
+        <v>210</v>
+      </c>
+      <c r="K7" t="s">
+        <v>234</v>
+      </c>
+      <c r="L7" s="2">
         <v>45840</v>
       </c>
-      <c r="L7" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -4610,31 +4615,34 @@
         <v>6</v>
       </c>
       <c r="E8">
+        <v>6</v>
+      </c>
+      <c r="F8">
         <v>329</v>
       </c>
-      <c r="F8" t="s">
-        <v>17</v>
-      </c>
       <c r="G8" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="H8" t="s">
-        <v>190</v>
+        <v>106</v>
       </c>
       <c r="I8" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J8" t="s">
-        <v>233</v>
-      </c>
-      <c r="K8" s="2">
+        <v>211</v>
+      </c>
+      <c r="K8" t="s">
+        <v>235</v>
+      </c>
+      <c r="L8" s="2">
         <v>45841</v>
       </c>
-      <c r="L8" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -4648,31 +4656,34 @@
         <v>7</v>
       </c>
       <c r="E9">
+        <v>7</v>
+      </c>
+      <c r="F9">
         <v>148</v>
       </c>
-      <c r="F9" t="s">
-        <v>18</v>
-      </c>
       <c r="G9" t="s">
-        <v>106</v>
+        <v>19</v>
       </c>
       <c r="H9" t="s">
-        <v>190</v>
+        <v>107</v>
       </c>
       <c r="I9" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J9" t="s">
-        <v>234</v>
-      </c>
-      <c r="K9" s="2">
+        <v>211</v>
+      </c>
+      <c r="K9" t="s">
+        <v>236</v>
+      </c>
+      <c r="L9" s="2">
         <v>45841</v>
       </c>
-      <c r="L9" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -4686,31 +4697,34 @@
         <v>8</v>
       </c>
       <c r="E10">
+        <v>8</v>
+      </c>
+      <c r="F10">
         <v>230</v>
       </c>
-      <c r="F10" t="s">
-        <v>19</v>
-      </c>
       <c r="G10" t="s">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="H10" t="s">
-        <v>188</v>
+        <v>108</v>
       </c>
       <c r="I10" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="J10" t="s">
-        <v>235</v>
-      </c>
-      <c r="K10" s="2">
+        <v>209</v>
+      </c>
+      <c r="K10" t="s">
+        <v>237</v>
+      </c>
+      <c r="L10" s="2">
         <v>45842</v>
       </c>
-      <c r="L10" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -4724,31 +4738,34 @@
         <v>9</v>
       </c>
       <c r="E11">
+        <v>9</v>
+      </c>
+      <c r="F11">
         <v>253</v>
       </c>
-      <c r="F11" t="s">
-        <v>20</v>
-      </c>
       <c r="G11" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="H11" t="s">
-        <v>187</v>
+        <v>109</v>
       </c>
       <c r="I11" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="J11" t="s">
-        <v>236</v>
-      </c>
-      <c r="K11" s="2">
+        <v>208</v>
+      </c>
+      <c r="K11" t="s">
+        <v>238</v>
+      </c>
+      <c r="L11" s="2">
         <v>45842</v>
       </c>
-      <c r="L11" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -4762,31 +4779,34 @@
         <v>10</v>
       </c>
       <c r="E12">
+        <v>10</v>
+      </c>
+      <c r="F12">
         <v>55</v>
       </c>
-      <c r="F12" t="s">
-        <v>21</v>
-      </c>
       <c r="G12" t="s">
-        <v>109</v>
+        <v>22</v>
       </c>
       <c r="H12" t="s">
-        <v>190</v>
+        <v>110</v>
       </c>
       <c r="I12" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J12" t="s">
-        <v>237</v>
-      </c>
-      <c r="K12" s="2">
+        <v>211</v>
+      </c>
+      <c r="K12" t="s">
+        <v>239</v>
+      </c>
+      <c r="L12" s="2">
         <v>45841</v>
       </c>
-      <c r="L12" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -4800,31 +4820,34 @@
         <v>11</v>
       </c>
       <c r="E13">
+        <v>11</v>
+      </c>
+      <c r="F13">
         <v>262</v>
       </c>
-      <c r="F13" t="s">
-        <v>22</v>
-      </c>
       <c r="G13" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="H13" t="s">
-        <v>190</v>
+        <v>111</v>
       </c>
       <c r="I13" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J13" t="s">
-        <v>238</v>
-      </c>
-      <c r="K13" s="2">
+        <v>211</v>
+      </c>
+      <c r="K13" t="s">
+        <v>240</v>
+      </c>
+      <c r="L13" s="2">
         <v>45841</v>
       </c>
-      <c r="L13" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -4838,31 +4861,34 @@
         <v>12</v>
       </c>
       <c r="E14">
+        <v>12</v>
+      </c>
+      <c r="F14">
         <v>250</v>
       </c>
-      <c r="F14" t="s">
-        <v>23</v>
-      </c>
       <c r="G14" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="H14" t="s">
-        <v>191</v>
+        <v>112</v>
       </c>
       <c r="I14" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="J14" t="s">
-        <v>239</v>
-      </c>
-      <c r="K14" s="2">
+        <v>212</v>
+      </c>
+      <c r="K14" t="s">
+        <v>241</v>
+      </c>
+      <c r="L14" s="2">
         <v>45841</v>
       </c>
-      <c r="L14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -4876,31 +4902,34 @@
         <v>13</v>
       </c>
       <c r="E15">
+        <v>13</v>
+      </c>
+      <c r="F15">
         <v>36</v>
       </c>
-      <c r="F15" t="s">
-        <v>24</v>
-      </c>
       <c r="G15" t="s">
-        <v>112</v>
+        <v>25</v>
       </c>
       <c r="H15" t="s">
-        <v>189</v>
+        <v>113</v>
       </c>
       <c r="I15" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="J15" t="s">
-        <v>240</v>
-      </c>
-      <c r="K15" s="2">
+        <v>210</v>
+      </c>
+      <c r="K15" t="s">
+        <v>242</v>
+      </c>
+      <c r="L15" s="2">
         <v>45840</v>
       </c>
-      <c r="L15" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -4914,31 +4943,34 @@
         <v>14</v>
       </c>
       <c r="E16">
+        <v>14</v>
+      </c>
+      <c r="F16">
         <v>431</v>
       </c>
-      <c r="F16" t="s">
-        <v>25</v>
-      </c>
       <c r="G16" t="s">
-        <v>113</v>
+        <v>26</v>
       </c>
       <c r="H16" t="s">
-        <v>192</v>
+        <v>114</v>
       </c>
       <c r="I16" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="J16" t="s">
-        <v>241</v>
-      </c>
-      <c r="K16" s="2">
+        <v>213</v>
+      </c>
+      <c r="K16" t="s">
+        <v>243</v>
+      </c>
+      <c r="L16" s="2">
         <v>45841</v>
       </c>
-      <c r="L16" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M16" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -4952,31 +4984,34 @@
         <v>15</v>
       </c>
       <c r="E17">
+        <v>15</v>
+      </c>
+      <c r="F17">
         <v>132</v>
       </c>
-      <c r="F17" t="s">
-        <v>26</v>
-      </c>
       <c r="G17" t="s">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c r="H17" t="s">
-        <v>193</v>
+        <v>115</v>
       </c>
       <c r="I17" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="J17" t="s">
-        <v>242</v>
-      </c>
-      <c r="K17" s="2">
+        <v>214</v>
+      </c>
+      <c r="K17" t="s">
+        <v>244</v>
+      </c>
+      <c r="L17" s="2">
         <v>45841</v>
       </c>
-      <c r="L17" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M17" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -4990,31 +5025,34 @@
         <v>16</v>
       </c>
       <c r="E18">
+        <v>16</v>
+      </c>
+      <c r="F18">
         <v>178</v>
       </c>
-      <c r="F18" t="s">
-        <v>27</v>
-      </c>
       <c r="G18" t="s">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="H18" t="s">
-        <v>193</v>
+        <v>116</v>
       </c>
       <c r="I18" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="J18" t="s">
-        <v>243</v>
-      </c>
-      <c r="K18" s="2">
+        <v>214</v>
+      </c>
+      <c r="K18" t="s">
+        <v>245</v>
+      </c>
+      <c r="L18" s="2">
         <v>45841</v>
       </c>
-      <c r="L18" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M18" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -5028,31 +5066,34 @@
         <v>17</v>
       </c>
       <c r="E19">
+        <v>17</v>
+      </c>
+      <c r="F19">
         <v>151</v>
       </c>
-      <c r="F19" t="s">
-        <v>28</v>
-      </c>
       <c r="G19" t="s">
-        <v>116</v>
+        <v>29</v>
       </c>
       <c r="H19" t="s">
-        <v>194</v>
+        <v>117</v>
       </c>
       <c r="I19" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="J19" t="s">
-        <v>244</v>
-      </c>
-      <c r="K19" s="2">
+        <v>215</v>
+      </c>
+      <c r="K19" t="s">
+        <v>246</v>
+      </c>
+      <c r="L19" s="2">
         <v>45840</v>
       </c>
-      <c r="L19" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M19" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -5066,31 +5107,34 @@
         <v>18</v>
       </c>
       <c r="E20">
+        <v>18</v>
+      </c>
+      <c r="F20">
         <v>440</v>
       </c>
-      <c r="F20" t="s">
-        <v>29</v>
-      </c>
       <c r="G20" t="s">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="H20" t="s">
-        <v>192</v>
+        <v>118</v>
       </c>
       <c r="I20" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="J20" t="s">
-        <v>245</v>
-      </c>
-      <c r="K20" s="2">
+        <v>213</v>
+      </c>
+      <c r="K20" t="s">
+        <v>247</v>
+      </c>
+      <c r="L20" s="2">
         <v>45841</v>
       </c>
-      <c r="L20" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M20" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -5104,31 +5148,34 @@
         <v>19</v>
       </c>
       <c r="E21">
+        <v>19</v>
+      </c>
+      <c r="F21">
         <v>198</v>
       </c>
-      <c r="F21" t="s">
-        <v>30</v>
-      </c>
       <c r="G21" t="s">
-        <v>118</v>
+        <v>31</v>
       </c>
       <c r="H21" t="s">
-        <v>191</v>
+        <v>119</v>
       </c>
       <c r="I21" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="J21" t="s">
-        <v>246</v>
-      </c>
-      <c r="K21" s="2">
+        <v>212</v>
+      </c>
+      <c r="K21" t="s">
+        <v>248</v>
+      </c>
+      <c r="L21" s="2">
         <v>45841</v>
       </c>
-      <c r="L21" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M21" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -5142,31 +5189,34 @@
         <v>20</v>
       </c>
       <c r="E22">
+        <v>20</v>
+      </c>
+      <c r="F22">
         <v>426</v>
       </c>
-      <c r="F22" t="s">
-        <v>31</v>
-      </c>
       <c r="G22" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="H22" t="s">
-        <v>195</v>
+        <v>120</v>
       </c>
       <c r="I22" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="J22" t="s">
-        <v>247</v>
-      </c>
-      <c r="K22" s="2">
+        <v>216</v>
+      </c>
+      <c r="K22" t="s">
+        <v>249</v>
+      </c>
+      <c r="L22" s="2">
         <v>45840</v>
       </c>
-      <c r="L22" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M22" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -5180,31 +5230,34 @@
         <v>21</v>
       </c>
       <c r="E23">
+        <v>21</v>
+      </c>
+      <c r="F23">
         <v>126</v>
       </c>
-      <c r="F23" t="s">
-        <v>32</v>
-      </c>
       <c r="G23" t="s">
-        <v>120</v>
+        <v>33</v>
       </c>
       <c r="H23" t="s">
-        <v>194</v>
+        <v>121</v>
       </c>
       <c r="I23" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="J23" t="s">
-        <v>248</v>
-      </c>
-      <c r="K23" s="2">
+        <v>215</v>
+      </c>
+      <c r="K23" t="s">
+        <v>250</v>
+      </c>
+      <c r="L23" s="2">
         <v>45840</v>
       </c>
-      <c r="L23" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M23" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -5218,31 +5271,34 @@
         <v>22</v>
       </c>
       <c r="E24">
+        <v>22</v>
+      </c>
+      <c r="F24">
         <v>193</v>
       </c>
-      <c r="F24" t="s">
-        <v>33</v>
-      </c>
       <c r="G24" t="s">
-        <v>121</v>
+        <v>34</v>
       </c>
       <c r="H24" t="s">
-        <v>193</v>
+        <v>122</v>
       </c>
       <c r="I24" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="J24" t="s">
-        <v>249</v>
-      </c>
-      <c r="K24" s="2">
+        <v>214</v>
+      </c>
+      <c r="K24" t="s">
+        <v>251</v>
+      </c>
+      <c r="L24" s="2">
         <v>45841</v>
       </c>
-      <c r="L24" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M24" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -5256,31 +5312,34 @@
         <v>23</v>
       </c>
       <c r="E25">
+        <v>23</v>
+      </c>
+      <c r="F25">
         <v>134</v>
       </c>
-      <c r="F25" t="s">
-        <v>34</v>
-      </c>
       <c r="G25" t="s">
-        <v>122</v>
+        <v>35</v>
       </c>
       <c r="H25" t="s">
-        <v>194</v>
+        <v>123</v>
       </c>
       <c r="I25" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="J25" t="s">
-        <v>250</v>
-      </c>
-      <c r="K25" s="2">
+        <v>215</v>
+      </c>
+      <c r="K25" t="s">
+        <v>252</v>
+      </c>
+      <c r="L25" s="2">
         <v>45840</v>
       </c>
-      <c r="L25" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M25" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -5294,31 +5353,34 @@
         <v>24</v>
       </c>
       <c r="E26">
+        <v>24</v>
+      </c>
+      <c r="F26">
         <v>50</v>
       </c>
-      <c r="F26" t="s">
-        <v>35</v>
-      </c>
       <c r="G26" t="s">
-        <v>123</v>
+        <v>36</v>
       </c>
       <c r="H26" t="s">
-        <v>191</v>
+        <v>124</v>
       </c>
       <c r="I26" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="J26" t="s">
-        <v>251</v>
-      </c>
-      <c r="K26" s="2">
+        <v>212</v>
+      </c>
+      <c r="K26" t="s">
+        <v>253</v>
+      </c>
+      <c r="L26" s="2">
         <v>45841</v>
       </c>
-      <c r="L26" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M26" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -5332,31 +5394,34 @@
         <v>25</v>
       </c>
       <c r="E27">
+        <v>25</v>
+      </c>
+      <c r="F27">
         <v>314</v>
       </c>
-      <c r="F27" t="s">
-        <v>36</v>
-      </c>
       <c r="G27" t="s">
-        <v>124</v>
+        <v>37</v>
       </c>
       <c r="H27" t="s">
-        <v>192</v>
+        <v>125</v>
       </c>
       <c r="I27" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="J27" t="s">
-        <v>252</v>
-      </c>
-      <c r="K27" s="2">
+        <v>213</v>
+      </c>
+      <c r="K27" t="s">
+        <v>254</v>
+      </c>
+      <c r="L27" s="2">
         <v>45841</v>
       </c>
-      <c r="L27" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M27" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -5370,31 +5435,34 @@
         <v>26</v>
       </c>
       <c r="E28">
+        <v>26</v>
+      </c>
+      <c r="F28">
         <v>386</v>
       </c>
-      <c r="F28" t="s">
-        <v>37</v>
-      </c>
       <c r="G28" t="s">
-        <v>125</v>
+        <v>38</v>
       </c>
       <c r="H28" t="s">
-        <v>193</v>
+        <v>126</v>
       </c>
       <c r="I28" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="J28" t="s">
-        <v>253</v>
-      </c>
-      <c r="K28" s="2">
+        <v>214</v>
+      </c>
+      <c r="K28" t="s">
+        <v>255</v>
+      </c>
+      <c r="L28" s="2">
         <v>45841</v>
       </c>
-      <c r="L28" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M28" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -5408,31 +5476,34 @@
         <v>27</v>
       </c>
       <c r="E29">
+        <v>27</v>
+      </c>
+      <c r="F29">
         <v>196</v>
       </c>
-      <c r="F29" t="s">
-        <v>38</v>
-      </c>
       <c r="G29" t="s">
-        <v>126</v>
+        <v>39</v>
       </c>
       <c r="H29" t="s">
-        <v>195</v>
+        <v>127</v>
       </c>
       <c r="I29" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="J29" t="s">
-        <v>254</v>
-      </c>
-      <c r="K29" s="2">
+        <v>216</v>
+      </c>
+      <c r="K29" t="s">
+        <v>256</v>
+      </c>
+      <c r="L29" s="2">
         <v>45840</v>
       </c>
-      <c r="L29" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M29" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -5446,31 +5517,34 @@
         <v>28</v>
       </c>
       <c r="E30">
+        <v>28</v>
+      </c>
+      <c r="F30">
         <v>135</v>
       </c>
-      <c r="F30" t="s">
-        <v>39</v>
-      </c>
       <c r="G30" t="s">
-        <v>127</v>
+        <v>40</v>
       </c>
       <c r="H30" t="s">
-        <v>196</v>
+        <v>128</v>
       </c>
       <c r="I30" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="J30" t="s">
-        <v>255</v>
-      </c>
-      <c r="K30" s="2">
+        <v>217</v>
+      </c>
+      <c r="K30" t="s">
+        <v>257</v>
+      </c>
+      <c r="L30" s="2">
         <v>45842</v>
       </c>
-      <c r="L30" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M30" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -5484,31 +5558,34 @@
         <v>29</v>
       </c>
       <c r="E31">
+        <v>29</v>
+      </c>
+      <c r="F31">
         <v>210</v>
       </c>
-      <c r="F31" t="s">
-        <v>40</v>
-      </c>
       <c r="G31" t="s">
-        <v>128</v>
+        <v>41</v>
       </c>
       <c r="H31" t="s">
-        <v>192</v>
+        <v>129</v>
       </c>
       <c r="I31" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="J31" t="s">
-        <v>256</v>
-      </c>
-      <c r="K31" s="2">
+        <v>213</v>
+      </c>
+      <c r="K31" t="s">
+        <v>258</v>
+      </c>
+      <c r="L31" s="2">
         <v>45841</v>
       </c>
-      <c r="L31" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M31" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -5522,31 +5599,34 @@
         <v>30</v>
       </c>
       <c r="E32">
+        <v>30</v>
+      </c>
+      <c r="F32">
         <v>162</v>
       </c>
-      <c r="F32" t="s">
-        <v>41</v>
-      </c>
       <c r="G32" t="s">
-        <v>129</v>
+        <v>42</v>
       </c>
       <c r="H32" t="s">
-        <v>197</v>
+        <v>130</v>
       </c>
       <c r="I32" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="J32" t="s">
-        <v>257</v>
-      </c>
-      <c r="K32" s="2">
+        <v>218</v>
+      </c>
+      <c r="K32" t="s">
+        <v>259</v>
+      </c>
+      <c r="L32" s="2">
         <v>45840</v>
       </c>
-      <c r="L32" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M32" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -5560,31 +5640,34 @@
         <v>31</v>
       </c>
       <c r="E33">
+        <v>31</v>
+      </c>
+      <c r="F33">
         <v>169</v>
       </c>
-      <c r="F33" t="s">
-        <v>42</v>
-      </c>
       <c r="G33" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="H33" t="s">
-        <v>198</v>
+        <v>131</v>
       </c>
       <c r="I33" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="J33" t="s">
-        <v>258</v>
-      </c>
-      <c r="K33" s="2">
+        <v>219</v>
+      </c>
+      <c r="K33" t="s">
+        <v>260</v>
+      </c>
+      <c r="L33" s="2">
         <v>45840</v>
       </c>
-      <c r="L33" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M33" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -5598,31 +5681,34 @@
         <v>32</v>
       </c>
       <c r="E34">
+        <v>32</v>
+      </c>
+      <c r="F34">
         <v>19</v>
       </c>
-      <c r="F34" t="s">
-        <v>43</v>
-      </c>
       <c r="G34" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="H34" t="s">
-        <v>196</v>
+        <v>132</v>
       </c>
       <c r="I34" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="J34" t="s">
-        <v>259</v>
-      </c>
-      <c r="K34" s="2">
+        <v>217</v>
+      </c>
+      <c r="K34" t="s">
+        <v>261</v>
+      </c>
+      <c r="L34" s="2">
         <v>45842</v>
       </c>
-      <c r="L34" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M34" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -5636,31 +5722,34 @@
         <v>33</v>
       </c>
       <c r="E35">
+        <v>33</v>
+      </c>
+      <c r="F35">
         <v>240</v>
       </c>
-      <c r="F35" t="s">
-        <v>44</v>
-      </c>
       <c r="G35" t="s">
-        <v>132</v>
+        <v>45</v>
       </c>
       <c r="H35" t="s">
-        <v>199</v>
+        <v>133</v>
       </c>
       <c r="I35" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="J35" t="s">
-        <v>260</v>
-      </c>
-      <c r="K35" s="2">
+        <v>220</v>
+      </c>
+      <c r="K35" t="s">
+        <v>262</v>
+      </c>
+      <c r="L35" s="2">
         <v>45840</v>
       </c>
-      <c r="L35" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M35" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -5674,31 +5763,34 @@
         <v>34</v>
       </c>
       <c r="E36">
+        <v>34</v>
+      </c>
+      <c r="F36">
         <v>379</v>
       </c>
-      <c r="F36" t="s">
-        <v>45</v>
-      </c>
       <c r="G36" t="s">
-        <v>133</v>
+        <v>46</v>
       </c>
       <c r="H36" t="s">
-        <v>200</v>
+        <v>134</v>
       </c>
       <c r="I36" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="J36" t="s">
-        <v>261</v>
-      </c>
-      <c r="K36" s="2">
+        <v>221</v>
+      </c>
+      <c r="K36" t="s">
+        <v>263</v>
+      </c>
+      <c r="L36" s="2">
         <v>45842</v>
       </c>
-      <c r="L36" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M36" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -5712,31 +5804,34 @@
         <v>35</v>
       </c>
       <c r="E37">
+        <v>35</v>
+      </c>
+      <c r="F37">
         <v>149</v>
       </c>
-      <c r="F37" t="s">
-        <v>46</v>
-      </c>
       <c r="G37" t="s">
-        <v>134</v>
+        <v>47</v>
       </c>
       <c r="H37" t="s">
-        <v>201</v>
+        <v>135</v>
       </c>
       <c r="I37" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="J37" t="s">
-        <v>262</v>
-      </c>
-      <c r="K37" s="2">
+        <v>222</v>
+      </c>
+      <c r="K37" t="s">
+        <v>264</v>
+      </c>
+      <c r="L37" s="2">
         <v>45840</v>
       </c>
-      <c r="L37" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M37" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -5750,31 +5845,34 @@
         <v>36</v>
       </c>
       <c r="E38">
+        <v>36</v>
+      </c>
+      <c r="F38">
         <v>87</v>
       </c>
-      <c r="F38" t="s">
-        <v>47</v>
-      </c>
       <c r="G38" t="s">
-        <v>135</v>
+        <v>48</v>
       </c>
       <c r="H38" t="s">
-        <v>201</v>
+        <v>136</v>
       </c>
       <c r="I38" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="J38" t="s">
-        <v>263</v>
-      </c>
-      <c r="K38" s="2">
+        <v>222</v>
+      </c>
+      <c r="K38" t="s">
+        <v>265</v>
+      </c>
+      <c r="L38" s="2">
         <v>45840</v>
       </c>
-      <c r="L38" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M38" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -5788,31 +5886,34 @@
         <v>37</v>
       </c>
       <c r="E39">
+        <v>37</v>
+      </c>
+      <c r="F39">
         <v>221</v>
       </c>
-      <c r="F39" t="s">
-        <v>48</v>
-      </c>
       <c r="G39" t="s">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="H39" t="s">
-        <v>193</v>
+        <v>137</v>
       </c>
       <c r="I39" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="J39" t="s">
-        <v>264</v>
-      </c>
-      <c r="K39" s="2">
+        <v>223</v>
+      </c>
+      <c r="K39" t="s">
+        <v>266</v>
+      </c>
+      <c r="L39" s="2">
         <v>45841</v>
       </c>
-      <c r="L39" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M39" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -5826,31 +5927,34 @@
         <v>38</v>
       </c>
       <c r="E40">
+        <v>38</v>
+      </c>
+      <c r="F40">
         <v>45</v>
       </c>
-      <c r="F40" t="s">
-        <v>49</v>
-      </c>
       <c r="G40" t="s">
-        <v>137</v>
+        <v>50</v>
       </c>
       <c r="H40" t="s">
-        <v>202</v>
+        <v>138</v>
       </c>
       <c r="I40" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="J40" t="s">
-        <v>265</v>
-      </c>
-      <c r="K40" s="2">
+        <v>224</v>
+      </c>
+      <c r="K40" t="s">
+        <v>267</v>
+      </c>
+      <c r="L40" s="2">
         <v>45841</v>
       </c>
-      <c r="L40" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M40" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -5864,31 +5968,34 @@
         <v>39</v>
       </c>
       <c r="E41">
+        <v>39</v>
+      </c>
+      <c r="F41">
         <v>141</v>
       </c>
-      <c r="F41" t="s">
-        <v>50</v>
-      </c>
       <c r="G41" t="s">
-        <v>138</v>
+        <v>51</v>
       </c>
       <c r="H41" t="s">
-        <v>198</v>
+        <v>139</v>
       </c>
       <c r="I41" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="J41" t="s">
-        <v>266</v>
-      </c>
-      <c r="K41" s="2">
+        <v>219</v>
+      </c>
+      <c r="K41" t="s">
+        <v>268</v>
+      </c>
+      <c r="L41" s="2">
         <v>45840</v>
       </c>
-      <c r="L41" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M41" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -5902,31 +6009,34 @@
         <v>40</v>
       </c>
       <c r="E42">
+        <v>40</v>
+      </c>
+      <c r="F42">
         <v>255</v>
       </c>
-      <c r="F42" t="s">
-        <v>51</v>
-      </c>
       <c r="G42" t="s">
-        <v>139</v>
+        <v>52</v>
       </c>
       <c r="H42" t="s">
-        <v>198</v>
+        <v>140</v>
       </c>
       <c r="I42" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="J42" t="s">
-        <v>267</v>
-      </c>
-      <c r="K42" s="2">
+        <v>219</v>
+      </c>
+      <c r="K42" t="s">
+        <v>269</v>
+      </c>
+      <c r="L42" s="2">
         <v>45840</v>
       </c>
-      <c r="L42" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M42" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -5940,31 +6050,34 @@
         <v>41</v>
       </c>
       <c r="E43">
+        <v>41</v>
+      </c>
+      <c r="F43">
         <v>276</v>
       </c>
-      <c r="F43" t="s">
-        <v>52</v>
-      </c>
       <c r="G43" t="s">
-        <v>140</v>
+        <v>53</v>
       </c>
       <c r="H43" t="s">
-        <v>200</v>
+        <v>141</v>
       </c>
       <c r="I43" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="J43" t="s">
-        <v>268</v>
-      </c>
-      <c r="K43" s="2">
+        <v>221</v>
+      </c>
+      <c r="K43" t="s">
+        <v>270</v>
+      </c>
+      <c r="L43" s="2">
         <v>45842</v>
       </c>
-      <c r="L43" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M43" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -5975,34 +6088,37 @@
         <v>42</v>
       </c>
       <c r="D44">
+        <v>42</v>
+      </c>
+      <c r="E44">
         <v>43</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>304</v>
       </c>
-      <c r="F44" t="s">
-        <v>53</v>
-      </c>
       <c r="G44" t="s">
-        <v>141</v>
+        <v>54</v>
       </c>
       <c r="H44" t="s">
-        <v>202</v>
+        <v>142</v>
       </c>
       <c r="I44" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="J44" t="s">
-        <v>269</v>
-      </c>
-      <c r="K44" s="2">
+        <v>224</v>
+      </c>
+      <c r="K44" t="s">
+        <v>271</v>
+      </c>
+      <c r="L44" s="2">
         <v>45841</v>
       </c>
-      <c r="L44" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M44" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -6013,34 +6129,37 @@
         <v>43</v>
       </c>
       <c r="D45">
+        <v>43</v>
+      </c>
+      <c r="E45">
         <v>44</v>
       </c>
-      <c r="E45">
+      <c r="F45">
         <v>33</v>
       </c>
-      <c r="F45" t="s">
-        <v>54</v>
-      </c>
       <c r="G45" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="H45" t="s">
-        <v>195</v>
+        <v>143</v>
       </c>
       <c r="I45" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="J45" t="s">
-        <v>270</v>
-      </c>
-      <c r="K45" s="2">
+        <v>216</v>
+      </c>
+      <c r="K45" t="s">
+        <v>272</v>
+      </c>
+      <c r="L45" s="2">
         <v>45840</v>
       </c>
-      <c r="L45" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M45" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -6051,34 +6170,37 @@
         <v>44</v>
       </c>
       <c r="D46">
+        <v>44</v>
+      </c>
+      <c r="E46">
         <v>45</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>127</v>
       </c>
-      <c r="F46" t="s">
-        <v>55</v>
-      </c>
       <c r="G46" t="s">
-        <v>143</v>
+        <v>56</v>
       </c>
       <c r="H46" t="s">
-        <v>197</v>
+        <v>144</v>
       </c>
       <c r="I46" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="J46" t="s">
-        <v>271</v>
-      </c>
-      <c r="K46" s="2">
+        <v>218</v>
+      </c>
+      <c r="K46" t="s">
+        <v>273</v>
+      </c>
+      <c r="L46" s="2">
         <v>45840</v>
       </c>
-      <c r="L46" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M46" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -6089,34 +6211,37 @@
         <v>45</v>
       </c>
       <c r="D47">
+        <v>45</v>
+      </c>
+      <c r="E47">
         <v>46</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>222</v>
       </c>
-      <c r="F47" t="s">
-        <v>56</v>
-      </c>
       <c r="G47" t="s">
-        <v>144</v>
+        <v>57</v>
       </c>
       <c r="H47" t="s">
-        <v>201</v>
+        <v>145</v>
       </c>
       <c r="I47" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="J47" t="s">
-        <v>272</v>
-      </c>
-      <c r="K47" s="2">
+        <v>222</v>
+      </c>
+      <c r="K47" t="s">
+        <v>274</v>
+      </c>
+      <c r="L47" s="2">
         <v>45840</v>
       </c>
-      <c r="L47" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M47" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -6127,34 +6252,37 @@
         <v>46</v>
       </c>
       <c r="D48">
+        <v>46</v>
+      </c>
+      <c r="E48">
         <v>47</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>252</v>
       </c>
-      <c r="F48" t="s">
-        <v>57</v>
-      </c>
       <c r="G48" t="s">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="H48" t="s">
-        <v>201</v>
+        <v>146</v>
       </c>
       <c r="I48" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="J48" t="s">
-        <v>273</v>
-      </c>
-      <c r="K48" s="2">
+        <v>222</v>
+      </c>
+      <c r="K48" t="s">
+        <v>275</v>
+      </c>
+      <c r="L48" s="2">
         <v>45840</v>
       </c>
-      <c r="L48" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M48" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -6165,34 +6293,37 @@
         <v>47</v>
       </c>
       <c r="D49">
+        <v>47</v>
+      </c>
+      <c r="E49">
         <v>48</v>
       </c>
-      <c r="E49">
+      <c r="F49">
         <v>155</v>
       </c>
-      <c r="F49" t="s">
-        <v>58</v>
-      </c>
       <c r="G49" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="H49" t="s">
-        <v>193</v>
+        <v>147</v>
       </c>
       <c r="I49" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="J49" t="s">
-        <v>274</v>
-      </c>
-      <c r="K49" s="2">
+        <v>223</v>
+      </c>
+      <c r="K49" t="s">
+        <v>276</v>
+      </c>
+      <c r="L49" s="2">
         <v>45841</v>
       </c>
-      <c r="L49" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M49" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -6203,34 +6334,37 @@
         <v>48</v>
       </c>
       <c r="D50">
+        <v>48</v>
+      </c>
+      <c r="E50">
         <v>49</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>133</v>
       </c>
-      <c r="F50" t="s">
-        <v>59</v>
-      </c>
       <c r="G50" t="s">
-        <v>147</v>
+        <v>60</v>
       </c>
       <c r="H50" t="s">
-        <v>203</v>
+        <v>148</v>
       </c>
       <c r="I50" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="J50" t="s">
-        <v>275</v>
-      </c>
-      <c r="K50" s="2">
+        <v>225</v>
+      </c>
+      <c r="K50" t="s">
+        <v>277</v>
+      </c>
+      <c r="L50" s="2">
         <v>45842</v>
       </c>
-      <c r="L50" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M50" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -6241,34 +6375,37 @@
         <v>49</v>
       </c>
       <c r="D51">
+        <v>49</v>
+      </c>
+      <c r="E51">
         <v>50</v>
       </c>
-      <c r="E51">
+      <c r="F51">
         <v>447</v>
       </c>
-      <c r="F51" t="s">
-        <v>60</v>
-      </c>
       <c r="G51" t="s">
-        <v>148</v>
+        <v>61</v>
       </c>
       <c r="H51" t="s">
-        <v>197</v>
+        <v>149</v>
       </c>
       <c r="I51" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="J51" t="s">
-        <v>276</v>
-      </c>
-      <c r="K51" s="2">
+        <v>218</v>
+      </c>
+      <c r="K51" t="s">
+        <v>278</v>
+      </c>
+      <c r="L51" s="2">
         <v>45840</v>
       </c>
-      <c r="L51" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M51" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -6279,34 +6416,37 @@
         <v>50</v>
       </c>
       <c r="D52">
+        <v>50</v>
+      </c>
+      <c r="E52">
         <v>52</v>
       </c>
-      <c r="E52">
+      <c r="F52">
         <v>150</v>
       </c>
-      <c r="F52" t="s">
-        <v>61</v>
-      </c>
       <c r="G52" t="s">
-        <v>149</v>
+        <v>62</v>
       </c>
       <c r="H52" t="s">
-        <v>202</v>
+        <v>150</v>
       </c>
       <c r="I52" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="J52" t="s">
-        <v>277</v>
-      </c>
-      <c r="K52" s="2">
+        <v>224</v>
+      </c>
+      <c r="K52" t="s">
+        <v>279</v>
+      </c>
+      <c r="L52" s="2">
         <v>45841</v>
       </c>
-      <c r="L52" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M52" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -6317,34 +6457,37 @@
         <v>51</v>
       </c>
       <c r="D53">
+        <v>51</v>
+      </c>
+      <c r="E53">
         <v>53</v>
       </c>
-      <c r="E53">
+      <c r="F53">
         <v>29</v>
       </c>
-      <c r="F53" t="s">
-        <v>62</v>
-      </c>
       <c r="G53" t="s">
-        <v>150</v>
+        <v>63</v>
       </c>
       <c r="H53" t="s">
-        <v>204</v>
+        <v>151</v>
       </c>
       <c r="I53" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="J53" t="s">
-        <v>278</v>
-      </c>
-      <c r="K53" s="2">
+        <v>226</v>
+      </c>
+      <c r="K53" t="s">
+        <v>280</v>
+      </c>
+      <c r="L53" s="2">
         <v>45841</v>
       </c>
-      <c r="L53" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M53" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -6355,34 +6498,37 @@
         <v>52</v>
       </c>
       <c r="D54">
+        <v>52</v>
+      </c>
+      <c r="E54">
         <v>54</v>
       </c>
-      <c r="E54">
+      <c r="F54">
         <v>121</v>
       </c>
-      <c r="F54" t="s">
-        <v>63</v>
-      </c>
       <c r="G54" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="H54" t="s">
-        <v>204</v>
+        <v>152</v>
       </c>
       <c r="I54" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="J54" t="s">
-        <v>279</v>
-      </c>
-      <c r="K54" s="2">
+        <v>226</v>
+      </c>
+      <c r="K54" t="s">
+        <v>281</v>
+      </c>
+      <c r="L54" s="2">
         <v>45841</v>
       </c>
-      <c r="L54" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M54" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -6393,34 +6539,37 @@
         <v>53</v>
       </c>
       <c r="D55">
+        <v>53</v>
+      </c>
+      <c r="E55">
         <v>55</v>
       </c>
-      <c r="E55">
+      <c r="F55">
         <v>111</v>
       </c>
-      <c r="F55" t="s">
-        <v>64</v>
-      </c>
       <c r="G55" t="s">
-        <v>152</v>
+        <v>65</v>
       </c>
       <c r="H55" t="s">
-        <v>200</v>
+        <v>153</v>
       </c>
       <c r="I55" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="J55" t="s">
-        <v>280</v>
-      </c>
-      <c r="K55" s="2">
+        <v>221</v>
+      </c>
+      <c r="K55" t="s">
+        <v>282</v>
+      </c>
+      <c r="L55" s="2">
         <v>45842</v>
       </c>
-      <c r="L55" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M55" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -6431,34 +6580,37 @@
         <v>54</v>
       </c>
       <c r="D56">
+        <v>54</v>
+      </c>
+      <c r="E56">
         <v>56</v>
       </c>
-      <c r="E56">
+      <c r="F56">
         <v>59</v>
       </c>
-      <c r="F56" t="s">
-        <v>65</v>
-      </c>
       <c r="G56" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
       <c r="H56" t="s">
-        <v>202</v>
+        <v>154</v>
       </c>
       <c r="I56" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="J56" t="s">
-        <v>281</v>
-      </c>
-      <c r="K56" s="2">
+        <v>224</v>
+      </c>
+      <c r="K56" t="s">
+        <v>283</v>
+      </c>
+      <c r="L56" s="2">
         <v>45841</v>
       </c>
-      <c r="L56" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M56" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -6469,34 +6621,37 @@
         <v>55</v>
       </c>
       <c r="D57">
+        <v>55</v>
+      </c>
+      <c r="E57">
         <v>57</v>
       </c>
-      <c r="E57">
+      <c r="F57">
         <v>34</v>
       </c>
-      <c r="F57" t="s">
-        <v>66</v>
-      </c>
       <c r="G57" t="s">
-        <v>154</v>
+        <v>67</v>
       </c>
       <c r="H57" t="s">
-        <v>193</v>
+        <v>155</v>
       </c>
       <c r="I57" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="J57" t="s">
-        <v>282</v>
-      </c>
-      <c r="K57" s="2">
+        <v>223</v>
+      </c>
+      <c r="K57" t="s">
+        <v>284</v>
+      </c>
+      <c r="L57" s="2">
         <v>45841</v>
       </c>
-      <c r="L57" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M57" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -6507,34 +6662,37 @@
         <v>56</v>
       </c>
       <c r="D58">
+        <v>56</v>
+      </c>
+      <c r="E58">
         <v>58</v>
       </c>
-      <c r="E58">
+      <c r="F58">
         <v>357</v>
       </c>
-      <c r="F58" t="s">
-        <v>67</v>
-      </c>
       <c r="G58" t="s">
-        <v>155</v>
+        <v>68</v>
       </c>
       <c r="H58" t="s">
-        <v>201</v>
+        <v>156</v>
       </c>
       <c r="I58" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="J58" t="s">
-        <v>283</v>
-      </c>
-      <c r="K58" s="2">
+        <v>222</v>
+      </c>
+      <c r="K58" t="s">
+        <v>285</v>
+      </c>
+      <c r="L58" s="2">
         <v>45840</v>
       </c>
-      <c r="L58" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M58" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -6545,34 +6703,37 @@
         <v>57</v>
       </c>
       <c r="D59">
+        <v>57</v>
+      </c>
+      <c r="E59">
         <v>59</v>
       </c>
-      <c r="E59">
+      <c r="F59">
         <v>41</v>
       </c>
-      <c r="F59" t="s">
-        <v>68</v>
-      </c>
       <c r="G59" t="s">
-        <v>156</v>
+        <v>69</v>
       </c>
       <c r="H59" t="s">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="I59" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="J59" t="s">
-        <v>284</v>
-      </c>
-      <c r="K59" s="2">
+        <v>219</v>
+      </c>
+      <c r="K59" t="s">
+        <v>286</v>
+      </c>
+      <c r="L59" s="2">
         <v>45840</v>
       </c>
-      <c r="L59" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M59" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -6583,34 +6744,37 @@
         <v>58</v>
       </c>
       <c r="D60">
+        <v>58</v>
+      </c>
+      <c r="E60">
         <v>60</v>
       </c>
-      <c r="E60">
+      <c r="F60">
         <v>46</v>
       </c>
-      <c r="F60" t="s">
-        <v>69</v>
-      </c>
       <c r="G60" t="s">
-        <v>157</v>
+        <v>70</v>
       </c>
       <c r="H60" t="s">
-        <v>199</v>
+        <v>158</v>
       </c>
       <c r="I60" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="J60" t="s">
-        <v>285</v>
-      </c>
-      <c r="K60" s="2">
+        <v>220</v>
+      </c>
+      <c r="K60" t="s">
+        <v>287</v>
+      </c>
+      <c r="L60" s="2">
         <v>45840</v>
       </c>
-      <c r="L60" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M60" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -6621,34 +6785,37 @@
         <v>59</v>
       </c>
       <c r="D61">
+        <v>59</v>
+      </c>
+      <c r="E61">
         <v>61</v>
       </c>
-      <c r="E61">
+      <c r="F61">
         <v>206</v>
       </c>
-      <c r="F61" t="s">
-        <v>70</v>
-      </c>
       <c r="G61" t="s">
-        <v>158</v>
+        <v>71</v>
       </c>
       <c r="H61" t="s">
-        <v>205</v>
+        <v>159</v>
       </c>
       <c r="I61" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="J61" t="s">
-        <v>286</v>
-      </c>
-      <c r="K61" s="2">
+        <v>227</v>
+      </c>
+      <c r="K61" t="s">
+        <v>288</v>
+      </c>
+      <c r="L61" s="2">
         <v>45841</v>
       </c>
-      <c r="L61" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M61" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -6659,34 +6826,37 @@
         <v>60</v>
       </c>
       <c r="D62">
+        <v>60</v>
+      </c>
+      <c r="E62">
         <v>62</v>
       </c>
-      <c r="E62">
+      <c r="F62">
         <v>428</v>
       </c>
-      <c r="F62" t="s">
-        <v>71</v>
-      </c>
       <c r="G62" t="s">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="H62" t="s">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="I62" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="J62" t="s">
-        <v>287</v>
-      </c>
-      <c r="K62" s="2">
+        <v>221</v>
+      </c>
+      <c r="K62" t="s">
+        <v>289</v>
+      </c>
+      <c r="L62" s="2">
         <v>45842</v>
       </c>
-      <c r="L62" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M62" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -6697,34 +6867,37 @@
         <v>61</v>
       </c>
       <c r="D63">
+        <v>61</v>
+      </c>
+      <c r="E63">
         <v>63</v>
       </c>
-      <c r="E63">
+      <c r="F63">
         <v>217</v>
       </c>
-      <c r="F63" t="s">
-        <v>72</v>
-      </c>
       <c r="G63" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="H63" t="s">
-        <v>198</v>
+        <v>161</v>
       </c>
       <c r="I63" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="J63" t="s">
-        <v>288</v>
-      </c>
-      <c r="K63" s="2">
+        <v>219</v>
+      </c>
+      <c r="K63" t="s">
+        <v>290</v>
+      </c>
+      <c r="L63" s="2">
         <v>45840</v>
       </c>
-      <c r="L63" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M63" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -6735,34 +6908,37 @@
         <v>62</v>
       </c>
       <c r="D64">
+        <v>62</v>
+      </c>
+      <c r="E64">
         <v>65</v>
       </c>
-      <c r="E64">
+      <c r="F64">
         <v>71</v>
       </c>
-      <c r="F64" t="s">
-        <v>73</v>
-      </c>
       <c r="G64" t="s">
-        <v>161</v>
+        <v>74</v>
       </c>
       <c r="H64" t="s">
-        <v>204</v>
+        <v>162</v>
       </c>
       <c r="I64" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="J64" t="s">
-        <v>289</v>
-      </c>
-      <c r="K64" s="2">
+        <v>226</v>
+      </c>
+      <c r="K64" t="s">
+        <v>291</v>
+      </c>
+      <c r="L64" s="2">
         <v>45841</v>
       </c>
-      <c r="L64" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M64" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -6773,34 +6949,37 @@
         <v>63</v>
       </c>
       <c r="D65">
+        <v>63</v>
+      </c>
+      <c r="E65">
         <v>66</v>
       </c>
-      <c r="E65">
+      <c r="F65">
         <v>395</v>
       </c>
-      <c r="F65" t="s">
-        <v>74</v>
-      </c>
       <c r="G65" t="s">
-        <v>162</v>
+        <v>75</v>
       </c>
       <c r="H65" t="s">
-        <v>203</v>
+        <v>163</v>
       </c>
       <c r="I65" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="J65" t="s">
-        <v>290</v>
-      </c>
-      <c r="K65" s="2">
+        <v>225</v>
+      </c>
+      <c r="K65" t="s">
+        <v>292</v>
+      </c>
+      <c r="L65" s="2">
         <v>45842</v>
       </c>
-      <c r="L65" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M65" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -6811,34 +6990,37 @@
         <v>64</v>
       </c>
       <c r="D66">
+        <v>64</v>
+      </c>
+      <c r="E66">
         <v>67</v>
       </c>
-      <c r="E66">
+      <c r="F66">
         <v>68</v>
       </c>
-      <c r="F66" t="s">
-        <v>75</v>
-      </c>
       <c r="G66" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="H66" t="s">
-        <v>200</v>
+        <v>164</v>
       </c>
       <c r="I66" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="J66" t="s">
-        <v>291</v>
-      </c>
-      <c r="K66" s="2">
+        <v>221</v>
+      </c>
+      <c r="K66" t="s">
+        <v>293</v>
+      </c>
+      <c r="L66" s="2">
         <v>45842</v>
       </c>
-      <c r="L66" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M66" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -6849,34 +7031,37 @@
         <v>65</v>
       </c>
       <c r="D67">
+        <v>65</v>
+      </c>
+      <c r="E67">
         <v>68</v>
       </c>
-      <c r="E67">
+      <c r="F67">
         <v>137</v>
       </c>
-      <c r="F67" t="s">
-        <v>76</v>
-      </c>
       <c r="G67" t="s">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="H67" t="s">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="I67" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="J67" t="s">
-        <v>292</v>
-      </c>
-      <c r="K67" s="2">
+        <v>227</v>
+      </c>
+      <c r="K67" t="s">
+        <v>294</v>
+      </c>
+      <c r="L67" s="2">
         <v>45841</v>
       </c>
-      <c r="L67" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M67" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -6887,34 +7072,37 @@
         <v>66</v>
       </c>
       <c r="D68">
+        <v>66</v>
+      </c>
+      <c r="E68">
         <v>70</v>
       </c>
-      <c r="E68">
+      <c r="F68">
         <v>74</v>
       </c>
-      <c r="F68" t="s">
-        <v>77</v>
-      </c>
       <c r="G68" t="s">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="H68" t="s">
-        <v>205</v>
+        <v>166</v>
       </c>
       <c r="I68" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="J68" t="s">
-        <v>293</v>
-      </c>
-      <c r="K68" s="2">
+        <v>227</v>
+      </c>
+      <c r="K68" t="s">
+        <v>295</v>
+      </c>
+      <c r="L68" s="2">
         <v>45841</v>
       </c>
-      <c r="L68" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M68" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -6925,34 +7113,37 @@
         <v>67</v>
       </c>
       <c r="D69">
+        <v>67</v>
+      </c>
+      <c r="E69">
         <v>71</v>
       </c>
-      <c r="E69">
+      <c r="F69">
         <v>278</v>
       </c>
-      <c r="F69" t="s">
-        <v>78</v>
-      </c>
       <c r="G69" t="s">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="H69" t="s">
-        <v>204</v>
+        <v>167</v>
       </c>
       <c r="I69" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="J69" t="s">
-        <v>294</v>
-      </c>
-      <c r="K69" s="2">
+        <v>226</v>
+      </c>
+      <c r="K69" t="s">
+        <v>296</v>
+      </c>
+      <c r="L69" s="2">
         <v>45841</v>
       </c>
-      <c r="L69" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M69" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -6963,34 +7154,37 @@
         <v>68</v>
       </c>
       <c r="D70">
+        <v>68</v>
+      </c>
+      <c r="E70">
         <v>72</v>
       </c>
-      <c r="E70">
+      <c r="F70">
         <v>299</v>
       </c>
-      <c r="F70" t="s">
-        <v>79</v>
-      </c>
       <c r="G70" t="s">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="H70" t="s">
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="I70" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="J70" t="s">
-        <v>295</v>
-      </c>
-      <c r="K70" s="2">
+        <v>226</v>
+      </c>
+      <c r="K70" t="s">
+        <v>297</v>
+      </c>
+      <c r="L70" s="2">
         <v>45841</v>
       </c>
-      <c r="L70" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M70" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -7001,34 +7195,37 @@
         <v>69</v>
       </c>
       <c r="D71">
+        <v>69</v>
+      </c>
+      <c r="E71">
         <v>73</v>
       </c>
-      <c r="E71">
+      <c r="F71">
         <v>313</v>
       </c>
-      <c r="F71" t="s">
-        <v>80</v>
-      </c>
       <c r="G71" t="s">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s">
-        <v>203</v>
+        <v>169</v>
       </c>
       <c r="I71" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="J71" t="s">
-        <v>296</v>
-      </c>
-      <c r="K71" s="2">
+        <v>225</v>
+      </c>
+      <c r="K71" t="s">
+        <v>298</v>
+      </c>
+      <c r="L71" s="2">
         <v>45842</v>
       </c>
-      <c r="L71" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M71" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -7039,34 +7236,37 @@
         <v>70</v>
       </c>
       <c r="D72">
+        <v>70</v>
+      </c>
+      <c r="E72">
         <v>74</v>
       </c>
-      <c r="E72">
+      <c r="F72">
         <v>145</v>
       </c>
-      <c r="F72" t="s">
-        <v>81</v>
-      </c>
       <c r="G72" t="s">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="H72" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="I72" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="J72" t="s">
-        <v>297</v>
-      </c>
-      <c r="K72" s="2">
+        <v>217</v>
+      </c>
+      <c r="K72" t="s">
+        <v>299</v>
+      </c>
+      <c r="L72" s="2">
         <v>45842</v>
       </c>
-      <c r="L72" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M72" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -7077,34 +7277,37 @@
         <v>71</v>
       </c>
       <c r="D73">
+        <v>71</v>
+      </c>
+      <c r="E73">
         <v>75</v>
       </c>
-      <c r="E73">
+      <c r="F73">
         <v>453</v>
       </c>
-      <c r="F73" t="s">
-        <v>82</v>
-      </c>
       <c r="G73" t="s">
-        <v>170</v>
+        <v>83</v>
       </c>
       <c r="H73" t="s">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="I73" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="J73" t="s">
-        <v>298</v>
-      </c>
-      <c r="K73" s="2">
+        <v>220</v>
+      </c>
+      <c r="K73" t="s">
+        <v>300</v>
+      </c>
+      <c r="L73" s="2">
         <v>45840</v>
       </c>
-      <c r="L73" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M73" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -7115,34 +7318,37 @@
         <v>72</v>
       </c>
       <c r="D74">
+        <v>72</v>
+      </c>
+      <c r="E74">
         <v>76</v>
       </c>
-      <c r="E74">
+      <c r="F74">
         <v>408</v>
       </c>
-      <c r="F74" t="s">
-        <v>83</v>
-      </c>
       <c r="G74" t="s">
-        <v>171</v>
+        <v>84</v>
       </c>
       <c r="H74" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="I74" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="J74" t="s">
-        <v>299</v>
-      </c>
-      <c r="K74" s="2">
+        <v>223</v>
+      </c>
+      <c r="K74" t="s">
+        <v>301</v>
+      </c>
+      <c r="L74" s="2">
         <v>45841</v>
       </c>
-      <c r="L74" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M74" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -7153,34 +7359,37 @@
         <v>73</v>
       </c>
       <c r="D75">
+        <v>73</v>
+      </c>
+      <c r="E75">
         <v>77</v>
       </c>
-      <c r="E75">
+      <c r="F75">
         <v>79</v>
       </c>
-      <c r="F75" t="s">
-        <v>84</v>
-      </c>
       <c r="G75" t="s">
-        <v>172</v>
+        <v>85</v>
       </c>
       <c r="H75" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="I75" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="J75" t="s">
-        <v>300</v>
-      </c>
-      <c r="K75" s="2">
+        <v>225</v>
+      </c>
+      <c r="K75" t="s">
+        <v>302</v>
+      </c>
+      <c r="L75" s="2">
         <v>45842</v>
       </c>
-      <c r="L75" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M75" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -7191,34 +7400,37 @@
         <v>74</v>
       </c>
       <c r="D76">
+        <v>74</v>
+      </c>
+      <c r="E76">
         <v>78</v>
       </c>
-      <c r="E76">
+      <c r="F76">
         <v>456</v>
       </c>
-      <c r="F76" t="s">
-        <v>85</v>
-      </c>
       <c r="G76" t="s">
-        <v>173</v>
+        <v>86</v>
       </c>
       <c r="H76" t="s">
-        <v>202</v>
+        <v>174</v>
       </c>
       <c r="I76" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="J76" t="s">
-        <v>301</v>
-      </c>
-      <c r="K76" s="2">
+        <v>224</v>
+      </c>
+      <c r="K76" t="s">
+        <v>303</v>
+      </c>
+      <c r="L76" s="2">
         <v>45841</v>
       </c>
-      <c r="L76" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M76" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -7229,34 +7441,37 @@
         <v>75</v>
       </c>
       <c r="D77">
+        <v>75</v>
+      </c>
+      <c r="E77">
         <v>79</v>
       </c>
-      <c r="E77">
+      <c r="F77">
         <v>5</v>
       </c>
-      <c r="F77" t="s">
-        <v>86</v>
-      </c>
       <c r="G77" t="s">
-        <v>174</v>
+        <v>87</v>
       </c>
       <c r="H77" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="I77" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="J77" t="s">
-        <v>302</v>
-      </c>
-      <c r="K77" s="2">
+        <v>220</v>
+      </c>
+      <c r="K77" t="s">
+        <v>304</v>
+      </c>
+      <c r="L77" s="2">
         <v>45840</v>
       </c>
-      <c r="L77" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M77" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -7267,34 +7482,37 @@
         <v>76</v>
       </c>
       <c r="D78">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E78">
         <v>80</v>
       </c>
-      <c r="F78" t="s">
-        <v>87</v>
+      <c r="F78">
+        <v>80</v>
       </c>
       <c r="G78" t="s">
-        <v>175</v>
+        <v>88</v>
       </c>
       <c r="H78" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="I78" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="J78" t="s">
-        <v>303</v>
-      </c>
-      <c r="K78" s="2">
+        <v>217</v>
+      </c>
+      <c r="K78" t="s">
+        <v>305</v>
+      </c>
+      <c r="L78" s="2">
         <v>45842</v>
       </c>
-      <c r="L78" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M78" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -7305,34 +7523,37 @@
         <v>77</v>
       </c>
       <c r="D79">
+        <v>77</v>
+      </c>
+      <c r="E79">
         <v>81</v>
       </c>
-      <c r="E79">
+      <c r="F79">
         <v>180</v>
       </c>
-      <c r="F79" t="s">
-        <v>88</v>
-      </c>
       <c r="G79" t="s">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="H79" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="I79" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="J79" t="s">
-        <v>304</v>
-      </c>
-      <c r="K79" s="2">
+        <v>227</v>
+      </c>
+      <c r="K79" t="s">
+        <v>306</v>
+      </c>
+      <c r="L79" s="2">
         <v>45841</v>
       </c>
-      <c r="L79" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M79" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -7343,34 +7564,37 @@
         <v>78</v>
       </c>
       <c r="D80">
+        <v>78</v>
+      </c>
+      <c r="E80">
         <v>82</v>
       </c>
-      <c r="E80">
+      <c r="F80">
         <v>48</v>
       </c>
-      <c r="F80" t="s">
-        <v>89</v>
-      </c>
       <c r="G80" t="s">
-        <v>177</v>
+        <v>90</v>
       </c>
       <c r="H80" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="I80" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="J80" t="s">
-        <v>305</v>
-      </c>
-      <c r="K80" s="2">
+        <v>218</v>
+      </c>
+      <c r="K80" t="s">
+        <v>307</v>
+      </c>
+      <c r="L80" s="2">
         <v>45840</v>
       </c>
-      <c r="L80" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M80" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -7381,34 +7605,37 @@
         <v>79</v>
       </c>
       <c r="D81">
+        <v>79</v>
+      </c>
+      <c r="E81">
         <v>83</v>
       </c>
-      <c r="E81">
+      <c r="F81">
         <v>339</v>
       </c>
-      <c r="F81" t="s">
-        <v>90</v>
-      </c>
       <c r="G81" t="s">
-        <v>178</v>
+        <v>91</v>
       </c>
       <c r="H81" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="I81" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="J81" t="s">
-        <v>306</v>
-      </c>
-      <c r="K81" s="2">
+        <v>223</v>
+      </c>
+      <c r="K81" t="s">
+        <v>308</v>
+      </c>
+      <c r="L81" s="2">
         <v>45841</v>
       </c>
-      <c r="L81" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M81" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -7419,34 +7646,37 @@
         <v>80</v>
       </c>
       <c r="D82">
+        <v>80</v>
+      </c>
+      <c r="E82">
         <v>84</v>
       </c>
-      <c r="E82">
+      <c r="F82">
         <v>187</v>
       </c>
-      <c r="F82" t="s">
-        <v>91</v>
-      </c>
       <c r="G82" t="s">
-        <v>179</v>
+        <v>92</v>
       </c>
       <c r="H82" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="I82" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="J82" t="s">
-        <v>307</v>
-      </c>
-      <c r="K82" s="2">
+        <v>218</v>
+      </c>
+      <c r="K82" t="s">
+        <v>309</v>
+      </c>
+      <c r="L82" s="2">
         <v>45840</v>
       </c>
-      <c r="L82" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M82" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -7457,28 +7687,31 @@
         <v>81</v>
       </c>
       <c r="D83">
+        <v>81</v>
+      </c>
+      <c r="E83">
         <v>85</v>
       </c>
-      <c r="E83">
+      <c r="F83">
         <v>457</v>
       </c>
-      <c r="F83" t="s">
-        <v>92</v>
-      </c>
       <c r="G83" t="s">
-        <v>180</v>
+        <v>93</v>
       </c>
       <c r="H83" t="s">
-        <v>196</v>
-      </c>
-      <c r="J83" t="s">
-        <v>308</v>
-      </c>
-      <c r="L83" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
+        <v>181</v>
+      </c>
+      <c r="I83" t="s">
+        <v>197</v>
+      </c>
+      <c r="K83" t="s">
+        <v>310</v>
+      </c>
+      <c r="M83" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -7489,34 +7722,37 @@
         <v>82</v>
       </c>
       <c r="D84">
+        <v>82</v>
+      </c>
+      <c r="E84">
         <v>86</v>
       </c>
-      <c r="E84">
+      <c r="F84">
         <v>82</v>
       </c>
-      <c r="F84" t="s">
-        <v>93</v>
-      </c>
       <c r="G84" t="s">
-        <v>181</v>
+        <v>94</v>
       </c>
       <c r="H84" t="s">
-        <v>359</v>
+        <v>182</v>
       </c>
       <c r="I84" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="J84" t="s">
-        <v>309</v>
-      </c>
-      <c r="K84" s="2">
+        <v>228</v>
+      </c>
+      <c r="K84" t="s">
+        <v>311</v>
+      </c>
+      <c r="L84" s="2">
         <v>45842</v>
       </c>
-      <c r="L84" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M84" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -7527,34 +7763,37 @@
         <v>83</v>
       </c>
       <c r="D85">
+        <v>83</v>
+      </c>
+      <c r="E85">
         <v>87</v>
       </c>
-      <c r="E85">
+      <c r="F85">
         <v>330</v>
       </c>
-      <c r="F85" t="s">
-        <v>94</v>
-      </c>
       <c r="G85" t="s">
-        <v>182</v>
+        <v>95</v>
       </c>
       <c r="H85" t="s">
-        <v>359</v>
+        <v>183</v>
       </c>
       <c r="I85" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="J85" t="s">
-        <v>310</v>
-      </c>
-      <c r="K85" s="2">
+        <v>228</v>
+      </c>
+      <c r="K85" t="s">
+        <v>312</v>
+      </c>
+      <c r="L85" s="2">
         <v>45842</v>
       </c>
-      <c r="L85" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M85" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -7565,34 +7804,37 @@
         <v>84</v>
       </c>
       <c r="D86">
+        <v>84</v>
+      </c>
+      <c r="E86">
         <v>88</v>
       </c>
-      <c r="E86">
+      <c r="F86">
         <v>389</v>
       </c>
-      <c r="F86" t="s">
-        <v>95</v>
-      </c>
       <c r="G86" t="s">
-        <v>183</v>
+        <v>96</v>
       </c>
       <c r="H86" t="s">
-        <v>359</v>
+        <v>184</v>
       </c>
       <c r="I86" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="J86" t="s">
-        <v>311</v>
-      </c>
-      <c r="K86" s="2">
+        <v>228</v>
+      </c>
+      <c r="K86" t="s">
+        <v>313</v>
+      </c>
+      <c r="L86" s="2">
         <v>45842</v>
       </c>
-      <c r="L86" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M86" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -7603,34 +7845,37 @@
         <v>85</v>
       </c>
       <c r="D87">
+        <v>85</v>
+      </c>
+      <c r="E87">
         <v>89</v>
       </c>
-      <c r="E87">
+      <c r="F87">
         <v>427</v>
       </c>
-      <c r="F87" t="s">
-        <v>96</v>
-      </c>
       <c r="G87" t="s">
-        <v>184</v>
+        <v>97</v>
       </c>
       <c r="H87" t="s">
-        <v>359</v>
+        <v>185</v>
       </c>
       <c r="I87" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="J87" t="s">
-        <v>312</v>
-      </c>
-      <c r="K87" s="2">
+        <v>228</v>
+      </c>
+      <c r="K87" t="s">
+        <v>314</v>
+      </c>
+      <c r="L87" s="2">
         <v>45842</v>
       </c>
-      <c r="L87" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M87" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -7641,34 +7886,37 @@
         <v>86</v>
       </c>
       <c r="D88">
+        <v>86</v>
+      </c>
+      <c r="E88">
         <v>90</v>
       </c>
-      <c r="E88">
+      <c r="F88">
         <v>445</v>
       </c>
-      <c r="F88" t="s">
-        <v>97</v>
-      </c>
       <c r="G88" t="s">
-        <v>185</v>
+        <v>98</v>
       </c>
       <c r="H88" t="s">
+        <v>186</v>
+      </c>
+      <c r="I88" t="s">
+        <v>207</v>
+      </c>
+      <c r="J88" t="s">
+        <v>228</v>
+      </c>
+      <c r="K88" t="s">
+        <v>315</v>
+      </c>
+      <c r="L88" s="2">
+        <v>45842</v>
+      </c>
+      <c r="M88" t="s">
         <v>359</v>
       </c>
-      <c r="I88" t="s">
-        <v>226</v>
-      </c>
-      <c r="J88" t="s">
-        <v>313</v>
-      </c>
-      <c r="K88" s="2">
-        <v>45842</v>
-      </c>
-      <c r="L88" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="89" spans="1:13">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -7679,31 +7927,34 @@
         <v>87</v>
       </c>
       <c r="D89">
+        <v>87</v>
+      </c>
+      <c r="E89">
         <v>91</v>
       </c>
-      <c r="E89">
+      <c r="F89">
         <v>458</v>
       </c>
-      <c r="F89" t="s">
-        <v>98</v>
-      </c>
       <c r="G89" t="s">
-        <v>186</v>
+        <v>99</v>
       </c>
       <c r="H89" t="s">
-        <v>359</v>
+        <v>187</v>
       </c>
       <c r="I89" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="J89" t="s">
-        <v>314</v>
-      </c>
-      <c r="K89" s="2">
+        <v>228</v>
+      </c>
+      <c r="K89" t="s">
+        <v>316</v>
+      </c>
+      <c r="L89" s="2">
         <v>45842</v>
       </c>
-      <c r="L89" t="s">
-        <v>357</v>
+      <c r="M89" t="s">
+        <v>360</v>
       </c>
     </row>
   </sheetData>

--- a/images/events/cf25dat.xlsx
+++ b/images/events/cf25dat.xlsx
@@ -1,29 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10714"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hsg/tprojs/clementinec.github.io/images/events/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBAD9BC4-B69F-D148-ACE1-7FC687653444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="660" windowWidth="25480" windowHeight="20760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="361">
-  <si>
-    <t>Unnamed: 0.2</t>
-  </si>
-  <si>
-    <t>Unnamed: 0.1</t>
-  </si>
-  <si>
-    <t>Unnamed: 0</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="358">
   <si>
     <t>index</t>
   </si>
@@ -268,9 +265,6 @@
     <t>DEEP PERCEPTUAL URBAN FORM</t>
   </si>
   <si>
-    <t>FROM TRADITION TO COMPUTATION: ADAPTIVE CERAMIC ‎FAÇADES INSPIRED BY PERSIAN ICE CAVES (YAKHCHALS) FOR ‎PASSIVE COOLING</t>
-  </si>
-  <si>
     <t>CONSOLIDATED EMPIRICAL BIO-MATERIAL REPOSITORY</t>
   </si>
   <si>
@@ -290,9 +284,6 @@
   </si>
   <si>
     <t>A FABRICATION GRAMMAR FOR ROBOTIC SAND PACKING:  FROM PRECISE ACTIONS TO EMERGENT SHAPES AND PATTERNS</t>
-  </si>
-  <si>
-    <t>COLLABORATIVE DEVELOPMENT OF EARTHQUAKE-RESISTANT AND VARIABLE 3D PRINTED HOUSING</t>
   </si>
   <si>
     <t>AUGMENTING IFC-BASED BIM MODELS FOR GRAPH NEURAL NETWORK
@@ -326,6 +317,11 @@
 </t>
   </si>
   <si>
+    <t>A Full-Process Digital Method for Recursive Geometric
+Structure and Machining Parameter Generation Targeting the
+Reutilization of Curved Timber</t>
+  </si>
+  <si>
     <t>Zixi Zhang, Wenshuo Zhang and Runjia Tian</t>
   </si>
   <si>
@@ -371,9 +367,6 @@
     <t>Chen-An Lee and June-Hao Hou</t>
   </si>
   <si>
-    <t>Haojie Fan, Xinyue Xia, Shunuo Li, Huangyan Zheng, Haoyi Xu and Sining Wang</t>
-  </si>
-  <si>
     <t>Juan Jose Castellon</t>
   </si>
   <si>
@@ -542,12 +535,6 @@
     <t>Chee Meng Chan and Frederick Kim</t>
   </si>
   <si>
-    <t>Maryam Badiei, Abolhassan Pishahang and Milad Heiranipour</t>
-  </si>
-  <si>
-    <t>M. Hank Haeusler, Azia Carrother and Cristina Ramos Jaime</t>
-  </si>
-  <si>
     <t>Li Zhang, Jiawei Wang, Zhicheng Wang, Yuetong Wu, Han Li and Bo Gao</t>
   </si>
   <si>
@@ -564,9 +551,6 @@
   </si>
   <si>
     <t>Kieron Cook and Benay Gursoy</t>
-  </si>
-  <si>
-    <t>Rodrigo Garcia-Alvarado</t>
   </si>
   <si>
     <t>Matthias Hornung, Markus Renner, Diellza Elshani, Mathias
@@ -595,6 +579,10 @@
   </si>
   <si>
     <t>Tejas Chavan, Houssame E. Hsain, Camiel Weijenberg and Sayjel V. Patel</t>
+  </si>
+  <si>
+    <t>Shenzhou Dai, Sihang Liu, Haojun Wang, Yulin Chen and
+Zixiong Lin</t>
   </si>
   <si>
     <t>PROMPTING ARCHITECTURE</t>
@@ -3130,37 +3118,6 @@
 evoke specific responses from their inhabitants.</t>
   </si>
   <si>
-    <t>This study investigates the adaptation of Yakhchal-inspired
-passive cooling strat-‎egies into modern ceramic façade
-systems. Yakhchals, ancient Persian icehouses, ‎utilized
-conical geometries, thermal mass, and natural ventilation
-for effective ‎cooling in arid climates. Inspired by these
-principles, modular cone-shaped ce-‎ramic tiles were
-designed to optimize shading and airflow, reducing solar
-heat ‎gain and improving building energy performance. Using
-Rhinoceros 3D for de-‎sign and ClimateStudio for
-simulation, five façade configurations were evaluated,
-‎including a benchmark flat surface and tile
-implementations on south, west, east, ‎and three façades
-simultaneously. Results showed a 19% reduction in energy
-use ‎intensity (EUI) and a 19.8% improvement in thermal
-comfort with the three-‎façade configuration. The east
-façade alone achieved a 60.5% reduction in solar ‎radiation
-absorption, demonstrating the tiles' effectiveness in
-managing solar gain. ‎Fabrication employed 3D-printed molds
-and hand-built clay tiles to test structural ‎integrity and
-aesthetic potential. These experiments provided a
-foundation for fu-‎ture work using advanced techniques like
-robotic arms and 3D clay printing to ‎create lightweight,
-geometrically optimized designs. This research bridges
-ver-‎nacular architecture and computational innovation,
-demonstrating how traditional ‎knowledge can inspire
-sustainable, energy-efficient solutions for modern façade
-‎design. The Yakhchal-inspired tiles offer a promising
-approach to reducing ener-‎gy consumption and enhancing
-thermal comfort in hot climates.‎</t>
-  </si>
-  <si>
     <t>This paper introduces mycelium-based composites as
 innovative, low-emission materials with potential
 applications in the built environment. With global
@@ -3383,46 +3340,6 @@
 through this process, culminating in cast concrete panels
 that demonstrate the potentials of this reconfigura-ble and
 reusable formwork system.</t>
-  </si>
-  <si>
-    <t>3D printed construction is a promising technology for
-housing, but it must address challenges related to its
-application and broader dissemination. This paper presents
-the multidisciplinary and multi-institutional development
-of a 3D printed housing prototype, incorporating seismic
-resistance strategies and flexible design programming,
-aimed at promoting the adoption of this technology in a
-country prone to earthquakes, climatic variability, and
-significant housing demand.
-The project leverages automated printing equipment,
-structural capacity analysis, and adaptable programming of
-architectural forms to suit diverse geographical and
-functional conditions, while also integrating with
-traditional construction processes. As a result, a
-generative design system for 3D-printed housing forms has
-been established, alongside a comprehensive workflow for
-BIM modeling and the toolpath programming. Additionally,
-the project has developed a reliable procedure for material
-preparation and verified printing techniques for
-residential-height walls, along with strategies for
-structural reinforcement, thermal insulation,
-transportation, and on-site assembly.
-Moreover, the initiative includes a thoroughly a plan for
-foundations, roofing, installations, and housing finishes.
-Ongoing environmental monitoring and displacement tracking
-for seismic performance will provide insights for adjusting
-designs to varying geographies and expanding architectural
-possibilities.
-This work has brought together architects, builders, and
-structural, mechanical, and electronic engineers, all
-contributing to the design, programming, execution and
-management. Collaboration agreements, comprehensive
-documentation, product testing, and equipment validation
-have been key components of the project, creating new
-avenues for university research and advancing the
-capabilities of participating organizations and
-professionals. Ultimately, this project opens a new horizon
-for technological advancement in construction.</t>
   </si>
   <si>
     <t>Building Information Modeling (BIM) and Industry Foundation
@@ -3823,6 +3740,40 @@
 in architectural education and practice.</t>
   </si>
   <si>
+    <t>The commercial wood processing industry, driven by North
+American construction, generates a substantial amount of
+by-products annually, including branches, bark, wood
+shavings, and sawdust. Building upon previous practices in
+reusing wood by-products, this study focuses on optimizing
+the utilization of curved timber generated during the
+logging process. A computational method is proposed to
+support the fabrication of non-standard wooden products
+using robotic arms or collaborative robots for future
+applications. This method facilitates the generation and
+visualization of structural schemes and construction
+parameters for the primary framework. The approach relies
+on GHPython components and is implemented through three key
+stages: a three-dimensional posture brute-force search
+based on fixed angle increments, structural combination
+solving using the SymPy computational library, and node
+visualization and generation on the Grasshopper platform.
+These steps enable the acquisition of manufacturing
+parameters for a stable recursive spatial truss structure
+while maximizing the utilization of raw materials. The
+study significantly enhances computational efficiency and
+validates the structural reliability of the generated
+framework through finite element analysis.</t>
+  </si>
+  <si>
+    <t>7/4/25</t>
+  </si>
+  <si>
+    <t>7/2/25</t>
+  </si>
+  <si>
+    <t>7/3/25</t>
+  </si>
+  <si>
     <t>10:50 - 11:05</t>
   </si>
   <si>
@@ -3859,7 +3810,7 @@
     <t>14:30 - 14:45</t>
   </si>
   <si>
-    <t>16:45 - 17:45</t>
+    <t>1/0/00</t>
   </si>
   <si>
     <t>17:30 - 17:45</t>
@@ -3953,16 +3904,19 @@
   </si>
   <si>
     <t>16:50 - 17:10</t>
+  </si>
+  <si>
+    <t>M. Hank Haeusler, Azia Carrother, Cristina Ramos Jaime, Christopher Bamborough and Ivana Kuzmanovska</t>
+  </si>
+  <si>
+    <t>Xinyue Xia, Haojie Fan, Shunuo Li, Huangyan Zheng, Haoyi Xu and Sining Wang</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4014,25 +3968,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4070,7 +4031,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4104,6 +4065,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4138,9 +4100,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4313,11 +4276,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M89"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J88"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4345,17 +4308,8 @@
       <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -4363,40 +4317,31 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
         <v>403</v>
       </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F2" t="s">
+        <v>181</v>
+      </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="H2" t="s">
-        <v>100</v>
+        <v>222</v>
       </c>
       <c r="I2" t="s">
-        <v>188</v>
+        <v>309</v>
       </c>
       <c r="J2" t="s">
-        <v>208</v>
-      </c>
-      <c r="K2" t="s">
-        <v>229</v>
-      </c>
-      <c r="L2" s="2">
-        <v>45842</v>
-      </c>
-      <c r="M2" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -4404,40 +4349,31 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
         <v>114</v>
       </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3" t="s">
+        <v>182</v>
+      </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>202</v>
       </c>
       <c r="H3" t="s">
-        <v>101</v>
+        <v>223</v>
       </c>
       <c r="I3" t="s">
-        <v>189</v>
+        <v>309</v>
       </c>
       <c r="J3" t="s">
-        <v>209</v>
-      </c>
-      <c r="K3" t="s">
-        <v>230</v>
-      </c>
-      <c r="L3" s="2">
-        <v>45842</v>
-      </c>
-      <c r="M3" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -4445,40 +4381,31 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
         <v>238</v>
       </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4" t="s">
+        <v>183</v>
+      </c>
       <c r="G4" t="s">
-        <v>14</v>
+        <v>203</v>
       </c>
       <c r="H4" t="s">
-        <v>102</v>
+        <v>224</v>
       </c>
       <c r="I4" t="s">
-        <v>190</v>
+        <v>310</v>
       </c>
       <c r="J4" t="s">
-        <v>210</v>
-      </c>
-      <c r="K4" t="s">
-        <v>231</v>
-      </c>
-      <c r="L4" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M4" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -4486,40 +4413,31 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
         <v>231</v>
       </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5" t="s">
+        <v>182</v>
+      </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>202</v>
       </c>
       <c r="H5" t="s">
-        <v>103</v>
+        <v>225</v>
       </c>
       <c r="I5" t="s">
-        <v>189</v>
+        <v>309</v>
       </c>
       <c r="J5" t="s">
-        <v>209</v>
-      </c>
-      <c r="K5" t="s">
-        <v>232</v>
-      </c>
-      <c r="L5" s="2">
-        <v>45842</v>
-      </c>
-      <c r="M5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -4527,40 +4445,31 @@
         <v>4</v>
       </c>
       <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
         <v>444</v>
       </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F6" t="s">
+        <v>181</v>
+      </c>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>201</v>
       </c>
       <c r="H6" t="s">
-        <v>104</v>
+        <v>226</v>
       </c>
       <c r="I6" t="s">
-        <v>188</v>
+        <v>309</v>
       </c>
       <c r="J6" t="s">
-        <v>208</v>
-      </c>
-      <c r="K6" t="s">
-        <v>233</v>
-      </c>
-      <c r="L6" s="2">
-        <v>45842</v>
-      </c>
-      <c r="M6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -4568,40 +4477,31 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7">
         <v>349</v>
       </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s">
+        <v>101</v>
+      </c>
+      <c r="F7" t="s">
+        <v>183</v>
+      </c>
       <c r="G7" t="s">
-        <v>17</v>
+        <v>203</v>
       </c>
       <c r="H7" t="s">
-        <v>105</v>
+        <v>227</v>
       </c>
       <c r="I7" t="s">
-        <v>190</v>
+        <v>310</v>
       </c>
       <c r="J7" t="s">
-        <v>210</v>
-      </c>
-      <c r="K7" t="s">
-        <v>234</v>
-      </c>
-      <c r="L7" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M7" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -4609,40 +4509,31 @@
         <v>6</v>
       </c>
       <c r="C8">
-        <v>6</v>
-      </c>
-      <c r="D8">
-        <v>6</v>
-      </c>
-      <c r="E8">
-        <v>6</v>
-      </c>
-      <c r="F8">
         <v>329</v>
       </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>102</v>
+      </c>
+      <c r="F8" t="s">
+        <v>184</v>
+      </c>
       <c r="G8" t="s">
-        <v>18</v>
+        <v>204</v>
       </c>
       <c r="H8" t="s">
-        <v>106</v>
+        <v>228</v>
       </c>
       <c r="I8" t="s">
-        <v>191</v>
+        <v>311</v>
       </c>
       <c r="J8" t="s">
-        <v>211</v>
-      </c>
-      <c r="K8" t="s">
-        <v>235</v>
-      </c>
-      <c r="L8" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M8" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -4650,40 +4541,31 @@
         <v>7</v>
       </c>
       <c r="C9">
-        <v>7</v>
-      </c>
-      <c r="D9">
-        <v>7</v>
-      </c>
-      <c r="E9">
-        <v>7</v>
-      </c>
-      <c r="F9">
         <v>148</v>
       </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
+        <v>103</v>
+      </c>
+      <c r="F9" t="s">
+        <v>184</v>
+      </c>
       <c r="G9" t="s">
-        <v>19</v>
+        <v>204</v>
       </c>
       <c r="H9" t="s">
-        <v>107</v>
+        <v>229</v>
       </c>
       <c r="I9" t="s">
-        <v>191</v>
+        <v>311</v>
       </c>
       <c r="J9" t="s">
-        <v>211</v>
-      </c>
-      <c r="K9" t="s">
-        <v>236</v>
-      </c>
-      <c r="L9" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M9" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -4691,40 +4573,31 @@
         <v>8</v>
       </c>
       <c r="C10">
-        <v>8</v>
-      </c>
-      <c r="D10">
-        <v>8</v>
-      </c>
-      <c r="E10">
-        <v>8</v>
-      </c>
-      <c r="F10">
         <v>230</v>
       </c>
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s">
+        <v>104</v>
+      </c>
+      <c r="F10" t="s">
+        <v>182</v>
+      </c>
       <c r="G10" t="s">
-        <v>20</v>
+        <v>202</v>
       </c>
       <c r="H10" t="s">
-        <v>108</v>
+        <v>230</v>
       </c>
       <c r="I10" t="s">
-        <v>189</v>
+        <v>309</v>
       </c>
       <c r="J10" t="s">
-        <v>209</v>
-      </c>
-      <c r="K10" t="s">
-        <v>237</v>
-      </c>
-      <c r="L10" s="2">
-        <v>45842</v>
-      </c>
-      <c r="M10" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -4732,40 +4605,31 @@
         <v>9</v>
       </c>
       <c r="C11">
-        <v>9</v>
-      </c>
-      <c r="D11">
-        <v>9</v>
-      </c>
-      <c r="E11">
-        <v>9</v>
-      </c>
-      <c r="F11">
         <v>253</v>
       </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>105</v>
+      </c>
+      <c r="F11" t="s">
+        <v>181</v>
+      </c>
       <c r="G11" t="s">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="H11" t="s">
-        <v>109</v>
+        <v>231</v>
       </c>
       <c r="I11" t="s">
-        <v>188</v>
+        <v>309</v>
       </c>
       <c r="J11" t="s">
-        <v>208</v>
-      </c>
-      <c r="K11" t="s">
-        <v>238</v>
-      </c>
-      <c r="L11" s="2">
-        <v>45842</v>
-      </c>
-      <c r="M11" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -4773,40 +4637,31 @@
         <v>10</v>
       </c>
       <c r="C12">
-        <v>10</v>
-      </c>
-      <c r="D12">
-        <v>10</v>
-      </c>
-      <c r="E12">
-        <v>10</v>
-      </c>
-      <c r="F12">
         <v>55</v>
       </c>
+      <c r="D12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" t="s">
+        <v>106</v>
+      </c>
+      <c r="F12" t="s">
+        <v>184</v>
+      </c>
       <c r="G12" t="s">
-        <v>22</v>
+        <v>204</v>
       </c>
       <c r="H12" t="s">
-        <v>110</v>
+        <v>232</v>
       </c>
       <c r="I12" t="s">
-        <v>191</v>
+        <v>311</v>
       </c>
       <c r="J12" t="s">
-        <v>211</v>
-      </c>
-      <c r="K12" t="s">
-        <v>239</v>
-      </c>
-      <c r="L12" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M12" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -4814,40 +4669,31 @@
         <v>11</v>
       </c>
       <c r="C13">
-        <v>11</v>
-      </c>
-      <c r="D13">
-        <v>11</v>
-      </c>
-      <c r="E13">
-        <v>11</v>
-      </c>
-      <c r="F13">
         <v>262</v>
       </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" t="s">
+        <v>107</v>
+      </c>
+      <c r="F13" t="s">
+        <v>184</v>
+      </c>
       <c r="G13" t="s">
-        <v>23</v>
+        <v>204</v>
       </c>
       <c r="H13" t="s">
-        <v>111</v>
+        <v>233</v>
       </c>
       <c r="I13" t="s">
-        <v>191</v>
+        <v>311</v>
       </c>
       <c r="J13" t="s">
-        <v>211</v>
-      </c>
-      <c r="K13" t="s">
-        <v>240</v>
-      </c>
-      <c r="L13" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M13" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -4855,40 +4701,31 @@
         <v>12</v>
       </c>
       <c r="C14">
-        <v>12</v>
-      </c>
-      <c r="D14">
-        <v>12</v>
-      </c>
-      <c r="E14">
-        <v>12</v>
-      </c>
-      <c r="F14">
         <v>250</v>
       </c>
+      <c r="D14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" t="s">
+        <v>108</v>
+      </c>
+      <c r="F14" t="s">
+        <v>185</v>
+      </c>
       <c r="G14" t="s">
-        <v>24</v>
+        <v>205</v>
       </c>
       <c r="H14" t="s">
-        <v>112</v>
+        <v>234</v>
       </c>
       <c r="I14" t="s">
-        <v>192</v>
+        <v>311</v>
       </c>
       <c r="J14" t="s">
-        <v>212</v>
-      </c>
-      <c r="K14" t="s">
-        <v>241</v>
-      </c>
-      <c r="L14" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M14" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -4896,40 +4733,31 @@
         <v>13</v>
       </c>
       <c r="C15">
-        <v>13</v>
-      </c>
-      <c r="D15">
-        <v>13</v>
-      </c>
-      <c r="E15">
-        <v>13</v>
-      </c>
-      <c r="F15">
         <v>36</v>
       </c>
+      <c r="D15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" t="s">
+        <v>109</v>
+      </c>
+      <c r="F15" t="s">
+        <v>183</v>
+      </c>
       <c r="G15" t="s">
-        <v>25</v>
+        <v>203</v>
       </c>
       <c r="H15" t="s">
-        <v>113</v>
+        <v>235</v>
       </c>
       <c r="I15" t="s">
-        <v>190</v>
+        <v>310</v>
       </c>
       <c r="J15" t="s">
-        <v>210</v>
-      </c>
-      <c r="K15" t="s">
-        <v>242</v>
-      </c>
-      <c r="L15" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M15" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -4937,40 +4765,31 @@
         <v>14</v>
       </c>
       <c r="C16">
-        <v>14</v>
-      </c>
-      <c r="D16">
-        <v>14</v>
-      </c>
-      <c r="E16">
-        <v>14</v>
-      </c>
-      <c r="F16">
         <v>431</v>
       </c>
+      <c r="D16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" t="s">
+        <v>110</v>
+      </c>
+      <c r="F16" t="s">
+        <v>186</v>
+      </c>
       <c r="G16" t="s">
-        <v>26</v>
+        <v>206</v>
       </c>
       <c r="H16" t="s">
-        <v>114</v>
+        <v>236</v>
       </c>
       <c r="I16" t="s">
-        <v>193</v>
+        <v>311</v>
       </c>
       <c r="J16" t="s">
-        <v>213</v>
-      </c>
-      <c r="K16" t="s">
-        <v>243</v>
-      </c>
-      <c r="L16" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M16" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -4978,40 +4797,31 @@
         <v>15</v>
       </c>
       <c r="C17">
-        <v>15</v>
-      </c>
-      <c r="D17">
-        <v>15</v>
-      </c>
-      <c r="E17">
-        <v>15</v>
-      </c>
-      <c r="F17">
         <v>132</v>
       </c>
+      <c r="D17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" t="s">
+        <v>357</v>
+      </c>
+      <c r="F17" t="s">
+        <v>187</v>
+      </c>
       <c r="G17" t="s">
-        <v>27</v>
+        <v>207</v>
       </c>
       <c r="H17" t="s">
-        <v>115</v>
+        <v>237</v>
       </c>
       <c r="I17" t="s">
-        <v>194</v>
+        <v>311</v>
       </c>
       <c r="J17" t="s">
-        <v>214</v>
-      </c>
-      <c r="K17" t="s">
-        <v>244</v>
-      </c>
-      <c r="L17" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M17" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -5019,40 +4829,31 @@
         <v>16</v>
       </c>
       <c r="C18">
-        <v>16</v>
-      </c>
-      <c r="D18">
-        <v>16</v>
-      </c>
-      <c r="E18">
-        <v>16</v>
-      </c>
-      <c r="F18">
         <v>178</v>
       </c>
+      <c r="D18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" t="s">
+        <v>111</v>
+      </c>
+      <c r="F18" t="s">
+        <v>187</v>
+      </c>
       <c r="G18" t="s">
-        <v>28</v>
+        <v>207</v>
       </c>
       <c r="H18" t="s">
-        <v>116</v>
+        <v>238</v>
       </c>
       <c r="I18" t="s">
-        <v>194</v>
+        <v>311</v>
       </c>
       <c r="J18" t="s">
-        <v>214</v>
-      </c>
-      <c r="K18" t="s">
-        <v>245</v>
-      </c>
-      <c r="L18" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M18" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -5060,40 +4861,31 @@
         <v>17</v>
       </c>
       <c r="C19">
-        <v>17</v>
-      </c>
-      <c r="D19">
-        <v>17</v>
-      </c>
-      <c r="E19">
-        <v>17</v>
-      </c>
-      <c r="F19">
         <v>151</v>
       </c>
+      <c r="D19" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" t="s">
+        <v>112</v>
+      </c>
+      <c r="F19" t="s">
+        <v>188</v>
+      </c>
       <c r="G19" t="s">
-        <v>29</v>
+        <v>208</v>
       </c>
       <c r="H19" t="s">
-        <v>117</v>
+        <v>239</v>
       </c>
       <c r="I19" t="s">
-        <v>195</v>
+        <v>310</v>
       </c>
       <c r="J19" t="s">
-        <v>215</v>
-      </c>
-      <c r="K19" t="s">
-        <v>246</v>
-      </c>
-      <c r="L19" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M19" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -5101,40 +4893,31 @@
         <v>18</v>
       </c>
       <c r="C20">
-        <v>18</v>
-      </c>
-      <c r="D20">
-        <v>18</v>
-      </c>
-      <c r="E20">
-        <v>18</v>
-      </c>
-      <c r="F20">
         <v>440</v>
       </c>
+      <c r="D20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" t="s">
+        <v>113</v>
+      </c>
+      <c r="F20" t="s">
+        <v>186</v>
+      </c>
       <c r="G20" t="s">
-        <v>30</v>
+        <v>206</v>
       </c>
       <c r="H20" t="s">
-        <v>118</v>
+        <v>240</v>
       </c>
       <c r="I20" t="s">
-        <v>193</v>
+        <v>311</v>
       </c>
       <c r="J20" t="s">
-        <v>213</v>
-      </c>
-      <c r="K20" t="s">
-        <v>247</v>
-      </c>
-      <c r="L20" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M20" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -5142,40 +4925,31 @@
         <v>19</v>
       </c>
       <c r="C21">
-        <v>19</v>
-      </c>
-      <c r="D21">
-        <v>19</v>
-      </c>
-      <c r="E21">
-        <v>19</v>
-      </c>
-      <c r="F21">
         <v>198</v>
       </c>
+      <c r="D21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" t="s">
+        <v>114</v>
+      </c>
+      <c r="F21" t="s">
+        <v>185</v>
+      </c>
       <c r="G21" t="s">
-        <v>31</v>
+        <v>205</v>
       </c>
       <c r="H21" t="s">
-        <v>119</v>
+        <v>241</v>
       </c>
       <c r="I21" t="s">
-        <v>192</v>
+        <v>311</v>
       </c>
       <c r="J21" t="s">
-        <v>212</v>
-      </c>
-      <c r="K21" t="s">
-        <v>248</v>
-      </c>
-      <c r="L21" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M21" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -5183,40 +4957,31 @@
         <v>20</v>
       </c>
       <c r="C22">
-        <v>20</v>
-      </c>
-      <c r="D22">
-        <v>20</v>
-      </c>
-      <c r="E22">
-        <v>20</v>
-      </c>
-      <c r="F22">
         <v>426</v>
       </c>
+      <c r="D22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" t="s">
+        <v>115</v>
+      </c>
+      <c r="F22" t="s">
+        <v>189</v>
+      </c>
       <c r="G22" t="s">
-        <v>32</v>
+        <v>209</v>
       </c>
       <c r="H22" t="s">
-        <v>120</v>
+        <v>242</v>
       </c>
       <c r="I22" t="s">
-        <v>196</v>
+        <v>310</v>
       </c>
       <c r="J22" t="s">
-        <v>216</v>
-      </c>
-      <c r="K22" t="s">
-        <v>249</v>
-      </c>
-      <c r="L22" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M22" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -5224,40 +4989,31 @@
         <v>21</v>
       </c>
       <c r="C23">
-        <v>21</v>
-      </c>
-      <c r="D23">
-        <v>21</v>
-      </c>
-      <c r="E23">
-        <v>21</v>
-      </c>
-      <c r="F23">
         <v>126</v>
       </c>
+      <c r="D23" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" t="s">
+        <v>116</v>
+      </c>
+      <c r="F23" t="s">
+        <v>188</v>
+      </c>
       <c r="G23" t="s">
-        <v>33</v>
+        <v>208</v>
       </c>
       <c r="H23" t="s">
-        <v>121</v>
+        <v>243</v>
       </c>
       <c r="I23" t="s">
-        <v>195</v>
+        <v>310</v>
       </c>
       <c r="J23" t="s">
-        <v>215</v>
-      </c>
-      <c r="K23" t="s">
-        <v>250</v>
-      </c>
-      <c r="L23" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M23" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -5265,40 +5021,31 @@
         <v>22</v>
       </c>
       <c r="C24">
-        <v>22</v>
-      </c>
-      <c r="D24">
-        <v>22</v>
-      </c>
-      <c r="E24">
-        <v>22</v>
-      </c>
-      <c r="F24">
         <v>193</v>
       </c>
+      <c r="D24" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" t="s">
+        <v>117</v>
+      </c>
+      <c r="F24" t="s">
+        <v>187</v>
+      </c>
       <c r="G24" t="s">
-        <v>34</v>
+        <v>207</v>
       </c>
       <c r="H24" t="s">
-        <v>122</v>
+        <v>244</v>
       </c>
       <c r="I24" t="s">
-        <v>194</v>
+        <v>311</v>
       </c>
       <c r="J24" t="s">
-        <v>214</v>
-      </c>
-      <c r="K24" t="s">
-        <v>251</v>
-      </c>
-      <c r="L24" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M24" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -5306,40 +5053,31 @@
         <v>23</v>
       </c>
       <c r="C25">
-        <v>23</v>
-      </c>
-      <c r="D25">
-        <v>23</v>
-      </c>
-      <c r="E25">
-        <v>23</v>
-      </c>
-      <c r="F25">
         <v>134</v>
       </c>
+      <c r="D25" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" t="s">
+        <v>118</v>
+      </c>
+      <c r="F25" t="s">
+        <v>188</v>
+      </c>
       <c r="G25" t="s">
-        <v>35</v>
+        <v>208</v>
       </c>
       <c r="H25" t="s">
-        <v>123</v>
+        <v>245</v>
       </c>
       <c r="I25" t="s">
-        <v>195</v>
+        <v>310</v>
       </c>
       <c r="J25" t="s">
-        <v>215</v>
-      </c>
-      <c r="K25" t="s">
-        <v>252</v>
-      </c>
-      <c r="L25" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M25" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -5347,40 +5085,31 @@
         <v>24</v>
       </c>
       <c r="C26">
-        <v>24</v>
-      </c>
-      <c r="D26">
-        <v>24</v>
-      </c>
-      <c r="E26">
-        <v>24</v>
-      </c>
-      <c r="F26">
         <v>50</v>
       </c>
+      <c r="D26" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" t="s">
+        <v>119</v>
+      </c>
+      <c r="F26" t="s">
+        <v>185</v>
+      </c>
       <c r="G26" t="s">
-        <v>36</v>
+        <v>205</v>
       </c>
       <c r="H26" t="s">
-        <v>124</v>
+        <v>246</v>
       </c>
       <c r="I26" t="s">
-        <v>192</v>
+        <v>311</v>
       </c>
       <c r="J26" t="s">
-        <v>212</v>
-      </c>
-      <c r="K26" t="s">
-        <v>253</v>
-      </c>
-      <c r="L26" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M26" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -5388,40 +5117,31 @@
         <v>25</v>
       </c>
       <c r="C27">
-        <v>25</v>
-      </c>
-      <c r="D27">
-        <v>25</v>
-      </c>
-      <c r="E27">
-        <v>25</v>
-      </c>
-      <c r="F27">
         <v>314</v>
       </c>
+      <c r="D27" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" t="s">
+        <v>120</v>
+      </c>
+      <c r="F27" t="s">
+        <v>186</v>
+      </c>
       <c r="G27" t="s">
-        <v>37</v>
+        <v>206</v>
       </c>
       <c r="H27" t="s">
-        <v>125</v>
+        <v>247</v>
       </c>
       <c r="I27" t="s">
-        <v>193</v>
+        <v>311</v>
       </c>
       <c r="J27" t="s">
-        <v>213</v>
-      </c>
-      <c r="K27" t="s">
-        <v>254</v>
-      </c>
-      <c r="L27" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M27" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -5429,40 +5149,31 @@
         <v>26</v>
       </c>
       <c r="C28">
-        <v>26</v>
-      </c>
-      <c r="D28">
-        <v>26</v>
-      </c>
-      <c r="E28">
-        <v>26</v>
-      </c>
-      <c r="F28">
         <v>386</v>
       </c>
+      <c r="D28" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" t="s">
+        <v>121</v>
+      </c>
+      <c r="F28" t="s">
+        <v>187</v>
+      </c>
       <c r="G28" t="s">
-        <v>38</v>
+        <v>207</v>
       </c>
       <c r="H28" t="s">
-        <v>126</v>
+        <v>248</v>
       </c>
       <c r="I28" t="s">
-        <v>194</v>
+        <v>311</v>
       </c>
       <c r="J28" t="s">
-        <v>214</v>
-      </c>
-      <c r="K28" t="s">
-        <v>255</v>
-      </c>
-      <c r="L28" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M28" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -5470,40 +5181,31 @@
         <v>27</v>
       </c>
       <c r="C29">
-        <v>27</v>
-      </c>
-      <c r="D29">
-        <v>27</v>
-      </c>
-      <c r="E29">
-        <v>27</v>
-      </c>
-      <c r="F29">
         <v>196</v>
       </c>
+      <c r="D29" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" t="s">
+        <v>122</v>
+      </c>
+      <c r="F29" t="s">
+        <v>189</v>
+      </c>
       <c r="G29" t="s">
-        <v>39</v>
+        <v>209</v>
       </c>
       <c r="H29" t="s">
-        <v>127</v>
+        <v>249</v>
       </c>
       <c r="I29" t="s">
-        <v>196</v>
+        <v>310</v>
       </c>
       <c r="J29" t="s">
-        <v>216</v>
-      </c>
-      <c r="K29" t="s">
-        <v>256</v>
-      </c>
-      <c r="L29" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M29" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -5511,40 +5213,31 @@
         <v>28</v>
       </c>
       <c r="C30">
-        <v>28</v>
-      </c>
-      <c r="D30">
-        <v>28</v>
-      </c>
-      <c r="E30">
-        <v>28</v>
-      </c>
-      <c r="F30">
         <v>135</v>
       </c>
+      <c r="D30" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30" t="s">
+        <v>123</v>
+      </c>
+      <c r="F30" t="s">
+        <v>190</v>
+      </c>
       <c r="G30" t="s">
-        <v>40</v>
+        <v>210</v>
       </c>
       <c r="H30" t="s">
-        <v>128</v>
+        <v>250</v>
       </c>
       <c r="I30" t="s">
-        <v>197</v>
+        <v>309</v>
       </c>
       <c r="J30" t="s">
-        <v>217</v>
-      </c>
-      <c r="K30" t="s">
-        <v>257</v>
-      </c>
-      <c r="L30" s="2">
-        <v>45842</v>
-      </c>
-      <c r="M30" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -5552,40 +5245,31 @@
         <v>29</v>
       </c>
       <c r="C31">
-        <v>29</v>
-      </c>
-      <c r="D31">
-        <v>29</v>
-      </c>
-      <c r="E31">
-        <v>29</v>
-      </c>
-      <c r="F31">
         <v>210</v>
       </c>
+      <c r="D31" t="s">
+        <v>38</v>
+      </c>
+      <c r="E31" t="s">
+        <v>124</v>
+      </c>
+      <c r="F31" t="s">
+        <v>186</v>
+      </c>
       <c r="G31" t="s">
-        <v>41</v>
+        <v>206</v>
       </c>
       <c r="H31" t="s">
-        <v>129</v>
+        <v>251</v>
       </c>
       <c r="I31" t="s">
-        <v>193</v>
+        <v>311</v>
       </c>
       <c r="J31" t="s">
-        <v>213</v>
-      </c>
-      <c r="K31" t="s">
-        <v>258</v>
-      </c>
-      <c r="L31" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M31" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -5593,40 +5277,31 @@
         <v>30</v>
       </c>
       <c r="C32">
-        <v>30</v>
-      </c>
-      <c r="D32">
-        <v>30</v>
-      </c>
-      <c r="E32">
-        <v>30</v>
-      </c>
-      <c r="F32">
         <v>162</v>
       </c>
+      <c r="D32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" t="s">
+        <v>125</v>
+      </c>
+      <c r="F32" t="s">
+        <v>191</v>
+      </c>
       <c r="G32" t="s">
-        <v>42</v>
+        <v>211</v>
       </c>
       <c r="H32" t="s">
-        <v>130</v>
+        <v>252</v>
       </c>
       <c r="I32" t="s">
-        <v>198</v>
+        <v>310</v>
       </c>
       <c r="J32" t="s">
-        <v>218</v>
-      </c>
-      <c r="K32" t="s">
-        <v>259</v>
-      </c>
-      <c r="L32" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M32" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -5634,40 +5309,31 @@
         <v>31</v>
       </c>
       <c r="C33">
-        <v>31</v>
-      </c>
-      <c r="D33">
-        <v>31</v>
-      </c>
-      <c r="E33">
-        <v>31</v>
-      </c>
-      <c r="F33">
         <v>169</v>
       </c>
+      <c r="D33" t="s">
+        <v>40</v>
+      </c>
+      <c r="E33" t="s">
+        <v>126</v>
+      </c>
+      <c r="F33" t="s">
+        <v>192</v>
+      </c>
       <c r="G33" t="s">
-        <v>43</v>
+        <v>212</v>
       </c>
       <c r="H33" t="s">
-        <v>131</v>
+        <v>253</v>
       </c>
       <c r="I33" t="s">
-        <v>199</v>
+        <v>310</v>
       </c>
       <c r="J33" t="s">
-        <v>219</v>
-      </c>
-      <c r="K33" t="s">
-        <v>260</v>
-      </c>
-      <c r="L33" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M33" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -5675,40 +5341,31 @@
         <v>32</v>
       </c>
       <c r="C34">
-        <v>32</v>
-      </c>
-      <c r="D34">
-        <v>32</v>
-      </c>
-      <c r="E34">
-        <v>32</v>
-      </c>
-      <c r="F34">
         <v>19</v>
       </c>
+      <c r="D34" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" t="s">
+        <v>127</v>
+      </c>
+      <c r="F34" t="s">
+        <v>190</v>
+      </c>
       <c r="G34" t="s">
-        <v>44</v>
+        <v>210</v>
       </c>
       <c r="H34" t="s">
-        <v>132</v>
+        <v>254</v>
       </c>
       <c r="I34" t="s">
-        <v>197</v>
+        <v>309</v>
       </c>
       <c r="J34" t="s">
-        <v>217</v>
-      </c>
-      <c r="K34" t="s">
-        <v>261</v>
-      </c>
-      <c r="L34" s="2">
-        <v>45842</v>
-      </c>
-      <c r="M34" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -5716,40 +5373,31 @@
         <v>33</v>
       </c>
       <c r="C35">
-        <v>33</v>
-      </c>
-      <c r="D35">
-        <v>33</v>
-      </c>
-      <c r="E35">
-        <v>33</v>
-      </c>
-      <c r="F35">
         <v>240</v>
       </c>
+      <c r="D35" t="s">
+        <v>42</v>
+      </c>
+      <c r="E35" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35" t="s">
+        <v>193</v>
+      </c>
       <c r="G35" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="H35" t="s">
-        <v>133</v>
+        <v>255</v>
       </c>
       <c r="I35" t="s">
-        <v>200</v>
+        <v>310</v>
       </c>
       <c r="J35" t="s">
-        <v>220</v>
-      </c>
-      <c r="K35" t="s">
-        <v>262</v>
-      </c>
-      <c r="L35" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M35" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -5757,40 +5405,31 @@
         <v>34</v>
       </c>
       <c r="C36">
-        <v>34</v>
-      </c>
-      <c r="D36">
-        <v>34</v>
-      </c>
-      <c r="E36">
-        <v>34</v>
-      </c>
-      <c r="F36">
         <v>379</v>
       </c>
+      <c r="D36" t="s">
+        <v>43</v>
+      </c>
+      <c r="E36" t="s">
+        <v>129</v>
+      </c>
+      <c r="F36" t="s">
+        <v>194</v>
+      </c>
       <c r="G36" t="s">
-        <v>46</v>
+        <v>214</v>
       </c>
       <c r="H36" t="s">
-        <v>134</v>
+        <v>256</v>
       </c>
       <c r="I36" t="s">
-        <v>201</v>
+        <v>309</v>
       </c>
       <c r="J36" t="s">
-        <v>221</v>
-      </c>
-      <c r="K36" t="s">
-        <v>263</v>
-      </c>
-      <c r="L36" s="2">
-        <v>45842</v>
-      </c>
-      <c r="M36" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -5798,40 +5437,31 @@
         <v>35</v>
       </c>
       <c r="C37">
-        <v>35</v>
-      </c>
-      <c r="D37">
-        <v>35</v>
-      </c>
-      <c r="E37">
-        <v>35</v>
-      </c>
-      <c r="F37">
         <v>149</v>
       </c>
+      <c r="D37" t="s">
+        <v>44</v>
+      </c>
+      <c r="E37" t="s">
+        <v>130</v>
+      </c>
+      <c r="F37" t="s">
+        <v>195</v>
+      </c>
       <c r="G37" t="s">
-        <v>47</v>
+        <v>215</v>
       </c>
       <c r="H37" t="s">
-        <v>135</v>
+        <v>257</v>
       </c>
       <c r="I37" t="s">
-        <v>202</v>
+        <v>310</v>
       </c>
       <c r="J37" t="s">
-        <v>222</v>
-      </c>
-      <c r="K37" t="s">
-        <v>264</v>
-      </c>
-      <c r="L37" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M37" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -5839,40 +5469,31 @@
         <v>36</v>
       </c>
       <c r="C38">
-        <v>36</v>
-      </c>
-      <c r="D38">
-        <v>36</v>
-      </c>
-      <c r="E38">
-        <v>36</v>
-      </c>
-      <c r="F38">
         <v>87</v>
       </c>
+      <c r="D38" t="s">
+        <v>45</v>
+      </c>
+      <c r="E38" t="s">
+        <v>131</v>
+      </c>
+      <c r="F38" t="s">
+        <v>195</v>
+      </c>
       <c r="G38" t="s">
-        <v>48</v>
+        <v>215</v>
       </c>
       <c r="H38" t="s">
-        <v>136</v>
+        <v>258</v>
       </c>
       <c r="I38" t="s">
-        <v>202</v>
+        <v>310</v>
       </c>
       <c r="J38" t="s">
-        <v>222</v>
-      </c>
-      <c r="K38" t="s">
-        <v>265</v>
-      </c>
-      <c r="L38" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M38" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -5880,40 +5501,31 @@
         <v>37</v>
       </c>
       <c r="C39">
-        <v>37</v>
-      </c>
-      <c r="D39">
-        <v>37</v>
-      </c>
-      <c r="E39">
-        <v>37</v>
-      </c>
-      <c r="F39">
         <v>221</v>
       </c>
+      <c r="D39" t="s">
+        <v>46</v>
+      </c>
+      <c r="E39" t="s">
+        <v>132</v>
+      </c>
+      <c r="F39" t="s">
+        <v>187</v>
+      </c>
       <c r="G39" t="s">
-        <v>49</v>
+        <v>216</v>
       </c>
       <c r="H39" t="s">
-        <v>137</v>
+        <v>259</v>
       </c>
       <c r="I39" t="s">
-        <v>194</v>
+        <v>311</v>
       </c>
       <c r="J39" t="s">
-        <v>223</v>
-      </c>
-      <c r="K39" t="s">
-        <v>266</v>
-      </c>
-      <c r="L39" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M39" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -5921,40 +5533,31 @@
         <v>38</v>
       </c>
       <c r="C40">
-        <v>38</v>
-      </c>
-      <c r="D40">
-        <v>38</v>
-      </c>
-      <c r="E40">
-        <v>38</v>
-      </c>
-      <c r="F40">
         <v>45</v>
       </c>
+      <c r="D40" t="s">
+        <v>47</v>
+      </c>
+      <c r="E40" t="s">
+        <v>133</v>
+      </c>
+      <c r="F40" t="s">
+        <v>196</v>
+      </c>
       <c r="G40" t="s">
-        <v>50</v>
+        <v>217</v>
       </c>
       <c r="H40" t="s">
-        <v>138</v>
+        <v>260</v>
       </c>
       <c r="I40" t="s">
-        <v>203</v>
+        <v>311</v>
       </c>
       <c r="J40" t="s">
-        <v>224</v>
-      </c>
-      <c r="K40" t="s">
-        <v>267</v>
-      </c>
-      <c r="L40" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M40" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -5962,40 +5565,31 @@
         <v>39</v>
       </c>
       <c r="C41">
-        <v>39</v>
-      </c>
-      <c r="D41">
-        <v>39</v>
-      </c>
-      <c r="E41">
-        <v>39</v>
-      </c>
-      <c r="F41">
         <v>141</v>
       </c>
+      <c r="D41" t="s">
+        <v>48</v>
+      </c>
+      <c r="E41" t="s">
+        <v>134</v>
+      </c>
+      <c r="F41" t="s">
+        <v>192</v>
+      </c>
       <c r="G41" t="s">
-        <v>51</v>
+        <v>212</v>
       </c>
       <c r="H41" t="s">
-        <v>139</v>
+        <v>261</v>
       </c>
       <c r="I41" t="s">
-        <v>199</v>
+        <v>310</v>
       </c>
       <c r="J41" t="s">
-        <v>219</v>
-      </c>
-      <c r="K41" t="s">
-        <v>268</v>
-      </c>
-      <c r="L41" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M41" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -6003,40 +5597,31 @@
         <v>40</v>
       </c>
       <c r="C42">
-        <v>40</v>
-      </c>
-      <c r="D42">
-        <v>40</v>
-      </c>
-      <c r="E42">
-        <v>40</v>
-      </c>
-      <c r="F42">
         <v>255</v>
       </c>
+      <c r="D42" t="s">
+        <v>49</v>
+      </c>
+      <c r="E42" t="s">
+        <v>135</v>
+      </c>
+      <c r="F42" t="s">
+        <v>192</v>
+      </c>
       <c r="G42" t="s">
-        <v>52</v>
+        <v>212</v>
       </c>
       <c r="H42" t="s">
-        <v>140</v>
+        <v>262</v>
       </c>
       <c r="I42" t="s">
-        <v>199</v>
+        <v>310</v>
       </c>
       <c r="J42" t="s">
-        <v>219</v>
-      </c>
-      <c r="K42" t="s">
-        <v>269</v>
-      </c>
-      <c r="L42" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M42" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -6044,40 +5629,31 @@
         <v>41</v>
       </c>
       <c r="C43">
-        <v>41</v>
-      </c>
-      <c r="D43">
-        <v>41</v>
-      </c>
-      <c r="E43">
-        <v>41</v>
-      </c>
-      <c r="F43">
         <v>276</v>
       </c>
+      <c r="D43" t="s">
+        <v>50</v>
+      </c>
+      <c r="E43" t="s">
+        <v>136</v>
+      </c>
+      <c r="F43" t="s">
+        <v>194</v>
+      </c>
       <c r="G43" t="s">
-        <v>53</v>
+        <v>214</v>
       </c>
       <c r="H43" t="s">
-        <v>141</v>
+        <v>263</v>
       </c>
       <c r="I43" t="s">
-        <v>201</v>
+        <v>309</v>
       </c>
       <c r="J43" t="s">
-        <v>221</v>
-      </c>
-      <c r="K43" t="s">
-        <v>270</v>
-      </c>
-      <c r="L43" s="2">
-        <v>45842</v>
-      </c>
-      <c r="M43" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -6085,40 +5661,31 @@
         <v>42</v>
       </c>
       <c r="C44">
-        <v>42</v>
-      </c>
-      <c r="D44">
-        <v>42</v>
-      </c>
-      <c r="E44">
-        <v>43</v>
-      </c>
-      <c r="F44">
         <v>304</v>
       </c>
+      <c r="D44" t="s">
+        <v>51</v>
+      </c>
+      <c r="E44" t="s">
+        <v>137</v>
+      </c>
+      <c r="F44" t="s">
+        <v>196</v>
+      </c>
       <c r="G44" t="s">
-        <v>54</v>
+        <v>217</v>
       </c>
       <c r="H44" t="s">
-        <v>142</v>
+        <v>264</v>
       </c>
       <c r="I44" t="s">
-        <v>203</v>
+        <v>311</v>
       </c>
       <c r="J44" t="s">
-        <v>224</v>
-      </c>
-      <c r="K44" t="s">
-        <v>271</v>
-      </c>
-      <c r="L44" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M44" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -6126,40 +5693,31 @@
         <v>43</v>
       </c>
       <c r="C45">
-        <v>43</v>
-      </c>
-      <c r="D45">
-        <v>43</v>
-      </c>
-      <c r="E45">
-        <v>44</v>
-      </c>
-      <c r="F45">
         <v>33</v>
       </c>
+      <c r="D45" t="s">
+        <v>52</v>
+      </c>
+      <c r="E45" t="s">
+        <v>138</v>
+      </c>
+      <c r="F45" t="s">
+        <v>189</v>
+      </c>
       <c r="G45" t="s">
-        <v>55</v>
+        <v>209</v>
       </c>
       <c r="H45" t="s">
-        <v>143</v>
+        <v>265</v>
       </c>
       <c r="I45" t="s">
-        <v>196</v>
+        <v>310</v>
       </c>
       <c r="J45" t="s">
-        <v>216</v>
-      </c>
-      <c r="K45" t="s">
-        <v>272</v>
-      </c>
-      <c r="L45" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M45" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -6167,40 +5725,31 @@
         <v>44</v>
       </c>
       <c r="C46">
-        <v>44</v>
-      </c>
-      <c r="D46">
-        <v>44</v>
-      </c>
-      <c r="E46">
-        <v>45</v>
-      </c>
-      <c r="F46">
         <v>127</v>
       </c>
+      <c r="D46" t="s">
+        <v>53</v>
+      </c>
+      <c r="E46" t="s">
+        <v>139</v>
+      </c>
+      <c r="F46" t="s">
+        <v>191</v>
+      </c>
       <c r="G46" t="s">
-        <v>56</v>
+        <v>211</v>
       </c>
       <c r="H46" t="s">
-        <v>144</v>
+        <v>266</v>
       </c>
       <c r="I46" t="s">
-        <v>198</v>
+        <v>310</v>
       </c>
       <c r="J46" t="s">
-        <v>218</v>
-      </c>
-      <c r="K46" t="s">
-        <v>273</v>
-      </c>
-      <c r="L46" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M46" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -6208,40 +5757,31 @@
         <v>45</v>
       </c>
       <c r="C47">
-        <v>45</v>
-      </c>
-      <c r="D47">
-        <v>45</v>
-      </c>
-      <c r="E47">
-        <v>46</v>
-      </c>
-      <c r="F47">
         <v>222</v>
       </c>
+      <c r="D47" t="s">
+        <v>54</v>
+      </c>
+      <c r="E47" t="s">
+        <v>140</v>
+      </c>
+      <c r="F47" t="s">
+        <v>195</v>
+      </c>
       <c r="G47" t="s">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="H47" t="s">
-        <v>145</v>
+        <v>267</v>
       </c>
       <c r="I47" t="s">
-        <v>202</v>
+        <v>310</v>
       </c>
       <c r="J47" t="s">
-        <v>222</v>
-      </c>
-      <c r="K47" t="s">
-        <v>274</v>
-      </c>
-      <c r="L47" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M47" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -6249,40 +5789,31 @@
         <v>46</v>
       </c>
       <c r="C48">
-        <v>46</v>
-      </c>
-      <c r="D48">
-        <v>46</v>
-      </c>
-      <c r="E48">
-        <v>47</v>
-      </c>
-      <c r="F48">
         <v>252</v>
       </c>
+      <c r="D48" t="s">
+        <v>55</v>
+      </c>
+      <c r="E48" t="s">
+        <v>141</v>
+      </c>
+      <c r="F48" t="s">
+        <v>195</v>
+      </c>
       <c r="G48" t="s">
-        <v>58</v>
+        <v>215</v>
       </c>
       <c r="H48" t="s">
-        <v>146</v>
+        <v>268</v>
       </c>
       <c r="I48" t="s">
-        <v>202</v>
+        <v>310</v>
       </c>
       <c r="J48" t="s">
-        <v>222</v>
-      </c>
-      <c r="K48" t="s">
-        <v>275</v>
-      </c>
-      <c r="L48" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M48" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -6290,40 +5821,31 @@
         <v>47</v>
       </c>
       <c r="C49">
-        <v>47</v>
-      </c>
-      <c r="D49">
-        <v>47</v>
-      </c>
-      <c r="E49">
-        <v>48</v>
-      </c>
-      <c r="F49">
         <v>155</v>
       </c>
+      <c r="D49" t="s">
+        <v>56</v>
+      </c>
+      <c r="E49" t="s">
+        <v>142</v>
+      </c>
+      <c r="F49" t="s">
+        <v>187</v>
+      </c>
       <c r="G49" t="s">
-        <v>59</v>
+        <v>216</v>
       </c>
       <c r="H49" t="s">
-        <v>147</v>
+        <v>269</v>
       </c>
       <c r="I49" t="s">
-        <v>194</v>
+        <v>311</v>
       </c>
       <c r="J49" t="s">
-        <v>223</v>
-      </c>
-      <c r="K49" t="s">
-        <v>276</v>
-      </c>
-      <c r="L49" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M49" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -6331,40 +5853,31 @@
         <v>48</v>
       </c>
       <c r="C50">
-        <v>48</v>
-      </c>
-      <c r="D50">
-        <v>48</v>
-      </c>
-      <c r="E50">
-        <v>49</v>
-      </c>
-      <c r="F50">
         <v>133</v>
       </c>
+      <c r="D50" t="s">
+        <v>57</v>
+      </c>
+      <c r="E50" t="s">
+        <v>143</v>
+      </c>
+      <c r="F50" t="s">
+        <v>197</v>
+      </c>
       <c r="G50" t="s">
-        <v>60</v>
+        <v>218</v>
       </c>
       <c r="H50" t="s">
-        <v>148</v>
+        <v>270</v>
       </c>
       <c r="I50" t="s">
-        <v>204</v>
+        <v>309</v>
       </c>
       <c r="J50" t="s">
-        <v>225</v>
-      </c>
-      <c r="K50" t="s">
-        <v>277</v>
-      </c>
-      <c r="L50" s="2">
-        <v>45842</v>
-      </c>
-      <c r="M50" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -6372,40 +5885,31 @@
         <v>49</v>
       </c>
       <c r="C51">
-        <v>49</v>
-      </c>
-      <c r="D51">
-        <v>49</v>
-      </c>
-      <c r="E51">
-        <v>50</v>
-      </c>
-      <c r="F51">
         <v>447</v>
       </c>
+      <c r="D51" t="s">
+        <v>58</v>
+      </c>
+      <c r="E51" t="s">
+        <v>144</v>
+      </c>
+      <c r="F51" t="s">
+        <v>191</v>
+      </c>
       <c r="G51" t="s">
-        <v>61</v>
+        <v>211</v>
       </c>
       <c r="H51" t="s">
-        <v>149</v>
+        <v>271</v>
       </c>
       <c r="I51" t="s">
-        <v>198</v>
+        <v>310</v>
       </c>
       <c r="J51" t="s">
-        <v>218</v>
-      </c>
-      <c r="K51" t="s">
-        <v>278</v>
-      </c>
-      <c r="L51" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M51" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -6413,40 +5917,31 @@
         <v>50</v>
       </c>
       <c r="C52">
-        <v>50</v>
-      </c>
-      <c r="D52">
-        <v>50</v>
-      </c>
-      <c r="E52">
-        <v>52</v>
-      </c>
-      <c r="F52">
         <v>150</v>
       </c>
+      <c r="D52" t="s">
+        <v>59</v>
+      </c>
+      <c r="E52" t="s">
+        <v>145</v>
+      </c>
+      <c r="F52" t="s">
+        <v>196</v>
+      </c>
       <c r="G52" t="s">
-        <v>62</v>
+        <v>217</v>
       </c>
       <c r="H52" t="s">
-        <v>150</v>
+        <v>272</v>
       </c>
       <c r="I52" t="s">
-        <v>203</v>
+        <v>311</v>
       </c>
       <c r="J52" t="s">
-        <v>224</v>
-      </c>
-      <c r="K52" t="s">
-        <v>279</v>
-      </c>
-      <c r="L52" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M52" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -6454,40 +5949,31 @@
         <v>51</v>
       </c>
       <c r="C53">
-        <v>51</v>
-      </c>
-      <c r="D53">
-        <v>51</v>
-      </c>
-      <c r="E53">
-        <v>53</v>
-      </c>
-      <c r="F53">
         <v>29</v>
       </c>
+      <c r="D53" t="s">
+        <v>60</v>
+      </c>
+      <c r="E53" t="s">
+        <v>146</v>
+      </c>
+      <c r="F53" t="s">
+        <v>198</v>
+      </c>
       <c r="G53" t="s">
-        <v>63</v>
+        <v>219</v>
       </c>
       <c r="H53" t="s">
-        <v>151</v>
+        <v>273</v>
       </c>
       <c r="I53" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="J53" t="s">
-        <v>226</v>
-      </c>
-      <c r="K53" t="s">
-        <v>280</v>
-      </c>
-      <c r="L53" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M53" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -6495,40 +5981,31 @@
         <v>52</v>
       </c>
       <c r="C54">
-        <v>52</v>
-      </c>
-      <c r="D54">
-        <v>52</v>
-      </c>
-      <c r="E54">
-        <v>54</v>
-      </c>
-      <c r="F54">
         <v>121</v>
       </c>
+      <c r="D54" t="s">
+        <v>61</v>
+      </c>
+      <c r="E54" t="s">
+        <v>147</v>
+      </c>
+      <c r="F54" t="s">
+        <v>198</v>
+      </c>
       <c r="G54" t="s">
-        <v>64</v>
+        <v>219</v>
       </c>
       <c r="H54" t="s">
-        <v>152</v>
+        <v>274</v>
       </c>
       <c r="I54" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="J54" t="s">
-        <v>226</v>
-      </c>
-      <c r="K54" t="s">
-        <v>281</v>
-      </c>
-      <c r="L54" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M54" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -6536,40 +6013,31 @@
         <v>53</v>
       </c>
       <c r="C55">
-        <v>53</v>
-      </c>
-      <c r="D55">
-        <v>53</v>
-      </c>
-      <c r="E55">
-        <v>55</v>
-      </c>
-      <c r="F55">
         <v>111</v>
       </c>
+      <c r="D55" t="s">
+        <v>62</v>
+      </c>
+      <c r="E55" t="s">
+        <v>148</v>
+      </c>
+      <c r="F55" t="s">
+        <v>194</v>
+      </c>
       <c r="G55" t="s">
-        <v>65</v>
+        <v>214</v>
       </c>
       <c r="H55" t="s">
-        <v>153</v>
+        <v>275</v>
       </c>
       <c r="I55" t="s">
-        <v>201</v>
+        <v>309</v>
       </c>
       <c r="J55" t="s">
-        <v>221</v>
-      </c>
-      <c r="K55" t="s">
-        <v>282</v>
-      </c>
-      <c r="L55" s="2">
-        <v>45842</v>
-      </c>
-      <c r="M55" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -6577,40 +6045,31 @@
         <v>54</v>
       </c>
       <c r="C56">
-        <v>54</v>
-      </c>
-      <c r="D56">
-        <v>54</v>
-      </c>
-      <c r="E56">
-        <v>56</v>
-      </c>
-      <c r="F56">
         <v>59</v>
       </c>
+      <c r="D56" t="s">
+        <v>63</v>
+      </c>
+      <c r="E56" t="s">
+        <v>149</v>
+      </c>
+      <c r="F56" t="s">
+        <v>196</v>
+      </c>
       <c r="G56" t="s">
-        <v>66</v>
+        <v>217</v>
       </c>
       <c r="H56" t="s">
-        <v>154</v>
+        <v>276</v>
       </c>
       <c r="I56" t="s">
-        <v>203</v>
+        <v>311</v>
       </c>
       <c r="J56" t="s">
-        <v>224</v>
-      </c>
-      <c r="K56" t="s">
-        <v>283</v>
-      </c>
-      <c r="L56" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M56" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -6618,40 +6077,31 @@
         <v>55</v>
       </c>
       <c r="C57">
-        <v>55</v>
-      </c>
-      <c r="D57">
-        <v>55</v>
-      </c>
-      <c r="E57">
-        <v>57</v>
-      </c>
-      <c r="F57">
         <v>34</v>
       </c>
+      <c r="D57" t="s">
+        <v>64</v>
+      </c>
+      <c r="E57" t="s">
+        <v>150</v>
+      </c>
+      <c r="F57" t="s">
+        <v>187</v>
+      </c>
       <c r="G57" t="s">
-        <v>67</v>
+        <v>216</v>
       </c>
       <c r="H57" t="s">
-        <v>155</v>
+        <v>277</v>
       </c>
       <c r="I57" t="s">
-        <v>194</v>
+        <v>311</v>
       </c>
       <c r="J57" t="s">
-        <v>223</v>
-      </c>
-      <c r="K57" t="s">
-        <v>284</v>
-      </c>
-      <c r="L57" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M57" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -6659,40 +6109,31 @@
         <v>56</v>
       </c>
       <c r="C58">
-        <v>56</v>
-      </c>
-      <c r="D58">
-        <v>56</v>
-      </c>
-      <c r="E58">
-        <v>58</v>
-      </c>
-      <c r="F58">
         <v>357</v>
       </c>
+      <c r="D58" t="s">
+        <v>65</v>
+      </c>
+      <c r="E58" t="s">
+        <v>151</v>
+      </c>
+      <c r="F58" t="s">
+        <v>195</v>
+      </c>
       <c r="G58" t="s">
-        <v>68</v>
+        <v>215</v>
       </c>
       <c r="H58" t="s">
-        <v>156</v>
+        <v>278</v>
       </c>
       <c r="I58" t="s">
-        <v>202</v>
+        <v>310</v>
       </c>
       <c r="J58" t="s">
-        <v>222</v>
-      </c>
-      <c r="K58" t="s">
-        <v>285</v>
-      </c>
-      <c r="L58" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M58" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -6700,40 +6141,31 @@
         <v>57</v>
       </c>
       <c r="C59">
-        <v>57</v>
-      </c>
-      <c r="D59">
-        <v>57</v>
-      </c>
-      <c r="E59">
-        <v>59</v>
-      </c>
-      <c r="F59">
         <v>41</v>
       </c>
+      <c r="D59" t="s">
+        <v>66</v>
+      </c>
+      <c r="E59" t="s">
+        <v>152</v>
+      </c>
+      <c r="F59" t="s">
+        <v>192</v>
+      </c>
       <c r="G59" t="s">
-        <v>69</v>
+        <v>212</v>
       </c>
       <c r="H59" t="s">
-        <v>157</v>
+        <v>279</v>
       </c>
       <c r="I59" t="s">
-        <v>199</v>
+        <v>310</v>
       </c>
       <c r="J59" t="s">
-        <v>219</v>
-      </c>
-      <c r="K59" t="s">
-        <v>286</v>
-      </c>
-      <c r="L59" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M59" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -6741,40 +6173,31 @@
         <v>58</v>
       </c>
       <c r="C60">
-        <v>58</v>
-      </c>
-      <c r="D60">
-        <v>58</v>
-      </c>
-      <c r="E60">
-        <v>60</v>
-      </c>
-      <c r="F60">
         <v>46</v>
       </c>
+      <c r="D60" t="s">
+        <v>67</v>
+      </c>
+      <c r="E60" t="s">
+        <v>153</v>
+      </c>
+      <c r="F60" t="s">
+        <v>193</v>
+      </c>
       <c r="G60" t="s">
-        <v>70</v>
+        <v>213</v>
       </c>
       <c r="H60" t="s">
-        <v>158</v>
+        <v>280</v>
       </c>
       <c r="I60" t="s">
-        <v>200</v>
+        <v>310</v>
       </c>
       <c r="J60" t="s">
-        <v>220</v>
-      </c>
-      <c r="K60" t="s">
-        <v>287</v>
-      </c>
-      <c r="L60" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M60" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -6782,40 +6205,31 @@
         <v>59</v>
       </c>
       <c r="C61">
-        <v>59</v>
-      </c>
-      <c r="D61">
-        <v>59</v>
-      </c>
-      <c r="E61">
-        <v>61</v>
-      </c>
-      <c r="F61">
         <v>206</v>
       </c>
+      <c r="D61" t="s">
+        <v>68</v>
+      </c>
+      <c r="E61" t="s">
+        <v>154</v>
+      </c>
+      <c r="F61" t="s">
+        <v>199</v>
+      </c>
       <c r="G61" t="s">
-        <v>71</v>
+        <v>220</v>
       </c>
       <c r="H61" t="s">
-        <v>159</v>
+        <v>281</v>
       </c>
       <c r="I61" t="s">
-        <v>206</v>
+        <v>311</v>
       </c>
       <c r="J61" t="s">
-        <v>227</v>
-      </c>
-      <c r="K61" t="s">
-        <v>288</v>
-      </c>
-      <c r="L61" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M61" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -6823,40 +6237,31 @@
         <v>60</v>
       </c>
       <c r="C62">
-        <v>60</v>
-      </c>
-      <c r="D62">
-        <v>60</v>
-      </c>
-      <c r="E62">
-        <v>62</v>
-      </c>
-      <c r="F62">
         <v>428</v>
       </c>
+      <c r="D62" t="s">
+        <v>69</v>
+      </c>
+      <c r="E62" t="s">
+        <v>155</v>
+      </c>
+      <c r="F62" t="s">
+        <v>194</v>
+      </c>
       <c r="G62" t="s">
-        <v>72</v>
+        <v>214</v>
       </c>
       <c r="H62" t="s">
-        <v>160</v>
+        <v>282</v>
       </c>
       <c r="I62" t="s">
-        <v>201</v>
+        <v>309</v>
       </c>
       <c r="J62" t="s">
-        <v>221</v>
-      </c>
-      <c r="K62" t="s">
-        <v>289</v>
-      </c>
-      <c r="L62" s="2">
-        <v>45842</v>
-      </c>
-      <c r="M62" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -6864,40 +6269,31 @@
         <v>61</v>
       </c>
       <c r="C63">
-        <v>61</v>
-      </c>
-      <c r="D63">
-        <v>61</v>
-      </c>
-      <c r="E63">
-        <v>63</v>
-      </c>
-      <c r="F63">
         <v>217</v>
       </c>
+      <c r="D63" t="s">
+        <v>70</v>
+      </c>
+      <c r="E63" t="s">
+        <v>156</v>
+      </c>
+      <c r="F63" t="s">
+        <v>192</v>
+      </c>
       <c r="G63" t="s">
-        <v>73</v>
+        <v>212</v>
       </c>
       <c r="H63" t="s">
-        <v>161</v>
+        <v>283</v>
       </c>
       <c r="I63" t="s">
-        <v>199</v>
+        <v>310</v>
       </c>
       <c r="J63" t="s">
-        <v>219</v>
-      </c>
-      <c r="K63" t="s">
-        <v>290</v>
-      </c>
-      <c r="L63" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M63" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -6905,40 +6301,31 @@
         <v>62</v>
       </c>
       <c r="C64">
-        <v>62</v>
-      </c>
-      <c r="D64">
-        <v>62</v>
-      </c>
-      <c r="E64">
-        <v>65</v>
-      </c>
-      <c r="F64">
         <v>71</v>
       </c>
+      <c r="D64" t="s">
+        <v>71</v>
+      </c>
+      <c r="E64" t="s">
+        <v>157</v>
+      </c>
+      <c r="F64" t="s">
+        <v>198</v>
+      </c>
       <c r="G64" t="s">
-        <v>74</v>
+        <v>219</v>
       </c>
       <c r="H64" t="s">
-        <v>162</v>
+        <v>284</v>
       </c>
       <c r="I64" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="J64" t="s">
-        <v>226</v>
-      </c>
-      <c r="K64" t="s">
-        <v>291</v>
-      </c>
-      <c r="L64" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M64" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -6946,40 +6333,31 @@
         <v>63</v>
       </c>
       <c r="C65">
-        <v>63</v>
-      </c>
-      <c r="D65">
-        <v>63</v>
-      </c>
-      <c r="E65">
-        <v>66</v>
-      </c>
-      <c r="F65">
         <v>395</v>
       </c>
+      <c r="D65" t="s">
+        <v>72</v>
+      </c>
+      <c r="E65" t="s">
+        <v>158</v>
+      </c>
+      <c r="F65" t="s">
+        <v>197</v>
+      </c>
       <c r="G65" t="s">
-        <v>75</v>
+        <v>218</v>
       </c>
       <c r="H65" t="s">
-        <v>163</v>
+        <v>285</v>
       </c>
       <c r="I65" t="s">
-        <v>204</v>
+        <v>309</v>
       </c>
       <c r="J65" t="s">
-        <v>225</v>
-      </c>
-      <c r="K65" t="s">
-        <v>292</v>
-      </c>
-      <c r="L65" s="2">
-        <v>45842</v>
-      </c>
-      <c r="M65" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -6987,40 +6365,31 @@
         <v>64</v>
       </c>
       <c r="C66">
-        <v>64</v>
-      </c>
-      <c r="D66">
-        <v>64</v>
-      </c>
-      <c r="E66">
-        <v>67</v>
-      </c>
-      <c r="F66">
         <v>68</v>
       </c>
+      <c r="D66" t="s">
+        <v>73</v>
+      </c>
+      <c r="E66" t="s">
+        <v>159</v>
+      </c>
+      <c r="F66" t="s">
+        <v>194</v>
+      </c>
       <c r="G66" t="s">
-        <v>76</v>
+        <v>214</v>
       </c>
       <c r="H66" t="s">
-        <v>164</v>
+        <v>286</v>
       </c>
       <c r="I66" t="s">
-        <v>201</v>
+        <v>309</v>
       </c>
       <c r="J66" t="s">
-        <v>221</v>
-      </c>
-      <c r="K66" t="s">
-        <v>293</v>
-      </c>
-      <c r="L66" s="2">
-        <v>45842</v>
-      </c>
-      <c r="M66" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -7028,40 +6397,31 @@
         <v>65</v>
       </c>
       <c r="C67">
-        <v>65</v>
-      </c>
-      <c r="D67">
-        <v>65</v>
-      </c>
-      <c r="E67">
-        <v>68</v>
-      </c>
-      <c r="F67">
         <v>137</v>
       </c>
+      <c r="D67" t="s">
+        <v>74</v>
+      </c>
+      <c r="E67" t="s">
+        <v>160</v>
+      </c>
+      <c r="F67" t="s">
+        <v>199</v>
+      </c>
       <c r="G67" t="s">
-        <v>77</v>
+        <v>220</v>
       </c>
       <c r="H67" t="s">
-        <v>165</v>
+        <v>287</v>
       </c>
       <c r="I67" t="s">
-        <v>206</v>
+        <v>311</v>
       </c>
       <c r="J67" t="s">
-        <v>227</v>
-      </c>
-      <c r="K67" t="s">
-        <v>294</v>
-      </c>
-      <c r="L67" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M67" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -7069,40 +6429,31 @@
         <v>66</v>
       </c>
       <c r="C68">
-        <v>66</v>
-      </c>
-      <c r="D68">
-        <v>66</v>
-      </c>
-      <c r="E68">
-        <v>70</v>
-      </c>
-      <c r="F68">
         <v>74</v>
       </c>
+      <c r="D68" t="s">
+        <v>75</v>
+      </c>
+      <c r="E68" t="s">
+        <v>161</v>
+      </c>
+      <c r="F68" t="s">
+        <v>199</v>
+      </c>
       <c r="G68" t="s">
-        <v>78</v>
+        <v>220</v>
       </c>
       <c r="H68" t="s">
-        <v>166</v>
+        <v>288</v>
       </c>
       <c r="I68" t="s">
-        <v>206</v>
+        <v>311</v>
       </c>
       <c r="J68" t="s">
-        <v>227</v>
-      </c>
-      <c r="K68" t="s">
-        <v>295</v>
-      </c>
-      <c r="L68" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M68" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -7110,40 +6461,31 @@
         <v>67</v>
       </c>
       <c r="C69">
-        <v>67</v>
-      </c>
-      <c r="D69">
-        <v>67</v>
-      </c>
-      <c r="E69">
-        <v>71</v>
-      </c>
-      <c r="F69">
         <v>278</v>
       </c>
+      <c r="D69" t="s">
+        <v>76</v>
+      </c>
+      <c r="E69" t="s">
+        <v>162</v>
+      </c>
+      <c r="F69" t="s">
+        <v>198</v>
+      </c>
       <c r="G69" t="s">
-        <v>79</v>
+        <v>219</v>
       </c>
       <c r="H69" t="s">
-        <v>167</v>
+        <v>289</v>
       </c>
       <c r="I69" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="J69" t="s">
-        <v>226</v>
-      </c>
-      <c r="K69" t="s">
-        <v>296</v>
-      </c>
-      <c r="L69" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M69" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -7151,40 +6493,31 @@
         <v>68</v>
       </c>
       <c r="C70">
-        <v>68</v>
-      </c>
-      <c r="D70">
-        <v>68</v>
-      </c>
-      <c r="E70">
-        <v>72</v>
-      </c>
-      <c r="F70">
         <v>299</v>
       </c>
+      <c r="D70" t="s">
+        <v>77</v>
+      </c>
+      <c r="E70" t="s">
+        <v>163</v>
+      </c>
+      <c r="F70" t="s">
+        <v>198</v>
+      </c>
       <c r="G70" t="s">
-        <v>80</v>
+        <v>219</v>
       </c>
       <c r="H70" t="s">
-        <v>168</v>
+        <v>290</v>
       </c>
       <c r="I70" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="J70" t="s">
-        <v>226</v>
-      </c>
-      <c r="K70" t="s">
-        <v>297</v>
-      </c>
-      <c r="L70" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M70" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -7192,40 +6525,31 @@
         <v>69</v>
       </c>
       <c r="C71">
-        <v>69</v>
-      </c>
-      <c r="D71">
-        <v>69</v>
-      </c>
-      <c r="E71">
-        <v>73</v>
-      </c>
-      <c r="F71">
         <v>313</v>
       </c>
+      <c r="D71" t="s">
+        <v>78</v>
+      </c>
+      <c r="E71" t="s">
+        <v>164</v>
+      </c>
+      <c r="F71" t="s">
+        <v>197</v>
+      </c>
       <c r="G71" t="s">
-        <v>81</v>
+        <v>218</v>
       </c>
       <c r="H71" t="s">
-        <v>169</v>
+        <v>291</v>
       </c>
       <c r="I71" t="s">
-        <v>204</v>
+        <v>309</v>
       </c>
       <c r="J71" t="s">
-        <v>225</v>
-      </c>
-      <c r="K71" t="s">
-        <v>298</v>
-      </c>
-      <c r="L71" s="2">
-        <v>45842</v>
-      </c>
-      <c r="M71" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -7233,40 +6557,31 @@
         <v>70</v>
       </c>
       <c r="C72">
-        <v>70</v>
-      </c>
-      <c r="D72">
-        <v>70</v>
-      </c>
-      <c r="E72">
-        <v>74</v>
-      </c>
-      <c r="F72">
         <v>145</v>
       </c>
+      <c r="D72" t="s">
+        <v>79</v>
+      </c>
+      <c r="E72" t="s">
+        <v>165</v>
+      </c>
+      <c r="F72" t="s">
+        <v>190</v>
+      </c>
       <c r="G72" t="s">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="H72" t="s">
-        <v>170</v>
+        <v>292</v>
       </c>
       <c r="I72" t="s">
-        <v>197</v>
+        <v>309</v>
       </c>
       <c r="J72" t="s">
-        <v>217</v>
-      </c>
-      <c r="K72" t="s">
-        <v>299</v>
-      </c>
-      <c r="L72" s="2">
-        <v>45842</v>
-      </c>
-      <c r="M72" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -7274,40 +6589,31 @@
         <v>71</v>
       </c>
       <c r="C73">
-        <v>71</v>
-      </c>
-      <c r="D73">
-        <v>71</v>
-      </c>
-      <c r="E73">
-        <v>75</v>
-      </c>
-      <c r="F73">
         <v>453</v>
       </c>
+      <c r="D73" t="s">
+        <v>80</v>
+      </c>
+      <c r="E73" t="s">
+        <v>166</v>
+      </c>
+      <c r="F73" t="s">
+        <v>193</v>
+      </c>
       <c r="G73" t="s">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="H73" t="s">
-        <v>171</v>
+        <v>293</v>
       </c>
       <c r="I73" t="s">
-        <v>200</v>
+        <v>310</v>
       </c>
       <c r="J73" t="s">
-        <v>220</v>
-      </c>
-      <c r="K73" t="s">
-        <v>300</v>
-      </c>
-      <c r="L73" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M73" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -7315,40 +6621,31 @@
         <v>72</v>
       </c>
       <c r="C74">
-        <v>72</v>
-      </c>
-      <c r="D74">
-        <v>72</v>
-      </c>
-      <c r="E74">
-        <v>76</v>
-      </c>
-      <c r="F74">
-        <v>408</v>
+        <v>79</v>
+      </c>
+      <c r="D74" t="s">
+        <v>81</v>
+      </c>
+      <c r="E74" t="s">
+        <v>356</v>
+      </c>
+      <c r="F74" t="s">
+        <v>197</v>
       </c>
       <c r="G74" t="s">
-        <v>84</v>
+        <v>218</v>
       </c>
       <c r="H74" t="s">
-        <v>172</v>
+        <v>294</v>
       </c>
       <c r="I74" t="s">
-        <v>194</v>
+        <v>309</v>
       </c>
       <c r="J74" t="s">
-        <v>223</v>
-      </c>
-      <c r="K74" t="s">
-        <v>301</v>
-      </c>
-      <c r="L74" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M74" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -7356,40 +6653,31 @@
         <v>73</v>
       </c>
       <c r="C75">
-        <v>73</v>
-      </c>
-      <c r="D75">
-        <v>73</v>
-      </c>
-      <c r="E75">
-        <v>77</v>
-      </c>
-      <c r="F75">
-        <v>79</v>
+        <v>456</v>
+      </c>
+      <c r="D75" t="s">
+        <v>82</v>
+      </c>
+      <c r="E75" t="s">
+        <v>167</v>
+      </c>
+      <c r="F75" t="s">
+        <v>196</v>
       </c>
       <c r="G75" t="s">
-        <v>85</v>
+        <v>217</v>
       </c>
       <c r="H75" t="s">
-        <v>173</v>
+        <v>295</v>
       </c>
       <c r="I75" t="s">
-        <v>204</v>
+        <v>311</v>
       </c>
       <c r="J75" t="s">
-        <v>225</v>
-      </c>
-      <c r="K75" t="s">
-        <v>302</v>
-      </c>
-      <c r="L75" s="2">
-        <v>45842</v>
-      </c>
-      <c r="M75" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -7397,40 +6685,31 @@
         <v>74</v>
       </c>
       <c r="C76">
-        <v>74</v>
-      </c>
-      <c r="D76">
-        <v>74</v>
-      </c>
-      <c r="E76">
-        <v>78</v>
-      </c>
-      <c r="F76">
-        <v>456</v>
+        <v>5</v>
+      </c>
+      <c r="D76" t="s">
+        <v>83</v>
+      </c>
+      <c r="E76" t="s">
+        <v>168</v>
+      </c>
+      <c r="F76" t="s">
+        <v>193</v>
       </c>
       <c r="G76" t="s">
-        <v>86</v>
+        <v>213</v>
       </c>
       <c r="H76" t="s">
-        <v>174</v>
+        <v>296</v>
       </c>
       <c r="I76" t="s">
-        <v>203</v>
+        <v>310</v>
       </c>
       <c r="J76" t="s">
-        <v>224</v>
-      </c>
-      <c r="K76" t="s">
-        <v>303</v>
-      </c>
-      <c r="L76" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M76" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -7438,40 +6717,31 @@
         <v>75</v>
       </c>
       <c r="C77">
-        <v>75</v>
-      </c>
-      <c r="D77">
-        <v>75</v>
-      </c>
-      <c r="E77">
-        <v>79</v>
-      </c>
-      <c r="F77">
-        <v>5</v>
+        <v>80</v>
+      </c>
+      <c r="D77" t="s">
+        <v>84</v>
+      </c>
+      <c r="E77" t="s">
+        <v>169</v>
+      </c>
+      <c r="F77" t="s">
+        <v>190</v>
       </c>
       <c r="G77" t="s">
-        <v>87</v>
+        <v>210</v>
       </c>
       <c r="H77" t="s">
-        <v>175</v>
+        <v>297</v>
       </c>
       <c r="I77" t="s">
-        <v>200</v>
+        <v>309</v>
       </c>
       <c r="J77" t="s">
-        <v>220</v>
-      </c>
-      <c r="K77" t="s">
-        <v>304</v>
-      </c>
-      <c r="L77" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M77" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -7479,40 +6749,31 @@
         <v>76</v>
       </c>
       <c r="C78">
-        <v>76</v>
-      </c>
-      <c r="D78">
-        <v>76</v>
-      </c>
-      <c r="E78">
-        <v>80</v>
-      </c>
-      <c r="F78">
-        <v>80</v>
+        <v>180</v>
+      </c>
+      <c r="D78" t="s">
+        <v>85</v>
+      </c>
+      <c r="E78" t="s">
+        <v>170</v>
+      </c>
+      <c r="F78" t="s">
+        <v>199</v>
       </c>
       <c r="G78" t="s">
-        <v>88</v>
+        <v>220</v>
       </c>
       <c r="H78" t="s">
-        <v>176</v>
+        <v>298</v>
       </c>
       <c r="I78" t="s">
-        <v>197</v>
+        <v>311</v>
       </c>
       <c r="J78" t="s">
-        <v>217</v>
-      </c>
-      <c r="K78" t="s">
-        <v>305</v>
-      </c>
-      <c r="L78" s="2">
-        <v>45842</v>
-      </c>
-      <c r="M78" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -7520,40 +6781,31 @@
         <v>77</v>
       </c>
       <c r="C79">
-        <v>77</v>
-      </c>
-      <c r="D79">
-        <v>77</v>
-      </c>
-      <c r="E79">
-        <v>81</v>
-      </c>
-      <c r="F79">
-        <v>180</v>
+        <v>48</v>
+      </c>
+      <c r="D79" t="s">
+        <v>86</v>
+      </c>
+      <c r="E79" t="s">
+        <v>171</v>
+      </c>
+      <c r="F79" t="s">
+        <v>191</v>
       </c>
       <c r="G79" t="s">
-        <v>89</v>
+        <v>211</v>
       </c>
       <c r="H79" t="s">
-        <v>177</v>
+        <v>299</v>
       </c>
       <c r="I79" t="s">
-        <v>206</v>
+        <v>310</v>
       </c>
       <c r="J79" t="s">
-        <v>227</v>
-      </c>
-      <c r="K79" t="s">
-        <v>306</v>
-      </c>
-      <c r="L79" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M79" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -7561,40 +6813,31 @@
         <v>78</v>
       </c>
       <c r="C80">
-        <v>78</v>
-      </c>
-      <c r="D80">
-        <v>78</v>
-      </c>
-      <c r="E80">
-        <v>82</v>
-      </c>
-      <c r="F80">
-        <v>48</v>
+        <v>339</v>
+      </c>
+      <c r="D80" t="s">
+        <v>87</v>
+      </c>
+      <c r="E80" t="s">
+        <v>172</v>
+      </c>
+      <c r="F80" t="s">
+        <v>187</v>
       </c>
       <c r="G80" t="s">
-        <v>90</v>
+        <v>216</v>
       </c>
       <c r="H80" t="s">
-        <v>178</v>
+        <v>300</v>
       </c>
       <c r="I80" t="s">
-        <v>198</v>
+        <v>311</v>
       </c>
       <c r="J80" t="s">
-        <v>218</v>
-      </c>
-      <c r="K80" t="s">
-        <v>307</v>
-      </c>
-      <c r="L80" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M80" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -7602,40 +6845,28 @@
         <v>79</v>
       </c>
       <c r="C81">
-        <v>79</v>
-      </c>
-      <c r="D81">
-        <v>79</v>
-      </c>
-      <c r="E81">
-        <v>83</v>
-      </c>
-      <c r="F81">
-        <v>339</v>
+        <v>457</v>
+      </c>
+      <c r="D81" t="s">
+        <v>88</v>
+      </c>
+      <c r="E81" t="s">
+        <v>173</v>
+      </c>
+      <c r="F81" t="s">
+        <v>190</v>
       </c>
       <c r="G81" t="s">
-        <v>91</v>
+        <v>210</v>
       </c>
       <c r="H81" t="s">
-        <v>179</v>
-      </c>
-      <c r="I81" t="s">
-        <v>194</v>
+        <v>301</v>
       </c>
       <c r="J81" t="s">
-        <v>223</v>
-      </c>
-      <c r="K81" t="s">
-        <v>308</v>
-      </c>
-      <c r="L81" s="2">
-        <v>45841</v>
-      </c>
-      <c r="M81" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -7643,40 +6874,31 @@
         <v>80</v>
       </c>
       <c r="C82">
-        <v>80</v>
-      </c>
-      <c r="D82">
-        <v>80</v>
-      </c>
-      <c r="E82">
-        <v>84</v>
-      </c>
-      <c r="F82">
-        <v>187</v>
+        <v>82</v>
+      </c>
+      <c r="D82" t="s">
+        <v>89</v>
+      </c>
+      <c r="E82" t="s">
+        <v>174</v>
+      </c>
+      <c r="F82" t="s">
+        <v>200</v>
       </c>
       <c r="G82" t="s">
-        <v>92</v>
+        <v>221</v>
       </c>
       <c r="H82" t="s">
-        <v>180</v>
+        <v>302</v>
       </c>
       <c r="I82" t="s">
-        <v>198</v>
+        <v>309</v>
       </c>
       <c r="J82" t="s">
-        <v>218</v>
-      </c>
-      <c r="K82" t="s">
-        <v>309</v>
-      </c>
-      <c r="L82" s="2">
-        <v>45840</v>
-      </c>
-      <c r="M82" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -7684,34 +6906,31 @@
         <v>81</v>
       </c>
       <c r="C83">
-        <v>81</v>
-      </c>
-      <c r="D83">
-        <v>81</v>
-      </c>
-      <c r="E83">
-        <v>85</v>
-      </c>
-      <c r="F83">
-        <v>457</v>
+        <v>330</v>
+      </c>
+      <c r="D83" t="s">
+        <v>90</v>
+      </c>
+      <c r="E83" t="s">
+        <v>175</v>
+      </c>
+      <c r="F83" t="s">
+        <v>200</v>
       </c>
       <c r="G83" t="s">
-        <v>93</v>
+        <v>221</v>
       </c>
       <c r="H83" t="s">
-        <v>181</v>
+        <v>303</v>
       </c>
       <c r="I83" t="s">
-        <v>197</v>
-      </c>
-      <c r="K83" t="s">
-        <v>310</v>
-      </c>
-      <c r="M83" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13">
+        <v>309</v>
+      </c>
+      <c r="J83" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -7719,40 +6938,31 @@
         <v>82</v>
       </c>
       <c r="C84">
-        <v>82</v>
-      </c>
-      <c r="D84">
-        <v>82</v>
-      </c>
-      <c r="E84">
-        <v>86</v>
-      </c>
-      <c r="F84">
-        <v>82</v>
+        <v>389</v>
+      </c>
+      <c r="D84" t="s">
+        <v>91</v>
+      </c>
+      <c r="E84" t="s">
+        <v>176</v>
+      </c>
+      <c r="F84" t="s">
+        <v>200</v>
       </c>
       <c r="G84" t="s">
-        <v>94</v>
+        <v>221</v>
       </c>
       <c r="H84" t="s">
-        <v>182</v>
+        <v>304</v>
       </c>
       <c r="I84" t="s">
-        <v>207</v>
+        <v>309</v>
       </c>
       <c r="J84" t="s">
-        <v>228</v>
-      </c>
-      <c r="K84" t="s">
-        <v>311</v>
-      </c>
-      <c r="L84" s="2">
-        <v>45842</v>
-      </c>
-      <c r="M84" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -7760,40 +6970,31 @@
         <v>83</v>
       </c>
       <c r="C85">
-        <v>83</v>
-      </c>
-      <c r="D85">
-        <v>83</v>
-      </c>
-      <c r="E85">
-        <v>87</v>
-      </c>
-      <c r="F85">
-        <v>330</v>
+        <v>427</v>
+      </c>
+      <c r="D85" t="s">
+        <v>92</v>
+      </c>
+      <c r="E85" t="s">
+        <v>177</v>
+      </c>
+      <c r="F85" t="s">
+        <v>200</v>
       </c>
       <c r="G85" t="s">
-        <v>95</v>
+        <v>221</v>
       </c>
       <c r="H85" t="s">
-        <v>183</v>
+        <v>305</v>
       </c>
       <c r="I85" t="s">
-        <v>207</v>
+        <v>309</v>
       </c>
       <c r="J85" t="s">
-        <v>228</v>
-      </c>
-      <c r="K85" t="s">
-        <v>312</v>
-      </c>
-      <c r="L85" s="2">
-        <v>45842</v>
-      </c>
-      <c r="M85" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -7801,40 +7002,31 @@
         <v>84</v>
       </c>
       <c r="C86">
-        <v>84</v>
-      </c>
-      <c r="D86">
-        <v>84</v>
-      </c>
-      <c r="E86">
-        <v>88</v>
-      </c>
-      <c r="F86">
-        <v>389</v>
+        <v>445</v>
+      </c>
+      <c r="D86" t="s">
+        <v>93</v>
+      </c>
+      <c r="E86" t="s">
+        <v>178</v>
+      </c>
+      <c r="F86" t="s">
+        <v>200</v>
       </c>
       <c r="G86" t="s">
-        <v>96</v>
+        <v>221</v>
       </c>
       <c r="H86" t="s">
-        <v>184</v>
+        <v>306</v>
       </c>
       <c r="I86" t="s">
-        <v>207</v>
+        <v>309</v>
       </c>
       <c r="J86" t="s">
-        <v>228</v>
-      </c>
-      <c r="K86" t="s">
-        <v>313</v>
-      </c>
-      <c r="L86" s="2">
-        <v>45842</v>
-      </c>
-      <c r="M86" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -7842,119 +7034,57 @@
         <v>85</v>
       </c>
       <c r="C87">
-        <v>85</v>
-      </c>
-      <c r="D87">
-        <v>85</v>
-      </c>
-      <c r="E87">
-        <v>89</v>
-      </c>
-      <c r="F87">
-        <v>427</v>
+        <v>458</v>
+      </c>
+      <c r="D87" t="s">
+        <v>94</v>
+      </c>
+      <c r="E87" t="s">
+        <v>179</v>
+      </c>
+      <c r="F87" t="s">
+        <v>200</v>
       </c>
       <c r="G87" t="s">
-        <v>97</v>
+        <v>221</v>
       </c>
       <c r="H87" t="s">
-        <v>185</v>
+        <v>307</v>
       </c>
       <c r="I87" t="s">
-        <v>207</v>
+        <v>309</v>
       </c>
       <c r="J87" t="s">
-        <v>228</v>
-      </c>
-      <c r="K87" t="s">
-        <v>314</v>
-      </c>
-      <c r="L87" s="2">
-        <v>45842</v>
-      </c>
-      <c r="M87" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
-        <v>86</v>
-      </c>
-      <c r="B88">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C88">
-        <v>86</v>
-      </c>
-      <c r="D88">
-        <v>86</v>
-      </c>
-      <c r="E88">
-        <v>90</v>
-      </c>
-      <c r="F88">
-        <v>445</v>
+        <v>27</v>
+      </c>
+      <c r="D88" t="s">
+        <v>95</v>
+      </c>
+      <c r="E88" t="s">
+        <v>180</v>
+      </c>
+      <c r="F88" t="s">
+        <v>187</v>
       </c>
       <c r="G88" t="s">
-        <v>98</v>
+        <v>217</v>
       </c>
       <c r="H88" t="s">
-        <v>186</v>
+        <v>308</v>
       </c>
       <c r="I88" t="s">
-        <v>207</v>
+        <v>311</v>
       </c>
       <c r="J88" t="s">
-        <v>228</v>
-      </c>
-      <c r="K88" t="s">
-        <v>315</v>
-      </c>
-      <c r="L88" s="2">
-        <v>45842</v>
-      </c>
-      <c r="M88" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13">
-      <c r="A89" s="1">
-        <v>87</v>
-      </c>
-      <c r="B89">
-        <v>87</v>
-      </c>
-      <c r="C89">
-        <v>87</v>
-      </c>
-      <c r="D89">
-        <v>87</v>
-      </c>
-      <c r="E89">
-        <v>91</v>
-      </c>
-      <c r="F89">
-        <v>458</v>
-      </c>
-      <c r="G89" t="s">
-        <v>99</v>
-      </c>
-      <c r="H89" t="s">
-        <v>187</v>
-      </c>
-      <c r="I89" t="s">
-        <v>207</v>
-      </c>
-      <c r="J89" t="s">
-        <v>228</v>
-      </c>
-      <c r="K89" t="s">
-        <v>316</v>
-      </c>
-      <c r="L89" s="2">
-        <v>45842</v>
-      </c>
-      <c r="M89" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>

--- a/images/events/cf25dat.xlsx
+++ b/images/events/cf25dat.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10714"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hsg/tprojs/clementinec.github.io/images/events/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F3E9E4-616A-4C48-940A-296F8E5A4D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="359">
   <si>
     <t>ID</t>
   </si>
@@ -3905,12 +3911,15 @@
   <si>
     <t>CATALYTIC INTERFACE</t>
   </si>
+  <si>
+    <t>Renner</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3973,13 +3982,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4017,7 +4034,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4051,6 +4068,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4085,9 +4103,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4260,11 +4279,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I88"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="23.1640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>358</v>
+      </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4290,7 +4315,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -4319,7 +4344,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -4348,7 +4373,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -4377,7 +4402,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -4406,7 +4431,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -4435,7 +4460,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -4464,7 +4489,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -4493,7 +4518,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -4522,7 +4547,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -4551,7 +4576,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -4580,7 +4605,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -4609,7 +4634,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -4638,7 +4663,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -4667,7 +4692,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -4696,7 +4721,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -4725,7 +4750,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -4754,7 +4779,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -4783,7 +4808,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -4812,7 +4837,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -4841,7 +4866,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -4870,7 +4895,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -4899,7 +4924,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -4928,7 +4953,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -4957,7 +4982,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>64</v>
       </c>
@@ -4986,7 +5011,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -5015,7 +5040,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -5044,7 +5069,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -5073,7 +5098,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -5102,7 +5127,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -5131,7 +5156,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -5160,7 +5185,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -5189,7 +5214,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -5218,7 +5243,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -5247,7 +5272,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>32</v>
       </c>
@@ -5276,7 +5301,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>33</v>
       </c>
@@ -5305,7 +5330,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>34</v>
       </c>
@@ -5334,7 +5359,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>35</v>
       </c>
@@ -5363,7 +5388,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>36</v>
       </c>
@@ -5392,7 +5417,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>37</v>
       </c>
@@ -5421,7 +5446,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>38</v>
       </c>
@@ -5450,7 +5475,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>39</v>
       </c>
@@ -5479,7 +5504,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>40</v>
       </c>
@@ -5508,7 +5533,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>41</v>
       </c>
@@ -5537,7 +5562,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>42</v>
       </c>
@@ -5566,7 +5591,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>43</v>
       </c>
@@ -5595,7 +5620,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>44</v>
       </c>
@@ -5624,7 +5649,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>45</v>
       </c>
@@ -5653,7 +5678,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>46</v>
       </c>
@@ -5682,7 +5707,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>47</v>
       </c>
@@ -5711,7 +5736,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>48</v>
       </c>
@@ -5740,7 +5765,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>49</v>
       </c>
@@ -5769,7 +5794,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>50</v>
       </c>
@@ -5798,7 +5823,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>51</v>
       </c>
@@ -5827,7 +5852,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>52</v>
       </c>
@@ -5856,7 +5881,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>53</v>
       </c>
@@ -5885,7 +5910,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>54</v>
       </c>
@@ -5914,7 +5939,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>55</v>
       </c>
@@ -5943,7 +5968,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>56</v>
       </c>
@@ -5972,7 +5997,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>57</v>
       </c>
@@ -6001,7 +6026,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>58</v>
       </c>
@@ -6030,7 +6055,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>59</v>
       </c>
@@ -6059,7 +6084,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>60</v>
       </c>
@@ -6088,7 +6113,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>61</v>
       </c>
@@ -6117,7 +6142,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>62</v>
       </c>
@@ -6146,7 +6171,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>63</v>
       </c>
@@ -6175,7 +6200,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -6204,7 +6229,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -6233,7 +6258,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -6262,7 +6287,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -6291,7 +6316,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -6320,7 +6345,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -6349,7 +6374,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -6378,7 +6403,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -6407,7 +6432,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -6436,7 +6461,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -6465,7 +6490,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -6494,7 +6519,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -6523,7 +6548,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -6552,7 +6577,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -6581,7 +6606,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -6610,7 +6635,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -6639,7 +6664,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -6668,7 +6693,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -6697,7 +6722,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -6726,7 +6751,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -6755,7 +6780,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -6784,7 +6809,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -6799,6 +6824,9 @@
       </c>
       <c r="E88" t="s">
         <v>268</v>
+      </c>
+      <c r="F88" t="s">
+        <v>271</v>
       </c>
       <c r="G88" t="s">
         <v>309</v>

--- a/images/events/cf25dat.xlsx
+++ b/images/events/cf25dat.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10714"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hsg/tprojs/clementinec.github.io/images/events/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F3E9E4-616A-4C48-940A-296F8E5A4D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="358">
   <si>
     <t>ID</t>
   </si>
@@ -128,9 +122,6 @@
   </si>
   <si>
     <t>OPEN-SOURCE APPROACHES TO INTEGRATING ADVANCED ROBOTIC SYSTEMS IN SUSTAINABLE DESIGN</t>
-  </si>
-  <si>
-    <t>ROBOTIC FABRICATION AND IN-SITU 3D PRINTING FOR A NATURAL TIMBER-BAMBOO STRUCTURE</t>
   </si>
   <si>
     <t>AN URBAN MORPHOLOGY ANALYSIS FRAMEWORK FOR SYNERGISTIC IMPROVEMENT OF MULTIPLE PERFORMANCE OBJECTIVES: EXEMPLIFIED BY OUTDOOR THERMAL COMFORT AND BUILDING ENERGY EFFICIENCY</t>
@@ -225,6 +216,9 @@
     <t>HOW CHINESE IS CHINATOWN: MEASURING THE RELATIONSHIP BETWEEN GEOGRAPHIC AUTHENTICITY PERCEPTION AND STREETSCAPE FEATURES THROUGH MACHINE LEARNING</t>
   </si>
   <si>
+    <t>ROBOTIC FABRICATION AND IN-SITU 3D PRINTING FOR A NATURAL TIMBER-BAMBOO STRUCTURE</t>
+  </si>
+  <si>
     <t>INVESTIGATING SELF-SHAPING FIBRE COMPOSITES: TUNNING CURING PARAMETERS TO OPTIMISE RESULTING CURVATURE</t>
   </si>
   <si>
@@ -277,6 +271,11 @@
   </si>
   <si>
     <t>RESONANT BLECH: EMERGENT SOUNDSCAPES THROUGH HUMAN-AI INTERACTION</t>
+  </si>
+  <si>
+    <t>AUGMENTING IFC-BASED BIM MODELS FOR GRAPH NEURAL NETWORK
+TRAINING OF NON-ORTHOGONAL SPATIAL TYPOLOGIES: A
+CONTEXT-INFORMED DESIGN METHODOLOGY</t>
   </si>
   <si>
     <t>CONSTRUCTGNN: A GRAPH NEURAL NETWORK FRAMEWORK FOR ADAPTIVE 3D ARCHITECTURAL LAYOUT</t>
@@ -314,11 +313,6 @@
 </t>
   </si>
   <si>
-    <t>AUGMENTING IFC-BASED BIM MODELS FOR GRAPH NEURAL NETWORK
-TRAINING OF NON-ORTHOGONAL SPATIAL TYPOLOGIES: A
-CONTEXT-INFORMED DESIGN METHODOLOGY</t>
-  </si>
-  <si>
     <t>Pok Yin Victor Leung and Yijiang Huang</t>
   </si>
   <si>
@@ -401,9 +395,6 @@
   </si>
   <si>
     <t>Celso Urroz and Shermeen Yousif</t>
-  </si>
-  <si>
-    <t>Xinyue Xia, Haojie Fan, Shunuo Li, Huangyan Zheng, Haoyi Xu and Sining Wang</t>
   </si>
   <si>
     <t>Minghao Wang, Chi Zhang and Yuchen Qin</t>
@@ -497,6 +488,9 @@
     <t>Zixi Zhang, Wenjing Li and Waishan Qiu</t>
   </si>
   <si>
+    <t>Xinyue Xia, Haojie Fan, Shunuo Li, Huangyan Zheng, Haoyi Xu and Sining Wang</t>
+  </si>
+  <si>
     <t>Ariel Yakobi, Eran Sharon and Arielle Blonder</t>
   </si>
   <si>
@@ -549,6 +543,10 @@
   </si>
   <si>
     <t>Alexander Urban, Moritz Koegel, Lukas Fink Pielsticker, Alexander Karaivanov, Nicolaj Kirisits and Zeynep Aksöz Balzar</t>
+  </si>
+  <si>
+    <t>Matthias Hornung, Markus Renner, Diellza Elshani, Mathias
+Niepert and Thomas Wortmann</t>
   </si>
   <si>
     <t>Quan Zhou, Yize Li, Zejian Li and Immanuel Koh</t>
@@ -582,10 +580,6 @@
   </si>
   <si>
     <t>Tejas Chavan, Houssame E. Hsain, Camiel Weijenberg and Sayjel V. Patel</t>
-  </si>
-  <si>
-    <t>Matthias Hornung, Markus Renner, Diellza Elshani, Mathias
-Niepert and Thomas Wortmann</t>
   </si>
   <si>
     <t>The use of robotics in construction offers transformative
@@ -1483,25 +1477,6 @@
 these workflows on GitHub, we offer an open-source
 collaborative computational design framework, coupling
 advanced computation and sustainable architectural robotics.</t>
-  </si>
-  <si>
-    <t>With advanced fabrication and computational design methods,
-non-standard building structures made from natural
-materials such as wood and bamboo are attracting the
-attention of architectural researchers. As current studies
-primarily focus on the design and fabrication of
-single-material systems, this work explores a robotic
-fabrication and in-situ 3D printing workflow for a hybrid
-natural timber-bamboo structure. It encompasses three major
-research components: 1) the scanning and virtual recreation
-of collected raw materials; 2) the design of a hybrid
-structural system based on the materials’ natural geometric
-features and structural performance; 3) a bespoke digital
-fabrication process that addresses robotic drill-ing and
-in-situ 3D printing for non-standard timber-bamboo joints.
-The proposed workflow is illustrated through the creation
-of a full-scale structural prototype, along with its future
-architectural applications.</t>
   </si>
   <si>
     <t>Urban morphology influences both outdoor thermal comfort
@@ -2526,6 +2501,25 @@
 cultures.</t>
   </si>
   <si>
+    <t>With advanced fabrication and computational design methods,
+non-standard building structures made from natural
+materials such as wood and bamboo are attracting the
+attention of architectural researchers. As current studies
+primarily focus on the design and fabrication of
+single-material systems, this work explores a robotic
+fabrication and in-situ 3D printing workflow for a hybrid
+natural timber-bamboo structure. It encompasses three major
+research components: 1) the scanning and virtual recreation
+of collected raw materials; 2) the design of a hybrid
+structural system based on the materials’ natural geometric
+features and structural performance; 3) a bespoke digital
+fabrication process that addresses robotic drill-ing and
+in-situ 3D printing for non-standard timber-bamboo joints.
+The proposed workflow is illustrated through the creation
+of a full-scale structural prototype, along with its future
+architectural applications.</t>
+  </si>
+  <si>
     <t>As part of a broader architectural initiative aimed at
 moldless fabrication of complex surfaces, this study
 investigates the potential of self-shaping mate-rials,
@@ -3164,6 +3158,40 @@
 transforming built environments into interactive,
 performative instruments that offer immersive sensory
 experiences.</t>
+  </si>
+  <si>
+    <t>Building Information Modeling (BIM) and Industry Foundation
+Classes (IFC) data are valuable resources in architecture,
+offering detailed and structured information on building
+elements.
+However, using such resources to develop artificial
+intelligence (AI) models that are capable of learning and
+generating spatial and geometrical suggestions remains a
+challenging problem.
+This study presents a systematic method for converting
+real-world BIM/IFC projects into graph representations,
+suitable for training Graph Neural Networks (GNNs), which
+overcome the limitations inherent to conventional AI
+techniques based on pixel and 3D voxels in architecture.
+First, a custom schema was defined to encode each building
+element and spatial relationship as triplets, allowing for
+the generation of heterogeneous graphs that capture
+geometry, topology and semantic labels.
+Using models provided by multiple architecture offices, we
+extracted over 180,000 subgraphs that represent diverse
+non-orthogonal spatial typologies.
+Next, each subgraph was annotated with multi-label
+classifications (element type) and continuous attributes
+(e.g. dimensions, orientation) to support both
+classification and regression tasks.
+Finally, to demonstrate the utility of the dataset, we
+trained a custom neural network (NN) to complete partial
+spatial graphs, producing non-orthogonal room layouts based
+on the existing building context.
+The custom NN suggests that the dataset has the capacity to
+support advanced 3D generative tasks in architecture and
+could lay the groundwork for future studies on automated
+design synthesis.</t>
   </si>
   <si>
     <t>This study proposes a workflow, ConStructGNN, that
@@ -3611,47 +3639,13 @@
 in architectural education and practice.</t>
   </si>
   <si>
-    <t>Building Information Modeling (BIM) and Industry Foundation
-Classes (IFC) data are valuable resources in architecture,
-offering detailed and structured information on building
-elements.
-However, using such resources to develop artificial
-intelligence (AI) models that are capable of learning and
-generating spatial and geometrical suggestions remains a
-challenging problem.
-This study presents a systematic method for converting
-real-world BIM/IFC projects into graph representations,
-suitable for training Graph Neural Networks (GNNs), which
-overcome the limitations inherent to conventional AI
-techniques based on pixel and 3D voxels in architecture.
-First, a custom schema was defined to encode each building
-element and spatial relationship as triplets, allowing for
-the generation of heterogeneous graphs that capture
-geometry, topology and semantic labels.
-Using models provided by multiple architecture offices, we
-extracted over 180,000 subgraphs that represent diverse
-non-orthogonal spatial typologies.
-Next, each subgraph was annotated with multi-label
-classifications (element type) and continuous attributes
-(e.g. dimensions, orientation) to support both
-classification and regression tasks.
-Finally, to demonstrate the utility of the dataset, we
-trained a custom neural network (NN) to complete partial
-spatial graphs, producing non-orthogonal room layouts based
-on the existing building context.
-The custom NN suggests that the dataset has the capacity to
-support advanced 3D generative tasks in architecture and
-could lay the groundwork for future studies on automated
-design synthesis.</t>
-  </si>
-  <si>
-    <t>7/2/25</t>
-  </si>
-  <si>
-    <t>7/3/25</t>
-  </si>
-  <si>
-    <t>7/4/25</t>
+    <t>7/2/2025</t>
+  </si>
+  <si>
+    <t>7/3/2025</t>
+  </si>
+  <si>
+    <t>7/4/2025</t>
   </si>
   <si>
     <t>11:25 - 11:40</t>
@@ -3699,9 +3693,6 @@
     <t>16:10 - 16:25</t>
   </si>
   <si>
-    <t>1/0/00</t>
-  </si>
-  <si>
     <t>10:35 - 10:50</t>
   </si>
   <si>
@@ -3744,6 +3735,9 @@
     <t>15:40 - 16:25</t>
   </si>
   <si>
+    <t>16:45 - 17:00</t>
+  </si>
+  <si>
     <t>17:00 - 17:15</t>
   </si>
   <si>
@@ -3810,30 +3804,30 @@
     <t>S-2</t>
   </si>
   <si>
+    <t>S-S2</t>
+  </si>
+  <si>
+    <t>P-B2</t>
+  </si>
+  <si>
+    <t>P-C2</t>
+  </si>
+  <si>
+    <t>P-D2</t>
+  </si>
+  <si>
+    <t>P-A2</t>
+  </si>
+  <si>
+    <t>S-S3</t>
+  </si>
+  <si>
+    <t>S-3</t>
+  </si>
+  <si>
     <t>S-4</t>
   </si>
   <si>
-    <t>S-S2</t>
-  </si>
-  <si>
-    <t>P-B2</t>
-  </si>
-  <si>
-    <t>P-C2</t>
-  </si>
-  <si>
-    <t>P-D2</t>
-  </si>
-  <si>
-    <t>P-A2</t>
-  </si>
-  <si>
-    <t>S-S3</t>
-  </si>
-  <si>
-    <t>S-3</t>
-  </si>
-  <si>
     <t>S-S4</t>
   </si>
   <si>
@@ -3873,15 +3867,15 @@
     <t>AUGMENTING &amp; ADVANCING DESIGN</t>
   </si>
   <si>
+    <t>URBAN PERCEPTIONS &amp; PATTERNS I</t>
+  </si>
+  <si>
+    <t>AI FOR DESIGN EVALUATION</t>
+  </si>
+  <si>
     <t>STRUCTURAL, FABRICATION &amp; MATERIAL LOGIC</t>
   </si>
   <si>
-    <t>URBAN PERCEPTIONS &amp; PATTERNS I</t>
-  </si>
-  <si>
-    <t>AI FOR DESIGN EVALUATION</t>
-  </si>
-  <si>
     <t>COMMUNITY &amp; COLLECTIVE INTELLIGENCE</t>
   </si>
   <si>
@@ -3910,16 +3904,13 @@
   </si>
   <si>
     <t>CATALYTIC INTERFACE</t>
-  </si>
-  <si>
-    <t>Renner</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3982,21 +3973,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4034,7 +4017,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4068,7 +4051,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4103,10 +4085,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4279,17 +4260,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I88"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="4" max="4" width="23.1640625" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>358</v>
-      </c>
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4315,7 +4290,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -4344,7 +4319,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -4373,7 +4348,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -4402,7 +4377,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -4431,7 +4406,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -4460,7 +4435,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -4489,7 +4464,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -4518,7 +4493,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -4547,7 +4522,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -4576,7 +4551,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -4605,7 +4580,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -4634,7 +4609,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -4663,7 +4638,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -4692,7 +4667,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -4721,7 +4696,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -4750,7 +4725,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -4779,7 +4754,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -4808,7 +4783,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -4837,7 +4812,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -4866,7 +4841,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -4895,7 +4870,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -4924,7 +4899,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -4953,7 +4928,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -4982,9 +4957,9 @@
         <v>343</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9">
       <c r="A25" s="1">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="B25">
         <v>135</v>
@@ -5011,9 +4986,9 @@
         <v>343</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9">
       <c r="A26" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B26">
         <v>151</v>
@@ -5040,9 +5015,9 @@
         <v>343</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9">
       <c r="A27" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B27">
         <v>33</v>
@@ -5069,9 +5044,9 @@
         <v>344</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9">
       <c r="A28" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B28">
         <v>426</v>
@@ -5098,9 +5073,9 @@
         <v>344</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9">
       <c r="A29" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B29">
         <v>196</v>
@@ -5127,12 +5102,12 @@
         <v>344</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9">
       <c r="A30" s="1">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B30">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="C30" t="s">
         <v>36</v>
@@ -5156,12 +5131,12 @@
         <v>345</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9">
       <c r="A31" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B31">
-        <v>148</v>
+        <v>55</v>
       </c>
       <c r="C31" t="s">
         <v>37</v>
@@ -5179,18 +5154,18 @@
         <v>288</v>
       </c>
       <c r="H31" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I31" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B32">
-        <v>55</v>
+        <v>329</v>
       </c>
       <c r="C32" t="s">
         <v>38</v>
@@ -5208,18 +5183,18 @@
         <v>289</v>
       </c>
       <c r="H32" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I32" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B33">
-        <v>329</v>
+        <v>262</v>
       </c>
       <c r="C33" t="s">
         <v>39</v>
@@ -5237,18 +5212,18 @@
         <v>290</v>
       </c>
       <c r="H33" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I33" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="1">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B34">
-        <v>262</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
         <v>40</v>
@@ -5272,12 +5247,12 @@
         <v>346</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9">
       <c r="A35" s="1">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B35">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C35" t="s">
         <v>41</v>
@@ -5292,7 +5267,7 @@
         <v>270</v>
       </c>
       <c r="G35" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H35" t="s">
         <v>326</v>
@@ -5301,12 +5276,12 @@
         <v>347</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9">
       <c r="A36" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B36">
-        <v>34</v>
+        <v>206</v>
       </c>
       <c r="C36" t="s">
         <v>42</v>
@@ -5321,21 +5296,21 @@
         <v>270</v>
       </c>
       <c r="G36" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H36" t="s">
         <v>327</v>
       </c>
       <c r="I36" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B37">
-        <v>206</v>
+        <v>299</v>
       </c>
       <c r="C37" t="s">
         <v>43</v>
@@ -5350,21 +5325,21 @@
         <v>270</v>
       </c>
       <c r="G37" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H37" t="s">
         <v>328</v>
       </c>
       <c r="I37" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="1">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B38">
-        <v>299</v>
+        <v>155</v>
       </c>
       <c r="C38" t="s">
         <v>44</v>
@@ -5382,18 +5357,18 @@
         <v>292</v>
       </c>
       <c r="H38" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="I38" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B39">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C39" t="s">
         <v>45</v>
@@ -5408,21 +5383,21 @@
         <v>270</v>
       </c>
       <c r="G39" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H39" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="I39" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" s="1">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B40">
-        <v>150</v>
+        <v>74</v>
       </c>
       <c r="C40" t="s">
         <v>46</v>
@@ -5437,21 +5412,21 @@
         <v>270</v>
       </c>
       <c r="G40" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H40" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I40" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" s="1">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B41">
-        <v>74</v>
+        <v>278</v>
       </c>
       <c r="C41" t="s">
         <v>47</v>
@@ -5466,21 +5441,21 @@
         <v>270</v>
       </c>
       <c r="G41" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H41" t="s">
         <v>328</v>
       </c>
       <c r="I41" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" s="1">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B42">
-        <v>278</v>
+        <v>221</v>
       </c>
       <c r="C42" t="s">
         <v>48</v>
@@ -5498,18 +5473,18 @@
         <v>293</v>
       </c>
       <c r="H42" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="I42" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" s="1">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B43">
-        <v>221</v>
+        <v>304</v>
       </c>
       <c r="C43" t="s">
         <v>49</v>
@@ -5524,21 +5499,21 @@
         <v>270</v>
       </c>
       <c r="G43" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H43" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="I43" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" s="1">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B44">
-        <v>304</v>
+        <v>29</v>
       </c>
       <c r="C44" t="s">
         <v>50</v>
@@ -5553,21 +5528,21 @@
         <v>270</v>
       </c>
       <c r="G44" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H44" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="I44" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" s="1">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B45">
-        <v>29</v>
+        <v>137</v>
       </c>
       <c r="C45" t="s">
         <v>51</v>
@@ -5582,21 +5557,21 @@
         <v>270</v>
       </c>
       <c r="G45" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H45" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="I45" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" s="1">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B46">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="C46" t="s">
         <v>52</v>
@@ -5617,15 +5592,15 @@
         <v>328</v>
       </c>
       <c r="I46" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" s="1">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B47">
-        <v>121</v>
+        <v>456</v>
       </c>
       <c r="C47" t="s">
         <v>53</v>
@@ -5640,21 +5615,21 @@
         <v>270</v>
       </c>
       <c r="G47" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H47" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="I47" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" s="1">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B48">
-        <v>456</v>
+        <v>180</v>
       </c>
       <c r="C48" t="s">
         <v>54</v>
@@ -5669,21 +5644,21 @@
         <v>270</v>
       </c>
       <c r="G48" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H48" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I48" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" s="1">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B49">
-        <v>180</v>
+        <v>339</v>
       </c>
       <c r="C49" t="s">
         <v>55</v>
@@ -5698,21 +5673,21 @@
         <v>270</v>
       </c>
       <c r="G49" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H49" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="I49" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" s="1">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B50">
-        <v>339</v>
+        <v>59</v>
       </c>
       <c r="C50" t="s">
         <v>56</v>
@@ -5730,18 +5705,18 @@
         <v>295</v>
       </c>
       <c r="H50" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="I50" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" s="1">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B51">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C51" t="s">
         <v>57</v>
@@ -5756,21 +5731,21 @@
         <v>270</v>
       </c>
       <c r="G51" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H51" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="I51" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" s="1">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B52">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="C52" t="s">
         <v>58</v>
@@ -5785,21 +5760,21 @@
         <v>270</v>
       </c>
       <c r="G52" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H52" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="I52" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B53">
-        <v>27</v>
+        <v>210</v>
       </c>
       <c r="C53" t="s">
         <v>59</v>
@@ -5817,18 +5792,18 @@
         <v>296</v>
       </c>
       <c r="H53" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I53" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" s="1">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B54">
-        <v>210</v>
+        <v>440</v>
       </c>
       <c r="C54" t="s">
         <v>60</v>
@@ -5846,18 +5821,18 @@
         <v>297</v>
       </c>
       <c r="H54" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I54" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9">
       <c r="A55" s="1">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B55">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="C55" t="s">
         <v>61</v>
@@ -5875,18 +5850,18 @@
         <v>298</v>
       </c>
       <c r="H55" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I55" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9">
       <c r="A56" s="1">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B56">
-        <v>431</v>
+        <v>314</v>
       </c>
       <c r="C56" t="s">
         <v>62</v>
@@ -5904,18 +5879,18 @@
         <v>299</v>
       </c>
       <c r="H56" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I56" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9">
       <c r="A57" s="1">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B57">
-        <v>314</v>
+        <v>50</v>
       </c>
       <c r="C57" t="s">
         <v>63</v>
@@ -5936,15 +5911,15 @@
         <v>330</v>
       </c>
       <c r="I57" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" s="1">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B58">
-        <v>50</v>
+        <v>198</v>
       </c>
       <c r="C58" t="s">
         <v>64</v>
@@ -5959,21 +5934,21 @@
         <v>270</v>
       </c>
       <c r="G58" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="H58" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I58" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9">
       <c r="A59" s="1">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B59">
-        <v>198</v>
+        <v>250</v>
       </c>
       <c r="C59" t="s">
         <v>65</v>
@@ -5988,21 +5963,21 @@
         <v>270</v>
       </c>
       <c r="G59" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I59" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9">
       <c r="A60" s="1">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="B60">
-        <v>250</v>
+        <v>132</v>
       </c>
       <c r="C60" t="s">
         <v>66</v>
@@ -6017,18 +5992,18 @@
         <v>270</v>
       </c>
       <c r="G60" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="H60" t="s">
         <v>331</v>
       </c>
       <c r="I60" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B61">
         <v>193</v>
@@ -6049,15 +6024,15 @@
         <v>302</v>
       </c>
       <c r="H61" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="I61" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B62">
         <v>386</v>
@@ -6078,15 +6053,15 @@
         <v>303</v>
       </c>
       <c r="H62" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="I62" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B63">
         <v>178</v>
@@ -6107,15 +6082,15 @@
         <v>304</v>
       </c>
       <c r="H63" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="I63" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B64">
         <v>444</v>
@@ -6133,7 +6108,7 @@
         <v>271</v>
       </c>
       <c r="G64" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H64" t="s">
         <v>332</v>
@@ -6142,9 +6117,9 @@
         <v>352</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9">
       <c r="A65" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B65">
         <v>403</v>
@@ -6162,7 +6137,7 @@
         <v>271</v>
       </c>
       <c r="G65" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H65" t="s">
         <v>332</v>
@@ -6171,9 +6146,9 @@
         <v>352</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9">
       <c r="A66" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B66">
         <v>253</v>
@@ -6191,7 +6166,7 @@
         <v>271</v>
       </c>
       <c r="G66" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H66" t="s">
         <v>332</v>
@@ -6200,7 +6175,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -6229,7 +6204,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -6258,7 +6233,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -6287,7 +6262,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -6316,7 +6291,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -6345,7 +6320,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -6374,7 +6349,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -6403,7 +6378,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:9">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -6432,7 +6407,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:9">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -6461,7 +6436,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:9">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -6490,7 +6465,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:9">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -6519,7 +6494,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:9">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -6548,12 +6523,12 @@
         <v>353</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:9">
       <c r="A79" s="1">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B79">
-        <v>114</v>
+        <v>457</v>
       </c>
       <c r="C79" t="s">
         <v>85</v>
@@ -6568,21 +6543,21 @@
         <v>271</v>
       </c>
       <c r="G79" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H79" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I79" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
       <c r="A80" s="1">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B80">
-        <v>231</v>
+        <v>114</v>
       </c>
       <c r="C80" t="s">
         <v>86</v>
@@ -6597,7 +6572,7 @@
         <v>271</v>
       </c>
       <c r="G80" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="H80" t="s">
         <v>336</v>
@@ -6606,12 +6581,12 @@
         <v>356</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9">
       <c r="A81" s="1">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B81">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C81" t="s">
         <v>87</v>
@@ -6626,7 +6601,7 @@
         <v>271</v>
       </c>
       <c r="G81" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="H81" t="s">
         <v>336</v>
@@ -6635,12 +6610,12 @@
         <v>356</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9">
       <c r="A82" s="1">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B82">
-        <v>82</v>
+        <v>230</v>
       </c>
       <c r="C82" t="s">
         <v>88</v>
@@ -6655,21 +6630,21 @@
         <v>271</v>
       </c>
       <c r="G82" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="H82" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="I82" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
       <c r="A83" s="1">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B83">
-        <v>330</v>
+        <v>82</v>
       </c>
       <c r="C83" t="s">
         <v>89</v>
@@ -6684,7 +6659,7 @@
         <v>271</v>
       </c>
       <c r="G83" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H83" t="s">
         <v>337</v>
@@ -6693,12 +6668,12 @@
         <v>357</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9">
       <c r="A84" s="1">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B84">
-        <v>389</v>
+        <v>330</v>
       </c>
       <c r="C84" t="s">
         <v>90</v>
@@ -6713,7 +6688,7 @@
         <v>271</v>
       </c>
       <c r="G84" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H84" t="s">
         <v>337</v>
@@ -6722,12 +6697,12 @@
         <v>357</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9">
       <c r="A85" s="1">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B85">
-        <v>427</v>
+        <v>389</v>
       </c>
       <c r="C85" t="s">
         <v>91</v>
@@ -6742,7 +6717,7 @@
         <v>271</v>
       </c>
       <c r="G85" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H85" t="s">
         <v>337</v>
@@ -6751,12 +6726,12 @@
         <v>357</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9">
       <c r="A86" s="1">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B86">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="C86" t="s">
         <v>92</v>
@@ -6771,7 +6746,7 @@
         <v>271</v>
       </c>
       <c r="G86" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H86" t="s">
         <v>337</v>
@@ -6780,12 +6755,12 @@
         <v>357</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9">
       <c r="A87" s="1">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B87">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="C87" t="s">
         <v>93</v>
@@ -6800,7 +6775,7 @@
         <v>271</v>
       </c>
       <c r="G87" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H87" t="s">
         <v>337</v>
@@ -6809,12 +6784,12 @@
         <v>357</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9">
       <c r="A88" s="1">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B88">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C88" t="s">
         <v>94</v>
@@ -6829,13 +6804,13 @@
         <v>271</v>
       </c>
       <c r="G88" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="H88" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I88" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>

--- a/images/events/cf25dat.xlsx
+++ b/images/events/cf25dat.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tamk/Documents/GitHub/clementinec.github.io/images/events/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB6294A-C209-5542-A5E3-0669429BCAE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="26880" yWindow="-20760" windowWidth="35240" windowHeight="19740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="362">
   <si>
     <t>ID</t>
   </si>
@@ -188,11 +194,6 @@
   </si>
   <si>
     <t>PERFORMANCE-BASED URBAN ENVIRONMENTAL RESTORATION: A MULTI-LAYER CELLULAR AUTOMATA MODEL FOR ECOLOGICAL DESIGN SIMULATION IN HIGH-DENSITY CITIES</t>
-  </si>
-  <si>
-    <t>A Full-Process Digital Method for Recursive Geometric
-Structure and Machining Parameter Generation Targeting the
-Reutilization of Curved Timber</t>
   </si>
   <si>
     <t>DISCOVERING PARETO-EFFICIENT URBAN NETWORKS THROUGH SHAPE GRAMMAR, MULTI-OBJECTIVE OPTIMISATION AND MACHINE LEARNING</t>
@@ -287,17 +288,9 @@
     <t>COMPUTING BEYOND THE VITRUVIAN CANON: AMBIGUITY AS A CATALYST IN COMPUTATIONAL DESIGN THEORY</t>
   </si>
   <si>
-    <t>(CI) COLLABORATIVE PATHWAYS TO SUSTAINABLE DIGITAL
-INNOVATION IN AEC</t>
-  </si>
-  <si>
     <t>RETHINKING PARTICIPATORY ARCHITECTURAL DESIGN: HARNESSING
 IMMERSIVE ENVIRONMENTS &amp; AI FOR FACILITATING
 DESIGNER-STAKEHOLDER COLLABORATION</t>
-  </si>
-  <si>
-    <t>(CI) AUGMENTATION IN DESIGN AND FABRICATION: EXPANDING THE
-ROLE OF AR AND HUMAN-MACHINE COLLABORATION</t>
   </si>
   <si>
     <t>TOWARD AIXR: DESIGNING A FRAMEWORK FOR AI-INFORMED
@@ -3726,15 +3719,6 @@
     <t>14:15 - 14:30</t>
   </si>
   <si>
-    <t>14:30 - 14:45</t>
-  </si>
-  <si>
-    <t>14:45 - 15:00</t>
-  </si>
-  <si>
-    <t>15:40 - 16:25</t>
-  </si>
-  <si>
     <t>16:45 - 17:00</t>
   </si>
   <si>
@@ -3904,13 +3888,45 @@
   </si>
   <si>
     <t>CATALYTIC INTERFACE</t>
+  </si>
+  <si>
+    <t>COLLABORATIVE PATHWAYS TO SUSTAINABLE DIGITAL
+INNOVATION IN AEC</t>
+  </si>
+  <si>
+    <t>AUGMENTATION IN DESIGN AND FABRICATION: EXPANDING THE
+ROLE OF AR AND HUMAN-MACHINE COLLABORATION</t>
+  </si>
+  <si>
+    <t>A FULL-PROCESS DIGITAL METHOD FOR RECURSIVE GEOMETRIC STRUCTURE AND MACHINING PARAMETER GENERATION TARGETING THE REUTILIZATION OF CURVED TIMBER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:05 – 15:20 </t>
+  </si>
+  <si>
+    <t>15:20 – 15:35</t>
+  </si>
+  <si>
+    <t>15:35 – 15:50</t>
+  </si>
+  <si>
+    <t>15:50 – 16:05</t>
+  </si>
+  <si>
+    <t>13:55 - 14:10</t>
+  </si>
+  <si>
+    <t>14:10 - 14:25</t>
+  </si>
+  <si>
+    <t>14:25 - 14:40</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3962,10 +3978,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3973,13 +3992,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4017,7 +4044,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4051,6 +4078,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4085,9 +4113,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4260,11 +4289,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I88"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="52.33203125" customWidth="1"/>
+    <col min="4" max="4" width="40.33203125" customWidth="1"/>
+    <col min="7" max="7" width="21.1640625" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" customWidth="1"/>
+    <col min="9" max="9" width="39.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4290,7 +4326,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -4301,25 +4337,25 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G2" t="s">
         <v>269</v>
       </c>
-      <c r="G2" t="s">
-        <v>272</v>
-      </c>
       <c r="H2" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="I2" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -4330,25 +4366,25 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G3" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="H3" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="I3" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -4359,25 +4395,25 @@
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G4" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="H4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="I4" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -4388,25 +4424,25 @@
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F5" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G5" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H5" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="I5" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -4417,25 +4453,25 @@
         <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H6" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="I6" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -4446,25 +4482,25 @@
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G7" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H7" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="I7" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -4475,25 +4511,25 @@
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G8" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H8" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="I8" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -4504,25 +4540,25 @@
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F9" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H9" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="I9" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -4533,25 +4569,25 @@
         <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F10" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G10" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H10" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="I10" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -4562,25 +4598,25 @@
         <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E11" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F11" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G11" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H11" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="I11" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -4591,25 +4627,25 @@
         <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E12" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F12" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G12" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H12" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="I12" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -4620,25 +4656,25 @@
         <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E13" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F13" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G13" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H13" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="I13" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -4649,25 +4685,25 @@
         <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E14" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F14" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G14" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H14" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="I14" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -4678,25 +4714,25 @@
         <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E15" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F15" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G15" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H15" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="I15" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -4707,25 +4743,25 @@
         <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E16" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F16" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G16" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H16" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="I16" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -4736,25 +4772,25 @@
         <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E17" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F17" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G17" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H17" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="I17" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -4765,25 +4801,25 @@
         <v>24</v>
       </c>
       <c r="D18" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E18" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F18" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G18" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H18" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="I18" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -4794,25 +4830,25 @@
         <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E19" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F19" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G19" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H19" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="I19" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -4823,25 +4859,25 @@
         <v>26</v>
       </c>
       <c r="D20" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E20" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F20" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G20" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="H20" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="I20" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -4852,25 +4888,25 @@
         <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E21" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F21" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G21" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="H21" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="I21" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -4881,25 +4917,25 @@
         <v>28</v>
       </c>
       <c r="D22" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E22" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F22" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G22" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="H22" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="I22" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -4910,25 +4946,25 @@
         <v>29</v>
       </c>
       <c r="D23" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E23" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F23" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G23" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H23" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="I23" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -4939,25 +4975,25 @@
         <v>30</v>
       </c>
       <c r="D24" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E24" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F24" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G24" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="H24" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="I24" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -4968,25 +5004,25 @@
         <v>31</v>
       </c>
       <c r="D25" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E25" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F25" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G25" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="H25" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="I25" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -4997,25 +5033,25 @@
         <v>32</v>
       </c>
       <c r="D26" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E26" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F26" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G26" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="H26" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="I26" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -5026,25 +5062,25 @@
         <v>33</v>
       </c>
       <c r="D27" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E27" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F27" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G27" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H27" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="I27" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -5055,25 +5091,25 @@
         <v>34</v>
       </c>
       <c r="D28" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E28" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F28" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G28" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H28" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="I28" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -5084,25 +5120,25 @@
         <v>35</v>
       </c>
       <c r="D29" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E29" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F29" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G29" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H29" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="I29" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -5113,25 +5149,25 @@
         <v>36</v>
       </c>
       <c r="D30" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E30" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F30" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G30" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="H30" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="I30" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -5142,25 +5178,25 @@
         <v>37</v>
       </c>
       <c r="D31" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E31" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F31" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G31" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H31" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="I31" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -5171,25 +5207,25 @@
         <v>38</v>
       </c>
       <c r="D32" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E32" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F32" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G32" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H32" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="I32" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -5200,25 +5236,25 @@
         <v>39</v>
       </c>
       <c r="D33" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E33" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F33" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G33" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H33" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="I33" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -5229,25 +5265,25 @@
         <v>40</v>
       </c>
       <c r="D34" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E34" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F34" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G34" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H34" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="I34" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -5258,25 +5294,25 @@
         <v>41</v>
       </c>
       <c r="D35" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E35" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F35" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G35" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H35" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="I35" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -5287,25 +5323,25 @@
         <v>42</v>
       </c>
       <c r="D36" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E36" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F36" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G36" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H36" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="I36" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -5316,25 +5352,25 @@
         <v>43</v>
       </c>
       <c r="D37" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E37" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F37" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G37" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H37" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="I37" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -5345,25 +5381,25 @@
         <v>44</v>
       </c>
       <c r="D38" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E38" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F38" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G38" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="H38" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="I38" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -5374,25 +5410,25 @@
         <v>45</v>
       </c>
       <c r="D39" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E39" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F39" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G39" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="H39" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="I39" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -5403,25 +5439,25 @@
         <v>46</v>
       </c>
       <c r="D40" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E40" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F40" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G40" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="H40" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="I40" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -5432,25 +5468,25 @@
         <v>47</v>
       </c>
       <c r="D41" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E41" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F41" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G41" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="H41" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="I41" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -5461,25 +5497,25 @@
         <v>48</v>
       </c>
       <c r="D42" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E42" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F42" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G42" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H42" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="I42" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -5490,25 +5526,25 @@
         <v>49</v>
       </c>
       <c r="D43" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E43" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F43" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G43" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H43" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="I43" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -5519,25 +5555,25 @@
         <v>50</v>
       </c>
       <c r="D44" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E44" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F44" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G44" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H44" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="I44" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -5548,25 +5584,25 @@
         <v>51</v>
       </c>
       <c r="D45" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E45" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F45" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G45" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H45" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="I45" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -5577,25 +5613,25 @@
         <v>52</v>
       </c>
       <c r="D46" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E46" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F46" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G46" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H46" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="I46" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -5606,25 +5642,25 @@
         <v>53</v>
       </c>
       <c r="D47" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E47" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F47" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G47" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H47" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="I47" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -5635,25 +5671,25 @@
         <v>54</v>
       </c>
       <c r="D48" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E48" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F48" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G48" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H48" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="I48" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -5664,25 +5700,25 @@
         <v>55</v>
       </c>
       <c r="D49" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E49" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F49" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G49" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H49" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="I49" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -5693,25 +5729,25 @@
         <v>56</v>
       </c>
       <c r="D50" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E50" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F50" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G50" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H50" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="I50" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -5722,25 +5758,25 @@
         <v>57</v>
       </c>
       <c r="D51" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E51" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F51" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G51" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H51" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="I51" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -5748,28 +5784,28 @@
         <v>27</v>
       </c>
       <c r="C52" t="s">
-        <v>58</v>
+        <v>354</v>
       </c>
       <c r="D52" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E52" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F52" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G52" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H52" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="I52" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -5777,28 +5813,28 @@
         <v>210</v>
       </c>
       <c r="C53" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D53" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E53" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F53" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G53" t="s">
-        <v>296</v>
+        <v>355</v>
       </c>
       <c r="H53" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="I53" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -5806,28 +5842,28 @@
         <v>440</v>
       </c>
       <c r="C54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D54" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E54" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F54" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G54" t="s">
-        <v>297</v>
+        <v>356</v>
       </c>
       <c r="H54" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="I54" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -5835,28 +5871,28 @@
         <v>431</v>
       </c>
       <c r="C55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D55" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E55" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F55" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G55" t="s">
-        <v>298</v>
+        <v>357</v>
       </c>
       <c r="H55" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="I55" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -5864,28 +5900,28 @@
         <v>314</v>
       </c>
       <c r="C56" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D56" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E56" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F56" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G56" t="s">
-        <v>299</v>
+        <v>358</v>
       </c>
       <c r="H56" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="I56" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -5893,28 +5929,28 @@
         <v>50</v>
       </c>
       <c r="C57" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D57" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E57" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F57" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G57" t="s">
-        <v>300</v>
+        <v>359</v>
       </c>
       <c r="H57" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="I57" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -5922,28 +5958,28 @@
         <v>198</v>
       </c>
       <c r="C58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D58" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E58" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F58" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G58" t="s">
-        <v>285</v>
+        <v>360</v>
       </c>
       <c r="H58" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="I58" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -5951,28 +5987,28 @@
         <v>250</v>
       </c>
       <c r="C59" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D59" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E59" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F59" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G59" t="s">
-        <v>286</v>
+        <v>361</v>
       </c>
       <c r="H59" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="I59" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>28</v>
       </c>
@@ -5980,28 +6016,28 @@
         <v>132</v>
       </c>
       <c r="C60" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D60" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E60" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F60" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G60" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="H60" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="I60" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -6009,28 +6045,28 @@
         <v>193</v>
       </c>
       <c r="C61" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D61" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E61" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F61" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G61" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="H61" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="I61" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -6038,28 +6074,28 @@
         <v>386</v>
       </c>
       <c r="C62" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D62" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E62" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F62" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G62" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="H62" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="I62" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -6067,28 +6103,28 @@
         <v>178</v>
       </c>
       <c r="C63" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D63" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E63" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F63" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G63" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H63" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="I63" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -6096,28 +6132,28 @@
         <v>444</v>
       </c>
       <c r="C64" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D64" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E64" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F64" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G64" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="H64" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="I64" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -6125,28 +6161,28 @@
         <v>403</v>
       </c>
       <c r="C65" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D65" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E65" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F65" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G65" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H65" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="I65" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -6154,28 +6190,28 @@
         <v>253</v>
       </c>
       <c r="C66" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D66" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E66" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F66" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G66" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H66" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="I66" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -6183,28 +6219,28 @@
         <v>68</v>
       </c>
       <c r="C67" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D67" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E67" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F67" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G67" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="H67" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="I67" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -6212,28 +6248,28 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D68" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E68" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F68" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G68" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="H68" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="I68" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -6241,28 +6277,28 @@
         <v>276</v>
       </c>
       <c r="C69" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D69" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E69" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F69" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G69" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="H69" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="I69" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -6270,28 +6306,28 @@
         <v>313</v>
       </c>
       <c r="C70" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D70" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E70" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F70" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G70" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="H70" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="I70" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -6299,28 +6335,28 @@
         <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D71" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E71" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F71" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G71" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="H71" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="I71" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -6328,28 +6364,28 @@
         <v>379</v>
       </c>
       <c r="C72" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D72" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E72" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F72" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G72" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="H72" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="I72" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -6357,28 +6393,28 @@
         <v>133</v>
       </c>
       <c r="C73" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D73" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E73" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="F73" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G73" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="H73" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="I73" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -6386,28 +6422,28 @@
         <v>145</v>
       </c>
       <c r="C74" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D74" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E74" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F74" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G74" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="H74" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="I74" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -6415,28 +6451,28 @@
         <v>19</v>
       </c>
       <c r="C75" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D75" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E75" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F75" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G75" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="H75" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="I75" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -6444,28 +6480,28 @@
         <v>428</v>
       </c>
       <c r="C76" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D76" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E76" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F76" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G76" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="H76" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="I76" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -6473,28 +6509,28 @@
         <v>395</v>
       </c>
       <c r="C77" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D77" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E77" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F77" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G77" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="H77" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="I77" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -6502,28 +6538,28 @@
         <v>111</v>
       </c>
       <c r="C78" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D78" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E78" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F78" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G78" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="H78" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="I78" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>86</v>
       </c>
@@ -6531,28 +6567,28 @@
         <v>457</v>
       </c>
       <c r="C79" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D79" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E79" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F79" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G79" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="H79" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="I79" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>77</v>
       </c>
@@ -6560,28 +6596,28 @@
         <v>114</v>
       </c>
       <c r="C80" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D80" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E80" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F80" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G80" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="H80" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="I80" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>78</v>
       </c>
@@ -6589,28 +6625,28 @@
         <v>231</v>
       </c>
       <c r="C81" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D81" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E81" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F81" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G81" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="H81" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="I81" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>79</v>
       </c>
@@ -6618,57 +6654,57 @@
         <v>230</v>
       </c>
       <c r="C82" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D82" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E82" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F82" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G82" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="H82" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="I82" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>80</v>
       </c>
       <c r="B83">
         <v>82</v>
       </c>
-      <c r="C83" t="s">
-        <v>89</v>
+      <c r="C83" s="2" t="s">
+        <v>352</v>
       </c>
       <c r="D83" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E83" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F83" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G83" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="H83" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="I83" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>81</v>
       </c>
@@ -6676,57 +6712,57 @@
         <v>330</v>
       </c>
       <c r="C84" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D84" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E84" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F84" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G84" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="H84" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="I84" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="64" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>82</v>
       </c>
       <c r="B85">
         <v>389</v>
       </c>
-      <c r="C85" t="s">
-        <v>91</v>
+      <c r="C85" s="2" t="s">
+        <v>353</v>
       </c>
       <c r="D85" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E85" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F85" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G85" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="H85" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="I85" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>83</v>
       </c>
@@ -6734,28 +6770,28 @@
         <v>427</v>
       </c>
       <c r="C86" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D86" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E86" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F86" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G86" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="H86" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="I86" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>84</v>
       </c>
@@ -6763,28 +6799,28 @@
         <v>445</v>
       </c>
       <c r="C87" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D87" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E87" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F87" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G87" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="H87" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="I87" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>85</v>
       </c>
@@ -6792,25 +6828,25 @@
         <v>458</v>
       </c>
       <c r="C88" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D88" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E88" t="s">
+        <v>265</v>
+      </c>
+      <c r="F88" t="s">
         <v>268</v>
       </c>
-      <c r="F88" t="s">
-        <v>271</v>
-      </c>
       <c r="G88" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="H88" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="I88" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>

--- a/images/events/cf25dat.xlsx
+++ b/images/events/cf25dat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tamk/Documents/GitHub/clementinec.github.io/images/events/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB6294A-C209-5542-A5E3-0669429BCAE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7326CEBF-7612-D44E-9BB2-D25F9D686D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="26880" yWindow="-20760" windowWidth="35240" windowHeight="19740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6675,7 +6675,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>80</v>
       </c>
@@ -6733,7 +6733,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="64" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>82</v>
       </c>

--- a/images/events/cf25dat.xlsx
+++ b/images/events/cf25dat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tamk/Documents/GitHub/clementinec.github.io/images/events/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7326CEBF-7612-D44E-9BB2-D25F9D686D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6492BC6E-B538-2448-8181-747C76334716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26880" yWindow="-20760" windowWidth="35240" windowHeight="19740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26860" yWindow="-20760" windowWidth="35240" windowHeight="19740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6675,21 +6675,21 @@
         <v>350</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>80</v>
       </c>
       <c r="B83">
-        <v>82</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>352</v>
+        <v>458</v>
+      </c>
+      <c r="C83" t="s">
+        <v>91</v>
       </c>
       <c r="D83" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E83" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F83" t="s">
         <v>268</v>
@@ -6704,21 +6704,21 @@
         <v>351</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>81</v>
       </c>
       <c r="B84">
-        <v>330</v>
-      </c>
-      <c r="C84" t="s">
-        <v>88</v>
+        <v>82</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>352</v>
       </c>
       <c r="D84" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E84" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F84" t="s">
         <v>268</v>
@@ -6733,21 +6733,21 @@
         <v>351</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>82</v>
       </c>
       <c r="B85">
-        <v>389</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>353</v>
+        <v>330</v>
+      </c>
+      <c r="C85" t="s">
+        <v>88</v>
       </c>
       <c r="D85" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E85" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F85" t="s">
         <v>268</v>
@@ -6762,21 +6762,21 @@
         <v>351</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>83</v>
       </c>
       <c r="B86">
-        <v>427</v>
-      </c>
-      <c r="C86" t="s">
-        <v>89</v>
+        <v>389</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>353</v>
       </c>
       <c r="D86" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E86" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F86" t="s">
         <v>268</v>
@@ -6796,16 +6796,16 @@
         <v>84</v>
       </c>
       <c r="B87">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="C87" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D87" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E87" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F87" t="s">
         <v>268</v>
@@ -6825,16 +6825,16 @@
         <v>85</v>
       </c>
       <c r="B88">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="C88" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D88" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E88" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F88" t="s">
         <v>268</v>

--- a/images/events/cf25dat.xlsx
+++ b/images/events/cf25dat.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10608"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tamk/Documents/GitHub/clementinec.github.io/images/events/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6492BC6E-B538-2448-8181-747C76334716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26860" yWindow="-20760" windowWidth="35240" windowHeight="19740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="358">
   <si>
     <t>ID</t>
   </si>
@@ -194,6 +188,11 @@
   </si>
   <si>
     <t>PERFORMANCE-BASED URBAN ENVIRONMENTAL RESTORATION: A MULTI-LAYER CELLULAR AUTOMATA MODEL FOR ECOLOGICAL DESIGN SIMULATION IN HIGH-DENSITY CITIES</t>
+  </si>
+  <si>
+    <t>A Full-Process Digital Method for Recursive Geometric
+Structure and Machining Parameter Generation Targeting the
+Reutilization of Curved Timber</t>
   </si>
   <si>
     <t>DISCOVERING PARETO-EFFICIENT URBAN NETWORKS THROUGH SHAPE GRAMMAR, MULTI-OBJECTIVE OPTIMISATION AND MACHINE LEARNING</t>
@@ -288,9 +287,17 @@
     <t>COMPUTING BEYOND THE VITRUVIAN CANON: AMBIGUITY AS A CATALYST IN COMPUTATIONAL DESIGN THEORY</t>
   </si>
   <si>
+    <t>(CI) COLLABORATIVE PATHWAYS TO SUSTAINABLE DIGITAL
+INNOVATION IN AEC</t>
+  </si>
+  <si>
     <t>RETHINKING PARTICIPATORY ARCHITECTURAL DESIGN: HARNESSING
 IMMERSIVE ENVIRONMENTS &amp; AI FOR FACILITATING
 DESIGNER-STAKEHOLDER COLLABORATION</t>
+  </si>
+  <si>
+    <t>(CI) AUGMENTATION IN DESIGN AND FABRICATION: EXPANDING THE
+ROLE OF AR AND HUMAN-MACHINE COLLABORATION</t>
   </si>
   <si>
     <t>TOWARD AIXR: DESIGNING A FRAMEWORK FOR AI-INFORMED
@@ -3719,6 +3726,15 @@
     <t>14:15 - 14:30</t>
   </si>
   <si>
+    <t>14:30 - 14:45</t>
+  </si>
+  <si>
+    <t>14:45 - 15:00</t>
+  </si>
+  <si>
+    <t>15:40 - 16:25</t>
+  </si>
+  <si>
     <t>16:45 - 17:00</t>
   </si>
   <si>
@@ -3888,45 +3904,13 @@
   </si>
   <si>
     <t>CATALYTIC INTERFACE</t>
-  </si>
-  <si>
-    <t>COLLABORATIVE PATHWAYS TO SUSTAINABLE DIGITAL
-INNOVATION IN AEC</t>
-  </si>
-  <si>
-    <t>AUGMENTATION IN DESIGN AND FABRICATION: EXPANDING THE
-ROLE OF AR AND HUMAN-MACHINE COLLABORATION</t>
-  </si>
-  <si>
-    <t>A FULL-PROCESS DIGITAL METHOD FOR RECURSIVE GEOMETRIC STRUCTURE AND MACHINING PARAMETER GENERATION TARGETING THE REUTILIZATION OF CURVED TIMBER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:05 – 15:20 </t>
-  </si>
-  <si>
-    <t>15:20 – 15:35</t>
-  </si>
-  <si>
-    <t>15:35 – 15:50</t>
-  </si>
-  <si>
-    <t>15:50 – 16:05</t>
-  </si>
-  <si>
-    <t>13:55 - 14:10</t>
-  </si>
-  <si>
-    <t>14:10 - 14:25</t>
-  </si>
-  <si>
-    <t>14:25 - 14:40</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3978,13 +3962,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3992,21 +3973,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4044,7 +4017,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4078,7 +4051,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4113,10 +4085,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4289,18 +4260,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I88"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="3" max="3" width="52.33203125" customWidth="1"/>
-    <col min="4" max="4" width="40.33203125" customWidth="1"/>
-    <col min="7" max="7" width="21.1640625" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
-    <col min="9" max="9" width="39.83203125" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4326,7 +4290,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -4337,25 +4301,25 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="H2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="I2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -4366,25 +4330,25 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H3" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="I3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -4395,25 +4359,25 @@
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G4" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="H4" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="I4" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -4424,25 +4388,25 @@
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F5" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G5" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="H5" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="I5" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -4453,25 +4417,25 @@
         <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G6" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="H6" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="I6" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -4482,25 +4446,25 @@
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F7" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G7" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="H7" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="I7" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -4511,25 +4475,25 @@
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F8" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G8" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="H8" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="I8" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -4540,25 +4504,25 @@
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F9" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G9" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H9" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="I9" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -4569,25 +4533,25 @@
         <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E10" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F10" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H10" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="I10" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -4598,25 +4562,25 @@
         <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E11" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F11" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H11" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="I11" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -4627,25 +4591,25 @@
         <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E12" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F12" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G12" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H12" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="I12" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -4656,25 +4620,25 @@
         <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E13" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F13" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G13" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="H13" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="I13" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -4685,25 +4649,25 @@
         <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E14" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F14" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G14" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="H14" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="I14" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -4714,25 +4678,25 @@
         <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F15" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G15" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="H15" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="I15" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -4743,25 +4707,25 @@
         <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F16" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G16" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="H16" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="I16" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -4772,25 +4736,25 @@
         <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E17" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F17" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G17" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H17" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="I17" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -4801,25 +4765,25 @@
         <v>24</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E18" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F18" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G18" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H18" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="I18" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -4830,25 +4794,25 @@
         <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E19" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F19" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G19" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H19" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="I19" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -4859,25 +4823,25 @@
         <v>26</v>
       </c>
       <c r="D20" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E20" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F20" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G20" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="H20" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="I20" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -4888,25 +4852,25 @@
         <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E21" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F21" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G21" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="H21" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="I21" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -4917,25 +4881,25 @@
         <v>28</v>
       </c>
       <c r="D22" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E22" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F22" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G22" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="H22" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="I22" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -4946,25 +4910,25 @@
         <v>29</v>
       </c>
       <c r="D23" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E23" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F23" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G23" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="H23" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="I23" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -4975,25 +4939,25 @@
         <v>30</v>
       </c>
       <c r="D24" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E24" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F24" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G24" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="H24" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="I24" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -5004,25 +4968,25 @@
         <v>31</v>
       </c>
       <c r="D25" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E25" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F25" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G25" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="H25" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="I25" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -5033,25 +4997,25 @@
         <v>32</v>
       </c>
       <c r="D26" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E26" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F26" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G26" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="H26" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="I26" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -5062,25 +5026,25 @@
         <v>33</v>
       </c>
       <c r="D27" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E27" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F27" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G27" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="H27" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="I27" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -5091,25 +5055,25 @@
         <v>34</v>
       </c>
       <c r="D28" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E28" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F28" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G28" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="H28" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="I28" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -5120,25 +5084,25 @@
         <v>35</v>
       </c>
       <c r="D29" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E29" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F29" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G29" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="H29" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="I29" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -5149,25 +5113,25 @@
         <v>36</v>
       </c>
       <c r="D30" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E30" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F30" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G30" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="H30" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="I30" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -5178,25 +5142,25 @@
         <v>37</v>
       </c>
       <c r="D31" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E31" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F31" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G31" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="H31" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="I31" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -5207,25 +5171,25 @@
         <v>38</v>
       </c>
       <c r="D32" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E32" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F32" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G32" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="H32" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="I32" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -5236,25 +5200,25 @@
         <v>39</v>
       </c>
       <c r="D33" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E33" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F33" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G33" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="H33" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="I33" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -5265,25 +5229,25 @@
         <v>40</v>
       </c>
       <c r="D34" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E34" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F34" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G34" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H34" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="I34" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -5294,25 +5258,25 @@
         <v>41</v>
       </c>
       <c r="D35" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E35" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F35" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G35" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H35" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="I35" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -5323,25 +5287,25 @@
         <v>42</v>
       </c>
       <c r="D36" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E36" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F36" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G36" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H36" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="I36" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -5352,25 +5316,25 @@
         <v>43</v>
       </c>
       <c r="D37" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E37" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F37" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G37" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H37" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="I37" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -5381,25 +5345,25 @@
         <v>44</v>
       </c>
       <c r="D38" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E38" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F38" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G38" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="H38" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="I38" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -5410,25 +5374,25 @@
         <v>45</v>
       </c>
       <c r="D39" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E39" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F39" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G39" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="H39" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="I39" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -5439,25 +5403,25 @@
         <v>46</v>
       </c>
       <c r="D40" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E40" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F40" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G40" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="H40" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="I40" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -5468,25 +5432,25 @@
         <v>47</v>
       </c>
       <c r="D41" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E41" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F41" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G41" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="H41" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="I41" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -5497,25 +5461,25 @@
         <v>48</v>
       </c>
       <c r="D42" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E42" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F42" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G42" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="H42" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="I42" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -5526,25 +5490,25 @@
         <v>49</v>
       </c>
       <c r="D43" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E43" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F43" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G43" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="H43" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="I43" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -5555,25 +5519,25 @@
         <v>50</v>
       </c>
       <c r="D44" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E44" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F44" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G44" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="H44" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="I44" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -5584,25 +5548,25 @@
         <v>51</v>
       </c>
       <c r="D45" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E45" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F45" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G45" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="H45" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="I45" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -5613,25 +5577,25 @@
         <v>52</v>
       </c>
       <c r="D46" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E46" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F46" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G46" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H46" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="I46" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -5642,25 +5606,25 @@
         <v>53</v>
       </c>
       <c r="D47" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E47" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F47" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G47" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H47" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="I47" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -5671,25 +5635,25 @@
         <v>54</v>
       </c>
       <c r="D48" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E48" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F48" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G48" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H48" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="I48" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -5700,25 +5664,25 @@
         <v>55</v>
       </c>
       <c r="D49" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E49" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F49" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G49" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H49" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="I49" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -5729,25 +5693,25 @@
         <v>56</v>
       </c>
       <c r="D50" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E50" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F50" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G50" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="H50" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="I50" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -5758,25 +5722,25 @@
         <v>57</v>
       </c>
       <c r="D51" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E51" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F51" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G51" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="H51" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="I51" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -5784,28 +5748,28 @@
         <v>27</v>
       </c>
       <c r="C52" t="s">
-        <v>354</v>
+        <v>58</v>
       </c>
       <c r="D52" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E52" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F52" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G52" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="H52" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="I52" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -5813,28 +5777,28 @@
         <v>210</v>
       </c>
       <c r="C53" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D53" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E53" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F53" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G53" t="s">
-        <v>355</v>
+        <v>296</v>
       </c>
       <c r="H53" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="I53" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -5842,28 +5806,28 @@
         <v>440</v>
       </c>
       <c r="C54" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D54" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E54" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F54" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G54" t="s">
-        <v>356</v>
+        <v>297</v>
       </c>
       <c r="H54" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="I54" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -5871,28 +5835,28 @@
         <v>431</v>
       </c>
       <c r="C55" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D55" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E55" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="F55" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G55" t="s">
-        <v>357</v>
+        <v>298</v>
       </c>
       <c r="H55" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="I55" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -5900,28 +5864,28 @@
         <v>314</v>
       </c>
       <c r="C56" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D56" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E56" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F56" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G56" t="s">
-        <v>358</v>
+        <v>299</v>
       </c>
       <c r="H56" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="I56" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -5929,28 +5893,28 @@
         <v>50</v>
       </c>
       <c r="C57" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D57" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E57" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F57" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G57" t="s">
-        <v>359</v>
+        <v>300</v>
       </c>
       <c r="H57" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="I57" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -5958,28 +5922,28 @@
         <v>198</v>
       </c>
       <c r="C58" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D58" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E58" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F58" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G58" t="s">
-        <v>360</v>
+        <v>285</v>
       </c>
       <c r="H58" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="I58" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -5987,28 +5951,28 @@
         <v>250</v>
       </c>
       <c r="C59" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D59" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E59" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F59" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G59" t="s">
-        <v>361</v>
+        <v>286</v>
       </c>
       <c r="H59" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="I59" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" s="1">
         <v>28</v>
       </c>
@@ -6016,28 +5980,28 @@
         <v>132</v>
       </c>
       <c r="C60" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D60" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E60" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F60" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G60" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="H60" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="I60" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -6045,28 +6009,28 @@
         <v>193</v>
       </c>
       <c r="C61" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D61" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E61" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F61" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G61" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="H61" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="I61" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -6074,28 +6038,28 @@
         <v>386</v>
       </c>
       <c r="C62" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D62" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E62" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F62" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G62" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="H62" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="I62" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -6103,28 +6067,28 @@
         <v>178</v>
       </c>
       <c r="C63" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D63" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E63" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F63" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G63" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="H63" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="I63" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -6132,28 +6096,28 @@
         <v>444</v>
       </c>
       <c r="C64" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D64" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E64" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="F64" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G64" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="H64" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="I64" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -6161,28 +6125,28 @@
         <v>403</v>
       </c>
       <c r="C65" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D65" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E65" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F65" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G65" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="H65" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="I65" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -6190,28 +6154,28 @@
         <v>253</v>
       </c>
       <c r="C66" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D66" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E66" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F66" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G66" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="H66" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="I66" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -6219,28 +6183,28 @@
         <v>68</v>
       </c>
       <c r="C67" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D67" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E67" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F67" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G67" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="H67" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="I67" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -6248,28 +6212,28 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D68" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E68" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F68" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G68" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="H68" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="I68" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -6277,28 +6241,28 @@
         <v>276</v>
       </c>
       <c r="C69" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D69" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E69" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F69" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G69" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="H69" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="I69" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -6306,28 +6270,28 @@
         <v>313</v>
       </c>
       <c r="C70" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D70" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E70" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F70" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G70" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="H70" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="I70" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -6335,28 +6299,28 @@
         <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D71" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E71" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F71" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G71" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="H71" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="I71" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -6364,28 +6328,28 @@
         <v>379</v>
       </c>
       <c r="C72" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D72" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E72" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F72" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G72" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="H72" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="I72" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -6393,28 +6357,28 @@
         <v>133</v>
       </c>
       <c r="C73" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D73" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E73" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F73" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G73" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="H73" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="I73" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -6422,28 +6386,28 @@
         <v>145</v>
       </c>
       <c r="C74" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D74" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E74" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F74" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G74" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="H74" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="I74" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -6451,28 +6415,28 @@
         <v>19</v>
       </c>
       <c r="C75" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D75" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E75" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F75" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G75" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="H75" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="I75" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -6480,28 +6444,28 @@
         <v>428</v>
       </c>
       <c r="C76" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D76" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E76" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F76" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G76" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="H76" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="I76" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -6509,28 +6473,28 @@
         <v>395</v>
       </c>
       <c r="C77" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D77" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E77" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F77" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G77" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="H77" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="I77" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -6538,28 +6502,28 @@
         <v>111</v>
       </c>
       <c r="C78" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D78" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E78" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F78" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G78" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="H78" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="I78" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
       <c r="A79" s="1">
         <v>86</v>
       </c>
@@ -6567,28 +6531,28 @@
         <v>457</v>
       </c>
       <c r="C79" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D79" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E79" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F79" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G79" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="H79" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="I79" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
       <c r="A80" s="1">
         <v>77</v>
       </c>
@@ -6596,28 +6560,28 @@
         <v>114</v>
       </c>
       <c r="C80" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D80" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E80" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F80" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G80" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="H80" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="I80" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
       <c r="A81" s="1">
         <v>78</v>
       </c>
@@ -6625,28 +6589,28 @@
         <v>231</v>
       </c>
       <c r="C81" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D81" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E81" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F81" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G81" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="H81" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="I81" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
       <c r="A82" s="1">
         <v>79</v>
       </c>
@@ -6654,199 +6618,199 @@
         <v>230</v>
       </c>
       <c r="C82" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D82" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E82" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F82" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G82" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="H82" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="I82" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
       <c r="A83" s="1">
         <v>80</v>
       </c>
       <c r="B83">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="C83" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D83" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E83" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F83" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G83" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="H83" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="I83" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
       <c r="A84" s="1">
         <v>81</v>
       </c>
       <c r="B84">
-        <v>82</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>352</v>
+        <v>330</v>
+      </c>
+      <c r="C84" t="s">
+        <v>90</v>
       </c>
       <c r="D84" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E84" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F84" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G84" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="H84" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="I84" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
       <c r="A85" s="1">
         <v>82</v>
       </c>
       <c r="B85">
-        <v>330</v>
+        <v>389</v>
       </c>
       <c r="C85" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D85" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E85" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="F85" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G85" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="H85" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="I85" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
       <c r="A86" s="1">
         <v>83</v>
       </c>
       <c r="B86">
-        <v>389</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>353</v>
+        <v>427</v>
+      </c>
+      <c r="C86" t="s">
+        <v>92</v>
       </c>
       <c r="D86" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E86" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="F86" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G86" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="H86" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="I86" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
       <c r="A87" s="1">
         <v>84</v>
       </c>
       <c r="B87">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="C87" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D87" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E87" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F87" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G87" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="H87" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="I87" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
       <c r="A88" s="1">
         <v>85</v>
       </c>
       <c r="B88">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="C88" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D88" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E88" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F88" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G88" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="H88" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="I88" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>

--- a/images/events/cf25dat.xlsx
+++ b/images/events/cf25dat.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="360">
   <si>
     <t>ID</t>
   </si>
@@ -40,276 +40,354 @@
     <t>Final Topic</t>
   </si>
   <si>
-    <t>DESIGN VALIDATION FOR ROBOTIC FABRICATION: A MULTI-STAGE FRAMEWORK FOR COMPLEX AND NON-REPETITIVE PROCESSES (EDITED)</t>
-  </si>
-  <si>
-    <t>TPACS: PHYGITAL-AIDED CONSTRUCTION SYSTEM BASED ON MODULAR CUSTOMIZABLE TIMBER FABRICATION</t>
-  </si>
-  <si>
-    <t>PARAMETRIC BIOMIMICRY: TRANSLATING SPIRAL SEASHELL FORMATION INTO ROBOTIC 3D PRINTING</t>
-  </si>
-  <si>
-    <t>REC-ARCH: A CASE STUDY RECOMMENDER SYSTEM FOR ARCHITECTS USING VISION AND LANGUAGE MODELS</t>
-  </si>
-  <si>
-    <t>MACHINE LEARNING AND MIXED REALITY-CONTROLLED CABLE ROBOTS FOR REAL-TIME CONSTRUCTION AUTOMATION</t>
-  </si>
-  <si>
-    <t>DESIGN AND MANUFACTURE OF WASTE TIMBER COMPOSITE PANELS: SUSTAINABLE AND INNOVATIVE USE OF RECYCLED TIMBER</t>
-  </si>
-  <si>
-    <t>SUPERIORITY OF HIGH-DIMENSIONAL LATENT VARIABLE REPRESENTATION IN URBAN SPATIAL STRUCTURE: EVIDENCE FROM AN URBAN CLIMATE STUDY</t>
-  </si>
-  <si>
-    <t>ENHANCING ROBOTIC EMBODIMENT IN ARCHITECTURE: AN INTELLIGENT APPROACH COMBINING VISION SYSTEMS AND GENERATIVE NEURAL NETWORKS FOR AUTONOMOUS DESIGN-TO-PRODUCTION</t>
-  </si>
-  <si>
-    <t>COLLABORATIVE, CONVERSATIONAL ARCHITECTURAL DESIGN PROCESS BETWEEN HUMAN DESIGNERS AND MULTIMODAL AI AGENTS FOR EARLY-STAGE DESIGN EXPLORATION</t>
-  </si>
-  <si>
-    <t>BOUNDARY VITALITY: ANALYZING URBAN PUBLIC PERCEPTION OF SPATIAL AND VISUAL ELEMENTS IN MANHATTAN</t>
-  </si>
-  <si>
-    <t>FROM CRAFT TO COMMUNITY: PARTICIPATORY UPCYCLING IN PUBLIC HOUSING VIA DIGITAL FABRICATION</t>
-  </si>
-  <si>
-    <t>MATERIAL REUSE IN HERITAGE CONSERVATION:  DEVELOPING A DIGITAL DESIGN-TO-PRODUCTION CIRCULAR WORKFLOW</t>
-  </si>
-  <si>
-    <t>ENHANCING END-TO-END PROCESSING, ANALYSIS, AND VISUALIZATION OF CITIZEN PARTICIPATION DATA IN URBAN DESIGN AND PLANNING</t>
-  </si>
-  <si>
-    <t>TWO-WAY INTERVENTIVE DESIGN AND MANUFACTURING: REAL-TIME DESIGN AND MATERIALITY VISUALIZATION THROUGH MIXED REALITY SYSTEMS BASED ON HAND TRACKING</t>
-  </si>
-  <si>
-    <t>GRASP-TO-MILL (GTM) INTEGRATED WORKFLOW FOR NATURAL LOG JOINT FABRICATION BASED ON MULTI-OBJECTIVE OPTIMIZATION ALGORITHM</t>
-  </si>
-  <si>
-    <t>AUGMENTED ASSEMBLY: AN EXPLORATION OF MODULAR DESIGN TO FABRICATION BASED ON EXTENDED REALITY</t>
-  </si>
-  <si>
-    <t>MORPHOLOGICAL SECTIONS THROUGH LATENT SPACE</t>
-  </si>
-  <si>
-    <t>DEEP PERCEPTUAL URBAN FORM</t>
-  </si>
-  <si>
-    <t>INTEGRATING AI TOOLS AND METHODS IN THE DESIGN PROCESS</t>
-  </si>
-  <si>
-    <t>BPMN-BASED BUILDING PROJECT LIFECYCLE ANALYSIS WITH A CORE OF BIM: TAKING A CAMPUS PROJECT AS AN EXAMPLE</t>
-  </si>
-  <si>
-    <t>STOCK-CONSTRAINED DESIGN OF IRREGULAR MATERIAL BASED ON GRAPH NEURAL NETWORKS</t>
-  </si>
-  <si>
-    <t>STEPWISE GENERATION METHOD FOR COMPETITION-LEVEL FLOOR PLANS OF MEDIUM AND LARGE-SCALE GYMNASIUMS BASED ON RULE CONSTRAINTS AND DIFFUSION MODELS</t>
-  </si>
-  <si>
-    <t>FLOOR PLAN AFFORDANCE PREDICTION:  IS THE FLOOR PLAN LAYOUT DETERMINED BY ITS OUTLINE OR THE ARCHITECT?</t>
-  </si>
-  <si>
-    <t>BRIDGING THE GAP: ENHANCING AI-GENERATED FLOOR PLANS WITH MULTI-MODAL DATA INTEGRATION</t>
-  </si>
-  <si>
-    <t>GENERATING OPEN OFFICE LAYOUTS USING FLEXIBLE ARCHITECTURAL COMPONENTS</t>
-  </si>
-  <si>
-    <t>TRANSFORMING ARCHITECTURAL EDUCATION: THE IMPACT OF VR AND AR ON UNDERSTANDING BUILDING ENERGY EFFICIENCY</t>
-  </si>
-  <si>
-    <t>EVALUATING AUGMENTED REALITY AS A TOOL FOR DEMOCRATIZING BUILT ENVIRONMENT DESIGN</t>
-  </si>
-  <si>
-    <t>OPEN-SOURCE APPROACHES TO INTEGRATING ADVANCED ROBOTIC SYSTEMS IN SUSTAINABLE DESIGN</t>
-  </si>
-  <si>
-    <t>AN URBAN MORPHOLOGY ANALYSIS FRAMEWORK FOR SYNERGISTIC IMPROVEMENT OF MULTIPLE PERFORMANCE OBJECTIVES: EXEMPLIFIED BY OUTDOOR THERMAL COMFORT AND BUILDING ENERGY EFFICIENCY</t>
-  </si>
-  <si>
-    <t>SHADOW-BASED PATH DETECTION IN RAPIDLY EXPANDING URBAN AREAS: UTILIZING SHADOW DETECTION AND GRAPH-BASED VECTORIZATION TO UNCOVER INFORMAL ROAD NETWORKS IN HIGH-DENSITY SLUM AREAS</t>
-  </si>
-  <si>
-    <t>A GRAPH-BASED PREDICTION MODEL FOR SUSTAINABLE URBAN RENEWAL: INTEGRATING GRAPH CONVOLUTIONAL NETWORKS FOR CONCRETE RECYCLING POTENTIAL EVALUATION</t>
-  </si>
-  <si>
-    <t>DIGITAL DESIGN SUPPORT FOR UAV DELIVERY NOISE REDUCTION STRATEGIES IN HIGH DENSITY URBAN ENVIRONMENTS</t>
-  </si>
-  <si>
-    <t>QUANTIFABLE AND UNQUANTIFABLE MACHINE LEARNING MODEL OR ARCHITECTURAL PREFERENCE PREDICTION BASED ON MBTI</t>
-  </si>
-  <si>
-    <t>ADAPTIVE DESIGN AND FABRICATION OF MODULAR TOPOLOGICAL INTERLOCKING ASSEMBLIES</t>
-  </si>
-  <si>
-    <t>GAMIFICATION AS A TOOL FOR ENHANCING PUBLIC ENGAGEMENT IN BUILT-ENVIRONMENT DESIGN.</t>
-  </si>
-  <si>
-    <t>COMPUTING URBAN TISSUE: LANDSLIDE MITIGATION STRATEGY OF URBAN INFRASTRUCTURE DESIGN</t>
-  </si>
-  <si>
-    <t>ADAPTIVE ORIGAMI: FABRICATION OF PNEUMATIC-ACTUATED ADAPTIVE FOLDING SYSTEM</t>
-  </si>
-  <si>
-    <t>QUANTIFYING ARCHITECTURAL EXPERIENCE USING VLMS: DOES AI DREAM OF RENDERED SPACES?</t>
-  </si>
-  <si>
-    <t>ARCHITECTURAL INTERFACES FOR SHARED SPACES – A MULTI-USER PERSPECTIVE ON INTELLIGENT ENVIRONMENT INTERACTIONS</t>
-  </si>
-  <si>
-    <t>SUSTAINABLE SUSTAINABLE SOCIAL BUILDING ASSISTANT (SSOBA): TRANSFORMING ENERGY USE VIA DIGITAL TWINS, ENVIRONMENTAL SENSING AND OCCUPANT BEHAVIOUR CHANGE</t>
-  </si>
-  <si>
-    <t>DEVELOPING STRESS-LINE RIBBED TIMBER SLABS: LAMINATING TIMBER RIBS WITH STAY-IN-PLACE FORMWORK</t>
-  </si>
-  <si>
-    <t>ZERO-SHOT ARCHITECTURAL STYLE CLASSIFICATION WITH LARGE LANGUAGE MODELS</t>
-  </si>
-  <si>
-    <t>UNDERSTAND URBAN BUILDING ENERGY CONSUMPTION WITH EXPLAINABLE MACHINE LEARNING APPROACHES</t>
-  </si>
-  <si>
-    <t>CRAFTING A PARTICIPATORY APPROACH TOWARDS TRADITIONAL VIETNAMESE WEAVING AND DIGITAL COMPUTATION</t>
-  </si>
-  <si>
-    <t>ENHANCING URBAN VITALITY THROUGH INTERACTIVE XR INSTALLATIONS: FOSTERING ENGAGEMENT AND ENVIRONMENTAL AWARENESS</t>
-  </si>
-  <si>
-    <t>EVALUATION METHOD OF AI-GENERATED ARCHITECTURAL FACADE IMAGES BASED ON DCNN</t>
-  </si>
-  <si>
-    <t>DESIGN QUALITY HOUSING ASSESSMENT METHODOLOGY: SUPPORTING HEURISTICS WITH EVIDENCE-BASED DECISION-MAKING</t>
-  </si>
-  <si>
-    <t>A FABRICATION GRAMMAR FOR ROBOTIC SAND PACKING:  FROM PRECISE ACTIONS TO EMERGENT SHAPES AND PATTERNS</t>
-  </si>
-  <si>
-    <t>INTELLIGENT SPATIAL PLANNING:  A MULTIDIMENSIONAL STUDY ON SWISS RESIDENTIAL DESIGN USING LARGE LANGUAGE MODEL (GPT-4)</t>
-  </si>
-  <si>
-    <t>PERFORMANCE-BASED URBAN ENVIRONMENTAL RESTORATION: A MULTI-LAYER CELLULAR AUTOMATA MODEL FOR ECOLOGICAL DESIGN SIMULATION IN HIGH-DENSITY CITIES</t>
-  </si>
-  <si>
-    <t>A Full-Process Digital Method for Recursive Geometric
-Structure and Machining Parameter Generation Targeting the
-Reutilization of Curved Timber</t>
-  </si>
-  <si>
-    <t>DISCOVERING PARETO-EFFICIENT URBAN NETWORKS THROUGH SHAPE GRAMMAR, MULTI-OBJECTIVE OPTIMISATION AND MACHINE LEARNING</t>
-  </si>
-  <si>
-    <t>ENCODING PERFORMANCE IN DIGITAL WEAVE DESIGN USING AI AND OPTIMISATION</t>
-  </si>
-  <si>
-    <t>IMPROVING ARCHITECTURAL FORM CLASSIFICATION THROUGH SALINGAROS’ METRICS AND TOPOLOGICAL DATA ANALYSIS</t>
-  </si>
-  <si>
-    <t>GENERATIVE DESIGN FOR COASTAL RESILIENCE: A COMPUTATIONAL APPROACH TO LIVING SHORELINES</t>
-  </si>
-  <si>
-    <t>URBAN VISUAL HETEROGENEITY: AN INTELLIGENT APPROACH TO EXAMINING TRAVEL PREFERENCES IN NANJING</t>
-  </si>
-  <si>
-    <t>REVEALING THE RELATIONSHIP BETWEEN SITE PLANNING STRATEGIES AND SENTIMENT THROUGH DEEP LEARNING: ENHANCING DATA-DRIVEN ARCHITECTURAL DESIGN STRATEGIES</t>
-  </si>
-  <si>
-    <t>HOW CHINESE IS CHINATOWN: MEASURING THE RELATIONSHIP BETWEEN GEOGRAPHIC AUTHENTICITY PERCEPTION AND STREETSCAPE FEATURES THROUGH MACHINE LEARNING</t>
-  </si>
-  <si>
-    <t>ROBOTIC FABRICATION AND IN-SITU 3D PRINTING FOR A NATURAL TIMBER-BAMBOO STRUCTURE</t>
-  </si>
-  <si>
-    <t>INVESTIGATING SELF-SHAPING FIBRE COMPOSITES: TUNNING CURING PARAMETERS TO OPTIMISE RESULTING CURVATURE</t>
-  </si>
-  <si>
-    <t>PREDICTING STRESS-STRAIN CHARACTERISTICS OF 3D PRINTED BCC LATTICE STRUCTURES WITH VARIABLE GRID GRADATION USING NEURAL NETWORKS</t>
-  </si>
-  <si>
-    <t>CNT FIBER-WOVEN PROTOTYPES: ZERO WEIGHT, INFINITE SPAN</t>
-  </si>
-  <si>
-    <t>INTERACTIVE BIM MODELLING ASSISTANT WITH MULTI-AGENT LLM</t>
-  </si>
-  <si>
-    <t>TEXT-TO-SIHEYUAN: LLM-BASED MULTI-AGENT PROCEDURAL GENERATION SYSTEM OF VERNACULAR ARCHITECTURE IN BEIJING</t>
-  </si>
-  <si>
-    <t>PROMPT-TO-PRODUCTION: AI-DRIVEN DESIGN AND ROBOTIC FABRICATION FOR RAPIDLY RECONFIGURABLE CIRCULAR TIMBER ASSEMBLIES</t>
-  </si>
-  <si>
-    <t>CAN AI-BASED SUGGESTIONS SUPPORT DESIGNING IN IMMERSIVE ENVIRONMENTS? OBSERVING THE USE OF GENERATED IMAGES AS VISUAL REFERENCES FOR ARCHITECTURAL DESIGN IN MIXED REALITY</t>
-  </si>
-  <si>
-    <t>CONSOLIDATED EMPIRICAL BIO-MATERIAL REPOSITORY</t>
-  </si>
-  <si>
-    <t>AUGMENTED SCALE PERCEPTION: EXPLORING A FULL-SCALE ARCHITECTURAL EDUCATION APPROACH BASED ON MAR</t>
-  </si>
-  <si>
-    <t>GENERATIVE DESIGN INTELLIGENCE: EXTRACTING DESIGN SPECIFIC SUSTAINABILITY INSIGHTS AND MATERIAL METRICS FROM GENERATIVE ARTIFICIAL INTELLIGENCE OUTPUT</t>
-  </si>
-  <si>
-    <t>AI2D-ARCHITECTURE: A BENCHMARK FOR EVALUATING MULTIMODAL LARGE LANGUAGE MODELS IN ARCHITECTURE</t>
-  </si>
-  <si>
-    <t>VIRTUAL SPACE DESIGN THROUGH PHYSICAL OBJECT RECOGNITION, HOLOLENS-BASED FURNITURE TRACKING AND AI-DRIVEN REAL-TIME LAYOUT GENERATION</t>
-  </si>
-  <si>
-    <t>ENVIRONMENTAL-DRIVEN DIGITAL FABRICATION: CONTROLLING 3D-PRINTING PARAMETERS WITH DATA FROM CFD SIMULATION</t>
-  </si>
-  <si>
-    <t>COMPARING DIFFERENT BUILDING REPRESENTATIONS FOR READABILITY BY LARGE LANGUAGE MODELS</t>
-  </si>
-  <si>
-    <t>INTEGRATING REGULATORY COMPLIANCE IN AI-ASSISTED ARCHITECTURAL DESIGN</t>
-  </si>
-  <si>
-    <t>A FRAMEWORK FOR VIRTUAL WINDOWS TO ENHANCE INDOOR SPATIAL EXPERIENCE IN EXTENDED REALITY</t>
-  </si>
-  <si>
-    <t>OPTIMIZED ACOUSTICS FOR MEETING PODS</t>
-  </si>
-  <si>
-    <t>RESONANT BLECH: EMERGENT SOUNDSCAPES THROUGH HUMAN-AI INTERACTION</t>
-  </si>
-  <si>
-    <t>AUGMENTING IFC-BASED BIM MODELS FOR GRAPH NEURAL NETWORK
-TRAINING OF NON-ORTHOGONAL SPATIAL TYPOLOGIES: A
-CONTEXT-INFORMED DESIGN METHODOLOGY</t>
-  </si>
-  <si>
-    <t>CONSTRUCTGNN: A GRAPH NEURAL NETWORK FRAMEWORK FOR ADAPTIVE 3D ARCHITECTURAL LAYOUT</t>
-  </si>
-  <si>
-    <t>READING BETWEEN THE LINES: BRIDGING AI AND ARCHITECTURAL KNOWLEDGE IN FLOORPLAN UNDERSTANDING</t>
-  </si>
-  <si>
-    <t>COMPUTING BEYOND THE VITRUVIAN CANON: AMBIGUITY AS A CATALYST IN COMPUTATIONAL DESIGN THEORY</t>
-  </si>
-  <si>
-    <t>(CI) COLLABORATIVE PATHWAYS TO SUSTAINABLE DIGITAL
-INNOVATION IN AEC</t>
-  </si>
-  <si>
-    <t>RETHINKING PARTICIPATORY ARCHITECTURAL DESIGN: HARNESSING
-IMMERSIVE ENVIRONMENTS &amp; AI FOR FACILITATING
-DESIGNER-STAKEHOLDER COLLABORATION</t>
-  </si>
-  <si>
-    <t>(CI) AUGMENTATION IN DESIGN AND FABRICATION: EXPANDING THE
-ROLE OF AR AND HUMAN-MACHINE COLLABORATION</t>
-  </si>
-  <si>
-    <t>TOWARD AIXR: DESIGNING A FRAMEWORK FOR AI-INFORMED
-HUMAN-ROBOT COLLABORATIVE ASSEMBLY OF NONUNIFORM MATERIAL
-IN EXTENDED REALITY</t>
-  </si>
-  <si>
-    <t>BUILDINGS AS SYMBIOTIC SYSTEMS: CYBERNETIC ADAPTATION
-BETWEEN TECHNICAL AND BIOLOGICAL SYSTEMS IN ARCHITECTURE</t>
+    <t>TitleAlt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESIGN VALIDATION FOR ROBOTIC FABRICATION: A MULTI-STAGE FRAMEWORK FOR COMPLEX AND NON-REPETITIVE PROCESSES 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPACS: PHYGITAL-AIDED CONSTRUCTION SYSTEM BASED ON MODULAR CUSTOMIZABLE TIMBER FABRICATION
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARAMETRIC BIOMIMICRY: TRANSLATING SPIRAL SEASHELL FORMATION INTO ROBOTIC 3D PRINTING
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REC-ARCH: A CASE STUDY RECOMMENDER SYSTEM FOR ARCHITECTS USING VISION AND LANGUAGE MODELS
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MACHINE LEARNING AND MIXED REALITY-CONTROLLED CABLE ROBOTS FOR REAL-TIME CONSTRUCTION AUTOMATION
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESIGN AND MANUFACTURE OF WASTE TIMBER COMPOSITE PANELS: SUSTAINABLE AND INNOVATIVE USE OF RECYCLED TIMBER
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUPERIORITY OF HIGH-DIMENSIONAL LATENT VARIABLE REPRESENTATION IN URBAN SPATIAL STRUCTURE: EVIDENCE FROM AN URBAN CLIMATE STUDY
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENHANCING ROBOTIC EMBODIMENT IN ARCHITECTURE: AN INTELLIGENT APPROACH COMBINING VISION SYSTEMS AND GENERATIVE NEURAL NETWORKS FOR AUTONOMOUS DESIGN-TO-PRODUCTION
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLLABORATIVE, CONVERSATIONAL ARCHITECTURAL DESIGN PROCESS BETWEEN HUMAN DESIGNERS AND MULTIMODAL AI AGENTS FOR EARLY-STAGE DESIGN EXPLORATION
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOUNDARY VITALITY: ANALYZING URBAN PUBLIC PERCEPTION OF SPATIAL AND VISUAL ELEMENTS IN MANHATTAN
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FROM CRAFT TO COMMUNITY: PARTICIPATORY UPCYCLING IN PUBLIC HOUSING VIA DIGITAL FABRICATION
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATERIAL REUSE IN HERITAGE CONSERVATION: DEVELOPING A DIGITAL DESIGN-TO-PRODUCTION CIRCULAR WORKFLOW
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENHANCING END-TO-END PROCESSING, ANALYSIS, AND VISUALIZATION OF CITIZEN PARTICIPATION DATA IN URBAN DESIGN AND PLANNING
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWO-WAY INTERVENTIVE DESIGN AND MANUFACTURING: REAL-TIME DESIGN AND MATERIALITY VISUALIZATION THROUGH MIXED REALITY SYSTEMS BASED ON HAND TRACKING
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRASP-TO-MILL (GTM) INTEGRATED WORKFLOW FOR NATURAL LOG JOINT FABRICATION BASED ON MULTI-OBJECTIVE OPTIMIZATION ALGORITHM
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUGMENTED ASSEMBLY: AN EXPLORATION OF MODULAR DESIGN TO FABRICATION BASED ON EXTENDED REALITY
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MORPHOLOGICAL SECTIONS THROUGH LATENT SPACE
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEEP PERCEPTUAL URBAN FORM
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INTEGRATING AI TOOLS AND METHODS IN THE DESIGN PROCESS
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPMN-BASED BUILDING PROJECT LIFECYCLE ANALYSIS WITH A CORE OF BIM: TAKING A CAMPUS PROJECT AS AN EXAMPLE
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STOCK-CONSTRAINED DESIGN OF IRREGULAR MATERIAL BASED ON GRAPH NEURAL NETWORKS
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STEPWISE GENERATION METHOD FOR COMPETITION-LEVEL FLOOR PLANS OF MEDIUM AND LARGE-SCALE GYMNASIUMS BASED ON RULE CONSTRAINTS AND DIFFUSION MODELS
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLOOR PLAN AFFORDANCE PREDICTION: IS THE FLOOR PLAN LAYOUT DETERMINED BY ITS OUTLINE OR THE ARCHITECT
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRIDGING THE GAP: ENHANCING AI-GENERATED FLOOR PLANS WITH MULTI-MODAL DATA INTEGRATION
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GENERATING OPEN OFFICE LAYOUTS USING FLEXIBLE ARCHITECTURAL COMPONENTS
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRANSFORMING ARCHITECTURAL EDUCATION: THE IMPACT OF VR AND AR ON UNDERSTANDING BUILDING ENERGY EFFICIENCY
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVALUATING AUGMENTED REALITY AS A TOOL FOR DEMOCRATIZING BUILT ENVIRONMENT DESIGN
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPEN-SOURCE APPROACHES TO INTEGRATING ADVANCED ROBOTIC SYSTEMS IN SUSTAINABLE DESIGN
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A GRAPH-BASED PREDICTION MODEL FOR SUSTAINABLE URBAN RENEWAL: INTEGRATING GRAPH CONVOLUTIONAL NETWORKS FOR CONCRETE RECYCLING POTENTIAL EVALUATION
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHADOW-BASED PATH DETECTION IN RAPIDLY EXPANDING URBAN AREAS: UTILIZING SHADOW DETECTION AND GRAPH-BASED VECTORIZATION TO UNCOVER INFORMAL ROAD NETWORKS IN HIGH-DENSITY SLUM AREAS
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AN URBAN MORPHOLOGY ANALYSIS FRAMEWORK FOR SYNERGISTIC IMPROVEMENT OF MULTIPLE PERFORMANCE OBJECTIVES: EXEMPLIFIED BY OUTDOOR THERMAL COMFORT AND BUILDING ENERGY EFFICIENCY
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIGITAL DESIGN SUPPORT FOR UAV DELIVERY NOISE REDUCTION STRATEGIES IN HIGH DENSITY URBAN ENVIRONMENTS
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUANTIFABLE AND UNQUANTIFABLE MACHINE LEARNING MODEL OR ARCHITECTURAL PREFERENCE PREDICTION BASED ON MBTI
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAPTIVE DESIGN AND FABRICATION OF MODULAR TOPOLOGICAL INTERLOCKING ASSEMBLIES
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAMIFICATION AS A TOOL FOR ENHANCING PUBLIC ENGAGEMENT IN BUILT-ENVIRONMENT DESIGN
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPUTING URBAN TISSUE: LANDSLIDE MITIGATION STRATEGY OF URBAN INFRASTRUCTURE DESIGN
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAPTIVE ORIGAMI: FABRICATION OF PNEUMATIC-ACTUATED ADAPTIVE FOLDING SYSTEM
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUANTIFYING ARCHITECTURAL EXPERIENCE USING VLMS: DOES AI DREAM OF RENDERED SPACES?
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARCHITECTURAL INTERFACES FOR SHARED SPACES – A MULTI-USER PERSPECTIVE ON INTELLIGENT ENVIRONMENT INTERACTIONS
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUSTAINABLE SUSTAINABLE SOCIAL BUILDING ASSISTANT (SSOBA): TRANSFORMING ENERGY USE VIA DIGITAL TWINS, ENVIRONMENTAL SENSING AND OCCUPANT BEHAVIOUR CHANGE
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEVELOPING STRESS-LINE RIBBED TIMBER SLABS: LAMINATING TIMBER RIBS WITH STAY-IN-PLACE FORMWORK
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZERO-SHOT ARCHITECTURAL STYLE CLASSIFICATION WITH LARGE LANGUAGE MODELS
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNDERSTAND URBAN BUILDING ENERGY CONSUMPTION WITH EXPLAINABLE MACHINE LEARNING APPROACHES
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRAFTING A PARTICIPATORY APPROACH TOWARDS TRADITIONAL VIETNAMESE WEAVING AND DIGITAL COMPUTATION
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENHANCING URBAN VITALITY THROUGH INTERACTIVE XR INSTALLATIONS: FOSTERING ENGAGEMENT AND ENVIRONMENTAL AWARENESS
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVALUATION METHOD OF AI-GENERATED ARCHITECTURAL FACADE IMAGES BASED ON DCNN
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESIGN QUALITY HOUSING ASSESSMENT METHODOLOGY: SUPPORTING HEURISTICS WITH EVIDENCE-BASED DECISION-MAKING
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A FABRICATION GRAMMAR FOR ROBOTIC SAND PACKING: FROM PRECISE ACTIONS TO EMERGENT SHAPES AND PATTERNS
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INTELLIGENT SPATIAL PLANNING: A MULTIDIMENSIONAL STUDY ON SWISS RESIDENTIAL DESIGN USING LARGE LANGUAGE MODEL (GPT-4)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERFORMANCE-BASED URBAN ENVIRONMENTAL RESTORATION: A MULTI-LAYER CELLULAR AUTOMATA MODEL FOR ECOLOGICAL DESIGN SIMULATION IN HIGH-DENSITY CITIES
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A FULL-PROCESS DIGITAL METHOD FOR RECURSIVE GEOMETRIC STRUCTURE AND MACHINING PARAMETER GENERATION TARGETING THE REUTILIZATION OF CURVED TIMBER
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URBAN VISUAL HETEROGENEITY: AN INTELLIGENT APPROACH TO EXAMINING TRAVEL PREFERENCES IN NANJING
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVEALING THE RELATIONSHIP BETWEEN SITE PLANNING STRATEGIES AND SENTIMENT THROUGH DEEP LEARNING: ENHANCING DATA-DRIVEN ARCHITECTURAL DESIGN STRATEGIES
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOW CHINESE IS CHINATOWN: MEASURING THE RELATIONSHIP BETWEEN GEOGRAPHIC AUTHENTICITY PERCEPTION AND STREETSCAPE FEATURES THROUGH MACHINE LEARNING
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISCOVERING PARETO-EFFICIENT URBAN NETWORKS THROUGH SHAPE GRAMMAR, MULTI-OBJECTIVE OPTIMISATION AND MACHINE LEARNING
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENCODING PERFORMANCE IN DIGITAL WEAVE DESIGN USING AI AND OPTIMISATION
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMPROVING ARCHITECTURAL FORM CLASSIFICATION THROUGH SALINGAROS’ METRICS AND TOPOLOGICAL DATA ANALYSIS
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GENERATIVE DESIGN FOR COASTAL RESILIENCE: A COMPUTATIONAL APPROACH TO LIVING SHORELINES
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROBOTIC FABRICATION AND IN-SITU 3D PRINTING FOR A NATURAL TIMBER-BAMBOO STRUCTURE
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVESTIGATING SELF-SHAPING FIBRE COMPOSITES: TUNNING CURING PARAMETERS TO OPTIMISE RESULTING CURVATURE
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PREDICTING STRESS-STRAIN CHARACTERISTICS OF 3D PRINTED BCC LATTICE STRUCTURES WITH VARIABLE GRID GRADATION USING NEURAL NETWORKS
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNT FIBER-WOVEN PROTOTYPES: ZERO WEIGHT, INFINITE SPAN
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INTERACTIVE BIM MODELLING ASSISTANT WITH MULTI-AGENT LLM
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEXT-TO-SIHEYUAN: LLM-BASED MULTI-AGENT PROCEDURAL GENERATION SYSTEM OF VERNACULAR ARCHITECTURE IN BEIJING
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROMPT-TO-PRODUCTION: AI-DRIVEN DESIGN AND ROBOTIC FABRICATION FOR RAPIDLY RECONFIGURABLE CIRCULAR TIMBER ASSEMBLIES
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAN AI-BASED SUGGESTIONS SUPPORT DESIGNING IN IMMERSIVE ENVIRONMENTS?
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONSOLIDATED EMPIRICAL BIO-MATERIAL REPOSITORY
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUGMENTED SCALE PERCEPTION: EXPLORING A FULL-SCALE ARCHITECTURAL EDUCATION APPROACH BASED ON MAR
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GENERATIVE DESIGN INTELLIGENCE: EXTRACTING DESIGN SPECIFIC SUSTAINABILITY INSIGHTS AND MATERIAL METRICS FROM GENERATIVE ARTIFICIAL INTELLIGENCE OUTPUT
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI2D-ARCHITECTURE: A BENCHMARK FOR EVALUATING MULTIMODAL LARGE LANGUAGE MODELS IN ARCHITECTURE
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIRTUAL SPACE DESIGN THROUGH PHYSICAL OBJECT RECOGNITION, HOLOLENS-BASED FURNITURE TRACKING AND AI-DRIVEN REAL-TIME LAYOUT GENERATION
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENVIRONMENTAL-DRIVEN DIGITAL FABRICATION: CONTROLLING 3D-PRINTING PARAMETERS WITH DATA FROM CFD SIMULATION
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPARING DIFFERENT BUILDING REPRESENTATIONS FOR READABILITY BY LARGE LANGUAGE MODELS
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INTEGRATING REGULATORY COMPLIANCE IN AI-ASSISTED ARCHITECTURAL DESIGN
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A FRAMEWORK FOR VIRTUAL WINDOWS TO ENHANCE INDOOR SPATIAL EXPERIENCE IN EXTENDED REALITY
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPTIMIZED ACOUSTICS FOR MEETING PODS
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESONANT BLECH: EMERGENT SOUNDSCAPES THROUGH HUMAN-AI INTERACTION
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Augmenting IFC-Based BIM Models for Graph Neural Network Training of Non-Orthogonal Spatial Typologies: A Context-Informed Design Methodology
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONSTRUCTGNN: A GRAPH NEURAL NETWORK FRAMEWORK FOR ADAPTIVE 3D ARCHITECTURAL LAYOUT
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">READING BETWEEN THE LINES: BRIDGING AI AND ARCHITECTURAL KNOWLEDGE IN FLOORPLAN UNDERSTANDING
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPUTING BEYOND THE VITRUVIAN CANON: AMBIGUITY AS A CATALYST IN COMPUTATIONAL DESIGN THEORY
+</t>
   </si>
   <si>
     <t xml:space="preserve">CATALYTIC DESIGN INTERFACES: AI-GUIDED BUILDING MASSING AND AUTOMATED COMPLIANCE
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOWARDS AN INTERDISCIPLINARY ACADEMIA INDUSTRY RESEARCH NEXUS - COLLABORATIVE PATHWAYS TO SUSTAINABLE DIGITAL INNOVATION IN AEC 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RETHINKING PARTICIPATORY ARCHITECTURAL DESIGN: HARNESSING IMMERSIVE ENVIRONMENTS &amp; AI FOR FACILITATING DESIGNER-STAKEHOLDER COLLABORATION
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FROM AUGMENTATION TO AUTONOMY: HUMAN–XR–ROBOT SYNERGIES IN ADVANCED DESIGN AND CONSTRUCTION
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOWARDS AIXR: DESIGNING A FRAMEWORK FOR AI-INFORMED HUMAN-ROBOT COLLABORATIVE ASSEMBLY OF NONUNIFORM MATERIAL IN EXTENDED REALITY 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUILDINGS AS SYMBIOTIC SYSTEMS: CYBERNETIC ADAPTATION BETWEEN TECHNICAL AND BIOLOGICAL SYSTEMS IN ARCHITECTURE 
 </t>
   </si>
   <si>
@@ -467,6 +545,15 @@
 Zixiong Lin</t>
   </si>
   <si>
+    <t>Zhixian Li</t>
+  </si>
+  <si>
+    <t>Qian Cao, Weijing Wang and Rudi Stouffs</t>
+  </si>
+  <si>
+    <t>Zixi Zhang, Wenjing Li and Waishan Qiu</t>
+  </si>
+  <si>
     <t>Yanran Shan and Kam-Ming Mark Tam</t>
   </si>
   <si>
@@ -477,15 +564,6 @@
   </si>
   <si>
     <t>Michael Dieffenthaller, Hallie Fischman, Christine Angelini and Karla Saldana Ochoa</t>
-  </si>
-  <si>
-    <t>Zhixian Li</t>
-  </si>
-  <si>
-    <t>Qian Cao, Weijing Wang and Rudi Stouffs</t>
-  </si>
-  <si>
-    <t>Zixi Zhang, Wenjing Li and Waishan Qiu</t>
   </si>
   <si>
     <t>Xinyue Xia, Haojie Fan, Shunuo Li, Huangyan Zheng, Haoyi Xu and Sining Wang</t>
@@ -556,6 +634,9 @@
   </si>
   <si>
     <t>Hayri Dortdivanlioglu</t>
+  </si>
+  <si>
+    <t>Tejas Chavan, Houssame E. Hsain, Camiel Weijenberg and Sayjel V. Patel</t>
   </si>
   <si>
     <t>M. Hank Haeusler, Ivana Kuzmanovska, Christopher
@@ -577,9 +658,6 @@
 Farahbod Heidari, Alex Binh Vinh Duc Nguyen, Yiming Liu,
 Umaru Mohammed Bongwirnso, Sihao Chen, Thomas Fischer and
 Christiane M. Herr</t>
-  </si>
-  <si>
-    <t>Tejas Chavan, Houssame E. Hsain, Camiel Weijenberg and Sayjel V. Patel</t>
   </si>
   <si>
     <t>The use of robotics in construction offers transformative
@@ -2206,6 +2284,116 @@
 framework through finite element analysis.</t>
   </si>
   <si>
+    <t>Understanding the heterogeneous travel preferences of
+residents and tourists is essential for the effective
+planning and sustainable development of tourist cities.
+While previous studies have suggested that travel
+preferences are influenced by individuals’ visual
+perception, the differences in travel choices between these
+groups remain underexplored. Moreover, existing research
+often relies heavily on subjective assessments, limiting
+the objectivity and scalability of the findings. To address
+these limitations, this study integrates social media data
+analysis, natural language processing (NLP), and computer
+vision techniques to examine the het-erogeneity in
+residents' and tourists' emotional responses to urban
+environments in Nanjing, China. Specifically, a
+Bi-directional Long Short-Term Memory (BiLSTM) network is
+employed to classify sentiments from 20,045 social media
+posts, and a deep convolutional neural network is used to
+extract semantic fea-tures from 6,008 Baidu Street View
+images. The results reveal that both resi-dents’ and
+tourists’ sentiments are positively associated with the
+presence of “na-ture” and negatively associated with
+“enclosure.” Additionally, the “imageability” of the urban
+environment exerts a significant positive effect on
+tourists’ emotions, but no significant impact is observed
+for residents. These findings offer a novel perspective and
+methodological framework for investigating the
+heterogeneity of travel preferences and provide insights
+for the design and development of more inclusive and
+appealing tourist cities.</t>
+  </si>
+  <si>
+    <t>Current architectural design research often overlooks
+users' emotional responses in high-density urban
+environments, limiting the effectiveness of design
+strategies. To address this gap, our study combines deep
+learning techniques with user-generated data from social
+media to explore the complex relationship between site
+functional layout and sentiment. By integrating the content
+of images accompanying with textual information that are
+collected from social media, we bridge the gap left by
+traditional design research, which fails to account for
+emotional feedback in decision-making.
+We integrate building morphology data, master plan,
+satellite imagery, and Points of Interest (POI) data,
+utilizing Graph Neural Networks (GNN) to classify building
+functions and extract relevant metrics. The site layout is
+defined based on five key dimensions: spatial organization,
+functional proportion, facility connectivity, physical
+environment response, and land use intensity. Emotional
+responses are categorized as negative, positive, and
+neutral. Through regression analysis, the interaction
+between emotional patterns and layout metrics is revealed,
+illustrating the complex relationship between emotions and
+site functional layout. We apply subjective dimension of
+the space as the weight of identified physical dimensions,
+constructing a comprehensive matrix for site planning. This
+provides a new perspective for better understanding the
+impact of functional layout on emotional experiences.
+The findings indicate that site functional layout
+significantly impacts users' emotional experiences. Highly
+connected layouts enhance positive emotion, while areas
+with better public facility availability and mixed-use
+zones are identified as hedonic hot spots. Conversely,
+isolated, single-function areas reduce users' happiness.
+This study provides a data-driven design tool, highlighting
+the critical role of site functional layout in shaping
+subjective well-being and improving urban operational
+efficiency.</t>
+  </si>
+  <si>
+    <t>In the context of globalization and cultural hybridization,
+immigrant communities significantly shape how streets are
+perceived. While existing research have utilized machine
+learning to create quantitative models that link subjective
+perceptions to street features, a quantitative correlation
+between geographic authenticity perception and streetscape
+visual features remains unexplored, highlighting a critical
+research gap.
+This research presents a framework to measure geographic
+authenticity perception by integrating large-scale Street
+View Images (SVIs) with crowdsourcing, machine learning,
+and computer vision. Chinatowns of New York City, the most
+prominent immigrant communities, are chosen as a case
+study. Specifically, (1) With a crowdsourcing survey
+platform and TrueSkill algorithm, five geographic
+authenticity perception scores associated with Chinatown
+were collected from SVIs—sense of Chinatown, sense of
+Cantonese, sense of China, sense of Asia and sense of
+East—as well as eleven mainstream streetscape quality
+perception scores (e.g., attractive, comfortable). (2)
+Computer vision models were employed to extract key visual
+features from SVIs. (3) Multiple machine learning
+algorithms modeled the relationship between each perception
+score and features. The correlation between geographic
+authenticity perceptions and mainstream streetscape quality
+perceptions was also explored.
+The results indicate that: (1) Eight out of twenty street
+visual features are significantly correlated with five
+geographical authenticity perceptions of Chinatown, with
+varying impacts on each perception. (2) Perceptions of
+mainstream streetscape quality differ in their correlation
+with five perceptions of geographical authenticity.
+This study extends the existing street perception
+categories to geographic authenticity perception that
+related to cultural attributes. It inspires the
+establishment of geographic authenticity perception
+indicators for immigrant communities of other countries or
+cultures.</t>
+  </si>
+  <si>
     <t>The concept of a “15-minute neighborhood” is a widely
 recognized and practiced global initiative that aims to
 create walkable cities, improving convenience and reducing
@@ -2391,116 +2579,6 @@
 of resilient shoreline ecosystems.</t>
   </si>
   <si>
-    <t>Understanding the heterogeneous travel preferences of
-residents and tourists is essential for the effective
-planning and sustainable development of tourist cities.
-While previous studies have suggested that travel
-preferences are influenced by individuals’ visual
-perception, the differences in travel choices between these
-groups remain underexplored. Moreover, existing research
-often relies heavily on subjective assessments, limiting
-the objectivity and scalability of the findings. To address
-these limitations, this study integrates social media data
-analysis, natural language processing (NLP), and computer
-vision techniques to examine the het-erogeneity in
-residents' and tourists' emotional responses to urban
-environments in Nanjing, China. Specifically, a
-Bi-directional Long Short-Term Memory (BiLSTM) network is
-employed to classify sentiments from 20,045 social media
-posts, and a deep convolutional neural network is used to
-extract semantic fea-tures from 6,008 Baidu Street View
-images. The results reveal that both resi-dents’ and
-tourists’ sentiments are positively associated with the
-presence of “na-ture” and negatively associated with
-“enclosure.” Additionally, the “imageability” of the urban
-environment exerts a significant positive effect on
-tourists’ emotions, but no significant impact is observed
-for residents. These findings offer a novel perspective and
-methodological framework for investigating the
-heterogeneity of travel preferences and provide insights
-for the design and development of more inclusive and
-appealing tourist cities.</t>
-  </si>
-  <si>
-    <t>Current architectural design research often overlooks
-users' emotional responses in high-density urban
-environments, limiting the effectiveness of design
-strategies. To address this gap, our study combines deep
-learning techniques with user-generated data from social
-media to explore the complex relationship between site
-functional layout and sentiment. By integrating the content
-of images accompanying with textual information that are
-collected from social media, we bridge the gap left by
-traditional design research, which fails to account for
-emotional feedback in decision-making.
-We integrate building morphology data, master plan,
-satellite imagery, and Points of Interest (POI) data,
-utilizing Graph Neural Networks (GNN) to classify building
-functions and extract relevant metrics. The site layout is
-defined based on five key dimensions: spatial organization,
-functional proportion, facility connectivity, physical
-environment response, and land use intensity. Emotional
-responses are categorized as negative, positive, and
-neutral. Through regression analysis, the interaction
-between emotional patterns and layout metrics is revealed,
-illustrating the complex relationship between emotions and
-site functional layout. We apply subjective dimension of
-the space as the weight of identified physical dimensions,
-constructing a comprehensive matrix for site planning. This
-provides a new perspective for better understanding the
-impact of functional layout on emotional experiences.
-The findings indicate that site functional layout
-significantly impacts users' emotional experiences. Highly
-connected layouts enhance positive emotion, while areas
-with better public facility availability and mixed-use
-zones are identified as hedonic hot spots. Conversely,
-isolated, single-function areas reduce users' happiness.
-This study provides a data-driven design tool, highlighting
-the critical role of site functional layout in shaping
-subjective well-being and improving urban operational
-efficiency.</t>
-  </si>
-  <si>
-    <t>In the context of globalization and cultural hybridization,
-immigrant communities significantly shape how streets are
-perceived. While existing research have utilized machine
-learning to create quantitative models that link subjective
-perceptions to street features, a quantitative correlation
-between geographic authenticity perception and streetscape
-visual features remains unexplored, highlighting a critical
-research gap.
-This research presents a framework to measure geographic
-authenticity perception by integrating large-scale Street
-View Images (SVIs) with crowdsourcing, machine learning,
-and computer vision. Chinatowns of New York City, the most
-prominent immigrant communities, are chosen as a case
-study. Specifically, (1) With a crowdsourcing survey
-platform and TrueSkill algorithm, five geographic
-authenticity perception scores associated with Chinatown
-were collected from SVIs—sense of Chinatown, sense of
-Cantonese, sense of China, sense of Asia and sense of
-East—as well as eleven mainstream streetscape quality
-perception scores (e.g., attractive, comfortable). (2)
-Computer vision models were employed to extract key visual
-features from SVIs. (3) Multiple machine learning
-algorithms modeled the relationship between each perception
-score and features. The correlation between geographic
-authenticity perceptions and mainstream streetscape quality
-perceptions was also explored.
-The results indicate that: (1) Eight out of twenty street
-visual features are significantly correlated with five
-geographical authenticity perceptions of Chinatown, with
-varying impacts on each perception. (2) Perceptions of
-mainstream streetscape quality differ in their correlation
-with five perceptions of geographical authenticity.
-This study extends the existing street perception
-categories to geographic authenticity perception that
-related to cultural attributes. It inspires the
-establishment of geographic authenticity perception
-indicators for immigrant communities of other countries or
-cultures.</t>
-  </si>
-  <si>
     <t>With advanced fabrication and computational design methods,
 non-standard building structures made from natural
 materials such as wood and bamboo are attracting the
@@ -3273,6 +3351,10 @@
 ambiguity functions as a catalytic interface for
 innovation, adaptability, and interdisciplinary exchange in
 architecture.</t>
+  </si>
+  <si>
+    <t>This paper presents HIKARI, a working prototype and design methodology for integrating generative AI into architectural design, focusing on automated compliance and building massing generation. Unlike purely speculative studies, HIKARI was developed in collaboration with a leading design firm to navigate complex building codes, offering concrete lessons on embedding AI within professional practice. The platform functions as a catalytic interface, combining generative algorithms for massing exploration, a regulatory engine for automated compliance checking against Japanese building codes, and a Retrieval-Augmented Generation (RAG) pipeline for explainable, natural-language queries. We discuss the co-creation methodology, system architecture, and key lessons on operationalizing trust and harmonizing data. Furthermore, we propose a workshop framework to empirically evaluate the platform's efficacy not only as a design tool but also as a pedagogical instrument for teaching complex regulations. This is measured by assessing knowledge acquisition through a pre- and post-test methodology, demonstrating how AI can serve as an interactive guide
+in architectural education and practice.</t>
   </si>
   <si>
     <t>The Architecture, Engineering, and Construction (AEC)
@@ -3635,19 +3717,6 @@
 human, ecological, and environmental health.</t>
   </si>
   <si>
-    <t>This paper presents HIKARI, a working prototype and design methodology for integrating generative AI into architectural design, focusing on automated compliance and building massing generation. Unlike purely speculative studies, HIKARI was developed in collaboration with a leading design firm to navigate complex building codes, offering concrete lessons on embedding AI within professional practice. The platform functions as a catalytic interface, combining generative algorithms for massing exploration, a regulatory engine for automated compliance checking against Japanese building codes, and a Retrieval-Augmented Generation (RAG) pipeline for explainable, natural-language queries. We discuss the co-creation methodology, system architecture, and key lessons on operationalizing trust and harmonizing data. Furthermore, we propose a workshop framework to empirically evaluate the platform's efficacy not only as a design tool but also as a pedagogical instrument for teaching complex regulations. This is measured by assessing knowledge acquisition through a pre- and post-test methodology, demonstrating how AI can serve as an interactive guide
-in architectural education and practice.</t>
-  </si>
-  <si>
-    <t>7/2/2025</t>
-  </si>
-  <si>
-    <t>7/3/2025</t>
-  </si>
-  <si>
-    <t>7/4/2025</t>
-  </si>
-  <si>
     <t>11:25 - 11:40</t>
   </si>
   <si>
@@ -3720,51 +3789,63 @@
     <t>13:25 - 13:35</t>
   </si>
   <si>
+    <t>13:55 - 14:40</t>
+  </si>
+  <si>
+    <t>14:10 - 14:25</t>
+  </si>
+  <si>
+    <t>14:25 - 14:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:05 – 15:20 </t>
+  </si>
+  <si>
+    <t>15:20 – 15:35</t>
+  </si>
+  <si>
+    <t>15:35 – 15:50</t>
+  </si>
+  <si>
+    <t>15:50 – 16:05</t>
+  </si>
+  <si>
+    <t>16:45 - 17:00</t>
+  </si>
+  <si>
+    <t>17:00 - 17:15</t>
+  </si>
+  <si>
+    <t>17:15 - 17:30</t>
+  </si>
+  <si>
+    <t>17:30 - 17:45</t>
+  </si>
+  <si>
+    <t>12:00 - 12:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:10 - 12:20 </t>
+  </si>
+  <si>
+    <t>12:20 - 12:30</t>
+  </si>
+  <si>
+    <t>12:30 - 12:40</t>
+  </si>
+  <si>
+    <t>12:40 - 12:50</t>
+  </si>
+  <si>
+    <t>13:45 - 14:00</t>
+  </si>
+  <si>
     <t>14:00 - 14:15</t>
   </si>
   <si>
     <t>14:15 - 14:30</t>
   </si>
   <si>
-    <t>14:30 - 14:45</t>
-  </si>
-  <si>
-    <t>14:45 - 15:00</t>
-  </si>
-  <si>
-    <t>15:40 - 16:25</t>
-  </si>
-  <si>
-    <t>16:45 - 17:00</t>
-  </si>
-  <si>
-    <t>17:00 - 17:15</t>
-  </si>
-  <si>
-    <t>17:15 - 17:30</t>
-  </si>
-  <si>
-    <t>17:30 - 17:45</t>
-  </si>
-  <si>
-    <t>12:00 - 12:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:10 - 12:20 </t>
-  </si>
-  <si>
-    <t>12:20 - 12:30</t>
-  </si>
-  <si>
-    <t>12:30 - 12:40</t>
-  </si>
-  <si>
-    <t>12:40 - 12:50</t>
-  </si>
-  <si>
-    <t>13:45 - 14:00</t>
-  </si>
-  <si>
     <t>15:10 - 15:30</t>
   </si>
   <si>
@@ -3819,12 +3900,12 @@
     <t>P-A2</t>
   </si>
   <si>
+    <t>S-3</t>
+  </si>
+  <si>
     <t>S-S3</t>
   </si>
   <si>
-    <t>S-3</t>
-  </si>
-  <si>
     <t>S-4</t>
   </si>
   <si>
@@ -3882,10 +3963,10 @@
     <t>URBAN INFRASTRUCTURE &amp; ENVIRONMENTAL SYSTEMS</t>
   </si>
   <si>
+    <t>URBAN PERCEPTIONS &amp; PATTERNS II</t>
+  </si>
+  <si>
     <t>MORPHOLOGY ACROSS SCALES</t>
-  </si>
-  <si>
-    <t>URBAN PERCEPTIONS &amp; PATTERNS II</t>
   </si>
   <si>
     <t>PROMPTING ARCHITECTURE</t>
@@ -3910,6 +3991,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -3962,11 +4046,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4261,10 +4346,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4289,8 +4374,11 @@
       <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -4298,28 +4386,31 @@
         <v>238</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>182</v>
-      </c>
-      <c r="F2" t="s">
-        <v>269</v>
+        <v>183</v>
+      </c>
+      <c r="F2" s="2">
+        <v>45840</v>
       </c>
       <c r="G2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="H2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="I2" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>340</v>
+      </c>
+      <c r="J2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -4327,28 +4418,31 @@
         <v>349</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F3" t="s">
-        <v>269</v>
+        <v>184</v>
+      </c>
+      <c r="F3" s="2">
+        <v>45840</v>
       </c>
       <c r="G3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="I3" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>340</v>
+      </c>
+      <c r="J3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -4356,28 +4450,31 @@
         <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>184</v>
-      </c>
-      <c r="F4" t="s">
-        <v>269</v>
+        <v>185</v>
+      </c>
+      <c r="F4" s="2">
+        <v>45840</v>
       </c>
       <c r="G4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="H4" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="I4" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>340</v>
+      </c>
+      <c r="J4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -4385,28 +4482,31 @@
         <v>169</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>185</v>
-      </c>
-      <c r="F5" t="s">
-        <v>269</v>
+        <v>186</v>
+      </c>
+      <c r="F5" s="2">
+        <v>45840</v>
       </c>
       <c r="G5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H5" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="I5" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>341</v>
+      </c>
+      <c r="J5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -4414,28 +4514,31 @@
         <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>186</v>
-      </c>
-      <c r="F6" t="s">
-        <v>269</v>
+        <v>187</v>
+      </c>
+      <c r="F6" s="2">
+        <v>45840</v>
       </c>
       <c r="G6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H6" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="I6" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>342</v>
+      </c>
+      <c r="J6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -4443,28 +4546,31 @@
         <v>447</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>187</v>
-      </c>
-      <c r="F7" t="s">
-        <v>269</v>
+        <v>188</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45840</v>
       </c>
       <c r="G7" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H7" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I7" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>343</v>
+      </c>
+      <c r="J7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -4472,28 +4578,31 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>188</v>
-      </c>
-      <c r="F8" t="s">
-        <v>269</v>
+        <v>189</v>
+      </c>
+      <c r="F8" s="2">
+        <v>45840</v>
       </c>
       <c r="G8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H8" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="I8" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>344</v>
+      </c>
+      <c r="J8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -4501,28 +4610,31 @@
         <v>149</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
-        <v>189</v>
-      </c>
-      <c r="F9" t="s">
-        <v>269</v>
+        <v>190</v>
+      </c>
+      <c r="F9" s="2">
+        <v>45840</v>
       </c>
       <c r="G9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H9" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="I9" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>342</v>
+      </c>
+      <c r="J9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -4530,28 +4642,31 @@
         <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
-        <v>190</v>
-      </c>
-      <c r="F10" t="s">
-        <v>269</v>
+        <v>191</v>
+      </c>
+      <c r="F10" s="2">
+        <v>45840</v>
       </c>
       <c r="G10" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H10" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="I10" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>341</v>
+      </c>
+      <c r="J10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -4559,28 +4674,31 @@
         <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E11" t="s">
-        <v>191</v>
-      </c>
-      <c r="F11" t="s">
-        <v>269</v>
+        <v>192</v>
+      </c>
+      <c r="F11" s="2">
+        <v>45840</v>
       </c>
       <c r="G11" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H11" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="I11" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>344</v>
+      </c>
+      <c r="J11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -4588,28 +4706,31 @@
         <v>48</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E12" t="s">
-        <v>192</v>
-      </c>
-      <c r="F12" t="s">
-        <v>269</v>
+        <v>193</v>
+      </c>
+      <c r="F12" s="2">
+        <v>45840</v>
       </c>
       <c r="G12" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I12" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>343</v>
+      </c>
+      <c r="J12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -4617,28 +4738,31 @@
         <v>162</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E13" t="s">
-        <v>193</v>
-      </c>
-      <c r="F13" t="s">
-        <v>269</v>
+        <v>194</v>
+      </c>
+      <c r="F13" s="2">
+        <v>45840</v>
       </c>
       <c r="G13" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H13" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I13" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>343</v>
+      </c>
+      <c r="J13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -4646,28 +4770,31 @@
         <v>240</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
-        <v>194</v>
-      </c>
-      <c r="F14" t="s">
-        <v>269</v>
+        <v>195</v>
+      </c>
+      <c r="F14" s="2">
+        <v>45840</v>
       </c>
       <c r="G14" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H14" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="I14" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>344</v>
+      </c>
+      <c r="J14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -4675,28 +4802,31 @@
         <v>255</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E15" t="s">
-        <v>195</v>
-      </c>
-      <c r="F15" t="s">
-        <v>269</v>
+        <v>196</v>
+      </c>
+      <c r="F15" s="2">
+        <v>45840</v>
       </c>
       <c r="G15" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H15" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="I15" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>341</v>
+      </c>
+      <c r="J15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -4704,28 +4834,31 @@
         <v>252</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E16" t="s">
-        <v>196</v>
-      </c>
-      <c r="F16" t="s">
-        <v>269</v>
+        <v>197</v>
+      </c>
+      <c r="F16" s="2">
+        <v>45840</v>
       </c>
       <c r="G16" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H16" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="I16" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+        <v>342</v>
+      </c>
+      <c r="J16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -4733,28 +4866,31 @@
         <v>357</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E17" t="s">
-        <v>197</v>
-      </c>
-      <c r="F17" t="s">
-        <v>269</v>
+        <v>198</v>
+      </c>
+      <c r="F17" s="2">
+        <v>45840</v>
       </c>
       <c r="G17" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H17" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="I17" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+        <v>342</v>
+      </c>
+      <c r="J17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -4762,28 +4898,31 @@
         <v>217</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E18" t="s">
-        <v>198</v>
-      </c>
-      <c r="F18" t="s">
-        <v>269</v>
+        <v>199</v>
+      </c>
+      <c r="F18" s="2">
+        <v>45840</v>
       </c>
       <c r="G18" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H18" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="I18" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+        <v>341</v>
+      </c>
+      <c r="J18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -4791,28 +4930,31 @@
         <v>453</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E19" t="s">
-        <v>199</v>
-      </c>
-      <c r="F19" t="s">
-        <v>269</v>
+        <v>200</v>
+      </c>
+      <c r="F19" s="2">
+        <v>45840</v>
       </c>
       <c r="G19" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H19" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="I19" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+        <v>344</v>
+      </c>
+      <c r="J19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -4820,28 +4962,31 @@
         <v>141</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E20" t="s">
-        <v>200</v>
-      </c>
-      <c r="F20" t="s">
-        <v>269</v>
+        <v>201</v>
+      </c>
+      <c r="F20" s="2">
+        <v>45840</v>
       </c>
       <c r="G20" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="H20" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="I20" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+        <v>341</v>
+      </c>
+      <c r="J20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -4849,28 +4994,31 @@
         <v>127</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E21" t="s">
-        <v>201</v>
-      </c>
-      <c r="F21" t="s">
-        <v>269</v>
+        <v>202</v>
+      </c>
+      <c r="F21" s="2">
+        <v>45840</v>
       </c>
       <c r="G21" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="H21" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I21" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <v>343</v>
+      </c>
+      <c r="J21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -4878,28 +5026,31 @@
         <v>222</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E22" t="s">
-        <v>202</v>
-      </c>
-      <c r="F22" t="s">
-        <v>269</v>
+        <v>203</v>
+      </c>
+      <c r="F22" s="2">
+        <v>45840</v>
       </c>
       <c r="G22" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="H22" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="I22" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <v>342</v>
+      </c>
+      <c r="J22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -4907,28 +5058,31 @@
         <v>126</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E23" t="s">
-        <v>203</v>
-      </c>
-      <c r="F23" t="s">
-        <v>269</v>
+        <v>204</v>
+      </c>
+      <c r="F23" s="2">
+        <v>45840</v>
       </c>
       <c r="G23" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H23" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I23" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+        <v>345</v>
+      </c>
+      <c r="J23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -4936,28 +5090,31 @@
         <v>134</v>
       </c>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E24" t="s">
-        <v>204</v>
-      </c>
-      <c r="F24" t="s">
-        <v>269</v>
+        <v>205</v>
+      </c>
+      <c r="F24" s="2">
+        <v>45840</v>
       </c>
       <c r="G24" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="H24" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I24" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+        <v>345</v>
+      </c>
+      <c r="J24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -4965,28 +5122,31 @@
         <v>135</v>
       </c>
       <c r="C25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E25" t="s">
-        <v>205</v>
-      </c>
-      <c r="F25" t="s">
-        <v>269</v>
+        <v>206</v>
+      </c>
+      <c r="F25" s="2">
+        <v>45840</v>
       </c>
       <c r="G25" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H25" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I25" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+        <v>345</v>
+      </c>
+      <c r="J25" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -4994,28 +5154,31 @@
         <v>151</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D26" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E26" t="s">
-        <v>206</v>
-      </c>
-      <c r="F26" t="s">
-        <v>269</v>
+        <v>207</v>
+      </c>
+      <c r="F26" s="2">
+        <v>45840</v>
       </c>
       <c r="G26" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="H26" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I26" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <v>345</v>
+      </c>
+      <c r="J26" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -5023,28 +5186,31 @@
         <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D27" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E27" t="s">
-        <v>207</v>
-      </c>
-      <c r="F27" t="s">
-        <v>269</v>
+        <v>208</v>
+      </c>
+      <c r="F27" s="2">
+        <v>45840</v>
       </c>
       <c r="G27" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="H27" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="I27" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
+        <v>346</v>
+      </c>
+      <c r="J27" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -5052,28 +5218,31 @@
         <v>426</v>
       </c>
       <c r="C28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D28" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E28" t="s">
-        <v>208</v>
-      </c>
-      <c r="F28" t="s">
-        <v>269</v>
+        <v>209</v>
+      </c>
+      <c r="F28" s="2">
+        <v>45840</v>
       </c>
       <c r="G28" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H28" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="I28" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
+        <v>346</v>
+      </c>
+      <c r="J28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -5081,927 +5250,1023 @@
         <v>196</v>
       </c>
       <c r="C29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D29" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E29" t="s">
-        <v>209</v>
-      </c>
-      <c r="F29" t="s">
-        <v>269</v>
+        <v>210</v>
+      </c>
+      <c r="F29" s="2">
+        <v>45840</v>
       </c>
       <c r="G29" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H29" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="I29" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+        <v>346</v>
+      </c>
+      <c r="J29" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30">
         <v>148</v>
       </c>
       <c r="C30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D30" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E30" t="s">
-        <v>210</v>
-      </c>
-      <c r="F30" t="s">
-        <v>270</v>
+        <v>211</v>
+      </c>
+      <c r="F30" s="2">
+        <v>45841</v>
       </c>
       <c r="G30" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H30" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="I30" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
+        <v>347</v>
+      </c>
+      <c r="J30" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31">
         <v>55</v>
       </c>
       <c r="C31" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D31" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E31" t="s">
-        <v>211</v>
-      </c>
-      <c r="F31" t="s">
-        <v>270</v>
+        <v>212</v>
+      </c>
+      <c r="F31" s="2">
+        <v>45841</v>
       </c>
       <c r="G31" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="I31" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+        <v>347</v>
+      </c>
+      <c r="J31" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32">
         <v>329</v>
       </c>
       <c r="C32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D32" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E32" t="s">
-        <v>212</v>
-      </c>
-      <c r="F32" t="s">
-        <v>270</v>
+        <v>213</v>
+      </c>
+      <c r="F32" s="2">
+        <v>45841</v>
       </c>
       <c r="G32" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H32" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="I32" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
+        <v>347</v>
+      </c>
+      <c r="J32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33">
         <v>262</v>
       </c>
       <c r="C33" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E33" t="s">
-        <v>213</v>
-      </c>
-      <c r="F33" t="s">
-        <v>270</v>
+        <v>214</v>
+      </c>
+      <c r="F33" s="2">
+        <v>45841</v>
       </c>
       <c r="G33" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H33" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="I33" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
+        <v>347</v>
+      </c>
+      <c r="J33" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34">
         <v>45</v>
       </c>
       <c r="C34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D34" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E34" t="s">
-        <v>214</v>
-      </c>
-      <c r="F34" t="s">
-        <v>270</v>
+        <v>215</v>
+      </c>
+      <c r="F34" s="2">
+        <v>45841</v>
       </c>
       <c r="G34" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H34" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I34" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
+        <v>348</v>
+      </c>
+      <c r="J34" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35">
         <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D35" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E35" t="s">
-        <v>215</v>
-      </c>
-      <c r="F35" t="s">
-        <v>270</v>
+        <v>216</v>
+      </c>
+      <c r="F35" s="2">
+        <v>45841</v>
       </c>
       <c r="G35" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H35" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="I35" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
+        <v>349</v>
+      </c>
+      <c r="J35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36">
         <v>206</v>
       </c>
       <c r="C36" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D36" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E36" t="s">
-        <v>216</v>
-      </c>
-      <c r="F36" t="s">
-        <v>270</v>
+        <v>217</v>
+      </c>
+      <c r="F36" s="2">
+        <v>45841</v>
       </c>
       <c r="G36" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H36" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I36" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
+        <v>350</v>
+      </c>
+      <c r="J36" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37">
         <v>299</v>
       </c>
       <c r="C37" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D37" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E37" t="s">
-        <v>217</v>
-      </c>
-      <c r="F37" t="s">
-        <v>270</v>
+        <v>218</v>
+      </c>
+      <c r="F37" s="2">
+        <v>45841</v>
       </c>
       <c r="G37" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H37" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I37" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
+        <v>351</v>
+      </c>
+      <c r="J37" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38">
         <v>155</v>
       </c>
       <c r="C38" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D38" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E38" t="s">
-        <v>218</v>
-      </c>
-      <c r="F38" t="s">
-        <v>270</v>
+        <v>219</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45841</v>
       </c>
       <c r="G38" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H38" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="I38" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
+        <v>349</v>
+      </c>
+      <c r="J38" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39">
         <v>150</v>
       </c>
       <c r="C39" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D39" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E39" t="s">
-        <v>219</v>
-      </c>
-      <c r="F39" t="s">
-        <v>270</v>
+        <v>220</v>
+      </c>
+      <c r="F39" s="2">
+        <v>45841</v>
       </c>
       <c r="G39" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H39" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I39" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
+        <v>348</v>
+      </c>
+      <c r="J39" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40">
         <v>74</v>
       </c>
       <c r="C40" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D40" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E40" t="s">
-        <v>220</v>
-      </c>
-      <c r="F40" t="s">
-        <v>270</v>
+        <v>221</v>
+      </c>
+      <c r="F40" s="2">
+        <v>45841</v>
       </c>
       <c r="G40" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H40" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I40" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
+        <v>350</v>
+      </c>
+      <c r="J40" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41">
         <v>278</v>
       </c>
       <c r="C41" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D41" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E41" t="s">
-        <v>221</v>
-      </c>
-      <c r="F41" t="s">
-        <v>270</v>
+        <v>222</v>
+      </c>
+      <c r="F41" s="2">
+        <v>45841</v>
       </c>
       <c r="G41" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H41" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I41" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
+        <v>351</v>
+      </c>
+      <c r="J41" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42">
         <v>221</v>
       </c>
       <c r="C42" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E42" t="s">
-        <v>222</v>
-      </c>
-      <c r="F42" t="s">
-        <v>270</v>
+        <v>223</v>
+      </c>
+      <c r="F42" s="2">
+        <v>45841</v>
       </c>
       <c r="G42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H42" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="I42" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
+        <v>349</v>
+      </c>
+      <c r="J42" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B43">
         <v>304</v>
       </c>
       <c r="C43" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D43" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E43" t="s">
-        <v>223</v>
-      </c>
-      <c r="F43" t="s">
-        <v>270</v>
+        <v>224</v>
+      </c>
+      <c r="F43" s="2">
+        <v>45841</v>
       </c>
       <c r="G43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H43" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I43" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
+        <v>348</v>
+      </c>
+      <c r="J43" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B44">
         <v>29</v>
       </c>
       <c r="C44" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D44" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E44" t="s">
-        <v>224</v>
-      </c>
-      <c r="F44" t="s">
-        <v>270</v>
+        <v>225</v>
+      </c>
+      <c r="F44" s="2">
+        <v>45841</v>
       </c>
       <c r="G44" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H44" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I44" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
+        <v>351</v>
+      </c>
+      <c r="J44" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B45">
         <v>137</v>
       </c>
       <c r="C45" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D45" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E45" t="s">
-        <v>225</v>
-      </c>
-      <c r="F45" t="s">
-        <v>270</v>
+        <v>226</v>
+      </c>
+      <c r="F45" s="2">
+        <v>45841</v>
       </c>
       <c r="G45" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H45" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I45" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
+        <v>350</v>
+      </c>
+      <c r="J45" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B46">
         <v>121</v>
       </c>
       <c r="C46" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D46" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E46" t="s">
-        <v>226</v>
-      </c>
-      <c r="F46" t="s">
-        <v>270</v>
+        <v>227</v>
+      </c>
+      <c r="F46" s="2">
+        <v>45841</v>
       </c>
       <c r="G46" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H46" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I46" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
+        <v>351</v>
+      </c>
+      <c r="J46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B47">
         <v>456</v>
       </c>
       <c r="C47" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D47" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E47" t="s">
-        <v>227</v>
-      </c>
-      <c r="F47" t="s">
-        <v>270</v>
+        <v>228</v>
+      </c>
+      <c r="F47" s="2">
+        <v>45841</v>
       </c>
       <c r="G47" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H47" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I47" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
+        <v>348</v>
+      </c>
+      <c r="J47" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48">
         <v>180</v>
       </c>
       <c r="C48" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D48" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E48" t="s">
-        <v>228</v>
-      </c>
-      <c r="F48" t="s">
-        <v>270</v>
+        <v>229</v>
+      </c>
+      <c r="F48" s="2">
+        <v>45841</v>
       </c>
       <c r="G48" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H48" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I48" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
+        <v>350</v>
+      </c>
+      <c r="J48" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B49">
         <v>339</v>
       </c>
       <c r="C49" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D49" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E49" t="s">
-        <v>229</v>
-      </c>
-      <c r="F49" t="s">
-        <v>270</v>
+        <v>230</v>
+      </c>
+      <c r="F49" s="2">
+        <v>45841</v>
       </c>
       <c r="G49" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H49" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="I49" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
+        <v>349</v>
+      </c>
+      <c r="J49" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B50">
         <v>59</v>
       </c>
       <c r="C50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E50" t="s">
-        <v>230</v>
-      </c>
-      <c r="F50" t="s">
-        <v>270</v>
+        <v>231</v>
+      </c>
+      <c r="F50" s="2">
+        <v>45841</v>
       </c>
       <c r="G50" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I50" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
+        <v>348</v>
+      </c>
+      <c r="J50" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" s="1">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B51">
         <v>71</v>
       </c>
       <c r="C51" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D51" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E51" t="s">
-        <v>231</v>
-      </c>
-      <c r="F51" t="s">
-        <v>270</v>
+        <v>232</v>
+      </c>
+      <c r="F51" s="2">
+        <v>45841</v>
       </c>
       <c r="G51" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H51" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I51" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
+        <v>351</v>
+      </c>
+      <c r="J51" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
       <c r="A52" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B52">
         <v>27</v>
       </c>
       <c r="C52" t="s">
+        <v>59</v>
+      </c>
+      <c r="D52" t="s">
+        <v>146</v>
+      </c>
+      <c r="E52" t="s">
+        <v>233</v>
+      </c>
+      <c r="F52" s="2">
+        <v>45841</v>
+      </c>
+      <c r="G52" t="s">
+        <v>293</v>
+      </c>
+      <c r="H52" t="s">
+        <v>328</v>
+      </c>
+      <c r="I52" t="s">
+        <v>349</v>
+      </c>
+      <c r="J52" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" s="1">
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <v>50</v>
+      </c>
+      <c r="C53" t="s">
+        <v>60</v>
+      </c>
+      <c r="D53" t="s">
+        <v>147</v>
+      </c>
+      <c r="E53" t="s">
+        <v>234</v>
+      </c>
+      <c r="F53" s="2">
+        <v>45841</v>
+      </c>
+      <c r="G53" t="s">
+        <v>294</v>
+      </c>
+      <c r="H53" t="s">
+        <v>331</v>
+      </c>
+      <c r="I53" t="s">
+        <v>352</v>
+      </c>
+      <c r="J53" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="1">
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>198</v>
+      </c>
+      <c r="C54" t="s">
+        <v>61</v>
+      </c>
+      <c r="D54" t="s">
+        <v>148</v>
+      </c>
+      <c r="E54" t="s">
+        <v>235</v>
+      </c>
+      <c r="F54" s="2">
+        <v>45841</v>
+      </c>
+      <c r="G54" t="s">
+        <v>295</v>
+      </c>
+      <c r="H54" t="s">
+        <v>331</v>
+      </c>
+      <c r="I54" t="s">
+        <v>352</v>
+      </c>
+      <c r="J54" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="1">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>250</v>
+      </c>
+      <c r="C55" t="s">
+        <v>62</v>
+      </c>
+      <c r="D55" t="s">
+        <v>149</v>
+      </c>
+      <c r="E55" t="s">
+        <v>236</v>
+      </c>
+      <c r="F55" s="2">
+        <v>45841</v>
+      </c>
+      <c r="G55" t="s">
+        <v>296</v>
+      </c>
+      <c r="H55" t="s">
+        <v>331</v>
+      </c>
+      <c r="I55" t="s">
+        <v>352</v>
+      </c>
+      <c r="J55" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="1">
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <v>210</v>
+      </c>
+      <c r="C56" t="s">
+        <v>63</v>
+      </c>
+      <c r="D56" t="s">
+        <v>150</v>
+      </c>
+      <c r="E56" t="s">
+        <v>237</v>
+      </c>
+      <c r="F56" s="2">
+        <v>45841</v>
+      </c>
+      <c r="G56" t="s">
+        <v>297</v>
+      </c>
+      <c r="H56" t="s">
+        <v>332</v>
+      </c>
+      <c r="I56" t="s">
+        <v>353</v>
+      </c>
+      <c r="J56" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="1">
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <v>440</v>
+      </c>
+      <c r="C57" t="s">
+        <v>64</v>
+      </c>
+      <c r="D57" t="s">
+        <v>151</v>
+      </c>
+      <c r="E57" t="s">
+        <v>238</v>
+      </c>
+      <c r="F57" s="2">
+        <v>45841</v>
+      </c>
+      <c r="G57" t="s">
+        <v>298</v>
+      </c>
+      <c r="H57" t="s">
+        <v>332</v>
+      </c>
+      <c r="I57" t="s">
+        <v>353</v>
+      </c>
+      <c r="J57" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="1">
+        <v>56</v>
+      </c>
+      <c r="B58">
+        <v>431</v>
+      </c>
+      <c r="C58" t="s">
+        <v>65</v>
+      </c>
+      <c r="D58" t="s">
+        <v>152</v>
+      </c>
+      <c r="E58" t="s">
+        <v>239</v>
+      </c>
+      <c r="F58" s="2">
+        <v>45841</v>
+      </c>
+      <c r="G58" t="s">
+        <v>299</v>
+      </c>
+      <c r="H58" t="s">
+        <v>332</v>
+      </c>
+      <c r="I58" t="s">
+        <v>353</v>
+      </c>
+      <c r="J58" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="1">
+        <v>57</v>
+      </c>
+      <c r="B59">
+        <v>314</v>
+      </c>
+      <c r="C59" t="s">
+        <v>66</v>
+      </c>
+      <c r="D59" t="s">
+        <v>153</v>
+      </c>
+      <c r="E59" t="s">
+        <v>240</v>
+      </c>
+      <c r="F59" s="2">
+        <v>45841</v>
+      </c>
+      <c r="G59" t="s">
+        <v>300</v>
+      </c>
+      <c r="H59" t="s">
+        <v>332</v>
+      </c>
+      <c r="I59" t="s">
+        <v>353</v>
+      </c>
+      <c r="J59" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="1">
         <v>58</v>
-      </c>
-      <c r="D52" t="s">
-        <v>145</v>
-      </c>
-      <c r="E52" t="s">
-        <v>232</v>
-      </c>
-      <c r="F52" t="s">
-        <v>270</v>
-      </c>
-      <c r="G52" t="s">
-        <v>295</v>
-      </c>
-      <c r="H52" t="s">
-        <v>326</v>
-      </c>
-      <c r="I52" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="1">
-        <v>52</v>
-      </c>
-      <c r="B53">
-        <v>210</v>
-      </c>
-      <c r="C53" t="s">
-        <v>59</v>
-      </c>
-      <c r="D53" t="s">
-        <v>146</v>
-      </c>
-      <c r="E53" t="s">
-        <v>233</v>
-      </c>
-      <c r="F53" t="s">
-        <v>270</v>
-      </c>
-      <c r="G53" t="s">
-        <v>296</v>
-      </c>
-      <c r="H53" t="s">
-        <v>329</v>
-      </c>
-      <c r="I53" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="1">
-        <v>53</v>
-      </c>
-      <c r="B54">
-        <v>440</v>
-      </c>
-      <c r="C54" t="s">
-        <v>60</v>
-      </c>
-      <c r="D54" t="s">
-        <v>147</v>
-      </c>
-      <c r="E54" t="s">
-        <v>234</v>
-      </c>
-      <c r="F54" t="s">
-        <v>270</v>
-      </c>
-      <c r="G54" t="s">
-        <v>297</v>
-      </c>
-      <c r="H54" t="s">
-        <v>329</v>
-      </c>
-      <c r="I54" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="1">
-        <v>54</v>
-      </c>
-      <c r="B55">
-        <v>431</v>
-      </c>
-      <c r="C55" t="s">
-        <v>61</v>
-      </c>
-      <c r="D55" t="s">
-        <v>148</v>
-      </c>
-      <c r="E55" t="s">
-        <v>235</v>
-      </c>
-      <c r="F55" t="s">
-        <v>270</v>
-      </c>
-      <c r="G55" t="s">
-        <v>298</v>
-      </c>
-      <c r="H55" t="s">
-        <v>329</v>
-      </c>
-      <c r="I55" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9">
-      <c r="A56" s="1">
-        <v>55</v>
-      </c>
-      <c r="B56">
-        <v>314</v>
-      </c>
-      <c r="C56" t="s">
-        <v>62</v>
-      </c>
-      <c r="D56" t="s">
-        <v>149</v>
-      </c>
-      <c r="E56" t="s">
-        <v>236</v>
-      </c>
-      <c r="F56" t="s">
-        <v>270</v>
-      </c>
-      <c r="G56" t="s">
-        <v>299</v>
-      </c>
-      <c r="H56" t="s">
-        <v>329</v>
-      </c>
-      <c r="I56" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9">
-      <c r="A57" s="1">
-        <v>56</v>
-      </c>
-      <c r="B57">
-        <v>50</v>
-      </c>
-      <c r="C57" t="s">
-        <v>63</v>
-      </c>
-      <c r="D57" t="s">
-        <v>150</v>
-      </c>
-      <c r="E57" t="s">
-        <v>237</v>
-      </c>
-      <c r="F57" t="s">
-        <v>270</v>
-      </c>
-      <c r="G57" t="s">
-        <v>300</v>
-      </c>
-      <c r="H57" t="s">
-        <v>330</v>
-      </c>
-      <c r="I57" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9">
-      <c r="A58" s="1">
-        <v>57</v>
-      </c>
-      <c r="B58">
-        <v>198</v>
-      </c>
-      <c r="C58" t="s">
-        <v>64</v>
-      </c>
-      <c r="D58" t="s">
-        <v>151</v>
-      </c>
-      <c r="E58" t="s">
-        <v>238</v>
-      </c>
-      <c r="F58" t="s">
-        <v>270</v>
-      </c>
-      <c r="G58" t="s">
-        <v>285</v>
-      </c>
-      <c r="H58" t="s">
-        <v>330</v>
-      </c>
-      <c r="I58" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9">
-      <c r="A59" s="1">
-        <v>58</v>
-      </c>
-      <c r="B59">
-        <v>250</v>
-      </c>
-      <c r="C59" t="s">
-        <v>65</v>
-      </c>
-      <c r="D59" t="s">
-        <v>152</v>
-      </c>
-      <c r="E59" t="s">
-        <v>239</v>
-      </c>
-      <c r="F59" t="s">
-        <v>270</v>
-      </c>
-      <c r="G59" t="s">
-        <v>286</v>
-      </c>
-      <c r="H59" t="s">
-        <v>330</v>
-      </c>
-      <c r="I59" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9">
-      <c r="A60" s="1">
-        <v>28</v>
       </c>
       <c r="B60">
         <v>132</v>
       </c>
       <c r="C60" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D60" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E60" t="s">
-        <v>240</v>
-      </c>
-      <c r="F60" t="s">
-        <v>270</v>
+        <v>241</v>
+      </c>
+      <c r="F60" s="2">
+        <v>45841</v>
       </c>
       <c r="G60" t="s">
         <v>301</v>
       </c>
       <c r="H60" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I60" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9">
+        <v>349</v>
+      </c>
+      <c r="J60" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -6009,28 +6274,31 @@
         <v>193</v>
       </c>
       <c r="C61" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D61" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E61" t="s">
-        <v>241</v>
-      </c>
-      <c r="F61" t="s">
-        <v>270</v>
+        <v>242</v>
+      </c>
+      <c r="F61" s="2">
+        <v>45841</v>
       </c>
       <c r="G61" t="s">
         <v>302</v>
       </c>
       <c r="H61" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I61" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9">
+        <v>349</v>
+      </c>
+      <c r="J61" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -6038,28 +6306,31 @@
         <v>386</v>
       </c>
       <c r="C62" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D62" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E62" t="s">
-        <v>242</v>
-      </c>
-      <c r="F62" t="s">
-        <v>270</v>
+        <v>243</v>
+      </c>
+      <c r="F62" s="2">
+        <v>45841</v>
       </c>
       <c r="G62" t="s">
         <v>303</v>
       </c>
       <c r="H62" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I62" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9">
+        <v>349</v>
+      </c>
+      <c r="J62" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -6067,28 +6338,31 @@
         <v>178</v>
       </c>
       <c r="C63" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D63" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E63" t="s">
-        <v>243</v>
-      </c>
-      <c r="F63" t="s">
-        <v>270</v>
+        <v>244</v>
+      </c>
+      <c r="F63" s="2">
+        <v>45841</v>
       </c>
       <c r="G63" t="s">
         <v>304</v>
       </c>
       <c r="H63" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I63" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9">
+        <v>349</v>
+      </c>
+      <c r="J63" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -6096,28 +6370,31 @@
         <v>444</v>
       </c>
       <c r="C64" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D64" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E64" t="s">
-        <v>244</v>
-      </c>
-      <c r="F64" t="s">
-        <v>271</v>
+        <v>245</v>
+      </c>
+      <c r="F64" s="2">
+        <v>45842</v>
       </c>
       <c r="G64" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H64" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I64" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9">
+        <v>354</v>
+      </c>
+      <c r="J64" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -6125,28 +6402,31 @@
         <v>403</v>
       </c>
       <c r="C65" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D65" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E65" t="s">
-        <v>245</v>
-      </c>
-      <c r="F65" t="s">
-        <v>271</v>
+        <v>246</v>
+      </c>
+      <c r="F65" s="2">
+        <v>45842</v>
       </c>
       <c r="G65" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H65" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I65" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9">
+        <v>354</v>
+      </c>
+      <c r="J65" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -6154,28 +6434,31 @@
         <v>253</v>
       </c>
       <c r="C66" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D66" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E66" t="s">
-        <v>246</v>
-      </c>
-      <c r="F66" t="s">
-        <v>271</v>
+        <v>247</v>
+      </c>
+      <c r="F66" s="2">
+        <v>45842</v>
       </c>
       <c r="G66" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H66" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I66" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9">
+        <v>354</v>
+      </c>
+      <c r="J66" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -6183,28 +6466,31 @@
         <v>68</v>
       </c>
       <c r="C67" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D67" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E67" t="s">
-        <v>247</v>
-      </c>
-      <c r="F67" t="s">
-        <v>271</v>
+        <v>248</v>
+      </c>
+      <c r="F67" s="2">
+        <v>45842</v>
       </c>
       <c r="G67" t="s">
         <v>305</v>
       </c>
       <c r="H67" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="I67" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9">
+        <v>355</v>
+      </c>
+      <c r="J67" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -6212,28 +6498,31 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E68" t="s">
-        <v>248</v>
-      </c>
-      <c r="F68" t="s">
-        <v>271</v>
+        <v>249</v>
+      </c>
+      <c r="F68" s="2">
+        <v>45842</v>
       </c>
       <c r="G68" t="s">
         <v>305</v>
       </c>
       <c r="H68" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="I68" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9">
+        <v>356</v>
+      </c>
+      <c r="J68" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -6241,28 +6530,31 @@
         <v>276</v>
       </c>
       <c r="C69" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D69" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E69" t="s">
-        <v>249</v>
-      </c>
-      <c r="F69" t="s">
-        <v>271</v>
+        <v>250</v>
+      </c>
+      <c r="F69" s="2">
+        <v>45842</v>
       </c>
       <c r="G69" t="s">
         <v>306</v>
       </c>
       <c r="H69" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="I69" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9">
+        <v>355</v>
+      </c>
+      <c r="J69" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -6270,28 +6562,31 @@
         <v>313</v>
       </c>
       <c r="C70" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D70" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E70" t="s">
-        <v>250</v>
-      </c>
-      <c r="F70" t="s">
-        <v>271</v>
+        <v>251</v>
+      </c>
+      <c r="F70" s="2">
+        <v>45842</v>
       </c>
       <c r="G70" t="s">
         <v>306</v>
       </c>
       <c r="H70" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="I70" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9">
+        <v>356</v>
+      </c>
+      <c r="J70" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -6299,28 +6594,31 @@
         <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D71" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E71" t="s">
-        <v>251</v>
-      </c>
-      <c r="F71" t="s">
-        <v>271</v>
+        <v>252</v>
+      </c>
+      <c r="F71" s="2">
+        <v>45842</v>
       </c>
       <c r="G71" t="s">
         <v>306</v>
       </c>
       <c r="H71" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I71" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9">
+        <v>357</v>
+      </c>
+      <c r="J71" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -6328,28 +6626,31 @@
         <v>379</v>
       </c>
       <c r="C72" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D72" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E72" t="s">
-        <v>252</v>
-      </c>
-      <c r="F72" t="s">
-        <v>271</v>
+        <v>253</v>
+      </c>
+      <c r="F72" s="2">
+        <v>45842</v>
       </c>
       <c r="G72" t="s">
         <v>307</v>
       </c>
       <c r="H72" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="I72" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9">
+        <v>355</v>
+      </c>
+      <c r="J72" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -6357,28 +6658,31 @@
         <v>133</v>
       </c>
       <c r="C73" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D73" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E73" t="s">
-        <v>253</v>
-      </c>
-      <c r="F73" t="s">
-        <v>271</v>
+        <v>254</v>
+      </c>
+      <c r="F73" s="2">
+        <v>45842</v>
       </c>
       <c r="G73" t="s">
         <v>307</v>
       </c>
       <c r="H73" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="I73" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9">
+        <v>356</v>
+      </c>
+      <c r="J73" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -6386,28 +6690,31 @@
         <v>145</v>
       </c>
       <c r="C74" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D74" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E74" t="s">
-        <v>254</v>
-      </c>
-      <c r="F74" t="s">
-        <v>271</v>
+        <v>255</v>
+      </c>
+      <c r="F74" s="2">
+        <v>45842</v>
       </c>
       <c r="G74" t="s">
         <v>307</v>
       </c>
       <c r="H74" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I74" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9">
+        <v>357</v>
+      </c>
+      <c r="J74" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -6415,28 +6722,31 @@
         <v>19</v>
       </c>
       <c r="C75" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D75" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E75" t="s">
-        <v>255</v>
-      </c>
-      <c r="F75" t="s">
-        <v>271</v>
+        <v>256</v>
+      </c>
+      <c r="F75" s="2">
+        <v>45842</v>
       </c>
       <c r="G75" t="s">
         <v>308</v>
       </c>
       <c r="H75" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I75" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9">
+        <v>357</v>
+      </c>
+      <c r="J75" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -6444,28 +6754,31 @@
         <v>428</v>
       </c>
       <c r="C76" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D76" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E76" t="s">
-        <v>256</v>
-      </c>
-      <c r="F76" t="s">
-        <v>271</v>
+        <v>257</v>
+      </c>
+      <c r="F76" s="2">
+        <v>45842</v>
       </c>
       <c r="G76" t="s">
         <v>308</v>
       </c>
       <c r="H76" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="I76" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9">
+        <v>355</v>
+      </c>
+      <c r="J76" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -6473,28 +6786,31 @@
         <v>395</v>
       </c>
       <c r="C77" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D77" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E77" t="s">
-        <v>257</v>
-      </c>
-      <c r="F77" t="s">
-        <v>271</v>
+        <v>258</v>
+      </c>
+      <c r="F77" s="2">
+        <v>45842</v>
       </c>
       <c r="G77" t="s">
         <v>308</v>
       </c>
       <c r="H77" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="I77" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9">
+        <v>356</v>
+      </c>
+      <c r="J77" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -6502,315 +6818,348 @@
         <v>111</v>
       </c>
       <c r="C78" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D78" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E78" t="s">
-        <v>258</v>
-      </c>
-      <c r="F78" t="s">
-        <v>271</v>
+        <v>259</v>
+      </c>
+      <c r="F78" s="2">
+        <v>45842</v>
       </c>
       <c r="G78" t="s">
         <v>309</v>
       </c>
       <c r="H78" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="I78" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9">
+        <v>355</v>
+      </c>
+      <c r="J78" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
       <c r="A79" s="1">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B79">
         <v>457</v>
       </c>
       <c r="C79" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D79" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E79" t="s">
-        <v>259</v>
-      </c>
-      <c r="F79" t="s">
-        <v>271</v>
+        <v>260</v>
+      </c>
+      <c r="F79" s="2">
+        <v>45842</v>
       </c>
       <c r="G79" t="s">
         <v>309</v>
       </c>
       <c r="H79" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I79" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9">
+        <v>357</v>
+      </c>
+      <c r="J79" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
       <c r="A80" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B80">
         <v>114</v>
       </c>
       <c r="C80" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D80" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>260</v>
-      </c>
-      <c r="F80" t="s">
-        <v>271</v>
+        <v>261</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45842</v>
       </c>
       <c r="G80" t="s">
         <v>310</v>
       </c>
       <c r="H80" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I80" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9">
+        <v>358</v>
+      </c>
+      <c r="J80" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
       <c r="A81" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B81">
         <v>231</v>
       </c>
       <c r="C81" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D81" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E81" t="s">
-        <v>261</v>
-      </c>
-      <c r="F81" t="s">
-        <v>271</v>
+        <v>262</v>
+      </c>
+      <c r="F81" s="2">
+        <v>45842</v>
       </c>
       <c r="G81" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="H81" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I81" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9">
+        <v>358</v>
+      </c>
+      <c r="J81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
       <c r="A82" s="1">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B82">
         <v>230</v>
       </c>
       <c r="C82" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D82" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E82" t="s">
-        <v>262</v>
-      </c>
-      <c r="F82" t="s">
-        <v>271</v>
+        <v>263</v>
+      </c>
+      <c r="F82" s="2">
+        <v>45842</v>
       </c>
       <c r="G82" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="H82" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I82" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9">
+        <v>358</v>
+      </c>
+      <c r="J82" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
       <c r="A83" s="1">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B83">
+        <v>458</v>
+      </c>
+      <c r="C83" t="s">
+        <v>90</v>
+      </c>
+      <c r="D83" t="s">
+        <v>177</v>
+      </c>
+      <c r="E83" t="s">
+        <v>264</v>
+      </c>
+      <c r="F83" s="2">
+        <v>45842</v>
+      </c>
+      <c r="G83" t="s">
+        <v>313</v>
+      </c>
+      <c r="H83" t="s">
+        <v>339</v>
+      </c>
+      <c r="I83" t="s">
+        <v>359</v>
+      </c>
+      <c r="J83" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84" s="1">
         <v>82</v>
       </c>
-      <c r="C83" t="s">
-        <v>89</v>
-      </c>
-      <c r="D83" t="s">
-        <v>176</v>
-      </c>
-      <c r="E83" t="s">
-        <v>263</v>
-      </c>
-      <c r="F83" t="s">
-        <v>271</v>
-      </c>
-      <c r="G83" t="s">
-        <v>311</v>
-      </c>
-      <c r="H83" t="s">
-        <v>337</v>
-      </c>
-      <c r="I83" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9">
-      <c r="A84" s="1">
-        <v>81</v>
-      </c>
       <c r="B84">
+        <v>82</v>
+      </c>
+      <c r="C84" t="s">
+        <v>91</v>
+      </c>
+      <c r="D84" t="s">
+        <v>178</v>
+      </c>
+      <c r="E84" t="s">
+        <v>265</v>
+      </c>
+      <c r="F84" s="2">
+        <v>45842</v>
+      </c>
+      <c r="G84" t="s">
+        <v>314</v>
+      </c>
+      <c r="H84" t="s">
+        <v>339</v>
+      </c>
+      <c r="I84" t="s">
+        <v>359</v>
+      </c>
+      <c r="J84" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" s="1">
+        <v>83</v>
+      </c>
+      <c r="B85">
         <v>330</v>
       </c>
-      <c r="C84" t="s">
-        <v>90</v>
-      </c>
-      <c r="D84" t="s">
-        <v>177</v>
-      </c>
-      <c r="E84" t="s">
-        <v>264</v>
-      </c>
-      <c r="F84" t="s">
-        <v>271</v>
-      </c>
-      <c r="G84" t="s">
-        <v>312</v>
-      </c>
-      <c r="H84" t="s">
-        <v>337</v>
-      </c>
-      <c r="I84" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9">
-      <c r="A85" s="1">
-        <v>82</v>
-      </c>
-      <c r="B85">
+      <c r="C85" t="s">
+        <v>92</v>
+      </c>
+      <c r="D85" t="s">
+        <v>179</v>
+      </c>
+      <c r="E85" t="s">
+        <v>266</v>
+      </c>
+      <c r="F85" s="2">
+        <v>45842</v>
+      </c>
+      <c r="G85" t="s">
+        <v>315</v>
+      </c>
+      <c r="H85" t="s">
+        <v>339</v>
+      </c>
+      <c r="I85" t="s">
+        <v>359</v>
+      </c>
+      <c r="J85" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86" s="1">
+        <v>84</v>
+      </c>
+      <c r="B86">
         <v>389</v>
       </c>
-      <c r="C85" t="s">
-        <v>91</v>
-      </c>
-      <c r="D85" t="s">
-        <v>178</v>
-      </c>
-      <c r="E85" t="s">
-        <v>265</v>
-      </c>
-      <c r="F85" t="s">
-        <v>271</v>
-      </c>
-      <c r="G85" t="s">
-        <v>313</v>
-      </c>
-      <c r="H85" t="s">
-        <v>337</v>
-      </c>
-      <c r="I85" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9">
-      <c r="A86" s="1">
-        <v>83</v>
-      </c>
-      <c r="B86">
+      <c r="C86" t="s">
+        <v>93</v>
+      </c>
+      <c r="D86" t="s">
+        <v>180</v>
+      </c>
+      <c r="E86" t="s">
+        <v>267</v>
+      </c>
+      <c r="F86" s="2">
+        <v>45842</v>
+      </c>
+      <c r="G86" t="s">
+        <v>316</v>
+      </c>
+      <c r="H86" t="s">
+        <v>339</v>
+      </c>
+      <c r="I86" t="s">
+        <v>359</v>
+      </c>
+      <c r="J86" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87" s="1">
+        <v>85</v>
+      </c>
+      <c r="B87">
         <v>427</v>
       </c>
-      <c r="C86" t="s">
-        <v>92</v>
-      </c>
-      <c r="D86" t="s">
-        <v>179</v>
-      </c>
-      <c r="E86" t="s">
-        <v>266</v>
-      </c>
-      <c r="F86" t="s">
-        <v>271</v>
-      </c>
-      <c r="G86" t="s">
-        <v>314</v>
-      </c>
-      <c r="H86" t="s">
-        <v>337</v>
-      </c>
-      <c r="I86" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9">
-      <c r="A87" s="1">
-        <v>84</v>
-      </c>
-      <c r="B87">
+      <c r="C87" t="s">
+        <v>94</v>
+      </c>
+      <c r="D87" t="s">
+        <v>181</v>
+      </c>
+      <c r="E87" t="s">
+        <v>268</v>
+      </c>
+      <c r="F87" s="2">
+        <v>45842</v>
+      </c>
+      <c r="G87" t="s">
+        <v>317</v>
+      </c>
+      <c r="H87" t="s">
+        <v>339</v>
+      </c>
+      <c r="I87" t="s">
+        <v>359</v>
+      </c>
+      <c r="J87" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10">
+      <c r="A88" s="1">
+        <v>86</v>
+      </c>
+      <c r="B88">
         <v>445</v>
       </c>
-      <c r="C87" t="s">
-        <v>93</v>
-      </c>
-      <c r="D87" t="s">
-        <v>180</v>
-      </c>
-      <c r="E87" t="s">
-        <v>267</v>
-      </c>
-      <c r="F87" t="s">
-        <v>271</v>
-      </c>
-      <c r="G87" t="s">
-        <v>315</v>
-      </c>
-      <c r="H87" t="s">
-        <v>337</v>
-      </c>
-      <c r="I87" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9">
-      <c r="A88" s="1">
-        <v>85</v>
-      </c>
-      <c r="B88">
-        <v>458</v>
-      </c>
       <c r="C88" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D88" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E88" t="s">
-        <v>268</v>
-      </c>
-      <c r="F88" t="s">
-        <v>271</v>
+        <v>269</v>
+      </c>
+      <c r="F88" s="2">
+        <v>45842</v>
       </c>
       <c r="G88" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H88" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="I88" t="s">
-        <v>357</v>
+        <v>359</v>
+      </c>
+      <c r="J88" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
